--- a/Grade3-Homeworks.xlsx
+++ b/Grade3-Homeworks.xlsx
@@ -17,15 +17,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+  <si>
+    <t>Monday</t>
+  </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Monday</t>
+    <t xml:space="preserve">Telugu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maths </t>
+  </si>
+  <si>
+    <t>Tuesday</t>
   </si>
   <si>
     <t>Languages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programming </t>
   </si>
   <si>
     <t>Telugu</t>
@@ -34,49 +49,22 @@
     <t>English</t>
   </si>
   <si>
-    <t>Devanagari - HindiSanskritKhatriMarathi</t>
+    <t>Wednesday</t>
   </si>
   <si>
-    <t xml:space="preserve">Telugu </t>
+    <t>Devanagari - HindiSanskritKhatriMarathi</t>
   </si>
   <si>
     <t>Maths</t>
   </si>
   <si>
-    <t xml:space="preserve">Maths </t>
+    <t xml:space="preserve">Science </t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
     <t>Programming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English </t>
-  </si>
-  <si>
-    <t>CarnaticMusic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programming </t>
-  </si>
-  <si>
-    <t>Science</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t>SocialStudies ( + LifeSkills)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Science </t>
-  </si>
-  <si>
-    <t>Overview</t>
   </si>
   <si>
     <t>Thursday</t>
@@ -85,10 +73,22 @@
     <t>Music</t>
   </si>
   <si>
+    <t>CarnaticMusic</t>
+  </si>
+  <si>
     <t xml:space="preserve">Social </t>
   </si>
   <si>
+    <t>Science</t>
+  </si>
+  <si>
     <t>Friday</t>
+  </si>
+  <si>
+    <t>SocialStudies ( + LifeSkills)</t>
+  </si>
+  <si>
+    <t>Overview</t>
   </si>
   <si>
     <t>KhatriHindiSanskrit</t>
@@ -122,6 +122,15 @@
   <si>
     <t>HW: Read and understand all of these and solve word problems on Geometry</t>
   </si>
+  <si>
+    <t>HW: Learn all of these operations and practice the exercises (Linux command line operations - AI notes)</t>
+  </si>
+  <si>
+    <t>HW: Read python book - Coder's apprentice and solve the exercises</t>
+  </si>
+  <si>
+    <t>HW: Make sure the website is updated with all the files for Grade 2 - All subjects</t>
+  </si>
 </sst>
 </file>
 
@@ -138,11 +147,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -266,49 +275,49 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -528,60 +537,58 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="35.25"/>
-    <col customWidth="1" min="4" max="4" width="22.13"/>
-    <col customWidth="1" min="6" max="6" width="15.5"/>
+    <col customWidth="1" min="3" max="12" width="19.38"/>
     <col hidden="1" min="13" max="23" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>17</v>
+      <c r="I1" s="2" t="s">
+        <v>18</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>19</v>
+      <c r="J1" s="2" t="s">
+        <v>20</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="K1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3">
@@ -779,18 +786,24 @@
       <c r="W9" s="7"/>
     </row>
     <row r="10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
+      <c r="A10" s="3">
+        <v>46294.0</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="6"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -804,18 +817,20 @@
       <c r="W10" s="7"/>
     </row>
     <row r="11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="14"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -829,7 +844,7 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12">
-      <c r="A12" s="1"/>
+      <c r="A12" s="2"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -854,7 +869,7 @@
       <c r="W12" s="7"/>
     </row>
     <row r="13">
-      <c r="A13" s="1"/>
+      <c r="A13" s="2"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -879,7 +894,7 @@
       <c r="W13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="1"/>
+      <c r="A14" s="2"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -904,7 +919,7 @@
       <c r="W14" s="7"/>
     </row>
     <row r="15">
-      <c r="A15" s="1"/>
+      <c r="A15" s="2"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -929,7 +944,7 @@
       <c r="W15" s="7"/>
     </row>
     <row r="16">
-      <c r="A16" s="1"/>
+      <c r="A16" s="2"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -954,7 +969,7 @@
       <c r="W16" s="7"/>
     </row>
     <row r="17">
-      <c r="A17" s="1"/>
+      <c r="A17" s="2"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -979,7 +994,7 @@
       <c r="W17" s="7"/>
     </row>
     <row r="18">
-      <c r="A18" s="1"/>
+      <c r="A18" s="2"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -1004,7 +1019,7 @@
       <c r="W18" s="7"/>
     </row>
     <row r="19">
-      <c r="A19" s="1"/>
+      <c r="A19" s="2"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -1029,7 +1044,7 @@
       <c r="W19" s="7"/>
     </row>
     <row r="20">
-      <c r="A20" s="1"/>
+      <c r="A20" s="2"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -1054,7 +1069,7 @@
       <c r="W20" s="7"/>
     </row>
     <row r="21">
-      <c r="A21" s="1"/>
+      <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -1079,7 +1094,7 @@
       <c r="W21" s="7"/>
     </row>
     <row r="22">
-      <c r="A22" s="1"/>
+      <c r="A22" s="2"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -1104,7 +1119,7 @@
       <c r="W22" s="7"/>
     </row>
     <row r="23">
-      <c r="A23" s="1"/>
+      <c r="A23" s="2"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -1129,7 +1144,7 @@
       <c r="W23" s="7"/>
     </row>
     <row r="24">
-      <c r="A24" s="1"/>
+      <c r="A24" s="2"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -1154,7 +1169,7 @@
       <c r="W24" s="7"/>
     </row>
     <row r="25">
-      <c r="A25" s="1"/>
+      <c r="A25" s="2"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -1179,7 +1194,7 @@
       <c r="W25" s="7"/>
     </row>
     <row r="26">
-      <c r="A26" s="1"/>
+      <c r="A26" s="2"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -1204,7 +1219,7 @@
       <c r="W26" s="7"/>
     </row>
     <row r="27">
-      <c r="A27" s="1"/>
+      <c r="A27" s="2"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -1229,7 +1244,7 @@
       <c r="W27" s="7"/>
     </row>
     <row r="28">
-      <c r="A28" s="1"/>
+      <c r="A28" s="2"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -1254,7 +1269,7 @@
       <c r="W28" s="7"/>
     </row>
     <row r="29">
-      <c r="A29" s="1"/>
+      <c r="A29" s="2"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1279,7 +1294,7 @@
       <c r="W29" s="7"/>
     </row>
     <row r="30">
-      <c r="A30" s="1"/>
+      <c r="A30" s="2"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -1304,7 +1319,7 @@
       <c r="W30" s="7"/>
     </row>
     <row r="31">
-      <c r="A31" s="1"/>
+      <c r="A31" s="2"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -1329,7 +1344,7 @@
       <c r="W31" s="7"/>
     </row>
     <row r="32">
-      <c r="A32" s="1"/>
+      <c r="A32" s="2"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -1354,7 +1369,7 @@
       <c r="W32" s="7"/>
     </row>
     <row r="33">
-      <c r="A33" s="1"/>
+      <c r="A33" s="2"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -1379,7 +1394,7 @@
       <c r="W33" s="7"/>
     </row>
     <row r="34">
-      <c r="A34" s="1"/>
+      <c r="A34" s="2"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -1404,7 +1419,7 @@
       <c r="W34" s="7"/>
     </row>
     <row r="35">
-      <c r="A35" s="1"/>
+      <c r="A35" s="2"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1429,7 +1444,7 @@
       <c r="W35" s="7"/>
     </row>
     <row r="36">
-      <c r="A36" s="1"/>
+      <c r="A36" s="2"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -1454,7 +1469,7 @@
       <c r="W36" s="7"/>
     </row>
     <row r="37">
-      <c r="A37" s="1"/>
+      <c r="A37" s="2"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -1479,7 +1494,7 @@
       <c r="W37" s="7"/>
     </row>
     <row r="38">
-      <c r="A38" s="1"/>
+      <c r="A38" s="2"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -1504,7 +1519,7 @@
       <c r="W38" s="7"/>
     </row>
     <row r="39">
-      <c r="A39" s="1"/>
+      <c r="A39" s="2"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -1529,7 +1544,7 @@
       <c r="W39" s="7"/>
     </row>
     <row r="40">
-      <c r="A40" s="1"/>
+      <c r="A40" s="2"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -1554,7 +1569,7 @@
       <c r="W40" s="7"/>
     </row>
     <row r="41">
-      <c r="A41" s="1"/>
+      <c r="A41" s="2"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1579,7 +1594,7 @@
       <c r="W41" s="7"/>
     </row>
     <row r="42">
-      <c r="A42" s="1"/>
+      <c r="A42" s="2"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -1604,7 +1619,7 @@
       <c r="W42" s="7"/>
     </row>
     <row r="43">
-      <c r="A43" s="1"/>
+      <c r="A43" s="2"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -1629,7 +1644,7 @@
       <c r="W43" s="7"/>
     </row>
     <row r="44">
-      <c r="A44" s="1"/>
+      <c r="A44" s="2"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -1654,7 +1669,7 @@
       <c r="W44" s="7"/>
     </row>
     <row r="45">
-      <c r="A45" s="1"/>
+      <c r="A45" s="2"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1679,7 +1694,7 @@
       <c r="W45" s="7"/>
     </row>
     <row r="46">
-      <c r="A46" s="1"/>
+      <c r="A46" s="2"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -1704,7 +1719,7 @@
       <c r="W46" s="7"/>
     </row>
     <row r="47">
-      <c r="A47" s="1"/>
+      <c r="A47" s="2"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -1729,7 +1744,7 @@
       <c r="W47" s="7"/>
     </row>
     <row r="48">
-      <c r="A48" s="1"/>
+      <c r="A48" s="2"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -1754,7 +1769,7 @@
       <c r="W48" s="7"/>
     </row>
     <row r="49">
-      <c r="A49" s="1"/>
+      <c r="A49" s="2"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -1779,7 +1794,7 @@
       <c r="W49" s="7"/>
     </row>
     <row r="50">
-      <c r="A50" s="1"/>
+      <c r="A50" s="2"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
@@ -1804,7 +1819,7 @@
       <c r="W50" s="7"/>
     </row>
     <row r="51">
-      <c r="A51" s="1"/>
+      <c r="A51" s="2"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -1829,7 +1844,7 @@
       <c r="W51" s="7"/>
     </row>
     <row r="52">
-      <c r="A52" s="1"/>
+      <c r="A52" s="2"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -1854,7 +1869,7 @@
       <c r="W52" s="7"/>
     </row>
     <row r="53">
-      <c r="A53" s="1"/>
+      <c r="A53" s="2"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -1879,7 +1894,7 @@
       <c r="W53" s="7"/>
     </row>
     <row r="54">
-      <c r="A54" s="1"/>
+      <c r="A54" s="2"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -1904,7 +1919,7 @@
       <c r="W54" s="7"/>
     </row>
     <row r="55">
-      <c r="A55" s="1"/>
+      <c r="A55" s="2"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -1929,7 +1944,7 @@
       <c r="W55" s="7"/>
     </row>
     <row r="56">
-      <c r="A56" s="1"/>
+      <c r="A56" s="2"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -1954,7 +1969,7 @@
       <c r="W56" s="7"/>
     </row>
     <row r="57">
-      <c r="A57" s="1"/>
+      <c r="A57" s="2"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -1979,7 +1994,7 @@
       <c r="W57" s="7"/>
     </row>
     <row r="58">
-      <c r="A58" s="1"/>
+      <c r="A58" s="2"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -2004,7 +2019,7 @@
       <c r="W58" s="7"/>
     </row>
     <row r="59">
-      <c r="A59" s="1"/>
+      <c r="A59" s="2"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -2029,7 +2044,7 @@
       <c r="W59" s="7"/>
     </row>
     <row r="60">
-      <c r="A60" s="1"/>
+      <c r="A60" s="2"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -2054,7 +2069,7 @@
       <c r="W60" s="7"/>
     </row>
     <row r="61">
-      <c r="A61" s="1"/>
+      <c r="A61" s="2"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -2079,7 +2094,7 @@
       <c r="W61" s="7"/>
     </row>
     <row r="62">
-      <c r="A62" s="1"/>
+      <c r="A62" s="2"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -2104,7 +2119,7 @@
       <c r="W62" s="7"/>
     </row>
     <row r="63">
-      <c r="A63" s="1"/>
+      <c r="A63" s="2"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -2129,7 +2144,7 @@
       <c r="W63" s="7"/>
     </row>
     <row r="64">
-      <c r="A64" s="1"/>
+      <c r="A64" s="2"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -2154,7 +2169,7 @@
       <c r="W64" s="7"/>
     </row>
     <row r="65">
-      <c r="A65" s="1"/>
+      <c r="A65" s="2"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -2179,7 +2194,7 @@
       <c r="W65" s="7"/>
     </row>
     <row r="66">
-      <c r="A66" s="1"/>
+      <c r="A66" s="2"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -2204,7 +2219,7 @@
       <c r="W66" s="7"/>
     </row>
     <row r="67">
-      <c r="A67" s="1"/>
+      <c r="A67" s="2"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -2229,7 +2244,7 @@
       <c r="W67" s="7"/>
     </row>
     <row r="68">
-      <c r="A68" s="1"/>
+      <c r="A68" s="2"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -2254,7 +2269,7 @@
       <c r="W68" s="7"/>
     </row>
     <row r="69">
-      <c r="A69" s="1"/>
+      <c r="A69" s="2"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -2279,7 +2294,7 @@
       <c r="W69" s="7"/>
     </row>
     <row r="70">
-      <c r="A70" s="1"/>
+      <c r="A70" s="2"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -2304,7 +2319,7 @@
       <c r="W70" s="7"/>
     </row>
     <row r="71">
-      <c r="A71" s="1"/>
+      <c r="A71" s="2"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -2329,7 +2344,7 @@
       <c r="W71" s="7"/>
     </row>
     <row r="72">
-      <c r="A72" s="1"/>
+      <c r="A72" s="2"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -2354,7 +2369,7 @@
       <c r="W72" s="7"/>
     </row>
     <row r="73">
-      <c r="A73" s="1"/>
+      <c r="A73" s="2"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -2379,7 +2394,7 @@
       <c r="W73" s="7"/>
     </row>
     <row r="74">
-      <c r="A74" s="1"/>
+      <c r="A74" s="2"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -2404,7 +2419,7 @@
       <c r="W74" s="7"/>
     </row>
     <row r="75">
-      <c r="A75" s="1"/>
+      <c r="A75" s="2"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
@@ -2429,7 +2444,7 @@
       <c r="W75" s="7"/>
     </row>
     <row r="76">
-      <c r="A76" s="1"/>
+      <c r="A76" s="2"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -2454,7 +2469,7 @@
       <c r="W76" s="7"/>
     </row>
     <row r="77">
-      <c r="A77" s="1"/>
+      <c r="A77" s="2"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -2479,7 +2494,7 @@
       <c r="W77" s="7"/>
     </row>
     <row r="78">
-      <c r="A78" s="1"/>
+      <c r="A78" s="2"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -2504,7 +2519,7 @@
       <c r="W78" s="7"/>
     </row>
     <row r="79">
-      <c r="A79" s="1"/>
+      <c r="A79" s="2"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -2529,7 +2544,7 @@
       <c r="W79" s="7"/>
     </row>
     <row r="80">
-      <c r="A80" s="1"/>
+      <c r="A80" s="2"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -2554,7 +2569,7 @@
       <c r="W80" s="7"/>
     </row>
     <row r="81">
-      <c r="A81" s="1"/>
+      <c r="A81" s="2"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -2579,7 +2594,7 @@
       <c r="W81" s="7"/>
     </row>
     <row r="82">
-      <c r="A82" s="1"/>
+      <c r="A82" s="2"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -2604,7 +2619,7 @@
       <c r="W82" s="7"/>
     </row>
     <row r="83">
-      <c r="A83" s="1"/>
+      <c r="A83" s="2"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -2629,7 +2644,7 @@
       <c r="W83" s="7"/>
     </row>
     <row r="84">
-      <c r="A84" s="1"/>
+      <c r="A84" s="2"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -2654,7 +2669,7 @@
       <c r="W84" s="7"/>
     </row>
     <row r="85">
-      <c r="A85" s="1"/>
+      <c r="A85" s="2"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
@@ -2679,7 +2694,7 @@
       <c r="W85" s="7"/>
     </row>
     <row r="86">
-      <c r="A86" s="1"/>
+      <c r="A86" s="2"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
@@ -2704,7 +2719,7 @@
       <c r="W86" s="7"/>
     </row>
     <row r="87">
-      <c r="A87" s="1"/>
+      <c r="A87" s="2"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
@@ -2729,7 +2744,7 @@
       <c r="W87" s="7"/>
     </row>
     <row r="88">
-      <c r="A88" s="1"/>
+      <c r="A88" s="2"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
@@ -2754,7 +2769,7 @@
       <c r="W88" s="7"/>
     </row>
     <row r="89">
-      <c r="A89" s="1"/>
+      <c r="A89" s="2"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
@@ -2779,7 +2794,7 @@
       <c r="W89" s="7"/>
     </row>
     <row r="90">
-      <c r="A90" s="1"/>
+      <c r="A90" s="2"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
@@ -2804,7 +2819,7 @@
       <c r="W90" s="7"/>
     </row>
     <row r="91">
-      <c r="A91" s="1"/>
+      <c r="A91" s="2"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -2829,7 +2844,7 @@
       <c r="W91" s="7"/>
     </row>
     <row r="92">
-      <c r="A92" s="1"/>
+      <c r="A92" s="2"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -2854,7 +2869,7 @@
       <c r="W92" s="7"/>
     </row>
     <row r="93">
-      <c r="A93" s="1"/>
+      <c r="A93" s="2"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -2879,7 +2894,7 @@
       <c r="W93" s="7"/>
     </row>
     <row r="94">
-      <c r="A94" s="1"/>
+      <c r="A94" s="2"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -2904,7 +2919,7 @@
       <c r="W94" s="7"/>
     </row>
     <row r="95">
-      <c r="A95" s="1"/>
+      <c r="A95" s="2"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -2929,7 +2944,7 @@
       <c r="W95" s="7"/>
     </row>
     <row r="96">
-      <c r="A96" s="1"/>
+      <c r="A96" s="2"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -2954,7 +2969,7 @@
       <c r="W96" s="7"/>
     </row>
     <row r="97">
-      <c r="A97" s="1"/>
+      <c r="A97" s="2"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
@@ -2979,7 +2994,7 @@
       <c r="W97" s="7"/>
     </row>
     <row r="98">
-      <c r="A98" s="1"/>
+      <c r="A98" s="2"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
@@ -3004,7 +3019,7 @@
       <c r="W98" s="7"/>
     </row>
     <row r="99">
-      <c r="A99" s="1"/>
+      <c r="A99" s="2"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
@@ -3029,7 +3044,7 @@
       <c r="W99" s="7"/>
     </row>
     <row r="100">
-      <c r="A100" s="1"/>
+      <c r="A100" s="2"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
@@ -3054,7 +3069,7 @@
       <c r="W100" s="7"/>
     </row>
     <row r="101">
-      <c r="A101" s="1"/>
+      <c r="A101" s="2"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
@@ -3079,7 +3094,7 @@
       <c r="W101" s="7"/>
     </row>
     <row r="102">
-      <c r="A102" s="1"/>
+      <c r="A102" s="2"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
@@ -3104,7 +3119,7 @@
       <c r="W102" s="7"/>
     </row>
     <row r="103">
-      <c r="A103" s="1"/>
+      <c r="A103" s="2"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
@@ -3129,7 +3144,7 @@
       <c r="W103" s="7"/>
     </row>
     <row r="104">
-      <c r="A104" s="1"/>
+      <c r="A104" s="2"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
@@ -3154,7 +3169,7 @@
       <c r="W104" s="7"/>
     </row>
     <row r="105">
-      <c r="A105" s="1"/>
+      <c r="A105" s="2"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
@@ -3179,7 +3194,7 @@
       <c r="W105" s="7"/>
     </row>
     <row r="106">
-      <c r="A106" s="1"/>
+      <c r="A106" s="2"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
@@ -3204,7 +3219,7 @@
       <c r="W106" s="7"/>
     </row>
     <row r="107">
-      <c r="A107" s="1"/>
+      <c r="A107" s="2"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
@@ -3229,7 +3244,7 @@
       <c r="W107" s="7"/>
     </row>
     <row r="108">
-      <c r="A108" s="1"/>
+      <c r="A108" s="2"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
@@ -3254,7 +3269,7 @@
       <c r="W108" s="7"/>
     </row>
     <row r="109">
-      <c r="A109" s="1"/>
+      <c r="A109" s="2"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
@@ -3279,7 +3294,7 @@
       <c r="W109" s="7"/>
     </row>
     <row r="110">
-      <c r="A110" s="1"/>
+      <c r="A110" s="2"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
@@ -3304,7 +3319,7 @@
       <c r="W110" s="7"/>
     </row>
     <row r="111">
-      <c r="A111" s="1"/>
+      <c r="A111" s="2"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
@@ -3329,7 +3344,7 @@
       <c r="W111" s="7"/>
     </row>
     <row r="112">
-      <c r="A112" s="1"/>
+      <c r="A112" s="2"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
@@ -3354,7 +3369,7 @@
       <c r="W112" s="7"/>
     </row>
     <row r="113">
-      <c r="A113" s="1"/>
+      <c r="A113" s="2"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
@@ -3379,7 +3394,7 @@
       <c r="W113" s="7"/>
     </row>
     <row r="114">
-      <c r="A114" s="1"/>
+      <c r="A114" s="2"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
@@ -3404,7 +3419,7 @@
       <c r="W114" s="7"/>
     </row>
     <row r="115">
-      <c r="A115" s="1"/>
+      <c r="A115" s="2"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
@@ -3429,7 +3444,7 @@
       <c r="W115" s="7"/>
     </row>
     <row r="116">
-      <c r="A116" s="1"/>
+      <c r="A116" s="2"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
@@ -3454,7 +3469,7 @@
       <c r="W116" s="7"/>
     </row>
     <row r="117">
-      <c r="A117" s="1"/>
+      <c r="A117" s="2"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
@@ -3479,7 +3494,7 @@
       <c r="W117" s="7"/>
     </row>
     <row r="118">
-      <c r="A118" s="1"/>
+      <c r="A118" s="2"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
@@ -3504,7 +3519,7 @@
       <c r="W118" s="7"/>
     </row>
     <row r="119">
-      <c r="A119" s="1"/>
+      <c r="A119" s="2"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
@@ -3529,7 +3544,7 @@
       <c r="W119" s="7"/>
     </row>
     <row r="120">
-      <c r="A120" s="1"/>
+      <c r="A120" s="2"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
@@ -3554,7 +3569,7 @@
       <c r="W120" s="7"/>
     </row>
     <row r="121">
-      <c r="A121" s="1"/>
+      <c r="A121" s="2"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
@@ -3579,7 +3594,7 @@
       <c r="W121" s="7"/>
     </row>
     <row r="122">
-      <c r="A122" s="1"/>
+      <c r="A122" s="2"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
@@ -3604,7 +3619,7 @@
       <c r="W122" s="7"/>
     </row>
     <row r="123">
-      <c r="A123" s="1"/>
+      <c r="A123" s="2"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
@@ -3629,7 +3644,7 @@
       <c r="W123" s="7"/>
     </row>
     <row r="124">
-      <c r="A124" s="1"/>
+      <c r="A124" s="2"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
@@ -3654,7 +3669,7 @@
       <c r="W124" s="7"/>
     </row>
     <row r="125">
-      <c r="A125" s="1"/>
+      <c r="A125" s="2"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
@@ -3679,7 +3694,7 @@
       <c r="W125" s="7"/>
     </row>
     <row r="126">
-      <c r="A126" s="1"/>
+      <c r="A126" s="2"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
@@ -3704,7 +3719,7 @@
       <c r="W126" s="7"/>
     </row>
     <row r="127">
-      <c r="A127" s="1"/>
+      <c r="A127" s="2"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
@@ -3729,7 +3744,7 @@
       <c r="W127" s="7"/>
     </row>
     <row r="128">
-      <c r="A128" s="1"/>
+      <c r="A128" s="2"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
@@ -3754,7 +3769,7 @@
       <c r="W128" s="7"/>
     </row>
     <row r="129">
-      <c r="A129" s="1"/>
+      <c r="A129" s="2"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
@@ -3779,7 +3794,7 @@
       <c r="W129" s="7"/>
     </row>
     <row r="130">
-      <c r="A130" s="1"/>
+      <c r="A130" s="2"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
@@ -3804,7 +3819,7 @@
       <c r="W130" s="7"/>
     </row>
     <row r="131">
-      <c r="A131" s="1"/>
+      <c r="A131" s="2"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
@@ -3829,7 +3844,7 @@
       <c r="W131" s="7"/>
     </row>
     <row r="132">
-      <c r="A132" s="1"/>
+      <c r="A132" s="2"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
@@ -3854,7 +3869,7 @@
       <c r="W132" s="7"/>
     </row>
     <row r="133">
-      <c r="A133" s="1"/>
+      <c r="A133" s="2"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
@@ -3879,7 +3894,7 @@
       <c r="W133" s="7"/>
     </row>
     <row r="134">
-      <c r="A134" s="1"/>
+      <c r="A134" s="2"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
@@ -3904,7 +3919,7 @@
       <c r="W134" s="7"/>
     </row>
     <row r="135">
-      <c r="A135" s="1"/>
+      <c r="A135" s="2"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -3929,7 +3944,7 @@
       <c r="W135" s="7"/>
     </row>
     <row r="136">
-      <c r="A136" s="1"/>
+      <c r="A136" s="2"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
@@ -3954,7 +3969,7 @@
       <c r="W136" s="7"/>
     </row>
     <row r="137">
-      <c r="A137" s="1"/>
+      <c r="A137" s="2"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -3979,7 +3994,7 @@
       <c r="W137" s="7"/>
     </row>
     <row r="138">
-      <c r="A138" s="1"/>
+      <c r="A138" s="2"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
@@ -4004,7 +4019,7 @@
       <c r="W138" s="7"/>
     </row>
     <row r="139">
-      <c r="A139" s="1"/>
+      <c r="A139" s="2"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -4029,7 +4044,7 @@
       <c r="W139" s="7"/>
     </row>
     <row r="140">
-      <c r="A140" s="1"/>
+      <c r="A140" s="2"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
@@ -4054,7 +4069,7 @@
       <c r="W140" s="7"/>
     </row>
     <row r="141">
-      <c r="A141" s="1"/>
+      <c r="A141" s="2"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -4079,7 +4094,7 @@
       <c r="W141" s="7"/>
     </row>
     <row r="142">
-      <c r="A142" s="1"/>
+      <c r="A142" s="2"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
@@ -4104,7 +4119,7 @@
       <c r="W142" s="7"/>
     </row>
     <row r="143">
-      <c r="A143" s="1"/>
+      <c r="A143" s="2"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -4129,7 +4144,7 @@
       <c r="W143" s="7"/>
     </row>
     <row r="144">
-      <c r="A144" s="1"/>
+      <c r="A144" s="2"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
@@ -4154,7 +4169,7 @@
       <c r="W144" s="7"/>
     </row>
     <row r="145">
-      <c r="A145" s="1"/>
+      <c r="A145" s="2"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -4179,7 +4194,7 @@
       <c r="W145" s="7"/>
     </row>
     <row r="146">
-      <c r="A146" s="1"/>
+      <c r="A146" s="2"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
@@ -4204,7 +4219,7 @@
       <c r="W146" s="7"/>
     </row>
     <row r="147">
-      <c r="A147" s="1"/>
+      <c r="A147" s="2"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -4229,7 +4244,7 @@
       <c r="W147" s="7"/>
     </row>
     <row r="148">
-      <c r="A148" s="1"/>
+      <c r="A148" s="2"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
@@ -4254,7 +4269,7 @@
       <c r="W148" s="7"/>
     </row>
     <row r="149">
-      <c r="A149" s="1"/>
+      <c r="A149" s="2"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -4279,7 +4294,7 @@
       <c r="W149" s="7"/>
     </row>
     <row r="150">
-      <c r="A150" s="1"/>
+      <c r="A150" s="2"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
@@ -4304,7 +4319,7 @@
       <c r="W150" s="7"/>
     </row>
     <row r="151">
-      <c r="A151" s="1"/>
+      <c r="A151" s="2"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
@@ -4329,7 +4344,7 @@
       <c r="W151" s="7"/>
     </row>
     <row r="152">
-      <c r="A152" s="1"/>
+      <c r="A152" s="2"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
@@ -4354,7 +4369,7 @@
       <c r="W152" s="7"/>
     </row>
     <row r="153">
-      <c r="A153" s="1"/>
+      <c r="A153" s="2"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
@@ -4379,7 +4394,7 @@
       <c r="W153" s="7"/>
     </row>
     <row r="154">
-      <c r="A154" s="1"/>
+      <c r="A154" s="2"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
@@ -4404,7 +4419,7 @@
       <c r="W154" s="7"/>
     </row>
     <row r="155">
-      <c r="A155" s="1"/>
+      <c r="A155" s="2"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -4429,7 +4444,7 @@
       <c r="W155" s="7"/>
     </row>
     <row r="156">
-      <c r="A156" s="1"/>
+      <c r="A156" s="2"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
@@ -4454,7 +4469,7 @@
       <c r="W156" s="7"/>
     </row>
     <row r="157">
-      <c r="A157" s="1"/>
+      <c r="A157" s="2"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
@@ -4479,7 +4494,7 @@
       <c r="W157" s="7"/>
     </row>
     <row r="158">
-      <c r="A158" s="1"/>
+      <c r="A158" s="2"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
@@ -4504,7 +4519,7 @@
       <c r="W158" s="7"/>
     </row>
     <row r="159">
-      <c r="A159" s="1"/>
+      <c r="A159" s="2"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -4529,7 +4544,7 @@
       <c r="W159" s="7"/>
     </row>
     <row r="160">
-      <c r="A160" s="1"/>
+      <c r="A160" s="2"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -4554,7 +4569,7 @@
       <c r="W160" s="7"/>
     </row>
     <row r="161">
-      <c r="A161" s="1"/>
+      <c r="A161" s="2"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -4579,7 +4594,7 @@
       <c r="W161" s="7"/>
     </row>
     <row r="162">
-      <c r="A162" s="1"/>
+      <c r="A162" s="2"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -4604,7 +4619,7 @@
       <c r="W162" s="7"/>
     </row>
     <row r="163">
-      <c r="A163" s="1"/>
+      <c r="A163" s="2"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
@@ -4629,7 +4644,7 @@
       <c r="W163" s="7"/>
     </row>
     <row r="164">
-      <c r="A164" s="1"/>
+      <c r="A164" s="2"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
@@ -4654,7 +4669,7 @@
       <c r="W164" s="7"/>
     </row>
     <row r="165">
-      <c r="A165" s="1"/>
+      <c r="A165" s="2"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
@@ -4679,7 +4694,7 @@
       <c r="W165" s="7"/>
     </row>
     <row r="166">
-      <c r="A166" s="1"/>
+      <c r="A166" s="2"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
@@ -4704,7 +4719,7 @@
       <c r="W166" s="7"/>
     </row>
     <row r="167">
-      <c r="A167" s="1"/>
+      <c r="A167" s="2"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -4729,7 +4744,7 @@
       <c r="W167" s="7"/>
     </row>
     <row r="168">
-      <c r="A168" s="1"/>
+      <c r="A168" s="2"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -4754,7 +4769,7 @@
       <c r="W168" s="7"/>
     </row>
     <row r="169">
-      <c r="A169" s="1"/>
+      <c r="A169" s="2"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -4779,7 +4794,7 @@
       <c r="W169" s="7"/>
     </row>
     <row r="170">
-      <c r="A170" s="1"/>
+      <c r="A170" s="2"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -4804,7 +4819,7 @@
       <c r="W170" s="7"/>
     </row>
     <row r="171">
-      <c r="A171" s="1"/>
+      <c r="A171" s="2"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -4829,7 +4844,7 @@
       <c r="W171" s="7"/>
     </row>
     <row r="172">
-      <c r="A172" s="1"/>
+      <c r="A172" s="2"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -4854,7 +4869,7 @@
       <c r="W172" s="7"/>
     </row>
     <row r="173">
-      <c r="A173" s="1"/>
+      <c r="A173" s="2"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -4879,7 +4894,7 @@
       <c r="W173" s="7"/>
     </row>
     <row r="174">
-      <c r="A174" s="1"/>
+      <c r="A174" s="2"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -4904,7 +4919,7 @@
       <c r="W174" s="7"/>
     </row>
     <row r="175">
-      <c r="A175" s="1"/>
+      <c r="A175" s="2"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -4929,7 +4944,7 @@
       <c r="W175" s="7"/>
     </row>
     <row r="176">
-      <c r="A176" s="1"/>
+      <c r="A176" s="2"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -4954,7 +4969,7 @@
       <c r="W176" s="7"/>
     </row>
     <row r="177">
-      <c r="A177" s="1"/>
+      <c r="A177" s="2"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -4979,7 +4994,7 @@
       <c r="W177" s="7"/>
     </row>
     <row r="178">
-      <c r="A178" s="1"/>
+      <c r="A178" s="2"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -5004,7 +5019,7 @@
       <c r="W178" s="7"/>
     </row>
     <row r="179">
-      <c r="A179" s="1"/>
+      <c r="A179" s="2"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -5029,7 +5044,7 @@
       <c r="W179" s="7"/>
     </row>
     <row r="180">
-      <c r="A180" s="1"/>
+      <c r="A180" s="2"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -5054,7 +5069,7 @@
       <c r="W180" s="7"/>
     </row>
     <row r="181">
-      <c r="A181" s="1"/>
+      <c r="A181" s="2"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -5079,7 +5094,7 @@
       <c r="W181" s="7"/>
     </row>
     <row r="182">
-      <c r="A182" s="1"/>
+      <c r="A182" s="2"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -5104,7 +5119,7 @@
       <c r="W182" s="7"/>
     </row>
     <row r="183">
-      <c r="A183" s="1"/>
+      <c r="A183" s="2"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -5129,7 +5144,7 @@
       <c r="W183" s="7"/>
     </row>
     <row r="184">
-      <c r="A184" s="1"/>
+      <c r="A184" s="2"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -5154,7 +5169,7 @@
       <c r="W184" s="7"/>
     </row>
     <row r="185">
-      <c r="A185" s="1"/>
+      <c r="A185" s="2"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -5179,7 +5194,7 @@
       <c r="W185" s="7"/>
     </row>
     <row r="186">
-      <c r="A186" s="1"/>
+      <c r="A186" s="2"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -5204,7 +5219,7 @@
       <c r="W186" s="7"/>
     </row>
     <row r="187">
-      <c r="A187" s="1"/>
+      <c r="A187" s="2"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -5229,7 +5244,7 @@
       <c r="W187" s="7"/>
     </row>
     <row r="188">
-      <c r="A188" s="1"/>
+      <c r="A188" s="2"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -5254,7 +5269,7 @@
       <c r="W188" s="7"/>
     </row>
     <row r="189">
-      <c r="A189" s="1"/>
+      <c r="A189" s="2"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -5279,7 +5294,7 @@
       <c r="W189" s="7"/>
     </row>
     <row r="190">
-      <c r="A190" s="1"/>
+      <c r="A190" s="2"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -5304,7 +5319,7 @@
       <c r="W190" s="7"/>
     </row>
     <row r="191">
-      <c r="A191" s="1"/>
+      <c r="A191" s="2"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -5329,7 +5344,7 @@
       <c r="W191" s="7"/>
     </row>
     <row r="192">
-      <c r="A192" s="1"/>
+      <c r="A192" s="2"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -5354,7 +5369,7 @@
       <c r="W192" s="7"/>
     </row>
     <row r="193">
-      <c r="A193" s="1"/>
+      <c r="A193" s="2"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
@@ -5379,7 +5394,7 @@
       <c r="W193" s="7"/>
     </row>
     <row r="194">
-      <c r="A194" s="1"/>
+      <c r="A194" s="2"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
@@ -5404,7 +5419,7 @@
       <c r="W194" s="7"/>
     </row>
     <row r="195">
-      <c r="A195" s="1"/>
+      <c r="A195" s="2"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
@@ -5429,7 +5444,7 @@
       <c r="W195" s="7"/>
     </row>
     <row r="196">
-      <c r="A196" s="1"/>
+      <c r="A196" s="2"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
@@ -5454,7 +5469,7 @@
       <c r="W196" s="7"/>
     </row>
     <row r="197">
-      <c r="A197" s="1"/>
+      <c r="A197" s="2"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
@@ -5479,7 +5494,7 @@
       <c r="W197" s="7"/>
     </row>
     <row r="198">
-      <c r="A198" s="1"/>
+      <c r="A198" s="2"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
@@ -5504,7 +5519,7 @@
       <c r="W198" s="7"/>
     </row>
     <row r="199">
-      <c r="A199" s="1"/>
+      <c r="A199" s="2"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
@@ -5529,7 +5544,7 @@
       <c r="W199" s="7"/>
     </row>
     <row r="200">
-      <c r="A200" s="1"/>
+      <c r="A200" s="2"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
@@ -5554,7 +5569,7 @@
       <c r="W200" s="7"/>
     </row>
     <row r="201">
-      <c r="A201" s="1"/>
+      <c r="A201" s="2"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
@@ -5579,7 +5594,7 @@
       <c r="W201" s="7"/>
     </row>
     <row r="202">
-      <c r="A202" s="1"/>
+      <c r="A202" s="2"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
@@ -5604,7 +5619,7 @@
       <c r="W202" s="7"/>
     </row>
     <row r="203">
-      <c r="A203" s="1"/>
+      <c r="A203" s="2"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
@@ -5629,7 +5644,7 @@
       <c r="W203" s="7"/>
     </row>
     <row r="204">
-      <c r="A204" s="1"/>
+      <c r="A204" s="2"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
@@ -5654,7 +5669,7 @@
       <c r="W204" s="7"/>
     </row>
     <row r="205">
-      <c r="A205" s="1"/>
+      <c r="A205" s="2"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -5679,7 +5694,7 @@
       <c r="W205" s="7"/>
     </row>
     <row r="206">
-      <c r="A206" s="1"/>
+      <c r="A206" s="2"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -5704,7 +5719,7 @@
       <c r="W206" s="7"/>
     </row>
     <row r="207">
-      <c r="A207" s="1"/>
+      <c r="A207" s="2"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
@@ -5729,7 +5744,7 @@
       <c r="W207" s="7"/>
     </row>
     <row r="208">
-      <c r="A208" s="1"/>
+      <c r="A208" s="2"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
@@ -5754,7 +5769,7 @@
       <c r="W208" s="7"/>
     </row>
     <row r="209">
-      <c r="A209" s="1"/>
+      <c r="A209" s="2"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
@@ -5779,7 +5794,7 @@
       <c r="W209" s="7"/>
     </row>
     <row r="210">
-      <c r="A210" s="1"/>
+      <c r="A210" s="2"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
@@ -5804,7 +5819,7 @@
       <c r="W210" s="7"/>
     </row>
     <row r="211">
-      <c r="A211" s="1"/>
+      <c r="A211" s="2"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
@@ -5829,7 +5844,7 @@
       <c r="W211" s="7"/>
     </row>
     <row r="212">
-      <c r="A212" s="1"/>
+      <c r="A212" s="2"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
@@ -5854,7 +5869,7 @@
       <c r="W212" s="7"/>
     </row>
     <row r="213">
-      <c r="A213" s="1"/>
+      <c r="A213" s="2"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
@@ -5879,7 +5894,7 @@
       <c r="W213" s="7"/>
     </row>
     <row r="214">
-      <c r="A214" s="1"/>
+      <c r="A214" s="2"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
@@ -5904,7 +5919,7 @@
       <c r="W214" s="7"/>
     </row>
     <row r="215">
-      <c r="A215" s="1"/>
+      <c r="A215" s="2"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
@@ -5929,7 +5944,7 @@
       <c r="W215" s="7"/>
     </row>
     <row r="216">
-      <c r="A216" s="1"/>
+      <c r="A216" s="2"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
@@ -5954,7 +5969,7 @@
       <c r="W216" s="7"/>
     </row>
     <row r="217">
-      <c r="A217" s="1"/>
+      <c r="A217" s="2"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -5979,7 +5994,7 @@
       <c r="W217" s="7"/>
     </row>
     <row r="218">
-      <c r="A218" s="1"/>
+      <c r="A218" s="2"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -6004,7 +6019,7 @@
       <c r="W218" s="7"/>
     </row>
     <row r="219">
-      <c r="A219" s="1"/>
+      <c r="A219" s="2"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
@@ -6029,7 +6044,7 @@
       <c r="W219" s="7"/>
     </row>
     <row r="220">
-      <c r="A220" s="1"/>
+      <c r="A220" s="2"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -6054,7 +6069,7 @@
       <c r="W220" s="7"/>
     </row>
     <row r="221">
-      <c r="A221" s="1"/>
+      <c r="A221" s="2"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
@@ -6079,7 +6094,7 @@
       <c r="W221" s="7"/>
     </row>
     <row r="222">
-      <c r="A222" s="1"/>
+      <c r="A222" s="2"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
@@ -6104,7 +6119,7 @@
       <c r="W222" s="7"/>
     </row>
     <row r="223">
-      <c r="A223" s="1"/>
+      <c r="A223" s="2"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
@@ -6129,7 +6144,7 @@
       <c r="W223" s="7"/>
     </row>
     <row r="224">
-      <c r="A224" s="1"/>
+      <c r="A224" s="2"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
@@ -6154,7 +6169,7 @@
       <c r="W224" s="7"/>
     </row>
     <row r="225">
-      <c r="A225" s="1"/>
+      <c r="A225" s="2"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
@@ -6179,7 +6194,7 @@
       <c r="W225" s="7"/>
     </row>
     <row r="226">
-      <c r="A226" s="1"/>
+      <c r="A226" s="2"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
@@ -6204,7 +6219,7 @@
       <c r="W226" s="7"/>
     </row>
     <row r="227">
-      <c r="A227" s="1"/>
+      <c r="A227" s="2"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
@@ -6229,7 +6244,7 @@
       <c r="W227" s="7"/>
     </row>
     <row r="228">
-      <c r="A228" s="1"/>
+      <c r="A228" s="2"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -6254,7 +6269,7 @@
       <c r="W228" s="7"/>
     </row>
     <row r="229">
-      <c r="A229" s="1"/>
+      <c r="A229" s="2"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
@@ -6279,7 +6294,7 @@
       <c r="W229" s="7"/>
     </row>
     <row r="230">
-      <c r="A230" s="1"/>
+      <c r="A230" s="2"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
@@ -6304,7 +6319,7 @@
       <c r="W230" s="7"/>
     </row>
     <row r="231">
-      <c r="A231" s="1"/>
+      <c r="A231" s="2"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
@@ -6329,7 +6344,7 @@
       <c r="W231" s="7"/>
     </row>
     <row r="232">
-      <c r="A232" s="1"/>
+      <c r="A232" s="2"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -6354,7 +6369,7 @@
       <c r="W232" s="7"/>
     </row>
     <row r="233">
-      <c r="A233" s="1"/>
+      <c r="A233" s="2"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
@@ -6379,7 +6394,7 @@
       <c r="W233" s="7"/>
     </row>
     <row r="234">
-      <c r="A234" s="1"/>
+      <c r="A234" s="2"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
@@ -6404,7 +6419,7 @@
       <c r="W234" s="7"/>
     </row>
     <row r="235">
-      <c r="A235" s="1"/>
+      <c r="A235" s="2"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
@@ -6429,7 +6444,7 @@
       <c r="W235" s="7"/>
     </row>
     <row r="236">
-      <c r="A236" s="1"/>
+      <c r="A236" s="2"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
@@ -6454,7 +6469,7 @@
       <c r="W236" s="7"/>
     </row>
     <row r="237">
-      <c r="A237" s="1"/>
+      <c r="A237" s="2"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
@@ -6479,7 +6494,7 @@
       <c r="W237" s="7"/>
     </row>
     <row r="238">
-      <c r="A238" s="1"/>
+      <c r="A238" s="2"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
@@ -6504,7 +6519,7 @@
       <c r="W238" s="7"/>
     </row>
     <row r="239">
-      <c r="A239" s="1"/>
+      <c r="A239" s="2"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
@@ -6529,7 +6544,7 @@
       <c r="W239" s="7"/>
     </row>
     <row r="240">
-      <c r="A240" s="1"/>
+      <c r="A240" s="2"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
@@ -6554,7 +6569,7 @@
       <c r="W240" s="7"/>
     </row>
     <row r="241">
-      <c r="A241" s="1"/>
+      <c r="A241" s="2"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
@@ -6579,7 +6594,7 @@
       <c r="W241" s="7"/>
     </row>
     <row r="242">
-      <c r="A242" s="1"/>
+      <c r="A242" s="2"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
@@ -6604,7 +6619,7 @@
       <c r="W242" s="7"/>
     </row>
     <row r="243">
-      <c r="A243" s="1"/>
+      <c r="A243" s="2"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
@@ -6629,7 +6644,7 @@
       <c r="W243" s="7"/>
     </row>
     <row r="244">
-      <c r="A244" s="1"/>
+      <c r="A244" s="2"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
@@ -6654,7 +6669,7 @@
       <c r="W244" s="7"/>
     </row>
     <row r="245">
-      <c r="A245" s="1"/>
+      <c r="A245" s="2"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
@@ -6679,7 +6694,7 @@
       <c r="W245" s="7"/>
     </row>
     <row r="246">
-      <c r="A246" s="1"/>
+      <c r="A246" s="2"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
@@ -6704,7 +6719,7 @@
       <c r="W246" s="7"/>
     </row>
     <row r="247">
-      <c r="A247" s="1"/>
+      <c r="A247" s="2"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
@@ -6729,7 +6744,7 @@
       <c r="W247" s="7"/>
     </row>
     <row r="248">
-      <c r="A248" s="1"/>
+      <c r="A248" s="2"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
@@ -6754,7 +6769,7 @@
       <c r="W248" s="7"/>
     </row>
     <row r="249">
-      <c r="A249" s="1"/>
+      <c r="A249" s="2"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
@@ -6779,7 +6794,7 @@
       <c r="W249" s="7"/>
     </row>
     <row r="250">
-      <c r="A250" s="1"/>
+      <c r="A250" s="2"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
@@ -6804,7 +6819,7 @@
       <c r="W250" s="7"/>
     </row>
     <row r="251">
-      <c r="A251" s="1"/>
+      <c r="A251" s="2"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
@@ -6829,7 +6844,7 @@
       <c r="W251" s="7"/>
     </row>
     <row r="252">
-      <c r="A252" s="1"/>
+      <c r="A252" s="2"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
@@ -6854,7 +6869,7 @@
       <c r="W252" s="7"/>
     </row>
     <row r="253">
-      <c r="A253" s="1"/>
+      <c r="A253" s="2"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
@@ -6879,7 +6894,7 @@
       <c r="W253" s="7"/>
     </row>
     <row r="254">
-      <c r="A254" s="1"/>
+      <c r="A254" s="2"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
@@ -6904,7 +6919,7 @@
       <c r="W254" s="7"/>
     </row>
     <row r="255">
-      <c r="A255" s="1"/>
+      <c r="A255" s="2"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
@@ -6929,7 +6944,7 @@
       <c r="W255" s="7"/>
     </row>
     <row r="256">
-      <c r="A256" s="1"/>
+      <c r="A256" s="2"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
@@ -6954,7 +6969,7 @@
       <c r="W256" s="7"/>
     </row>
     <row r="257">
-      <c r="A257" s="1"/>
+      <c r="A257" s="2"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
@@ -6979,7 +6994,7 @@
       <c r="W257" s="7"/>
     </row>
     <row r="258">
-      <c r="A258" s="1"/>
+      <c r="A258" s="2"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
@@ -7004,7 +7019,7 @@
       <c r="W258" s="7"/>
     </row>
     <row r="259">
-      <c r="A259" s="1"/>
+      <c r="A259" s="2"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
@@ -7029,7 +7044,7 @@
       <c r="W259" s="7"/>
     </row>
     <row r="260">
-      <c r="A260" s="1"/>
+      <c r="A260" s="2"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
@@ -7054,7 +7069,7 @@
       <c r="W260" s="7"/>
     </row>
     <row r="261">
-      <c r="A261" s="1"/>
+      <c r="A261" s="2"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
@@ -7079,7 +7094,7 @@
       <c r="W261" s="7"/>
     </row>
     <row r="262">
-      <c r="A262" s="1"/>
+      <c r="A262" s="2"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
@@ -7104,7 +7119,7 @@
       <c r="W262" s="7"/>
     </row>
     <row r="263">
-      <c r="A263" s="1"/>
+      <c r="A263" s="2"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
@@ -7129,7 +7144,7 @@
       <c r="W263" s="7"/>
     </row>
     <row r="264">
-      <c r="A264" s="1"/>
+      <c r="A264" s="2"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
@@ -7154,7 +7169,7 @@
       <c r="W264" s="7"/>
     </row>
     <row r="265">
-      <c r="A265" s="1"/>
+      <c r="A265" s="2"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
@@ -7179,7 +7194,7 @@
       <c r="W265" s="7"/>
     </row>
     <row r="266">
-      <c r="A266" s="1"/>
+      <c r="A266" s="2"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
@@ -7204,7 +7219,7 @@
       <c r="W266" s="7"/>
     </row>
     <row r="267">
-      <c r="A267" s="1"/>
+      <c r="A267" s="2"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
@@ -7229,7 +7244,7 @@
       <c r="W267" s="7"/>
     </row>
     <row r="268">
-      <c r="A268" s="1"/>
+      <c r="A268" s="2"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
@@ -7254,7 +7269,7 @@
       <c r="W268" s="7"/>
     </row>
     <row r="269">
-      <c r="A269" s="1"/>
+      <c r="A269" s="2"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
@@ -7279,7 +7294,7 @@
       <c r="W269" s="7"/>
     </row>
     <row r="270">
-      <c r="A270" s="1"/>
+      <c r="A270" s="2"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
@@ -7304,7 +7319,7 @@
       <c r="W270" s="7"/>
     </row>
     <row r="271">
-      <c r="A271" s="1"/>
+      <c r="A271" s="2"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
@@ -7329,7 +7344,7 @@
       <c r="W271" s="7"/>
     </row>
     <row r="272">
-      <c r="A272" s="1"/>
+      <c r="A272" s="2"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
@@ -7354,7 +7369,7 @@
       <c r="W272" s="7"/>
     </row>
     <row r="273">
-      <c r="A273" s="1"/>
+      <c r="A273" s="2"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
@@ -7379,7 +7394,7 @@
       <c r="W273" s="7"/>
     </row>
     <row r="274">
-      <c r="A274" s="1"/>
+      <c r="A274" s="2"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
@@ -7404,7 +7419,7 @@
       <c r="W274" s="7"/>
     </row>
     <row r="275">
-      <c r="A275" s="1"/>
+      <c r="A275" s="2"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
@@ -7429,7 +7444,7 @@
       <c r="W275" s="7"/>
     </row>
     <row r="276">
-      <c r="A276" s="1"/>
+      <c r="A276" s="2"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
@@ -7454,7 +7469,7 @@
       <c r="W276" s="7"/>
     </row>
     <row r="277">
-      <c r="A277" s="1"/>
+      <c r="A277" s="2"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
@@ -7479,7 +7494,7 @@
       <c r="W277" s="7"/>
     </row>
     <row r="278">
-      <c r="A278" s="1"/>
+      <c r="A278" s="2"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
@@ -7504,7 +7519,7 @@
       <c r="W278" s="7"/>
     </row>
     <row r="279">
-      <c r="A279" s="1"/>
+      <c r="A279" s="2"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
@@ -7529,7 +7544,7 @@
       <c r="W279" s="7"/>
     </row>
     <row r="280">
-      <c r="A280" s="1"/>
+      <c r="A280" s="2"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
@@ -7554,7 +7569,7 @@
       <c r="W280" s="7"/>
     </row>
     <row r="281">
-      <c r="A281" s="1"/>
+      <c r="A281" s="2"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
@@ -7579,7 +7594,7 @@
       <c r="W281" s="7"/>
     </row>
     <row r="282">
-      <c r="A282" s="1"/>
+      <c r="A282" s="2"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
@@ -7604,7 +7619,7 @@
       <c r="W282" s="7"/>
     </row>
     <row r="283">
-      <c r="A283" s="1"/>
+      <c r="A283" s="2"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
@@ -7629,7 +7644,7 @@
       <c r="W283" s="7"/>
     </row>
     <row r="284">
-      <c r="A284" s="1"/>
+      <c r="A284" s="2"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
@@ -7654,7 +7669,7 @@
       <c r="W284" s="7"/>
     </row>
     <row r="285">
-      <c r="A285" s="1"/>
+      <c r="A285" s="2"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
@@ -7679,7 +7694,7 @@
       <c r="W285" s="7"/>
     </row>
     <row r="286">
-      <c r="A286" s="1"/>
+      <c r="A286" s="2"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
@@ -7704,7 +7719,7 @@
       <c r="W286" s="7"/>
     </row>
     <row r="287">
-      <c r="A287" s="1"/>
+      <c r="A287" s="2"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
@@ -7729,7 +7744,7 @@
       <c r="W287" s="7"/>
     </row>
     <row r="288">
-      <c r="A288" s="1"/>
+      <c r="A288" s="2"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
@@ -7754,7 +7769,7 @@
       <c r="W288" s="7"/>
     </row>
     <row r="289">
-      <c r="A289" s="1"/>
+      <c r="A289" s="2"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
@@ -7779,7 +7794,7 @@
       <c r="W289" s="7"/>
     </row>
     <row r="290">
-      <c r="A290" s="1"/>
+      <c r="A290" s="2"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
@@ -7804,7 +7819,7 @@
       <c r="W290" s="7"/>
     </row>
     <row r="291">
-      <c r="A291" s="1"/>
+      <c r="A291" s="2"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
@@ -7829,7 +7844,7 @@
       <c r="W291" s="7"/>
     </row>
     <row r="292">
-      <c r="A292" s="1"/>
+      <c r="A292" s="2"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
@@ -7854,7 +7869,7 @@
       <c r="W292" s="7"/>
     </row>
     <row r="293">
-      <c r="A293" s="1"/>
+      <c r="A293" s="2"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
@@ -7879,7 +7894,7 @@
       <c r="W293" s="7"/>
     </row>
     <row r="294">
-      <c r="A294" s="1"/>
+      <c r="A294" s="2"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
@@ -7904,7 +7919,7 @@
       <c r="W294" s="7"/>
     </row>
     <row r="295">
-      <c r="A295" s="1"/>
+      <c r="A295" s="2"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
@@ -7929,7 +7944,7 @@
       <c r="W295" s="7"/>
     </row>
     <row r="296">
-      <c r="A296" s="1"/>
+      <c r="A296" s="2"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
@@ -7954,7 +7969,7 @@
       <c r="W296" s="7"/>
     </row>
     <row r="297">
-      <c r="A297" s="1"/>
+      <c r="A297" s="2"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
@@ -7979,7 +7994,7 @@
       <c r="W297" s="7"/>
     </row>
     <row r="298">
-      <c r="A298" s="1"/>
+      <c r="A298" s="2"/>
       <c r="B298" s="7"/>
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
@@ -8004,7 +8019,7 @@
       <c r="W298" s="7"/>
     </row>
     <row r="299">
-      <c r="A299" s="1"/>
+      <c r="A299" s="2"/>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
@@ -8029,7 +8044,7 @@
       <c r="W299" s="7"/>
     </row>
     <row r="300">
-      <c r="A300" s="1"/>
+      <c r="A300" s="2"/>
       <c r="B300" s="7"/>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
@@ -8054,7 +8069,7 @@
       <c r="W300" s="7"/>
     </row>
     <row r="301">
-      <c r="A301" s="1"/>
+      <c r="A301" s="2"/>
       <c r="B301" s="7"/>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
@@ -8079,7 +8094,7 @@
       <c r="W301" s="7"/>
     </row>
     <row r="302">
-      <c r="A302" s="1"/>
+      <c r="A302" s="2"/>
       <c r="B302" s="7"/>
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
@@ -8104,7 +8119,7 @@
       <c r="W302" s="7"/>
     </row>
     <row r="303">
-      <c r="A303" s="1"/>
+      <c r="A303" s="2"/>
       <c r="B303" s="7"/>
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
@@ -8129,7 +8144,7 @@
       <c r="W303" s="7"/>
     </row>
     <row r="304">
-      <c r="A304" s="1"/>
+      <c r="A304" s="2"/>
       <c r="B304" s="7"/>
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
@@ -8154,7 +8169,7 @@
       <c r="W304" s="7"/>
     </row>
     <row r="305">
-      <c r="A305" s="1"/>
+      <c r="A305" s="2"/>
       <c r="B305" s="7"/>
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
@@ -8179,7 +8194,7 @@
       <c r="W305" s="7"/>
     </row>
     <row r="306">
-      <c r="A306" s="1"/>
+      <c r="A306" s="2"/>
       <c r="B306" s="7"/>
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
@@ -8204,7 +8219,7 @@
       <c r="W306" s="7"/>
     </row>
     <row r="307">
-      <c r="A307" s="1"/>
+      <c r="A307" s="2"/>
       <c r="B307" s="7"/>
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
@@ -8229,7 +8244,7 @@
       <c r="W307" s="7"/>
     </row>
     <row r="308">
-      <c r="A308" s="1"/>
+      <c r="A308" s="2"/>
       <c r="B308" s="7"/>
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
@@ -8254,7 +8269,7 @@
       <c r="W308" s="7"/>
     </row>
     <row r="309">
-      <c r="A309" s="1"/>
+      <c r="A309" s="2"/>
       <c r="B309" s="7"/>
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
@@ -8279,7 +8294,7 @@
       <c r="W309" s="7"/>
     </row>
     <row r="310">
-      <c r="A310" s="1"/>
+      <c r="A310" s="2"/>
       <c r="B310" s="7"/>
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
@@ -8304,7 +8319,7 @@
       <c r="W310" s="7"/>
     </row>
     <row r="311">
-      <c r="A311" s="1"/>
+      <c r="A311" s="2"/>
       <c r="B311" s="7"/>
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
@@ -8329,7 +8344,7 @@
       <c r="W311" s="7"/>
     </row>
     <row r="312">
-      <c r="A312" s="1"/>
+      <c r="A312" s="2"/>
       <c r="B312" s="7"/>
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
@@ -8354,7 +8369,7 @@
       <c r="W312" s="7"/>
     </row>
     <row r="313">
-      <c r="A313" s="1"/>
+      <c r="A313" s="2"/>
       <c r="B313" s="7"/>
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
@@ -8379,7 +8394,7 @@
       <c r="W313" s="7"/>
     </row>
     <row r="314">
-      <c r="A314" s="1"/>
+      <c r="A314" s="2"/>
       <c r="B314" s="7"/>
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
@@ -8404,7 +8419,7 @@
       <c r="W314" s="7"/>
     </row>
     <row r="315">
-      <c r="A315" s="1"/>
+      <c r="A315" s="2"/>
       <c r="B315" s="7"/>
       <c r="C315" s="7"/>
       <c r="D315" s="7"/>
@@ -8429,7 +8444,7 @@
       <c r="W315" s="7"/>
     </row>
     <row r="316">
-      <c r="A316" s="1"/>
+      <c r="A316" s="2"/>
       <c r="B316" s="7"/>
       <c r="C316" s="7"/>
       <c r="D316" s="7"/>
@@ -8454,7 +8469,7 @@
       <c r="W316" s="7"/>
     </row>
     <row r="317">
-      <c r="A317" s="1"/>
+      <c r="A317" s="2"/>
       <c r="B317" s="7"/>
       <c r="C317" s="7"/>
       <c r="D317" s="7"/>
@@ -8479,7 +8494,7 @@
       <c r="W317" s="7"/>
     </row>
     <row r="318">
-      <c r="A318" s="1"/>
+      <c r="A318" s="2"/>
       <c r="B318" s="7"/>
       <c r="C318" s="7"/>
       <c r="D318" s="7"/>
@@ -8504,7 +8519,7 @@
       <c r="W318" s="7"/>
     </row>
     <row r="319">
-      <c r="A319" s="1"/>
+      <c r="A319" s="2"/>
       <c r="B319" s="7"/>
       <c r="C319" s="7"/>
       <c r="D319" s="7"/>
@@ -8529,7 +8544,7 @@
       <c r="W319" s="7"/>
     </row>
     <row r="320">
-      <c r="A320" s="1"/>
+      <c r="A320" s="2"/>
       <c r="B320" s="7"/>
       <c r="C320" s="7"/>
       <c r="D320" s="7"/>
@@ -8554,7 +8569,7 @@
       <c r="W320" s="7"/>
     </row>
     <row r="321">
-      <c r="A321" s="1"/>
+      <c r="A321" s="2"/>
       <c r="B321" s="7"/>
       <c r="C321" s="7"/>
       <c r="D321" s="7"/>
@@ -8579,7 +8594,7 @@
       <c r="W321" s="7"/>
     </row>
     <row r="322">
-      <c r="A322" s="1"/>
+      <c r="A322" s="2"/>
       <c r="B322" s="7"/>
       <c r="C322" s="7"/>
       <c r="D322" s="7"/>
@@ -8604,7 +8619,7 @@
       <c r="W322" s="7"/>
     </row>
     <row r="323">
-      <c r="A323" s="1"/>
+      <c r="A323" s="2"/>
       <c r="B323" s="7"/>
       <c r="C323" s="7"/>
       <c r="D323" s="7"/>
@@ -8629,7 +8644,7 @@
       <c r="W323" s="7"/>
     </row>
     <row r="324">
-      <c r="A324" s="1"/>
+      <c r="A324" s="2"/>
       <c r="B324" s="7"/>
       <c r="C324" s="7"/>
       <c r="D324" s="7"/>
@@ -8654,7 +8669,7 @@
       <c r="W324" s="7"/>
     </row>
     <row r="325">
-      <c r="A325" s="1"/>
+      <c r="A325" s="2"/>
       <c r="B325" s="7"/>
       <c r="C325" s="7"/>
       <c r="D325" s="7"/>
@@ -8679,7 +8694,7 @@
       <c r="W325" s="7"/>
     </row>
     <row r="326">
-      <c r="A326" s="1"/>
+      <c r="A326" s="2"/>
       <c r="B326" s="7"/>
       <c r="C326" s="7"/>
       <c r="D326" s="7"/>
@@ -8704,7 +8719,7 @@
       <c r="W326" s="7"/>
     </row>
     <row r="327">
-      <c r="A327" s="1"/>
+      <c r="A327" s="2"/>
       <c r="B327" s="7"/>
       <c r="C327" s="7"/>
       <c r="D327" s="7"/>
@@ -8729,7 +8744,7 @@
       <c r="W327" s="7"/>
     </row>
     <row r="328">
-      <c r="A328" s="1"/>
+      <c r="A328" s="2"/>
       <c r="B328" s="7"/>
       <c r="C328" s="7"/>
       <c r="D328" s="7"/>
@@ -8754,7 +8769,7 @@
       <c r="W328" s="7"/>
     </row>
     <row r="329">
-      <c r="A329" s="1"/>
+      <c r="A329" s="2"/>
       <c r="B329" s="7"/>
       <c r="C329" s="7"/>
       <c r="D329" s="7"/>
@@ -8779,7 +8794,7 @@
       <c r="W329" s="7"/>
     </row>
     <row r="330">
-      <c r="A330" s="1"/>
+      <c r="A330" s="2"/>
       <c r="B330" s="7"/>
       <c r="C330" s="7"/>
       <c r="D330" s="7"/>
@@ -8804,7 +8819,7 @@
       <c r="W330" s="7"/>
     </row>
     <row r="331">
-      <c r="A331" s="1"/>
+      <c r="A331" s="2"/>
       <c r="B331" s="7"/>
       <c r="C331" s="7"/>
       <c r="D331" s="7"/>
@@ -8829,7 +8844,7 @@
       <c r="W331" s="7"/>
     </row>
     <row r="332">
-      <c r="A332" s="1"/>
+      <c r="A332" s="2"/>
       <c r="B332" s="7"/>
       <c r="C332" s="7"/>
       <c r="D332" s="7"/>
@@ -8854,7 +8869,7 @@
       <c r="W332" s="7"/>
     </row>
     <row r="333">
-      <c r="A333" s="1"/>
+      <c r="A333" s="2"/>
       <c r="B333" s="7"/>
       <c r="C333" s="7"/>
       <c r="D333" s="7"/>
@@ -8879,7 +8894,7 @@
       <c r="W333" s="7"/>
     </row>
     <row r="334">
-      <c r="A334" s="1"/>
+      <c r="A334" s="2"/>
       <c r="B334" s="7"/>
       <c r="C334" s="7"/>
       <c r="D334" s="7"/>
@@ -8904,7 +8919,7 @@
       <c r="W334" s="7"/>
     </row>
     <row r="335">
-      <c r="A335" s="1"/>
+      <c r="A335" s="2"/>
       <c r="B335" s="7"/>
       <c r="C335" s="7"/>
       <c r="D335" s="7"/>
@@ -8929,7 +8944,7 @@
       <c r="W335" s="7"/>
     </row>
     <row r="336">
-      <c r="A336" s="1"/>
+      <c r="A336" s="2"/>
       <c r="B336" s="7"/>
       <c r="C336" s="7"/>
       <c r="D336" s="7"/>
@@ -8954,7 +8969,7 @@
       <c r="W336" s="7"/>
     </row>
     <row r="337">
-      <c r="A337" s="1"/>
+      <c r="A337" s="2"/>
       <c r="B337" s="7"/>
       <c r="C337" s="7"/>
       <c r="D337" s="7"/>
@@ -8979,7 +8994,7 @@
       <c r="W337" s="7"/>
     </row>
     <row r="338">
-      <c r="A338" s="1"/>
+      <c r="A338" s="2"/>
       <c r="B338" s="7"/>
       <c r="C338" s="7"/>
       <c r="D338" s="7"/>
@@ -9004,7 +9019,7 @@
       <c r="W338" s="7"/>
     </row>
     <row r="339">
-      <c r="A339" s="1"/>
+      <c r="A339" s="2"/>
       <c r="B339" s="7"/>
       <c r="C339" s="7"/>
       <c r="D339" s="7"/>
@@ -9029,7 +9044,7 @@
       <c r="W339" s="7"/>
     </row>
     <row r="340">
-      <c r="A340" s="1"/>
+      <c r="A340" s="2"/>
       <c r="B340" s="7"/>
       <c r="C340" s="7"/>
       <c r="D340" s="7"/>
@@ -9054,7 +9069,7 @@
       <c r="W340" s="7"/>
     </row>
     <row r="341">
-      <c r="A341" s="1"/>
+      <c r="A341" s="2"/>
       <c r="B341" s="7"/>
       <c r="C341" s="7"/>
       <c r="D341" s="7"/>
@@ -9079,7 +9094,7 @@
       <c r="W341" s="7"/>
     </row>
     <row r="342">
-      <c r="A342" s="1"/>
+      <c r="A342" s="2"/>
       <c r="B342" s="7"/>
       <c r="C342" s="7"/>
       <c r="D342" s="7"/>
@@ -9104,7 +9119,7 @@
       <c r="W342" s="7"/>
     </row>
     <row r="343">
-      <c r="A343" s="1"/>
+      <c r="A343" s="2"/>
       <c r="B343" s="7"/>
       <c r="C343" s="7"/>
       <c r="D343" s="7"/>
@@ -9129,7 +9144,7 @@
       <c r="W343" s="7"/>
     </row>
     <row r="344">
-      <c r="A344" s="1"/>
+      <c r="A344" s="2"/>
       <c r="B344" s="7"/>
       <c r="C344" s="7"/>
       <c r="D344" s="7"/>
@@ -9154,7 +9169,7 @@
       <c r="W344" s="7"/>
     </row>
     <row r="345">
-      <c r="A345" s="1"/>
+      <c r="A345" s="2"/>
       <c r="B345" s="7"/>
       <c r="C345" s="7"/>
       <c r="D345" s="7"/>
@@ -9179,7 +9194,7 @@
       <c r="W345" s="7"/>
     </row>
     <row r="346">
-      <c r="A346" s="1"/>
+      <c r="A346" s="2"/>
       <c r="B346" s="7"/>
       <c r="C346" s="7"/>
       <c r="D346" s="7"/>
@@ -9204,7 +9219,7 @@
       <c r="W346" s="7"/>
     </row>
     <row r="347">
-      <c r="A347" s="1"/>
+      <c r="A347" s="2"/>
       <c r="B347" s="7"/>
       <c r="C347" s="7"/>
       <c r="D347" s="7"/>
@@ -9229,7 +9244,7 @@
       <c r="W347" s="7"/>
     </row>
     <row r="348">
-      <c r="A348" s="1"/>
+      <c r="A348" s="2"/>
       <c r="B348" s="7"/>
       <c r="C348" s="7"/>
       <c r="D348" s="7"/>
@@ -9254,7 +9269,7 @@
       <c r="W348" s="7"/>
     </row>
     <row r="349">
-      <c r="A349" s="1"/>
+      <c r="A349" s="2"/>
       <c r="B349" s="7"/>
       <c r="C349" s="7"/>
       <c r="D349" s="7"/>
@@ -9279,7 +9294,7 @@
       <c r="W349" s="7"/>
     </row>
     <row r="350">
-      <c r="A350" s="1"/>
+      <c r="A350" s="2"/>
       <c r="B350" s="7"/>
       <c r="C350" s="7"/>
       <c r="D350" s="7"/>
@@ -9304,7 +9319,7 @@
       <c r="W350" s="7"/>
     </row>
     <row r="351">
-      <c r="A351" s="1"/>
+      <c r="A351" s="2"/>
       <c r="B351" s="7"/>
       <c r="C351" s="7"/>
       <c r="D351" s="7"/>
@@ -9329,7 +9344,7 @@
       <c r="W351" s="7"/>
     </row>
     <row r="352">
-      <c r="A352" s="1"/>
+      <c r="A352" s="2"/>
       <c r="B352" s="7"/>
       <c r="C352" s="7"/>
       <c r="D352" s="7"/>
@@ -9354,7 +9369,7 @@
       <c r="W352" s="7"/>
     </row>
     <row r="353">
-      <c r="A353" s="1"/>
+      <c r="A353" s="2"/>
       <c r="B353" s="7"/>
       <c r="C353" s="7"/>
       <c r="D353" s="7"/>
@@ -9379,7 +9394,7 @@
       <c r="W353" s="7"/>
     </row>
     <row r="354">
-      <c r="A354" s="1"/>
+      <c r="A354" s="2"/>
       <c r="B354" s="7"/>
       <c r="C354" s="7"/>
       <c r="D354" s="7"/>
@@ -9404,7 +9419,7 @@
       <c r="W354" s="7"/>
     </row>
     <row r="355">
-      <c r="A355" s="1"/>
+      <c r="A355" s="2"/>
       <c r="B355" s="7"/>
       <c r="C355" s="7"/>
       <c r="D355" s="7"/>
@@ -9429,7 +9444,7 @@
       <c r="W355" s="7"/>
     </row>
     <row r="356">
-      <c r="A356" s="1"/>
+      <c r="A356" s="2"/>
       <c r="B356" s="7"/>
       <c r="C356" s="7"/>
       <c r="D356" s="7"/>
@@ -9454,7 +9469,7 @@
       <c r="W356" s="7"/>
     </row>
     <row r="357">
-      <c r="A357" s="1"/>
+      <c r="A357" s="2"/>
       <c r="B357" s="7"/>
       <c r="C357" s="7"/>
       <c r="D357" s="7"/>
@@ -9479,7 +9494,7 @@
       <c r="W357" s="7"/>
     </row>
     <row r="358">
-      <c r="A358" s="1"/>
+      <c r="A358" s="2"/>
       <c r="B358" s="7"/>
       <c r="C358" s="7"/>
       <c r="D358" s="7"/>
@@ -9504,7 +9519,7 @@
       <c r="W358" s="7"/>
     </row>
     <row r="359">
-      <c r="A359" s="1"/>
+      <c r="A359" s="2"/>
       <c r="B359" s="7"/>
       <c r="C359" s="7"/>
       <c r="D359" s="7"/>
@@ -9529,7 +9544,7 @@
       <c r="W359" s="7"/>
     </row>
     <row r="360">
-      <c r="A360" s="1"/>
+      <c r="A360" s="2"/>
       <c r="B360" s="7"/>
       <c r="C360" s="7"/>
       <c r="D360" s="7"/>
@@ -9554,7 +9569,7 @@
       <c r="W360" s="7"/>
     </row>
     <row r="361">
-      <c r="A361" s="1"/>
+      <c r="A361" s="2"/>
       <c r="B361" s="7"/>
       <c r="C361" s="7"/>
       <c r="D361" s="7"/>
@@ -9579,7 +9594,7 @@
       <c r="W361" s="7"/>
     </row>
     <row r="362">
-      <c r="A362" s="1"/>
+      <c r="A362" s="2"/>
       <c r="B362" s="7"/>
       <c r="C362" s="7"/>
       <c r="D362" s="7"/>
@@ -9604,7 +9619,7 @@
       <c r="W362" s="7"/>
     </row>
     <row r="363">
-      <c r="A363" s="1"/>
+      <c r="A363" s="2"/>
       <c r="B363" s="7"/>
       <c r="C363" s="7"/>
       <c r="D363" s="7"/>
@@ -9629,7 +9644,7 @@
       <c r="W363" s="7"/>
     </row>
     <row r="364">
-      <c r="A364" s="1"/>
+      <c r="A364" s="2"/>
       <c r="B364" s="7"/>
       <c r="C364" s="7"/>
       <c r="D364" s="7"/>
@@ -9654,7 +9669,7 @@
       <c r="W364" s="7"/>
     </row>
     <row r="365">
-      <c r="A365" s="1"/>
+      <c r="A365" s="2"/>
       <c r="B365" s="7"/>
       <c r="C365" s="7"/>
       <c r="D365" s="7"/>
@@ -9679,7 +9694,7 @@
       <c r="W365" s="7"/>
     </row>
     <row r="366">
-      <c r="A366" s="1"/>
+      <c r="A366" s="2"/>
       <c r="B366" s="7"/>
       <c r="C366" s="7"/>
       <c r="D366" s="7"/>
@@ -9704,7 +9719,7 @@
       <c r="W366" s="7"/>
     </row>
     <row r="367">
-      <c r="A367" s="1"/>
+      <c r="A367" s="2"/>
       <c r="B367" s="7"/>
       <c r="C367" s="7"/>
       <c r="D367" s="7"/>
@@ -9729,7 +9744,7 @@
       <c r="W367" s="7"/>
     </row>
     <row r="368">
-      <c r="A368" s="1"/>
+      <c r="A368" s="2"/>
       <c r="B368" s="7"/>
       <c r="C368" s="7"/>
       <c r="D368" s="7"/>
@@ -9754,7 +9769,7 @@
       <c r="W368" s="7"/>
     </row>
     <row r="369">
-      <c r="A369" s="1"/>
+      <c r="A369" s="2"/>
       <c r="B369" s="7"/>
       <c r="C369" s="7"/>
       <c r="D369" s="7"/>
@@ -9779,7 +9794,7 @@
       <c r="W369" s="7"/>
     </row>
     <row r="370">
-      <c r="A370" s="1"/>
+      <c r="A370" s="2"/>
       <c r="B370" s="7"/>
       <c r="C370" s="7"/>
       <c r="D370" s="7"/>
@@ -9804,7 +9819,7 @@
       <c r="W370" s="7"/>
     </row>
     <row r="371">
-      <c r="A371" s="1"/>
+      <c r="A371" s="2"/>
       <c r="B371" s="7"/>
       <c r="C371" s="7"/>
       <c r="D371" s="7"/>
@@ -9829,7 +9844,7 @@
       <c r="W371" s="7"/>
     </row>
     <row r="372">
-      <c r="A372" s="1"/>
+      <c r="A372" s="2"/>
       <c r="B372" s="7"/>
       <c r="C372" s="7"/>
       <c r="D372" s="7"/>
@@ -9854,7 +9869,7 @@
       <c r="W372" s="7"/>
     </row>
     <row r="373">
-      <c r="A373" s="1"/>
+      <c r="A373" s="2"/>
       <c r="B373" s="7"/>
       <c r="C373" s="7"/>
       <c r="D373" s="7"/>
@@ -9879,7 +9894,7 @@
       <c r="W373" s="7"/>
     </row>
     <row r="374">
-      <c r="A374" s="1"/>
+      <c r="A374" s="2"/>
       <c r="B374" s="7"/>
       <c r="C374" s="7"/>
       <c r="D374" s="7"/>
@@ -9904,7 +9919,7 @@
       <c r="W374" s="7"/>
     </row>
     <row r="375">
-      <c r="A375" s="1"/>
+      <c r="A375" s="2"/>
       <c r="B375" s="7"/>
       <c r="C375" s="7"/>
       <c r="D375" s="7"/>
@@ -9929,7 +9944,7 @@
       <c r="W375" s="7"/>
     </row>
     <row r="376">
-      <c r="A376" s="1"/>
+      <c r="A376" s="2"/>
       <c r="B376" s="7"/>
       <c r="C376" s="7"/>
       <c r="D376" s="7"/>
@@ -9954,7 +9969,7 @@
       <c r="W376" s="7"/>
     </row>
     <row r="377">
-      <c r="A377" s="1"/>
+      <c r="A377" s="2"/>
       <c r="B377" s="7"/>
       <c r="C377" s="7"/>
       <c r="D377" s="7"/>
@@ -9979,7 +9994,7 @@
       <c r="W377" s="7"/>
     </row>
     <row r="378">
-      <c r="A378" s="1"/>
+      <c r="A378" s="2"/>
       <c r="B378" s="7"/>
       <c r="C378" s="7"/>
       <c r="D378" s="7"/>
@@ -10004,7 +10019,7 @@
       <c r="W378" s="7"/>
     </row>
     <row r="379">
-      <c r="A379" s="1"/>
+      <c r="A379" s="2"/>
       <c r="B379" s="7"/>
       <c r="C379" s="7"/>
       <c r="D379" s="7"/>
@@ -10029,7 +10044,7 @@
       <c r="W379" s="7"/>
     </row>
     <row r="380">
-      <c r="A380" s="1"/>
+      <c r="A380" s="2"/>
       <c r="B380" s="7"/>
       <c r="C380" s="7"/>
       <c r="D380" s="7"/>
@@ -10054,7 +10069,7 @@
       <c r="W380" s="7"/>
     </row>
     <row r="381">
-      <c r="A381" s="1"/>
+      <c r="A381" s="2"/>
       <c r="B381" s="7"/>
       <c r="C381" s="7"/>
       <c r="D381" s="7"/>
@@ -10079,7 +10094,7 @@
       <c r="W381" s="7"/>
     </row>
     <row r="382">
-      <c r="A382" s="1"/>
+      <c r="A382" s="2"/>
       <c r="B382" s="7"/>
       <c r="C382" s="7"/>
       <c r="D382" s="7"/>
@@ -10104,7 +10119,7 @@
       <c r="W382" s="7"/>
     </row>
     <row r="383">
-      <c r="A383" s="1"/>
+      <c r="A383" s="2"/>
       <c r="B383" s="7"/>
       <c r="C383" s="7"/>
       <c r="D383" s="7"/>
@@ -10129,7 +10144,7 @@
       <c r="W383" s="7"/>
     </row>
     <row r="384">
-      <c r="A384" s="1"/>
+      <c r="A384" s="2"/>
       <c r="B384" s="7"/>
       <c r="C384" s="7"/>
       <c r="D384" s="7"/>
@@ -10154,7 +10169,7 @@
       <c r="W384" s="7"/>
     </row>
     <row r="385">
-      <c r="A385" s="1"/>
+      <c r="A385" s="2"/>
       <c r="B385" s="7"/>
       <c r="C385" s="7"/>
       <c r="D385" s="7"/>
@@ -10179,7 +10194,7 @@
       <c r="W385" s="7"/>
     </row>
     <row r="386">
-      <c r="A386" s="1"/>
+      <c r="A386" s="2"/>
       <c r="B386" s="7"/>
       <c r="C386" s="7"/>
       <c r="D386" s="7"/>
@@ -10204,7 +10219,7 @@
       <c r="W386" s="7"/>
     </row>
     <row r="387">
-      <c r="A387" s="1"/>
+      <c r="A387" s="2"/>
       <c r="B387" s="7"/>
       <c r="C387" s="7"/>
       <c r="D387" s="7"/>
@@ -10229,7 +10244,7 @@
       <c r="W387" s="7"/>
     </row>
     <row r="388">
-      <c r="A388" s="1"/>
+      <c r="A388" s="2"/>
       <c r="B388" s="7"/>
       <c r="C388" s="7"/>
       <c r="D388" s="7"/>
@@ -10254,7 +10269,7 @@
       <c r="W388" s="7"/>
     </row>
     <row r="389">
-      <c r="A389" s="1"/>
+      <c r="A389" s="2"/>
       <c r="B389" s="7"/>
       <c r="C389" s="7"/>
       <c r="D389" s="7"/>
@@ -10279,7 +10294,7 @@
       <c r="W389" s="7"/>
     </row>
     <row r="390">
-      <c r="A390" s="1"/>
+      <c r="A390" s="2"/>
       <c r="B390" s="7"/>
       <c r="C390" s="7"/>
       <c r="D390" s="7"/>
@@ -10304,7 +10319,7 @@
       <c r="W390" s="7"/>
     </row>
     <row r="391">
-      <c r="A391" s="1"/>
+      <c r="A391" s="2"/>
       <c r="B391" s="7"/>
       <c r="C391" s="7"/>
       <c r="D391" s="7"/>
@@ -10329,7 +10344,7 @@
       <c r="W391" s="7"/>
     </row>
     <row r="392">
-      <c r="A392" s="1"/>
+      <c r="A392" s="2"/>
       <c r="B392" s="7"/>
       <c r="C392" s="7"/>
       <c r="D392" s="7"/>
@@ -10354,7 +10369,7 @@
       <c r="W392" s="7"/>
     </row>
     <row r="393">
-      <c r="A393" s="1"/>
+      <c r="A393" s="2"/>
       <c r="B393" s="7"/>
       <c r="C393" s="7"/>
       <c r="D393" s="7"/>
@@ -10379,7 +10394,7 @@
       <c r="W393" s="7"/>
     </row>
     <row r="394">
-      <c r="A394" s="1"/>
+      <c r="A394" s="2"/>
       <c r="B394" s="7"/>
       <c r="C394" s="7"/>
       <c r="D394" s="7"/>
@@ -10404,7 +10419,7 @@
       <c r="W394" s="7"/>
     </row>
     <row r="395">
-      <c r="A395" s="1"/>
+      <c r="A395" s="2"/>
       <c r="B395" s="7"/>
       <c r="C395" s="7"/>
       <c r="D395" s="7"/>
@@ -10429,7 +10444,7 @@
       <c r="W395" s="7"/>
     </row>
     <row r="396">
-      <c r="A396" s="1"/>
+      <c r="A396" s="2"/>
       <c r="B396" s="7"/>
       <c r="C396" s="7"/>
       <c r="D396" s="7"/>
@@ -10454,7 +10469,7 @@
       <c r="W396" s="7"/>
     </row>
     <row r="397">
-      <c r="A397" s="1"/>
+      <c r="A397" s="2"/>
       <c r="B397" s="7"/>
       <c r="C397" s="7"/>
       <c r="D397" s="7"/>
@@ -10479,7 +10494,7 @@
       <c r="W397" s="7"/>
     </row>
     <row r="398">
-      <c r="A398" s="1"/>
+      <c r="A398" s="2"/>
       <c r="B398" s="7"/>
       <c r="C398" s="7"/>
       <c r="D398" s="7"/>
@@ -10504,7 +10519,7 @@
       <c r="W398" s="7"/>
     </row>
     <row r="399">
-      <c r="A399" s="1"/>
+      <c r="A399" s="2"/>
       <c r="B399" s="7"/>
       <c r="C399" s="7"/>
       <c r="D399" s="7"/>
@@ -10529,7 +10544,7 @@
       <c r="W399" s="7"/>
     </row>
     <row r="400">
-      <c r="A400" s="1"/>
+      <c r="A400" s="2"/>
       <c r="B400" s="7"/>
       <c r="C400" s="7"/>
       <c r="D400" s="7"/>
@@ -10554,7 +10569,7 @@
       <c r="W400" s="7"/>
     </row>
     <row r="401">
-      <c r="A401" s="1"/>
+      <c r="A401" s="2"/>
       <c r="B401" s="7"/>
       <c r="C401" s="7"/>
       <c r="D401" s="7"/>
@@ -10579,7 +10594,7 @@
       <c r="W401" s="7"/>
     </row>
     <row r="402">
-      <c r="A402" s="1"/>
+      <c r="A402" s="2"/>
       <c r="B402" s="7"/>
       <c r="C402" s="7"/>
       <c r="D402" s="7"/>
@@ -10604,7 +10619,7 @@
       <c r="W402" s="7"/>
     </row>
     <row r="403">
-      <c r="A403" s="1"/>
+      <c r="A403" s="2"/>
       <c r="B403" s="7"/>
       <c r="C403" s="7"/>
       <c r="D403" s="7"/>
@@ -10629,7 +10644,7 @@
       <c r="W403" s="7"/>
     </row>
     <row r="404">
-      <c r="A404" s="1"/>
+      <c r="A404" s="2"/>
       <c r="B404" s="7"/>
       <c r="C404" s="7"/>
       <c r="D404" s="7"/>
@@ -10654,7 +10669,7 @@
       <c r="W404" s="7"/>
     </row>
     <row r="405">
-      <c r="A405" s="1"/>
+      <c r="A405" s="2"/>
       <c r="B405" s="7"/>
       <c r="C405" s="7"/>
       <c r="D405" s="7"/>
@@ -10679,7 +10694,7 @@
       <c r="W405" s="7"/>
     </row>
     <row r="406">
-      <c r="A406" s="1"/>
+      <c r="A406" s="2"/>
       <c r="B406" s="7"/>
       <c r="C406" s="7"/>
       <c r="D406" s="7"/>
@@ -10704,7 +10719,7 @@
       <c r="W406" s="7"/>
     </row>
     <row r="407">
-      <c r="A407" s="1"/>
+      <c r="A407" s="2"/>
       <c r="B407" s="7"/>
       <c r="C407" s="7"/>
       <c r="D407" s="7"/>
@@ -10729,7 +10744,7 @@
       <c r="W407" s="7"/>
     </row>
     <row r="408">
-      <c r="A408" s="1"/>
+      <c r="A408" s="2"/>
       <c r="B408" s="7"/>
       <c r="C408" s="7"/>
       <c r="D408" s="7"/>
@@ -10754,7 +10769,7 @@
       <c r="W408" s="7"/>
     </row>
     <row r="409">
-      <c r="A409" s="1"/>
+      <c r="A409" s="2"/>
       <c r="B409" s="7"/>
       <c r="C409" s="7"/>
       <c r="D409" s="7"/>
@@ -10779,7 +10794,7 @@
       <c r="W409" s="7"/>
     </row>
     <row r="410">
-      <c r="A410" s="1"/>
+      <c r="A410" s="2"/>
       <c r="B410" s="7"/>
       <c r="C410" s="7"/>
       <c r="D410" s="7"/>
@@ -10804,7 +10819,7 @@
       <c r="W410" s="7"/>
     </row>
     <row r="411">
-      <c r="A411" s="1"/>
+      <c r="A411" s="2"/>
       <c r="B411" s="7"/>
       <c r="C411" s="7"/>
       <c r="D411" s="7"/>
@@ -10829,7 +10844,7 @@
       <c r="W411" s="7"/>
     </row>
     <row r="412">
-      <c r="A412" s="1"/>
+      <c r="A412" s="2"/>
       <c r="B412" s="7"/>
       <c r="C412" s="7"/>
       <c r="D412" s="7"/>
@@ -10854,7 +10869,7 @@
       <c r="W412" s="7"/>
     </row>
     <row r="413">
-      <c r="A413" s="1"/>
+      <c r="A413" s="2"/>
       <c r="B413" s="7"/>
       <c r="C413" s="7"/>
       <c r="D413" s="7"/>
@@ -10879,7 +10894,7 @@
       <c r="W413" s="7"/>
     </row>
     <row r="414">
-      <c r="A414" s="1"/>
+      <c r="A414" s="2"/>
       <c r="B414" s="7"/>
       <c r="C414" s="7"/>
       <c r="D414" s="7"/>
@@ -10904,7 +10919,7 @@
       <c r="W414" s="7"/>
     </row>
     <row r="415">
-      <c r="A415" s="1"/>
+      <c r="A415" s="2"/>
       <c r="B415" s="7"/>
       <c r="C415" s="7"/>
       <c r="D415" s="7"/>
@@ -10929,7 +10944,7 @@
       <c r="W415" s="7"/>
     </row>
     <row r="416">
-      <c r="A416" s="1"/>
+      <c r="A416" s="2"/>
       <c r="B416" s="7"/>
       <c r="C416" s="7"/>
       <c r="D416" s="7"/>
@@ -10954,7 +10969,7 @@
       <c r="W416" s="7"/>
     </row>
     <row r="417">
-      <c r="A417" s="1"/>
+      <c r="A417" s="2"/>
       <c r="B417" s="7"/>
       <c r="C417" s="7"/>
       <c r="D417" s="7"/>
@@ -10979,7 +10994,7 @@
       <c r="W417" s="7"/>
     </row>
     <row r="418">
-      <c r="A418" s="1"/>
+      <c r="A418" s="2"/>
       <c r="B418" s="7"/>
       <c r="C418" s="7"/>
       <c r="D418" s="7"/>
@@ -11004,7 +11019,7 @@
       <c r="W418" s="7"/>
     </row>
     <row r="419">
-      <c r="A419" s="1"/>
+      <c r="A419" s="2"/>
       <c r="B419" s="7"/>
       <c r="C419" s="7"/>
       <c r="D419" s="7"/>
@@ -11029,7 +11044,7 @@
       <c r="W419" s="7"/>
     </row>
     <row r="420">
-      <c r="A420" s="1"/>
+      <c r="A420" s="2"/>
       <c r="B420" s="7"/>
       <c r="C420" s="7"/>
       <c r="D420" s="7"/>
@@ -11054,7 +11069,7 @@
       <c r="W420" s="7"/>
     </row>
     <row r="421">
-      <c r="A421" s="1"/>
+      <c r="A421" s="2"/>
       <c r="B421" s="7"/>
       <c r="C421" s="7"/>
       <c r="D421" s="7"/>
@@ -11079,7 +11094,7 @@
       <c r="W421" s="7"/>
     </row>
     <row r="422">
-      <c r="A422" s="1"/>
+      <c r="A422" s="2"/>
       <c r="B422" s="7"/>
       <c r="C422" s="7"/>
       <c r="D422" s="7"/>
@@ -11104,7 +11119,7 @@
       <c r="W422" s="7"/>
     </row>
     <row r="423">
-      <c r="A423" s="1"/>
+      <c r="A423" s="2"/>
       <c r="B423" s="7"/>
       <c r="C423" s="7"/>
       <c r="D423" s="7"/>
@@ -11129,7 +11144,7 @@
       <c r="W423" s="7"/>
     </row>
     <row r="424">
-      <c r="A424" s="1"/>
+      <c r="A424" s="2"/>
       <c r="B424" s="7"/>
       <c r="C424" s="7"/>
       <c r="D424" s="7"/>
@@ -11154,7 +11169,7 @@
       <c r="W424" s="7"/>
     </row>
     <row r="425">
-      <c r="A425" s="1"/>
+      <c r="A425" s="2"/>
       <c r="B425" s="7"/>
       <c r="C425" s="7"/>
       <c r="D425" s="7"/>
@@ -11179,7 +11194,7 @@
       <c r="W425" s="7"/>
     </row>
     <row r="426">
-      <c r="A426" s="1"/>
+      <c r="A426" s="2"/>
       <c r="B426" s="7"/>
       <c r="C426" s="7"/>
       <c r="D426" s="7"/>
@@ -11204,7 +11219,7 @@
       <c r="W426" s="7"/>
     </row>
     <row r="427">
-      <c r="A427" s="1"/>
+      <c r="A427" s="2"/>
       <c r="B427" s="7"/>
       <c r="C427" s="7"/>
       <c r="D427" s="7"/>
@@ -11229,7 +11244,7 @@
       <c r="W427" s="7"/>
     </row>
     <row r="428">
-      <c r="A428" s="1"/>
+      <c r="A428" s="2"/>
       <c r="B428" s="7"/>
       <c r="C428" s="7"/>
       <c r="D428" s="7"/>
@@ -11254,7 +11269,7 @@
       <c r="W428" s="7"/>
     </row>
     <row r="429">
-      <c r="A429" s="1"/>
+      <c r="A429" s="2"/>
       <c r="B429" s="7"/>
       <c r="C429" s="7"/>
       <c r="D429" s="7"/>
@@ -11279,7 +11294,7 @@
       <c r="W429" s="7"/>
     </row>
     <row r="430">
-      <c r="A430" s="1"/>
+      <c r="A430" s="2"/>
       <c r="B430" s="7"/>
       <c r="C430" s="7"/>
       <c r="D430" s="7"/>
@@ -11304,7 +11319,7 @@
       <c r="W430" s="7"/>
     </row>
     <row r="431">
-      <c r="A431" s="1"/>
+      <c r="A431" s="2"/>
       <c r="B431" s="7"/>
       <c r="C431" s="7"/>
       <c r="D431" s="7"/>
@@ -11329,7 +11344,7 @@
       <c r="W431" s="7"/>
     </row>
     <row r="432">
-      <c r="A432" s="1"/>
+      <c r="A432" s="2"/>
       <c r="B432" s="7"/>
       <c r="C432" s="7"/>
       <c r="D432" s="7"/>
@@ -11354,7 +11369,7 @@
       <c r="W432" s="7"/>
     </row>
     <row r="433">
-      <c r="A433" s="1"/>
+      <c r="A433" s="2"/>
       <c r="B433" s="7"/>
       <c r="C433" s="7"/>
       <c r="D433" s="7"/>
@@ -11379,7 +11394,7 @@
       <c r="W433" s="7"/>
     </row>
     <row r="434">
-      <c r="A434" s="1"/>
+      <c r="A434" s="2"/>
       <c r="B434" s="7"/>
       <c r="C434" s="7"/>
       <c r="D434" s="7"/>
@@ -11404,7 +11419,7 @@
       <c r="W434" s="7"/>
     </row>
     <row r="435">
-      <c r="A435" s="1"/>
+      <c r="A435" s="2"/>
       <c r="B435" s="7"/>
       <c r="C435" s="7"/>
       <c r="D435" s="7"/>
@@ -11429,7 +11444,7 @@
       <c r="W435" s="7"/>
     </row>
     <row r="436">
-      <c r="A436" s="1"/>
+      <c r="A436" s="2"/>
       <c r="B436" s="7"/>
       <c r="C436" s="7"/>
       <c r="D436" s="7"/>
@@ -11454,7 +11469,7 @@
       <c r="W436" s="7"/>
     </row>
     <row r="437">
-      <c r="A437" s="1"/>
+      <c r="A437" s="2"/>
       <c r="B437" s="7"/>
       <c r="C437" s="7"/>
       <c r="D437" s="7"/>
@@ -11479,7 +11494,7 @@
       <c r="W437" s="7"/>
     </row>
     <row r="438">
-      <c r="A438" s="1"/>
+      <c r="A438" s="2"/>
       <c r="B438" s="7"/>
       <c r="C438" s="7"/>
       <c r="D438" s="7"/>
@@ -11504,7 +11519,7 @@
       <c r="W438" s="7"/>
     </row>
     <row r="439">
-      <c r="A439" s="1"/>
+      <c r="A439" s="2"/>
       <c r="B439" s="7"/>
       <c r="C439" s="7"/>
       <c r="D439" s="7"/>
@@ -11529,7 +11544,7 @@
       <c r="W439" s="7"/>
     </row>
     <row r="440">
-      <c r="A440" s="1"/>
+      <c r="A440" s="2"/>
       <c r="B440" s="7"/>
       <c r="C440" s="7"/>
       <c r="D440" s="7"/>
@@ -11554,7 +11569,7 @@
       <c r="W440" s="7"/>
     </row>
     <row r="441">
-      <c r="A441" s="1"/>
+      <c r="A441" s="2"/>
       <c r="B441" s="7"/>
       <c r="C441" s="7"/>
       <c r="D441" s="7"/>
@@ -11579,7 +11594,7 @@
       <c r="W441" s="7"/>
     </row>
     <row r="442">
-      <c r="A442" s="1"/>
+      <c r="A442" s="2"/>
       <c r="B442" s="7"/>
       <c r="C442" s="7"/>
       <c r="D442" s="7"/>
@@ -11604,7 +11619,7 @@
       <c r="W442" s="7"/>
     </row>
     <row r="443">
-      <c r="A443" s="1"/>
+      <c r="A443" s="2"/>
       <c r="B443" s="7"/>
       <c r="C443" s="7"/>
       <c r="D443" s="7"/>
@@ -11629,7 +11644,7 @@
       <c r="W443" s="7"/>
     </row>
     <row r="444">
-      <c r="A444" s="1"/>
+      <c r="A444" s="2"/>
       <c r="B444" s="7"/>
       <c r="C444" s="7"/>
       <c r="D444" s="7"/>
@@ -11654,7 +11669,7 @@
       <c r="W444" s="7"/>
     </row>
     <row r="445">
-      <c r="A445" s="1"/>
+      <c r="A445" s="2"/>
       <c r="B445" s="7"/>
       <c r="C445" s="7"/>
       <c r="D445" s="7"/>
@@ -11679,7 +11694,7 @@
       <c r="W445" s="7"/>
     </row>
     <row r="446">
-      <c r="A446" s="1"/>
+      <c r="A446" s="2"/>
       <c r="B446" s="7"/>
       <c r="C446" s="7"/>
       <c r="D446" s="7"/>
@@ -11704,7 +11719,7 @@
       <c r="W446" s="7"/>
     </row>
     <row r="447">
-      <c r="A447" s="1"/>
+      <c r="A447" s="2"/>
       <c r="B447" s="7"/>
       <c r="C447" s="7"/>
       <c r="D447" s="7"/>
@@ -11729,7 +11744,7 @@
       <c r="W447" s="7"/>
     </row>
     <row r="448">
-      <c r="A448" s="1"/>
+      <c r="A448" s="2"/>
       <c r="B448" s="7"/>
       <c r="C448" s="7"/>
       <c r="D448" s="7"/>
@@ -11754,7 +11769,7 @@
       <c r="W448" s="7"/>
     </row>
     <row r="449">
-      <c r="A449" s="1"/>
+      <c r="A449" s="2"/>
       <c r="B449" s="7"/>
       <c r="C449" s="7"/>
       <c r="D449" s="7"/>
@@ -11779,7 +11794,7 @@
       <c r="W449" s="7"/>
     </row>
     <row r="450">
-      <c r="A450" s="1"/>
+      <c r="A450" s="2"/>
       <c r="B450" s="7"/>
       <c r="C450" s="7"/>
       <c r="D450" s="7"/>
@@ -11804,7 +11819,7 @@
       <c r="W450" s="7"/>
     </row>
     <row r="451">
-      <c r="A451" s="1"/>
+      <c r="A451" s="2"/>
       <c r="B451" s="7"/>
       <c r="C451" s="7"/>
       <c r="D451" s="7"/>
@@ -11829,7 +11844,7 @@
       <c r="W451" s="7"/>
     </row>
     <row r="452">
-      <c r="A452" s="1"/>
+      <c r="A452" s="2"/>
       <c r="B452" s="7"/>
       <c r="C452" s="7"/>
       <c r="D452" s="7"/>
@@ -11854,7 +11869,7 @@
       <c r="W452" s="7"/>
     </row>
     <row r="453">
-      <c r="A453" s="1"/>
+      <c r="A453" s="2"/>
       <c r="B453" s="7"/>
       <c r="C453" s="7"/>
       <c r="D453" s="7"/>
@@ -11879,7 +11894,7 @@
       <c r="W453" s="7"/>
     </row>
     <row r="454">
-      <c r="A454" s="1"/>
+      <c r="A454" s="2"/>
       <c r="B454" s="7"/>
       <c r="C454" s="7"/>
       <c r="D454" s="7"/>
@@ -11904,7 +11919,7 @@
       <c r="W454" s="7"/>
     </row>
     <row r="455">
-      <c r="A455" s="1"/>
+      <c r="A455" s="2"/>
       <c r="B455" s="7"/>
       <c r="C455" s="7"/>
       <c r="D455" s="7"/>
@@ -11929,7 +11944,7 @@
       <c r="W455" s="7"/>
     </row>
     <row r="456">
-      <c r="A456" s="1"/>
+      <c r="A456" s="2"/>
       <c r="B456" s="7"/>
       <c r="C456" s="7"/>
       <c r="D456" s="7"/>
@@ -11954,7 +11969,7 @@
       <c r="W456" s="7"/>
     </row>
     <row r="457">
-      <c r="A457" s="1"/>
+      <c r="A457" s="2"/>
       <c r="B457" s="7"/>
       <c r="C457" s="7"/>
       <c r="D457" s="7"/>
@@ -11979,7 +11994,7 @@
       <c r="W457" s="7"/>
     </row>
     <row r="458">
-      <c r="A458" s="1"/>
+      <c r="A458" s="2"/>
       <c r="B458" s="7"/>
       <c r="C458" s="7"/>
       <c r="D458" s="7"/>
@@ -12004,7 +12019,7 @@
       <c r="W458" s="7"/>
     </row>
     <row r="459">
-      <c r="A459" s="1"/>
+      <c r="A459" s="2"/>
       <c r="B459" s="7"/>
       <c r="C459" s="7"/>
       <c r="D459" s="7"/>
@@ -12029,7 +12044,7 @@
       <c r="W459" s="7"/>
     </row>
     <row r="460">
-      <c r="A460" s="1"/>
+      <c r="A460" s="2"/>
       <c r="B460" s="7"/>
       <c r="C460" s="7"/>
       <c r="D460" s="7"/>
@@ -12054,7 +12069,7 @@
       <c r="W460" s="7"/>
     </row>
     <row r="461">
-      <c r="A461" s="1"/>
+      <c r="A461" s="2"/>
       <c r="B461" s="7"/>
       <c r="C461" s="7"/>
       <c r="D461" s="7"/>
@@ -12079,7 +12094,7 @@
       <c r="W461" s="7"/>
     </row>
     <row r="462">
-      <c r="A462" s="1"/>
+      <c r="A462" s="2"/>
       <c r="B462" s="7"/>
       <c r="C462" s="7"/>
       <c r="D462" s="7"/>
@@ -12104,7 +12119,7 @@
       <c r="W462" s="7"/>
     </row>
     <row r="463">
-      <c r="A463" s="1"/>
+      <c r="A463" s="2"/>
       <c r="B463" s="7"/>
       <c r="C463" s="7"/>
       <c r="D463" s="7"/>
@@ -12129,7 +12144,7 @@
       <c r="W463" s="7"/>
     </row>
     <row r="464">
-      <c r="A464" s="1"/>
+      <c r="A464" s="2"/>
       <c r="B464" s="7"/>
       <c r="C464" s="7"/>
       <c r="D464" s="7"/>
@@ -12154,7 +12169,7 @@
       <c r="W464" s="7"/>
     </row>
     <row r="465">
-      <c r="A465" s="1"/>
+      <c r="A465" s="2"/>
       <c r="B465" s="7"/>
       <c r="C465" s="7"/>
       <c r="D465" s="7"/>
@@ -12179,7 +12194,7 @@
       <c r="W465" s="7"/>
     </row>
     <row r="466">
-      <c r="A466" s="1"/>
+      <c r="A466" s="2"/>
       <c r="B466" s="7"/>
       <c r="C466" s="7"/>
       <c r="D466" s="7"/>
@@ -12204,7 +12219,7 @@
       <c r="W466" s="7"/>
     </row>
     <row r="467">
-      <c r="A467" s="1"/>
+      <c r="A467" s="2"/>
       <c r="B467" s="7"/>
       <c r="C467" s="7"/>
       <c r="D467" s="7"/>
@@ -12229,7 +12244,7 @@
       <c r="W467" s="7"/>
     </row>
     <row r="468">
-      <c r="A468" s="1"/>
+      <c r="A468" s="2"/>
       <c r="B468" s="7"/>
       <c r="C468" s="7"/>
       <c r="D468" s="7"/>
@@ -12254,7 +12269,7 @@
       <c r="W468" s="7"/>
     </row>
     <row r="469">
-      <c r="A469" s="1"/>
+      <c r="A469" s="2"/>
       <c r="B469" s="7"/>
       <c r="C469" s="7"/>
       <c r="D469" s="7"/>
@@ -12279,7 +12294,7 @@
       <c r="W469" s="7"/>
     </row>
     <row r="470">
-      <c r="A470" s="1"/>
+      <c r="A470" s="2"/>
       <c r="B470" s="7"/>
       <c r="C470" s="7"/>
       <c r="D470" s="7"/>
@@ -12304,7 +12319,7 @@
       <c r="W470" s="7"/>
     </row>
     <row r="471">
-      <c r="A471" s="1"/>
+      <c r="A471" s="2"/>
       <c r="B471" s="7"/>
       <c r="C471" s="7"/>
       <c r="D471" s="7"/>
@@ -12329,7 +12344,7 @@
       <c r="W471" s="7"/>
     </row>
     <row r="472">
-      <c r="A472" s="1"/>
+      <c r="A472" s="2"/>
       <c r="B472" s="7"/>
       <c r="C472" s="7"/>
       <c r="D472" s="7"/>
@@ -12354,7 +12369,7 @@
       <c r="W472" s="7"/>
     </row>
     <row r="473">
-      <c r="A473" s="1"/>
+      <c r="A473" s="2"/>
       <c r="B473" s="7"/>
       <c r="C473" s="7"/>
       <c r="D473" s="7"/>
@@ -12379,7 +12394,7 @@
       <c r="W473" s="7"/>
     </row>
     <row r="474">
-      <c r="A474" s="1"/>
+      <c r="A474" s="2"/>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
       <c r="D474" s="7"/>
@@ -12404,7 +12419,7 @@
       <c r="W474" s="7"/>
     </row>
     <row r="475">
-      <c r="A475" s="1"/>
+      <c r="A475" s="2"/>
       <c r="B475" s="7"/>
       <c r="C475" s="7"/>
       <c r="D475" s="7"/>
@@ -12429,7 +12444,7 @@
       <c r="W475" s="7"/>
     </row>
     <row r="476">
-      <c r="A476" s="1"/>
+      <c r="A476" s="2"/>
       <c r="B476" s="7"/>
       <c r="C476" s="7"/>
       <c r="D476" s="7"/>
@@ -12454,7 +12469,7 @@
       <c r="W476" s="7"/>
     </row>
     <row r="477">
-      <c r="A477" s="1"/>
+      <c r="A477" s="2"/>
       <c r="B477" s="7"/>
       <c r="C477" s="7"/>
       <c r="D477" s="7"/>
@@ -12479,7 +12494,7 @@
       <c r="W477" s="7"/>
     </row>
     <row r="478">
-      <c r="A478" s="1"/>
+      <c r="A478" s="2"/>
       <c r="B478" s="7"/>
       <c r="C478" s="7"/>
       <c r="D478" s="7"/>
@@ -12504,7 +12519,7 @@
       <c r="W478" s="7"/>
     </row>
     <row r="479">
-      <c r="A479" s="1"/>
+      <c r="A479" s="2"/>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
       <c r="D479" s="7"/>
@@ -12529,7 +12544,7 @@
       <c r="W479" s="7"/>
     </row>
     <row r="480">
-      <c r="A480" s="1"/>
+      <c r="A480" s="2"/>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
       <c r="D480" s="7"/>
@@ -12554,7 +12569,7 @@
       <c r="W480" s="7"/>
     </row>
     <row r="481">
-      <c r="A481" s="1"/>
+      <c r="A481" s="2"/>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
       <c r="D481" s="7"/>
@@ -12579,7 +12594,7 @@
       <c r="W481" s="7"/>
     </row>
     <row r="482">
-      <c r="A482" s="1"/>
+      <c r="A482" s="2"/>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
       <c r="D482" s="7"/>
@@ -12604,7 +12619,7 @@
       <c r="W482" s="7"/>
     </row>
     <row r="483">
-      <c r="A483" s="1"/>
+      <c r="A483" s="2"/>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
       <c r="D483" s="7"/>
@@ -12629,7 +12644,7 @@
       <c r="W483" s="7"/>
     </row>
     <row r="484">
-      <c r="A484" s="1"/>
+      <c r="A484" s="2"/>
       <c r="B484" s="7"/>
       <c r="C484" s="7"/>
       <c r="D484" s="7"/>
@@ -12654,7 +12669,7 @@
       <c r="W484" s="7"/>
     </row>
     <row r="485">
-      <c r="A485" s="1"/>
+      <c r="A485" s="2"/>
       <c r="B485" s="7"/>
       <c r="C485" s="7"/>
       <c r="D485" s="7"/>
@@ -12679,7 +12694,7 @@
       <c r="W485" s="7"/>
     </row>
     <row r="486">
-      <c r="A486" s="1"/>
+      <c r="A486" s="2"/>
       <c r="B486" s="7"/>
       <c r="C486" s="7"/>
       <c r="D486" s="7"/>
@@ -12704,7 +12719,7 @@
       <c r="W486" s="7"/>
     </row>
     <row r="487">
-      <c r="A487" s="1"/>
+      <c r="A487" s="2"/>
       <c r="B487" s="7"/>
       <c r="C487" s="7"/>
       <c r="D487" s="7"/>
@@ -12729,7 +12744,7 @@
       <c r="W487" s="7"/>
     </row>
     <row r="488">
-      <c r="A488" s="1"/>
+      <c r="A488" s="2"/>
       <c r="B488" s="7"/>
       <c r="C488" s="7"/>
       <c r="D488" s="7"/>
@@ -12754,7 +12769,7 @@
       <c r="W488" s="7"/>
     </row>
     <row r="489">
-      <c r="A489" s="1"/>
+      <c r="A489" s="2"/>
       <c r="B489" s="7"/>
       <c r="C489" s="7"/>
       <c r="D489" s="7"/>
@@ -12779,7 +12794,7 @@
       <c r="W489" s="7"/>
     </row>
     <row r="490">
-      <c r="A490" s="1"/>
+      <c r="A490" s="2"/>
       <c r="B490" s="7"/>
       <c r="C490" s="7"/>
       <c r="D490" s="7"/>
@@ -12804,7 +12819,7 @@
       <c r="W490" s="7"/>
     </row>
     <row r="491">
-      <c r="A491" s="1"/>
+      <c r="A491" s="2"/>
       <c r="B491" s="7"/>
       <c r="C491" s="7"/>
       <c r="D491" s="7"/>
@@ -12829,7 +12844,7 @@
       <c r="W491" s="7"/>
     </row>
     <row r="492">
-      <c r="A492" s="1"/>
+      <c r="A492" s="2"/>
       <c r="B492" s="7"/>
       <c r="C492" s="7"/>
       <c r="D492" s="7"/>
@@ -12854,7 +12869,7 @@
       <c r="W492" s="7"/>
     </row>
     <row r="493">
-      <c r="A493" s="1"/>
+      <c r="A493" s="2"/>
       <c r="B493" s="7"/>
       <c r="C493" s="7"/>
       <c r="D493" s="7"/>
@@ -12879,7 +12894,7 @@
       <c r="W493" s="7"/>
     </row>
     <row r="494">
-      <c r="A494" s="1"/>
+      <c r="A494" s="2"/>
       <c r="B494" s="7"/>
       <c r="C494" s="7"/>
       <c r="D494" s="7"/>
@@ -12904,7 +12919,7 @@
       <c r="W494" s="7"/>
     </row>
     <row r="495">
-      <c r="A495" s="1"/>
+      <c r="A495" s="2"/>
       <c r="B495" s="7"/>
       <c r="C495" s="7"/>
       <c r="D495" s="7"/>
@@ -12929,7 +12944,7 @@
       <c r="W495" s="7"/>
     </row>
     <row r="496">
-      <c r="A496" s="1"/>
+      <c r="A496" s="2"/>
       <c r="B496" s="7"/>
       <c r="C496" s="7"/>
       <c r="D496" s="7"/>
@@ -12954,7 +12969,7 @@
       <c r="W496" s="7"/>
     </row>
     <row r="497">
-      <c r="A497" s="1"/>
+      <c r="A497" s="2"/>
       <c r="B497" s="7"/>
       <c r="C497" s="7"/>
       <c r="D497" s="7"/>
@@ -12979,7 +12994,7 @@
       <c r="W497" s="7"/>
     </row>
     <row r="498">
-      <c r="A498" s="1"/>
+      <c r="A498" s="2"/>
       <c r="B498" s="7"/>
       <c r="C498" s="7"/>
       <c r="D498" s="7"/>
@@ -13004,7 +13019,7 @@
       <c r="W498" s="7"/>
     </row>
     <row r="499">
-      <c r="A499" s="1"/>
+      <c r="A499" s="2"/>
       <c r="B499" s="7"/>
       <c r="C499" s="7"/>
       <c r="D499" s="7"/>
@@ -13029,7 +13044,7 @@
       <c r="W499" s="7"/>
     </row>
     <row r="500">
-      <c r="A500" s="1"/>
+      <c r="A500" s="2"/>
       <c r="B500" s="7"/>
       <c r="C500" s="7"/>
       <c r="D500" s="7"/>
@@ -13054,7 +13069,7 @@
       <c r="W500" s="7"/>
     </row>
     <row r="501">
-      <c r="A501" s="1"/>
+      <c r="A501" s="2"/>
       <c r="B501" s="7"/>
       <c r="C501" s="7"/>
       <c r="D501" s="7"/>
@@ -13079,7 +13094,7 @@
       <c r="W501" s="7"/>
     </row>
     <row r="502">
-      <c r="A502" s="1"/>
+      <c r="A502" s="2"/>
       <c r="B502" s="7"/>
       <c r="C502" s="7"/>
       <c r="D502" s="7"/>
@@ -13104,7 +13119,7 @@
       <c r="W502" s="7"/>
     </row>
     <row r="503">
-      <c r="A503" s="1"/>
+      <c r="A503" s="2"/>
       <c r="B503" s="7"/>
       <c r="C503" s="7"/>
       <c r="D503" s="7"/>
@@ -13129,7 +13144,7 @@
       <c r="W503" s="7"/>
     </row>
     <row r="504">
-      <c r="A504" s="1"/>
+      <c r="A504" s="2"/>
       <c r="B504" s="7"/>
       <c r="C504" s="7"/>
       <c r="D504" s="7"/>
@@ -13154,7 +13169,7 @@
       <c r="W504" s="7"/>
     </row>
     <row r="505">
-      <c r="A505" s="1"/>
+      <c r="A505" s="2"/>
       <c r="B505" s="7"/>
       <c r="C505" s="7"/>
       <c r="D505" s="7"/>
@@ -13179,7 +13194,7 @@
       <c r="W505" s="7"/>
     </row>
     <row r="506">
-      <c r="A506" s="1"/>
+      <c r="A506" s="2"/>
       <c r="B506" s="7"/>
       <c r="C506" s="7"/>
       <c r="D506" s="7"/>
@@ -13204,7 +13219,7 @@
       <c r="W506" s="7"/>
     </row>
     <row r="507">
-      <c r="A507" s="1"/>
+      <c r="A507" s="2"/>
       <c r="B507" s="7"/>
       <c r="C507" s="7"/>
       <c r="D507" s="7"/>
@@ -13229,7 +13244,7 @@
       <c r="W507" s="7"/>
     </row>
     <row r="508">
-      <c r="A508" s="1"/>
+      <c r="A508" s="2"/>
       <c r="B508" s="7"/>
       <c r="C508" s="7"/>
       <c r="D508" s="7"/>
@@ -13254,7 +13269,7 @@
       <c r="W508" s="7"/>
     </row>
     <row r="509">
-      <c r="A509" s="1"/>
+      <c r="A509" s="2"/>
       <c r="B509" s="7"/>
       <c r="C509" s="7"/>
       <c r="D509" s="7"/>
@@ -13279,7 +13294,7 @@
       <c r="W509" s="7"/>
     </row>
     <row r="510">
-      <c r="A510" s="1"/>
+      <c r="A510" s="2"/>
       <c r="B510" s="7"/>
       <c r="C510" s="7"/>
       <c r="D510" s="7"/>
@@ -13304,7 +13319,7 @@
       <c r="W510" s="7"/>
     </row>
     <row r="511">
-      <c r="A511" s="1"/>
+      <c r="A511" s="2"/>
       <c r="B511" s="7"/>
       <c r="C511" s="7"/>
       <c r="D511" s="7"/>
@@ -13329,7 +13344,7 @@
       <c r="W511" s="7"/>
     </row>
     <row r="512">
-      <c r="A512" s="1"/>
+      <c r="A512" s="2"/>
       <c r="B512" s="7"/>
       <c r="C512" s="7"/>
       <c r="D512" s="7"/>
@@ -13354,7 +13369,7 @@
       <c r="W512" s="7"/>
     </row>
     <row r="513">
-      <c r="A513" s="1"/>
+      <c r="A513" s="2"/>
       <c r="B513" s="7"/>
       <c r="C513" s="7"/>
       <c r="D513" s="7"/>
@@ -13379,7 +13394,7 @@
       <c r="W513" s="7"/>
     </row>
     <row r="514">
-      <c r="A514" s="1"/>
+      <c r="A514" s="2"/>
       <c r="B514" s="7"/>
       <c r="C514" s="7"/>
       <c r="D514" s="7"/>
@@ -13404,7 +13419,7 @@
       <c r="W514" s="7"/>
     </row>
     <row r="515">
-      <c r="A515" s="1"/>
+      <c r="A515" s="2"/>
       <c r="B515" s="7"/>
       <c r="C515" s="7"/>
       <c r="D515" s="7"/>
@@ -13429,7 +13444,7 @@
       <c r="W515" s="7"/>
     </row>
     <row r="516">
-      <c r="A516" s="1"/>
+      <c r="A516" s="2"/>
       <c r="B516" s="7"/>
       <c r="C516" s="7"/>
       <c r="D516" s="7"/>
@@ -13454,7 +13469,7 @@
       <c r="W516" s="7"/>
     </row>
     <row r="517">
-      <c r="A517" s="1"/>
+      <c r="A517" s="2"/>
       <c r="B517" s="7"/>
       <c r="C517" s="7"/>
       <c r="D517" s="7"/>
@@ -13479,7 +13494,7 @@
       <c r="W517" s="7"/>
     </row>
     <row r="518">
-      <c r="A518" s="1"/>
+      <c r="A518" s="2"/>
       <c r="B518" s="7"/>
       <c r="C518" s="7"/>
       <c r="D518" s="7"/>
@@ -13504,7 +13519,7 @@
       <c r="W518" s="7"/>
     </row>
     <row r="519">
-      <c r="A519" s="1"/>
+      <c r="A519" s="2"/>
       <c r="B519" s="7"/>
       <c r="C519" s="7"/>
       <c r="D519" s="7"/>
@@ -13529,7 +13544,7 @@
       <c r="W519" s="7"/>
     </row>
     <row r="520">
-      <c r="A520" s="1"/>
+      <c r="A520" s="2"/>
       <c r="B520" s="7"/>
       <c r="C520" s="7"/>
       <c r="D520" s="7"/>
@@ -13554,7 +13569,7 @@
       <c r="W520" s="7"/>
     </row>
     <row r="521">
-      <c r="A521" s="1"/>
+      <c r="A521" s="2"/>
       <c r="B521" s="7"/>
       <c r="C521" s="7"/>
       <c r="D521" s="7"/>
@@ -13579,7 +13594,7 @@
       <c r="W521" s="7"/>
     </row>
     <row r="522">
-      <c r="A522" s="1"/>
+      <c r="A522" s="2"/>
       <c r="B522" s="7"/>
       <c r="C522" s="7"/>
       <c r="D522" s="7"/>
@@ -13604,7 +13619,7 @@
       <c r="W522" s="7"/>
     </row>
     <row r="523">
-      <c r="A523" s="1"/>
+      <c r="A523" s="2"/>
       <c r="B523" s="7"/>
       <c r="C523" s="7"/>
       <c r="D523" s="7"/>
@@ -13629,7 +13644,7 @@
       <c r="W523" s="7"/>
     </row>
     <row r="524">
-      <c r="A524" s="1"/>
+      <c r="A524" s="2"/>
       <c r="B524" s="7"/>
       <c r="C524" s="7"/>
       <c r="D524" s="7"/>
@@ -13654,7 +13669,7 @@
       <c r="W524" s="7"/>
     </row>
     <row r="525">
-      <c r="A525" s="1"/>
+      <c r="A525" s="2"/>
       <c r="B525" s="7"/>
       <c r="C525" s="7"/>
       <c r="D525" s="7"/>
@@ -13679,7 +13694,7 @@
       <c r="W525" s="7"/>
     </row>
     <row r="526">
-      <c r="A526" s="1"/>
+      <c r="A526" s="2"/>
       <c r="B526" s="7"/>
       <c r="C526" s="7"/>
       <c r="D526" s="7"/>
@@ -13704,7 +13719,7 @@
       <c r="W526" s="7"/>
     </row>
     <row r="527">
-      <c r="A527" s="1"/>
+      <c r="A527" s="2"/>
       <c r="B527" s="7"/>
       <c r="C527" s="7"/>
       <c r="D527" s="7"/>
@@ -13729,7 +13744,7 @@
       <c r="W527" s="7"/>
     </row>
     <row r="528">
-      <c r="A528" s="1"/>
+      <c r="A528" s="2"/>
       <c r="B528" s="7"/>
       <c r="C528" s="7"/>
       <c r="D528" s="7"/>
@@ -13754,7 +13769,7 @@
       <c r="W528" s="7"/>
     </row>
     <row r="529">
-      <c r="A529" s="1"/>
+      <c r="A529" s="2"/>
       <c r="B529" s="7"/>
       <c r="C529" s="7"/>
       <c r="D529" s="7"/>
@@ -13779,7 +13794,7 @@
       <c r="W529" s="7"/>
     </row>
     <row r="530">
-      <c r="A530" s="1"/>
+      <c r="A530" s="2"/>
       <c r="B530" s="7"/>
       <c r="C530" s="7"/>
       <c r="D530" s="7"/>
@@ -13804,7 +13819,7 @@
       <c r="W530" s="7"/>
     </row>
     <row r="531">
-      <c r="A531" s="1"/>
+      <c r="A531" s="2"/>
       <c r="B531" s="7"/>
       <c r="C531" s="7"/>
       <c r="D531" s="7"/>
@@ -13829,7 +13844,7 @@
       <c r="W531" s="7"/>
     </row>
     <row r="532">
-      <c r="A532" s="1"/>
+      <c r="A532" s="2"/>
       <c r="B532" s="7"/>
       <c r="C532" s="7"/>
       <c r="D532" s="7"/>
@@ -13854,7 +13869,7 @@
       <c r="W532" s="7"/>
     </row>
     <row r="533">
-      <c r="A533" s="1"/>
+      <c r="A533" s="2"/>
       <c r="B533" s="7"/>
       <c r="C533" s="7"/>
       <c r="D533" s="7"/>
@@ -13879,7 +13894,7 @@
       <c r="W533" s="7"/>
     </row>
     <row r="534">
-      <c r="A534" s="1"/>
+      <c r="A534" s="2"/>
       <c r="B534" s="7"/>
       <c r="C534" s="7"/>
       <c r="D534" s="7"/>
@@ -13904,7 +13919,7 @@
       <c r="W534" s="7"/>
     </row>
     <row r="535">
-      <c r="A535" s="1"/>
+      <c r="A535" s="2"/>
       <c r="B535" s="7"/>
       <c r="C535" s="7"/>
       <c r="D535" s="7"/>
@@ -13929,7 +13944,7 @@
       <c r="W535" s="7"/>
     </row>
     <row r="536">
-      <c r="A536" s="1"/>
+      <c r="A536" s="2"/>
       <c r="B536" s="7"/>
       <c r="C536" s="7"/>
       <c r="D536" s="7"/>
@@ -13954,7 +13969,7 @@
       <c r="W536" s="7"/>
     </row>
     <row r="537">
-      <c r="A537" s="1"/>
+      <c r="A537" s="2"/>
       <c r="B537" s="7"/>
       <c r="C537" s="7"/>
       <c r="D537" s="7"/>
@@ -13979,7 +13994,7 @@
       <c r="W537" s="7"/>
     </row>
     <row r="538">
-      <c r="A538" s="1"/>
+      <c r="A538" s="2"/>
       <c r="B538" s="7"/>
       <c r="C538" s="7"/>
       <c r="D538" s="7"/>
@@ -14004,7 +14019,7 @@
       <c r="W538" s="7"/>
     </row>
     <row r="539">
-      <c r="A539" s="1"/>
+      <c r="A539" s="2"/>
       <c r="B539" s="7"/>
       <c r="C539" s="7"/>
       <c r="D539" s="7"/>
@@ -14029,7 +14044,7 @@
       <c r="W539" s="7"/>
     </row>
     <row r="540">
-      <c r="A540" s="1"/>
+      <c r="A540" s="2"/>
       <c r="B540" s="7"/>
       <c r="C540" s="7"/>
       <c r="D540" s="7"/>
@@ -14054,7 +14069,7 @@
       <c r="W540" s="7"/>
     </row>
     <row r="541">
-      <c r="A541" s="1"/>
+      <c r="A541" s="2"/>
       <c r="B541" s="7"/>
       <c r="C541" s="7"/>
       <c r="D541" s="7"/>
@@ -14079,7 +14094,7 @@
       <c r="W541" s="7"/>
     </row>
     <row r="542">
-      <c r="A542" s="1"/>
+      <c r="A542" s="2"/>
       <c r="B542" s="7"/>
       <c r="C542" s="7"/>
       <c r="D542" s="7"/>
@@ -14104,7 +14119,7 @@
       <c r="W542" s="7"/>
     </row>
     <row r="543">
-      <c r="A543" s="1"/>
+      <c r="A543" s="2"/>
       <c r="B543" s="7"/>
       <c r="C543" s="7"/>
       <c r="D543" s="7"/>
@@ -14129,7 +14144,7 @@
       <c r="W543" s="7"/>
     </row>
     <row r="544">
-      <c r="A544" s="1"/>
+      <c r="A544" s="2"/>
       <c r="B544" s="7"/>
       <c r="C544" s="7"/>
       <c r="D544" s="7"/>
@@ -14154,7 +14169,7 @@
       <c r="W544" s="7"/>
     </row>
     <row r="545">
-      <c r="A545" s="1"/>
+      <c r="A545" s="2"/>
       <c r="B545" s="7"/>
       <c r="C545" s="7"/>
       <c r="D545" s="7"/>
@@ -14179,7 +14194,7 @@
       <c r="W545" s="7"/>
     </row>
     <row r="546">
-      <c r="A546" s="1"/>
+      <c r="A546" s="2"/>
       <c r="B546" s="7"/>
       <c r="C546" s="7"/>
       <c r="D546" s="7"/>
@@ -14204,7 +14219,7 @@
       <c r="W546" s="7"/>
     </row>
     <row r="547">
-      <c r="A547" s="1"/>
+      <c r="A547" s="2"/>
       <c r="B547" s="7"/>
       <c r="C547" s="7"/>
       <c r="D547" s="7"/>
@@ -14229,7 +14244,7 @@
       <c r="W547" s="7"/>
     </row>
     <row r="548">
-      <c r="A548" s="1"/>
+      <c r="A548" s="2"/>
       <c r="B548" s="7"/>
       <c r="C548" s="7"/>
       <c r="D548" s="7"/>
@@ -14254,7 +14269,7 @@
       <c r="W548" s="7"/>
     </row>
     <row r="549">
-      <c r="A549" s="1"/>
+      <c r="A549" s="2"/>
       <c r="B549" s="7"/>
       <c r="C549" s="7"/>
       <c r="D549" s="7"/>
@@ -14279,7 +14294,7 @@
       <c r="W549" s="7"/>
     </row>
     <row r="550">
-      <c r="A550" s="1"/>
+      <c r="A550" s="2"/>
       <c r="B550" s="7"/>
       <c r="C550" s="7"/>
       <c r="D550" s="7"/>
@@ -14304,7 +14319,7 @@
       <c r="W550" s="7"/>
     </row>
     <row r="551">
-      <c r="A551" s="1"/>
+      <c r="A551" s="2"/>
       <c r="B551" s="7"/>
       <c r="C551" s="7"/>
       <c r="D551" s="7"/>
@@ -14329,7 +14344,7 @@
       <c r="W551" s="7"/>
     </row>
     <row r="552">
-      <c r="A552" s="1"/>
+      <c r="A552" s="2"/>
       <c r="B552" s="7"/>
       <c r="C552" s="7"/>
       <c r="D552" s="7"/>
@@ -14354,7 +14369,7 @@
       <c r="W552" s="7"/>
     </row>
     <row r="553">
-      <c r="A553" s="1"/>
+      <c r="A553" s="2"/>
       <c r="B553" s="7"/>
       <c r="C553" s="7"/>
       <c r="D553" s="7"/>
@@ -14379,7 +14394,7 @@
       <c r="W553" s="7"/>
     </row>
     <row r="554">
-      <c r="A554" s="1"/>
+      <c r="A554" s="2"/>
       <c r="B554" s="7"/>
       <c r="C554" s="7"/>
       <c r="D554" s="7"/>
@@ -14404,7 +14419,7 @@
       <c r="W554" s="7"/>
     </row>
     <row r="555">
-      <c r="A555" s="1"/>
+      <c r="A555" s="2"/>
       <c r="B555" s="7"/>
       <c r="C555" s="7"/>
       <c r="D555" s="7"/>
@@ -14429,7 +14444,7 @@
       <c r="W555" s="7"/>
     </row>
     <row r="556">
-      <c r="A556" s="1"/>
+      <c r="A556" s="2"/>
       <c r="B556" s="7"/>
       <c r="C556" s="7"/>
       <c r="D556" s="7"/>
@@ -14454,7 +14469,7 @@
       <c r="W556" s="7"/>
     </row>
     <row r="557">
-      <c r="A557" s="1"/>
+      <c r="A557" s="2"/>
       <c r="B557" s="7"/>
       <c r="C557" s="7"/>
       <c r="D557" s="7"/>
@@ -14479,7 +14494,7 @@
       <c r="W557" s="7"/>
     </row>
     <row r="558">
-      <c r="A558" s="1"/>
+      <c r="A558" s="2"/>
       <c r="B558" s="7"/>
       <c r="C558" s="7"/>
       <c r="D558" s="7"/>
@@ -14504,7 +14519,7 @@
       <c r="W558" s="7"/>
     </row>
     <row r="559">
-      <c r="A559" s="1"/>
+      <c r="A559" s="2"/>
       <c r="B559" s="7"/>
       <c r="C559" s="7"/>
       <c r="D559" s="7"/>
@@ -14529,7 +14544,7 @@
       <c r="W559" s="7"/>
     </row>
     <row r="560">
-      <c r="A560" s="1"/>
+      <c r="A560" s="2"/>
       <c r="B560" s="7"/>
       <c r="C560" s="7"/>
       <c r="D560" s="7"/>
@@ -14554,7 +14569,7 @@
       <c r="W560" s="7"/>
     </row>
     <row r="561">
-      <c r="A561" s="1"/>
+      <c r="A561" s="2"/>
       <c r="B561" s="7"/>
       <c r="C561" s="7"/>
       <c r="D561" s="7"/>
@@ -14579,7 +14594,7 @@
       <c r="W561" s="7"/>
     </row>
     <row r="562">
-      <c r="A562" s="1"/>
+      <c r="A562" s="2"/>
       <c r="B562" s="7"/>
       <c r="C562" s="7"/>
       <c r="D562" s="7"/>
@@ -14604,7 +14619,7 @@
       <c r="W562" s="7"/>
     </row>
     <row r="563">
-      <c r="A563" s="1"/>
+      <c r="A563" s="2"/>
       <c r="B563" s="7"/>
       <c r="C563" s="7"/>
       <c r="D563" s="7"/>
@@ -14629,7 +14644,7 @@
       <c r="W563" s="7"/>
     </row>
     <row r="564">
-      <c r="A564" s="1"/>
+      <c r="A564" s="2"/>
       <c r="B564" s="7"/>
       <c r="C564" s="7"/>
       <c r="D564" s="7"/>
@@ -14654,7 +14669,7 @@
       <c r="W564" s="7"/>
     </row>
     <row r="565">
-      <c r="A565" s="1"/>
+      <c r="A565" s="2"/>
       <c r="B565" s="7"/>
       <c r="C565" s="7"/>
       <c r="D565" s="7"/>
@@ -14679,7 +14694,7 @@
       <c r="W565" s="7"/>
     </row>
     <row r="566">
-      <c r="A566" s="1"/>
+      <c r="A566" s="2"/>
       <c r="B566" s="7"/>
       <c r="C566" s="7"/>
       <c r="D566" s="7"/>
@@ -14704,7 +14719,7 @@
       <c r="W566" s="7"/>
     </row>
     <row r="567">
-      <c r="A567" s="1"/>
+      <c r="A567" s="2"/>
       <c r="B567" s="7"/>
       <c r="C567" s="7"/>
       <c r="D567" s="7"/>
@@ -14729,7 +14744,7 @@
       <c r="W567" s="7"/>
     </row>
     <row r="568">
-      <c r="A568" s="1"/>
+      <c r="A568" s="2"/>
       <c r="B568" s="7"/>
       <c r="C568" s="7"/>
       <c r="D568" s="7"/>
@@ -14754,7 +14769,7 @@
       <c r="W568" s="7"/>
     </row>
     <row r="569">
-      <c r="A569" s="1"/>
+      <c r="A569" s="2"/>
       <c r="B569" s="7"/>
       <c r="C569" s="7"/>
       <c r="D569" s="7"/>
@@ -14779,7 +14794,7 @@
       <c r="W569" s="7"/>
     </row>
     <row r="570">
-      <c r="A570" s="1"/>
+      <c r="A570" s="2"/>
       <c r="B570" s="7"/>
       <c r="C570" s="7"/>
       <c r="D570" s="7"/>
@@ -14804,7 +14819,7 @@
       <c r="W570" s="7"/>
     </row>
     <row r="571">
-      <c r="A571" s="1"/>
+      <c r="A571" s="2"/>
       <c r="B571" s="7"/>
       <c r="C571" s="7"/>
       <c r="D571" s="7"/>
@@ -14829,7 +14844,7 @@
       <c r="W571" s="7"/>
     </row>
     <row r="572">
-      <c r="A572" s="1"/>
+      <c r="A572" s="2"/>
       <c r="B572" s="7"/>
       <c r="C572" s="7"/>
       <c r="D572" s="7"/>
@@ -14854,7 +14869,7 @@
       <c r="W572" s="7"/>
     </row>
     <row r="573">
-      <c r="A573" s="1"/>
+      <c r="A573" s="2"/>
       <c r="B573" s="7"/>
       <c r="C573" s="7"/>
       <c r="D573" s="7"/>
@@ -14879,7 +14894,7 @@
       <c r="W573" s="7"/>
     </row>
     <row r="574">
-      <c r="A574" s="1"/>
+      <c r="A574" s="2"/>
       <c r="B574" s="7"/>
       <c r="C574" s="7"/>
       <c r="D574" s="7"/>
@@ -14904,7 +14919,7 @@
       <c r="W574" s="7"/>
     </row>
     <row r="575">
-      <c r="A575" s="1"/>
+      <c r="A575" s="2"/>
       <c r="B575" s="7"/>
       <c r="C575" s="7"/>
       <c r="D575" s="7"/>
@@ -14929,7 +14944,7 @@
       <c r="W575" s="7"/>
     </row>
     <row r="576">
-      <c r="A576" s="1"/>
+      <c r="A576" s="2"/>
       <c r="B576" s="7"/>
       <c r="C576" s="7"/>
       <c r="D576" s="7"/>
@@ -14954,7 +14969,7 @@
       <c r="W576" s="7"/>
     </row>
     <row r="577">
-      <c r="A577" s="1"/>
+      <c r="A577" s="2"/>
       <c r="B577" s="7"/>
       <c r="C577" s="7"/>
       <c r="D577" s="7"/>
@@ -14979,7 +14994,7 @@
       <c r="W577" s="7"/>
     </row>
     <row r="578">
-      <c r="A578" s="1"/>
+      <c r="A578" s="2"/>
       <c r="B578" s="7"/>
       <c r="C578" s="7"/>
       <c r="D578" s="7"/>
@@ -15004,7 +15019,7 @@
       <c r="W578" s="7"/>
     </row>
     <row r="579">
-      <c r="A579" s="1"/>
+      <c r="A579" s="2"/>
       <c r="B579" s="7"/>
       <c r="C579" s="7"/>
       <c r="D579" s="7"/>
@@ -15029,7 +15044,7 @@
       <c r="W579" s="7"/>
     </row>
     <row r="580">
-      <c r="A580" s="1"/>
+      <c r="A580" s="2"/>
       <c r="B580" s="7"/>
       <c r="C580" s="7"/>
       <c r="D580" s="7"/>
@@ -15054,7 +15069,7 @@
       <c r="W580" s="7"/>
     </row>
     <row r="581">
-      <c r="A581" s="1"/>
+      <c r="A581" s="2"/>
       <c r="B581" s="7"/>
       <c r="C581" s="7"/>
       <c r="D581" s="7"/>
@@ -15079,7 +15094,7 @@
       <c r="W581" s="7"/>
     </row>
     <row r="582">
-      <c r="A582" s="1"/>
+      <c r="A582" s="2"/>
       <c r="B582" s="7"/>
       <c r="C582" s="7"/>
       <c r="D582" s="7"/>
@@ -15104,7 +15119,7 @@
       <c r="W582" s="7"/>
     </row>
     <row r="583">
-      <c r="A583" s="1"/>
+      <c r="A583" s="2"/>
       <c r="B583" s="7"/>
       <c r="C583" s="7"/>
       <c r="D583" s="7"/>
@@ -15129,7 +15144,7 @@
       <c r="W583" s="7"/>
     </row>
     <row r="584">
-      <c r="A584" s="1"/>
+      <c r="A584" s="2"/>
       <c r="B584" s="7"/>
       <c r="C584" s="7"/>
       <c r="D584" s="7"/>
@@ -15154,7 +15169,7 @@
       <c r="W584" s="7"/>
     </row>
     <row r="585">
-      <c r="A585" s="1"/>
+      <c r="A585" s="2"/>
       <c r="B585" s="7"/>
       <c r="C585" s="7"/>
       <c r="D585" s="7"/>
@@ -15179,7 +15194,7 @@
       <c r="W585" s="7"/>
     </row>
     <row r="586">
-      <c r="A586" s="1"/>
+      <c r="A586" s="2"/>
       <c r="B586" s="7"/>
       <c r="C586" s="7"/>
       <c r="D586" s="7"/>
@@ -15204,7 +15219,7 @@
       <c r="W586" s="7"/>
     </row>
     <row r="587">
-      <c r="A587" s="1"/>
+      <c r="A587" s="2"/>
       <c r="B587" s="7"/>
       <c r="C587" s="7"/>
       <c r="D587" s="7"/>
@@ -15229,7 +15244,7 @@
       <c r="W587" s="7"/>
     </row>
     <row r="588">
-      <c r="A588" s="1"/>
+      <c r="A588" s="2"/>
       <c r="B588" s="7"/>
       <c r="C588" s="7"/>
       <c r="D588" s="7"/>
@@ -15254,7 +15269,7 @@
       <c r="W588" s="7"/>
     </row>
     <row r="589">
-      <c r="A589" s="1"/>
+      <c r="A589" s="2"/>
       <c r="B589" s="7"/>
       <c r="C589" s="7"/>
       <c r="D589" s="7"/>
@@ -15279,7 +15294,7 @@
       <c r="W589" s="7"/>
     </row>
     <row r="590">
-      <c r="A590" s="1"/>
+      <c r="A590" s="2"/>
       <c r="B590" s="7"/>
       <c r="C590" s="7"/>
       <c r="D590" s="7"/>
@@ -15304,7 +15319,7 @@
       <c r="W590" s="7"/>
     </row>
     <row r="591">
-      <c r="A591" s="1"/>
+      <c r="A591" s="2"/>
       <c r="B591" s="7"/>
       <c r="C591" s="7"/>
       <c r="D591" s="7"/>
@@ -15329,7 +15344,7 @@
       <c r="W591" s="7"/>
     </row>
     <row r="592">
-      <c r="A592" s="1"/>
+      <c r="A592" s="2"/>
       <c r="B592" s="7"/>
       <c r="C592" s="7"/>
       <c r="D592" s="7"/>
@@ -15354,7 +15369,7 @@
       <c r="W592" s="7"/>
     </row>
     <row r="593">
-      <c r="A593" s="1"/>
+      <c r="A593" s="2"/>
       <c r="B593" s="7"/>
       <c r="C593" s="7"/>
       <c r="D593" s="7"/>
@@ -15379,7 +15394,7 @@
       <c r="W593" s="7"/>
     </row>
     <row r="594">
-      <c r="A594" s="1"/>
+      <c r="A594" s="2"/>
       <c r="B594" s="7"/>
       <c r="C594" s="7"/>
       <c r="D594" s="7"/>
@@ -15404,7 +15419,7 @@
       <c r="W594" s="7"/>
     </row>
     <row r="595">
-      <c r="A595" s="1"/>
+      <c r="A595" s="2"/>
       <c r="B595" s="7"/>
       <c r="C595" s="7"/>
       <c r="D595" s="7"/>
@@ -15429,7 +15444,7 @@
       <c r="W595" s="7"/>
     </row>
     <row r="596">
-      <c r="A596" s="1"/>
+      <c r="A596" s="2"/>
       <c r="B596" s="7"/>
       <c r="C596" s="7"/>
       <c r="D596" s="7"/>
@@ -15454,7 +15469,7 @@
       <c r="W596" s="7"/>
     </row>
     <row r="597">
-      <c r="A597" s="1"/>
+      <c r="A597" s="2"/>
       <c r="B597" s="7"/>
       <c r="C597" s="7"/>
       <c r="D597" s="7"/>
@@ -15479,7 +15494,7 @@
       <c r="W597" s="7"/>
     </row>
     <row r="598">
-      <c r="A598" s="1"/>
+      <c r="A598" s="2"/>
       <c r="B598" s="7"/>
       <c r="C598" s="7"/>
       <c r="D598" s="7"/>
@@ -15504,7 +15519,7 @@
       <c r="W598" s="7"/>
     </row>
     <row r="599">
-      <c r="A599" s="1"/>
+      <c r="A599" s="2"/>
       <c r="B599" s="7"/>
       <c r="C599" s="7"/>
       <c r="D599" s="7"/>
@@ -15529,7 +15544,7 @@
       <c r="W599" s="7"/>
     </row>
     <row r="600">
-      <c r="A600" s="1"/>
+      <c r="A600" s="2"/>
       <c r="B600" s="7"/>
       <c r="C600" s="7"/>
       <c r="D600" s="7"/>
@@ -15554,7 +15569,7 @@
       <c r="W600" s="7"/>
     </row>
     <row r="601">
-      <c r="A601" s="1"/>
+      <c r="A601" s="2"/>
       <c r="B601" s="7"/>
       <c r="C601" s="7"/>
       <c r="D601" s="7"/>
@@ -15579,7 +15594,7 @@
       <c r="W601" s="7"/>
     </row>
     <row r="602">
-      <c r="A602" s="1"/>
+      <c r="A602" s="2"/>
       <c r="B602" s="7"/>
       <c r="C602" s="7"/>
       <c r="D602" s="7"/>
@@ -15604,7 +15619,7 @@
       <c r="W602" s="7"/>
     </row>
     <row r="603">
-      <c r="A603" s="1"/>
+      <c r="A603" s="2"/>
       <c r="B603" s="7"/>
       <c r="C603" s="7"/>
       <c r="D603" s="7"/>
@@ -15629,7 +15644,7 @@
       <c r="W603" s="7"/>
     </row>
     <row r="604">
-      <c r="A604" s="1"/>
+      <c r="A604" s="2"/>
       <c r="B604" s="7"/>
       <c r="C604" s="7"/>
       <c r="D604" s="7"/>
@@ -15654,7 +15669,7 @@
       <c r="W604" s="7"/>
     </row>
     <row r="605">
-      <c r="A605" s="1"/>
+      <c r="A605" s="2"/>
       <c r="B605" s="7"/>
       <c r="C605" s="7"/>
       <c r="D605" s="7"/>
@@ -15679,7 +15694,7 @@
       <c r="W605" s="7"/>
     </row>
     <row r="606">
-      <c r="A606" s="1"/>
+      <c r="A606" s="2"/>
       <c r="B606" s="7"/>
       <c r="C606" s="7"/>
       <c r="D606" s="7"/>
@@ -15704,7 +15719,7 @@
       <c r="W606" s="7"/>
     </row>
     <row r="607">
-      <c r="A607" s="1"/>
+      <c r="A607" s="2"/>
       <c r="B607" s="7"/>
       <c r="C607" s="7"/>
       <c r="D607" s="7"/>
@@ -15729,7 +15744,7 @@
       <c r="W607" s="7"/>
     </row>
     <row r="608">
-      <c r="A608" s="1"/>
+      <c r="A608" s="2"/>
       <c r="B608" s="7"/>
       <c r="C608" s="7"/>
       <c r="D608" s="7"/>
@@ -15754,7 +15769,7 @@
       <c r="W608" s="7"/>
     </row>
     <row r="609">
-      <c r="A609" s="1"/>
+      <c r="A609" s="2"/>
       <c r="B609" s="7"/>
       <c r="C609" s="7"/>
       <c r="D609" s="7"/>
@@ -15779,7 +15794,7 @@
       <c r="W609" s="7"/>
     </row>
     <row r="610">
-      <c r="A610" s="1"/>
+      <c r="A610" s="2"/>
       <c r="B610" s="7"/>
       <c r="C610" s="7"/>
       <c r="D610" s="7"/>
@@ -15804,7 +15819,7 @@
       <c r="W610" s="7"/>
     </row>
     <row r="611">
-      <c r="A611" s="1"/>
+      <c r="A611" s="2"/>
       <c r="B611" s="7"/>
       <c r="C611" s="7"/>
       <c r="D611" s="7"/>
@@ -15829,7 +15844,7 @@
       <c r="W611" s="7"/>
     </row>
     <row r="612">
-      <c r="A612" s="1"/>
+      <c r="A612" s="2"/>
       <c r="B612" s="7"/>
       <c r="C612" s="7"/>
       <c r="D612" s="7"/>
@@ -15854,7 +15869,7 @@
       <c r="W612" s="7"/>
     </row>
     <row r="613">
-      <c r="A613" s="1"/>
+      <c r="A613" s="2"/>
       <c r="B613" s="7"/>
       <c r="C613" s="7"/>
       <c r="D613" s="7"/>
@@ -15879,7 +15894,7 @@
       <c r="W613" s="7"/>
     </row>
     <row r="614">
-      <c r="A614" s="1"/>
+      <c r="A614" s="2"/>
       <c r="B614" s="7"/>
       <c r="C614" s="7"/>
       <c r="D614" s="7"/>
@@ -15904,7 +15919,7 @@
       <c r="W614" s="7"/>
     </row>
     <row r="615">
-      <c r="A615" s="1"/>
+      <c r="A615" s="2"/>
       <c r="B615" s="7"/>
       <c r="C615" s="7"/>
       <c r="D615" s="7"/>
@@ -15929,7 +15944,7 @@
       <c r="W615" s="7"/>
     </row>
     <row r="616">
-      <c r="A616" s="1"/>
+      <c r="A616" s="2"/>
       <c r="B616" s="7"/>
       <c r="C616" s="7"/>
       <c r="D616" s="7"/>
@@ -15954,7 +15969,7 @@
       <c r="W616" s="7"/>
     </row>
     <row r="617">
-      <c r="A617" s="1"/>
+      <c r="A617" s="2"/>
       <c r="B617" s="7"/>
       <c r="C617" s="7"/>
       <c r="D617" s="7"/>
@@ -15979,7 +15994,7 @@
       <c r="W617" s="7"/>
     </row>
     <row r="618">
-      <c r="A618" s="1"/>
+      <c r="A618" s="2"/>
       <c r="B618" s="7"/>
       <c r="C618" s="7"/>
       <c r="D618" s="7"/>
@@ -16004,7 +16019,7 @@
       <c r="W618" s="7"/>
     </row>
     <row r="619">
-      <c r="A619" s="1"/>
+      <c r="A619" s="2"/>
       <c r="B619" s="7"/>
       <c r="C619" s="7"/>
       <c r="D619" s="7"/>
@@ -16029,7 +16044,7 @@
       <c r="W619" s="7"/>
     </row>
     <row r="620">
-      <c r="A620" s="1"/>
+      <c r="A620" s="2"/>
       <c r="B620" s="7"/>
       <c r="C620" s="7"/>
       <c r="D620" s="7"/>
@@ -16054,7 +16069,7 @@
       <c r="W620" s="7"/>
     </row>
     <row r="621">
-      <c r="A621" s="1"/>
+      <c r="A621" s="2"/>
       <c r="B621" s="7"/>
       <c r="C621" s="7"/>
       <c r="D621" s="7"/>
@@ -16079,7 +16094,7 @@
       <c r="W621" s="7"/>
     </row>
     <row r="622">
-      <c r="A622" s="1"/>
+      <c r="A622" s="2"/>
       <c r="B622" s="7"/>
       <c r="C622" s="7"/>
       <c r="D622" s="7"/>
@@ -16104,7 +16119,7 @@
       <c r="W622" s="7"/>
     </row>
     <row r="623">
-      <c r="A623" s="1"/>
+      <c r="A623" s="2"/>
       <c r="B623" s="7"/>
       <c r="C623" s="7"/>
       <c r="D623" s="7"/>
@@ -16129,7 +16144,7 @@
       <c r="W623" s="7"/>
     </row>
     <row r="624">
-      <c r="A624" s="1"/>
+      <c r="A624" s="2"/>
       <c r="B624" s="7"/>
       <c r="C624" s="7"/>
       <c r="D624" s="7"/>
@@ -16154,7 +16169,7 @@
       <c r="W624" s="7"/>
     </row>
     <row r="625">
-      <c r="A625" s="1"/>
+      <c r="A625" s="2"/>
       <c r="B625" s="7"/>
       <c r="C625" s="7"/>
       <c r="D625" s="7"/>
@@ -16179,7 +16194,7 @@
       <c r="W625" s="7"/>
     </row>
     <row r="626">
-      <c r="A626" s="1"/>
+      <c r="A626" s="2"/>
       <c r="B626" s="7"/>
       <c r="C626" s="7"/>
       <c r="D626" s="7"/>
@@ -16204,7 +16219,7 @@
       <c r="W626" s="7"/>
     </row>
     <row r="627">
-      <c r="A627" s="1"/>
+      <c r="A627" s="2"/>
       <c r="B627" s="7"/>
       <c r="C627" s="7"/>
       <c r="D627" s="7"/>
@@ -16229,7 +16244,7 @@
       <c r="W627" s="7"/>
     </row>
     <row r="628">
-      <c r="A628" s="1"/>
+      <c r="A628" s="2"/>
       <c r="B628" s="7"/>
       <c r="C628" s="7"/>
       <c r="D628" s="7"/>
@@ -16254,7 +16269,7 @@
       <c r="W628" s="7"/>
     </row>
     <row r="629">
-      <c r="A629" s="1"/>
+      <c r="A629" s="2"/>
       <c r="B629" s="7"/>
       <c r="C629" s="7"/>
       <c r="D629" s="7"/>
@@ -16279,7 +16294,7 @@
       <c r="W629" s="7"/>
     </row>
     <row r="630">
-      <c r="A630" s="1"/>
+      <c r="A630" s="2"/>
       <c r="B630" s="7"/>
       <c r="C630" s="7"/>
       <c r="D630" s="7"/>
@@ -16304,7 +16319,7 @@
       <c r="W630" s="7"/>
     </row>
     <row r="631">
-      <c r="A631" s="1"/>
+      <c r="A631" s="2"/>
       <c r="B631" s="7"/>
       <c r="C631" s="7"/>
       <c r="D631" s="7"/>
@@ -16329,7 +16344,7 @@
       <c r="W631" s="7"/>
     </row>
     <row r="632">
-      <c r="A632" s="1"/>
+      <c r="A632" s="2"/>
       <c r="B632" s="7"/>
       <c r="C632" s="7"/>
       <c r="D632" s="7"/>
@@ -16354,7 +16369,7 @@
       <c r="W632" s="7"/>
     </row>
     <row r="633">
-      <c r="A633" s="1"/>
+      <c r="A633" s="2"/>
       <c r="B633" s="7"/>
       <c r="C633" s="7"/>
       <c r="D633" s="7"/>
@@ -16379,7 +16394,7 @@
       <c r="W633" s="7"/>
     </row>
     <row r="634">
-      <c r="A634" s="1"/>
+      <c r="A634" s="2"/>
       <c r="B634" s="7"/>
       <c r="C634" s="7"/>
       <c r="D634" s="7"/>
@@ -16404,7 +16419,7 @@
       <c r="W634" s="7"/>
     </row>
     <row r="635">
-      <c r="A635" s="1"/>
+      <c r="A635" s="2"/>
       <c r="B635" s="7"/>
       <c r="C635" s="7"/>
       <c r="D635" s="7"/>
@@ -16429,7 +16444,7 @@
       <c r="W635" s="7"/>
     </row>
     <row r="636">
-      <c r="A636" s="1"/>
+      <c r="A636" s="2"/>
       <c r="B636" s="7"/>
       <c r="C636" s="7"/>
       <c r="D636" s="7"/>
@@ -16454,7 +16469,7 @@
       <c r="W636" s="7"/>
     </row>
     <row r="637">
-      <c r="A637" s="1"/>
+      <c r="A637" s="2"/>
       <c r="B637" s="7"/>
       <c r="C637" s="7"/>
       <c r="D637" s="7"/>
@@ -16479,7 +16494,7 @@
       <c r="W637" s="7"/>
     </row>
     <row r="638">
-      <c r="A638" s="1"/>
+      <c r="A638" s="2"/>
       <c r="B638" s="7"/>
       <c r="C638" s="7"/>
       <c r="D638" s="7"/>
@@ -16504,7 +16519,7 @@
       <c r="W638" s="7"/>
     </row>
     <row r="639">
-      <c r="A639" s="1"/>
+      <c r="A639" s="2"/>
       <c r="B639" s="7"/>
       <c r="C639" s="7"/>
       <c r="D639" s="7"/>
@@ -16529,7 +16544,7 @@
       <c r="W639" s="7"/>
     </row>
     <row r="640">
-      <c r="A640" s="1"/>
+      <c r="A640" s="2"/>
       <c r="B640" s="7"/>
       <c r="C640" s="7"/>
       <c r="D640" s="7"/>
@@ -16554,7 +16569,7 @@
       <c r="W640" s="7"/>
     </row>
     <row r="641">
-      <c r="A641" s="1"/>
+      <c r="A641" s="2"/>
       <c r="B641" s="7"/>
       <c r="C641" s="7"/>
       <c r="D641" s="7"/>
@@ -16579,7 +16594,7 @@
       <c r="W641" s="7"/>
     </row>
     <row r="642">
-      <c r="A642" s="1"/>
+      <c r="A642" s="2"/>
       <c r="B642" s="7"/>
       <c r="C642" s="7"/>
       <c r="D642" s="7"/>
@@ -16604,7 +16619,7 @@
       <c r="W642" s="7"/>
     </row>
     <row r="643">
-      <c r="A643" s="1"/>
+      <c r="A643" s="2"/>
       <c r="B643" s="7"/>
       <c r="C643" s="7"/>
       <c r="D643" s="7"/>
@@ -16629,7 +16644,7 @@
       <c r="W643" s="7"/>
     </row>
     <row r="644">
-      <c r="A644" s="1"/>
+      <c r="A644" s="2"/>
       <c r="B644" s="7"/>
       <c r="C644" s="7"/>
       <c r="D644" s="7"/>
@@ -16654,7 +16669,7 @@
       <c r="W644" s="7"/>
     </row>
     <row r="645">
-      <c r="A645" s="1"/>
+      <c r="A645" s="2"/>
       <c r="B645" s="7"/>
       <c r="C645" s="7"/>
       <c r="D645" s="7"/>
@@ -16679,7 +16694,7 @@
       <c r="W645" s="7"/>
     </row>
     <row r="646">
-      <c r="A646" s="1"/>
+      <c r="A646" s="2"/>
       <c r="B646" s="7"/>
       <c r="C646" s="7"/>
       <c r="D646" s="7"/>
@@ -16704,7 +16719,7 @@
       <c r="W646" s="7"/>
     </row>
     <row r="647">
-      <c r="A647" s="1"/>
+      <c r="A647" s="2"/>
       <c r="B647" s="7"/>
       <c r="C647" s="7"/>
       <c r="D647" s="7"/>
@@ -16729,7 +16744,7 @@
       <c r="W647" s="7"/>
     </row>
     <row r="648">
-      <c r="A648" s="1"/>
+      <c r="A648" s="2"/>
       <c r="B648" s="7"/>
       <c r="C648" s="7"/>
       <c r="D648" s="7"/>
@@ -16754,7 +16769,7 @@
       <c r="W648" s="7"/>
     </row>
     <row r="649">
-      <c r="A649" s="1"/>
+      <c r="A649" s="2"/>
       <c r="B649" s="7"/>
       <c r="C649" s="7"/>
       <c r="D649" s="7"/>
@@ -16779,7 +16794,7 @@
       <c r="W649" s="7"/>
     </row>
     <row r="650">
-      <c r="A650" s="1"/>
+      <c r="A650" s="2"/>
       <c r="B650" s="7"/>
       <c r="C650" s="7"/>
       <c r="D650" s="7"/>
@@ -16804,7 +16819,7 @@
       <c r="W650" s="7"/>
     </row>
     <row r="651">
-      <c r="A651" s="1"/>
+      <c r="A651" s="2"/>
       <c r="B651" s="7"/>
       <c r="C651" s="7"/>
       <c r="D651" s="7"/>
@@ -16829,7 +16844,7 @@
       <c r="W651" s="7"/>
     </row>
     <row r="652">
-      <c r="A652" s="1"/>
+      <c r="A652" s="2"/>
       <c r="B652" s="7"/>
       <c r="C652" s="7"/>
       <c r="D652" s="7"/>
@@ -16854,7 +16869,7 @@
       <c r="W652" s="7"/>
     </row>
     <row r="653">
-      <c r="A653" s="1"/>
+      <c r="A653" s="2"/>
       <c r="B653" s="7"/>
       <c r="C653" s="7"/>
       <c r="D653" s="7"/>
@@ -16879,7 +16894,7 @@
       <c r="W653" s="7"/>
     </row>
     <row r="654">
-      <c r="A654" s="1"/>
+      <c r="A654" s="2"/>
       <c r="B654" s="7"/>
       <c r="C654" s="7"/>
       <c r="D654" s="7"/>
@@ -16904,7 +16919,7 @@
       <c r="W654" s="7"/>
     </row>
     <row r="655">
-      <c r="A655" s="1"/>
+      <c r="A655" s="2"/>
       <c r="B655" s="7"/>
       <c r="C655" s="7"/>
       <c r="D655" s="7"/>
@@ -16929,7 +16944,7 @@
       <c r="W655" s="7"/>
     </row>
     <row r="656">
-      <c r="A656" s="1"/>
+      <c r="A656" s="2"/>
       <c r="B656" s="7"/>
       <c r="C656" s="7"/>
       <c r="D656" s="7"/>
@@ -16954,7 +16969,7 @@
       <c r="W656" s="7"/>
     </row>
     <row r="657">
-      <c r="A657" s="1"/>
+      <c r="A657" s="2"/>
       <c r="B657" s="7"/>
       <c r="C657" s="7"/>
       <c r="D657" s="7"/>
@@ -16979,7 +16994,7 @@
       <c r="W657" s="7"/>
     </row>
     <row r="658">
-      <c r="A658" s="1"/>
+      <c r="A658" s="2"/>
       <c r="B658" s="7"/>
       <c r="C658" s="7"/>
       <c r="D658" s="7"/>
@@ -17004,7 +17019,7 @@
       <c r="W658" s="7"/>
     </row>
     <row r="659">
-      <c r="A659" s="1"/>
+      <c r="A659" s="2"/>
       <c r="B659" s="7"/>
       <c r="C659" s="7"/>
       <c r="D659" s="7"/>
@@ -17029,7 +17044,7 @@
       <c r="W659" s="7"/>
     </row>
     <row r="660">
-      <c r="A660" s="1"/>
+      <c r="A660" s="2"/>
       <c r="B660" s="7"/>
       <c r="C660" s="7"/>
       <c r="D660" s="7"/>
@@ -17054,7 +17069,7 @@
       <c r="W660" s="7"/>
     </row>
     <row r="661">
-      <c r="A661" s="1"/>
+      <c r="A661" s="2"/>
       <c r="B661" s="7"/>
       <c r="C661" s="7"/>
       <c r="D661" s="7"/>
@@ -17079,7 +17094,7 @@
       <c r="W661" s="7"/>
     </row>
     <row r="662">
-      <c r="A662" s="1"/>
+      <c r="A662" s="2"/>
       <c r="B662" s="7"/>
       <c r="C662" s="7"/>
       <c r="D662" s="7"/>
@@ -17104,7 +17119,7 @@
       <c r="W662" s="7"/>
     </row>
     <row r="663">
-      <c r="A663" s="1"/>
+      <c r="A663" s="2"/>
       <c r="B663" s="7"/>
       <c r="C663" s="7"/>
       <c r="D663" s="7"/>
@@ -17129,7 +17144,7 @@
       <c r="W663" s="7"/>
     </row>
     <row r="664">
-      <c r="A664" s="1"/>
+      <c r="A664" s="2"/>
       <c r="B664" s="7"/>
       <c r="C664" s="7"/>
       <c r="D664" s="7"/>
@@ -17154,7 +17169,7 @@
       <c r="W664" s="7"/>
     </row>
     <row r="665">
-      <c r="A665" s="1"/>
+      <c r="A665" s="2"/>
       <c r="B665" s="7"/>
       <c r="C665" s="7"/>
       <c r="D665" s="7"/>
@@ -17179,7 +17194,7 @@
       <c r="W665" s="7"/>
     </row>
     <row r="666">
-      <c r="A666" s="1"/>
+      <c r="A666" s="2"/>
       <c r="B666" s="7"/>
       <c r="C666" s="7"/>
       <c r="D666" s="7"/>
@@ -17204,7 +17219,7 @@
       <c r="W666" s="7"/>
     </row>
     <row r="667">
-      <c r="A667" s="1"/>
+      <c r="A667" s="2"/>
       <c r="B667" s="7"/>
       <c r="C667" s="7"/>
       <c r="D667" s="7"/>
@@ -17229,7 +17244,7 @@
       <c r="W667" s="7"/>
     </row>
     <row r="668">
-      <c r="A668" s="1"/>
+      <c r="A668" s="2"/>
       <c r="B668" s="7"/>
       <c r="C668" s="7"/>
       <c r="D668" s="7"/>
@@ -17254,7 +17269,7 @@
       <c r="W668" s="7"/>
     </row>
     <row r="669">
-      <c r="A669" s="1"/>
+      <c r="A669" s="2"/>
       <c r="B669" s="7"/>
       <c r="C669" s="7"/>
       <c r="D669" s="7"/>
@@ -17279,7 +17294,7 @@
       <c r="W669" s="7"/>
     </row>
     <row r="670">
-      <c r="A670" s="1"/>
+      <c r="A670" s="2"/>
       <c r="B670" s="7"/>
       <c r="C670" s="7"/>
       <c r="D670" s="7"/>
@@ -17304,7 +17319,7 @@
       <c r="W670" s="7"/>
     </row>
     <row r="671">
-      <c r="A671" s="1"/>
+      <c r="A671" s="2"/>
       <c r="B671" s="7"/>
       <c r="C671" s="7"/>
       <c r="D671" s="7"/>
@@ -17329,7 +17344,7 @@
       <c r="W671" s="7"/>
     </row>
     <row r="672">
-      <c r="A672" s="1"/>
+      <c r="A672" s="2"/>
       <c r="B672" s="7"/>
       <c r="C672" s="7"/>
       <c r="D672" s="7"/>
@@ -17354,7 +17369,7 @@
       <c r="W672" s="7"/>
     </row>
     <row r="673">
-      <c r="A673" s="1"/>
+      <c r="A673" s="2"/>
       <c r="B673" s="7"/>
       <c r="C673" s="7"/>
       <c r="D673" s="7"/>
@@ -17379,7 +17394,7 @@
       <c r="W673" s="7"/>
     </row>
     <row r="674">
-      <c r="A674" s="1"/>
+      <c r="A674" s="2"/>
       <c r="B674" s="7"/>
       <c r="C674" s="7"/>
       <c r="D674" s="7"/>
@@ -17404,7 +17419,7 @@
       <c r="W674" s="7"/>
     </row>
     <row r="675">
-      <c r="A675" s="1"/>
+      <c r="A675" s="2"/>
       <c r="B675" s="7"/>
       <c r="C675" s="7"/>
       <c r="D675" s="7"/>
@@ -17429,7 +17444,7 @@
       <c r="W675" s="7"/>
     </row>
     <row r="676">
-      <c r="A676" s="1"/>
+      <c r="A676" s="2"/>
       <c r="B676" s="7"/>
       <c r="C676" s="7"/>
       <c r="D676" s="7"/>
@@ -17454,7 +17469,7 @@
       <c r="W676" s="7"/>
     </row>
     <row r="677">
-      <c r="A677" s="1"/>
+      <c r="A677" s="2"/>
       <c r="B677" s="7"/>
       <c r="C677" s="7"/>
       <c r="D677" s="7"/>
@@ -17479,7 +17494,7 @@
       <c r="W677" s="7"/>
     </row>
     <row r="678">
-      <c r="A678" s="1"/>
+      <c r="A678" s="2"/>
       <c r="B678" s="7"/>
       <c r="C678" s="7"/>
       <c r="D678" s="7"/>
@@ -17504,7 +17519,7 @@
       <c r="W678" s="7"/>
     </row>
     <row r="679">
-      <c r="A679" s="1"/>
+      <c r="A679" s="2"/>
       <c r="B679" s="7"/>
       <c r="C679" s="7"/>
       <c r="D679" s="7"/>
@@ -17529,7 +17544,7 @@
       <c r="W679" s="7"/>
     </row>
     <row r="680">
-      <c r="A680" s="1"/>
+      <c r="A680" s="2"/>
       <c r="B680" s="7"/>
       <c r="C680" s="7"/>
       <c r="D680" s="7"/>
@@ -17554,7 +17569,7 @@
       <c r="W680" s="7"/>
     </row>
     <row r="681">
-      <c r="A681" s="1"/>
+      <c r="A681" s="2"/>
       <c r="B681" s="7"/>
       <c r="C681" s="7"/>
       <c r="D681" s="7"/>
@@ -17579,7 +17594,7 @@
       <c r="W681" s="7"/>
     </row>
     <row r="682">
-      <c r="A682" s="1"/>
+      <c r="A682" s="2"/>
       <c r="B682" s="7"/>
       <c r="C682" s="7"/>
       <c r="D682" s="7"/>
@@ -17604,7 +17619,7 @@
       <c r="W682" s="7"/>
     </row>
     <row r="683">
-      <c r="A683" s="1"/>
+      <c r="A683" s="2"/>
       <c r="B683" s="7"/>
       <c r="C683" s="7"/>
       <c r="D683" s="7"/>
@@ -17629,7 +17644,7 @@
       <c r="W683" s="7"/>
     </row>
     <row r="684">
-      <c r="A684" s="1"/>
+      <c r="A684" s="2"/>
       <c r="B684" s="7"/>
       <c r="C684" s="7"/>
       <c r="D684" s="7"/>
@@ -17654,7 +17669,7 @@
       <c r="W684" s="7"/>
     </row>
     <row r="685">
-      <c r="A685" s="1"/>
+      <c r="A685" s="2"/>
       <c r="B685" s="7"/>
       <c r="C685" s="7"/>
       <c r="D685" s="7"/>
@@ -17679,7 +17694,7 @@
       <c r="W685" s="7"/>
     </row>
     <row r="686">
-      <c r="A686" s="1"/>
+      <c r="A686" s="2"/>
       <c r="B686" s="7"/>
       <c r="C686" s="7"/>
       <c r="D686" s="7"/>
@@ -17704,7 +17719,7 @@
       <c r="W686" s="7"/>
     </row>
     <row r="687">
-      <c r="A687" s="1"/>
+      <c r="A687" s="2"/>
       <c r="B687" s="7"/>
       <c r="C687" s="7"/>
       <c r="D687" s="7"/>
@@ -17729,7 +17744,7 @@
       <c r="W687" s="7"/>
     </row>
     <row r="688">
-      <c r="A688" s="1"/>
+      <c r="A688" s="2"/>
       <c r="B688" s="7"/>
       <c r="C688" s="7"/>
       <c r="D688" s="7"/>
@@ -17754,7 +17769,7 @@
       <c r="W688" s="7"/>
     </row>
     <row r="689">
-      <c r="A689" s="1"/>
+      <c r="A689" s="2"/>
       <c r="B689" s="7"/>
       <c r="C689" s="7"/>
       <c r="D689" s="7"/>
@@ -17779,7 +17794,7 @@
       <c r="W689" s="7"/>
     </row>
     <row r="690">
-      <c r="A690" s="1"/>
+      <c r="A690" s="2"/>
       <c r="B690" s="7"/>
       <c r="C690" s="7"/>
       <c r="D690" s="7"/>
@@ -17804,7 +17819,7 @@
       <c r="W690" s="7"/>
     </row>
     <row r="691">
-      <c r="A691" s="1"/>
+      <c r="A691" s="2"/>
       <c r="B691" s="7"/>
       <c r="C691" s="7"/>
       <c r="D691" s="7"/>
@@ -17829,7 +17844,7 @@
       <c r="W691" s="7"/>
     </row>
     <row r="692">
-      <c r="A692" s="1"/>
+      <c r="A692" s="2"/>
       <c r="B692" s="7"/>
       <c r="C692" s="7"/>
       <c r="D692" s="7"/>
@@ -17854,7 +17869,7 @@
       <c r="W692" s="7"/>
     </row>
     <row r="693">
-      <c r="A693" s="1"/>
+      <c r="A693" s="2"/>
       <c r="B693" s="7"/>
       <c r="C693" s="7"/>
       <c r="D693" s="7"/>
@@ -17879,7 +17894,7 @@
       <c r="W693" s="7"/>
     </row>
     <row r="694">
-      <c r="A694" s="1"/>
+      <c r="A694" s="2"/>
       <c r="B694" s="7"/>
       <c r="C694" s="7"/>
       <c r="D694" s="7"/>
@@ -17904,7 +17919,7 @@
       <c r="W694" s="7"/>
     </row>
     <row r="695">
-      <c r="A695" s="1"/>
+      <c r="A695" s="2"/>
       <c r="B695" s="7"/>
       <c r="C695" s="7"/>
       <c r="D695" s="7"/>
@@ -17929,7 +17944,7 @@
       <c r="W695" s="7"/>
     </row>
     <row r="696">
-      <c r="A696" s="1"/>
+      <c r="A696" s="2"/>
       <c r="B696" s="7"/>
       <c r="C696" s="7"/>
       <c r="D696" s="7"/>
@@ -17954,7 +17969,7 @@
       <c r="W696" s="7"/>
     </row>
     <row r="697">
-      <c r="A697" s="1"/>
+      <c r="A697" s="2"/>
       <c r="B697" s="7"/>
       <c r="C697" s="7"/>
       <c r="D697" s="7"/>
@@ -17979,7 +17994,7 @@
       <c r="W697" s="7"/>
     </row>
     <row r="698">
-      <c r="A698" s="1"/>
+      <c r="A698" s="2"/>
       <c r="B698" s="7"/>
       <c r="C698" s="7"/>
       <c r="D698" s="7"/>
@@ -18004,7 +18019,7 @@
       <c r="W698" s="7"/>
     </row>
     <row r="699">
-      <c r="A699" s="1"/>
+      <c r="A699" s="2"/>
       <c r="B699" s="7"/>
       <c r="C699" s="7"/>
       <c r="D699" s="7"/>
@@ -18029,7 +18044,7 @@
       <c r="W699" s="7"/>
     </row>
     <row r="700">
-      <c r="A700" s="1"/>
+      <c r="A700" s="2"/>
       <c r="B700" s="7"/>
       <c r="C700" s="7"/>
       <c r="D700" s="7"/>
@@ -18054,7 +18069,7 @@
       <c r="W700" s="7"/>
     </row>
     <row r="701">
-      <c r="A701" s="1"/>
+      <c r="A701" s="2"/>
       <c r="B701" s="7"/>
       <c r="C701" s="7"/>
       <c r="D701" s="7"/>
@@ -18079,7 +18094,7 @@
       <c r="W701" s="7"/>
     </row>
     <row r="702">
-      <c r="A702" s="1"/>
+      <c r="A702" s="2"/>
       <c r="B702" s="7"/>
       <c r="C702" s="7"/>
       <c r="D702" s="7"/>
@@ -18104,7 +18119,7 @@
       <c r="W702" s="7"/>
     </row>
     <row r="703">
-      <c r="A703" s="1"/>
+      <c r="A703" s="2"/>
       <c r="B703" s="7"/>
       <c r="C703" s="7"/>
       <c r="D703" s="7"/>
@@ -18129,7 +18144,7 @@
       <c r="W703" s="7"/>
     </row>
     <row r="704">
-      <c r="A704" s="1"/>
+      <c r="A704" s="2"/>
       <c r="B704" s="7"/>
       <c r="C704" s="7"/>
       <c r="D704" s="7"/>
@@ -18154,7 +18169,7 @@
       <c r="W704" s="7"/>
     </row>
     <row r="705">
-      <c r="A705" s="1"/>
+      <c r="A705" s="2"/>
       <c r="B705" s="7"/>
       <c r="C705" s="7"/>
       <c r="D705" s="7"/>
@@ -18179,7 +18194,7 @@
       <c r="W705" s="7"/>
     </row>
     <row r="706">
-      <c r="A706" s="1"/>
+      <c r="A706" s="2"/>
       <c r="B706" s="7"/>
       <c r="C706" s="7"/>
       <c r="D706" s="7"/>
@@ -18204,7 +18219,7 @@
       <c r="W706" s="7"/>
     </row>
     <row r="707">
-      <c r="A707" s="1"/>
+      <c r="A707" s="2"/>
       <c r="B707" s="7"/>
       <c r="C707" s="7"/>
       <c r="D707" s="7"/>
@@ -18229,7 +18244,7 @@
       <c r="W707" s="7"/>
     </row>
     <row r="708">
-      <c r="A708" s="1"/>
+      <c r="A708" s="2"/>
       <c r="B708" s="7"/>
       <c r="C708" s="7"/>
       <c r="D708" s="7"/>
@@ -18254,7 +18269,7 @@
       <c r="W708" s="7"/>
     </row>
     <row r="709">
-      <c r="A709" s="1"/>
+      <c r="A709" s="2"/>
       <c r="B709" s="7"/>
       <c r="C709" s="7"/>
       <c r="D709" s="7"/>
@@ -18279,7 +18294,7 @@
       <c r="W709" s="7"/>
     </row>
     <row r="710">
-      <c r="A710" s="1"/>
+      <c r="A710" s="2"/>
       <c r="B710" s="7"/>
       <c r="C710" s="7"/>
       <c r="D710" s="7"/>
@@ -18304,7 +18319,7 @@
       <c r="W710" s="7"/>
     </row>
     <row r="711">
-      <c r="A711" s="1"/>
+      <c r="A711" s="2"/>
       <c r="B711" s="7"/>
       <c r="C711" s="7"/>
       <c r="D711" s="7"/>
@@ -18329,7 +18344,7 @@
       <c r="W711" s="7"/>
     </row>
     <row r="712">
-      <c r="A712" s="1"/>
+      <c r="A712" s="2"/>
       <c r="B712" s="7"/>
       <c r="C712" s="7"/>
       <c r="D712" s="7"/>
@@ -18354,7 +18369,7 @@
       <c r="W712" s="7"/>
     </row>
     <row r="713">
-      <c r="A713" s="1"/>
+      <c r="A713" s="2"/>
       <c r="B713" s="7"/>
       <c r="C713" s="7"/>
       <c r="D713" s="7"/>
@@ -18379,7 +18394,7 @@
       <c r="W713" s="7"/>
     </row>
     <row r="714">
-      <c r="A714" s="1"/>
+      <c r="A714" s="2"/>
       <c r="B714" s="7"/>
       <c r="C714" s="7"/>
       <c r="D714" s="7"/>
@@ -18404,7 +18419,7 @@
       <c r="W714" s="7"/>
     </row>
     <row r="715">
-      <c r="A715" s="1"/>
+      <c r="A715" s="2"/>
       <c r="B715" s="7"/>
       <c r="C715" s="7"/>
       <c r="D715" s="7"/>
@@ -18429,7 +18444,7 @@
       <c r="W715" s="7"/>
     </row>
     <row r="716">
-      <c r="A716" s="1"/>
+      <c r="A716" s="2"/>
       <c r="B716" s="7"/>
       <c r="C716" s="7"/>
       <c r="D716" s="7"/>
@@ -18454,7 +18469,7 @@
       <c r="W716" s="7"/>
     </row>
     <row r="717">
-      <c r="A717" s="1"/>
+      <c r="A717" s="2"/>
       <c r="B717" s="7"/>
       <c r="C717" s="7"/>
       <c r="D717" s="7"/>
@@ -18479,7 +18494,7 @@
       <c r="W717" s="7"/>
     </row>
     <row r="718">
-      <c r="A718" s="1"/>
+      <c r="A718" s="2"/>
       <c r="B718" s="7"/>
       <c r="C718" s="7"/>
       <c r="D718" s="7"/>
@@ -18504,7 +18519,7 @@
       <c r="W718" s="7"/>
     </row>
     <row r="719">
-      <c r="A719" s="1"/>
+      <c r="A719" s="2"/>
       <c r="B719" s="7"/>
       <c r="C719" s="7"/>
       <c r="D719" s="7"/>
@@ -18529,7 +18544,7 @@
       <c r="W719" s="7"/>
     </row>
     <row r="720">
-      <c r="A720" s="1"/>
+      <c r="A720" s="2"/>
       <c r="B720" s="7"/>
       <c r="C720" s="7"/>
       <c r="D720" s="7"/>
@@ -18554,7 +18569,7 @@
       <c r="W720" s="7"/>
     </row>
     <row r="721">
-      <c r="A721" s="1"/>
+      <c r="A721" s="2"/>
       <c r="B721" s="7"/>
       <c r="C721" s="7"/>
       <c r="D721" s="7"/>
@@ -18579,7 +18594,7 @@
       <c r="W721" s="7"/>
     </row>
     <row r="722">
-      <c r="A722" s="1"/>
+      <c r="A722" s="2"/>
       <c r="B722" s="7"/>
       <c r="C722" s="7"/>
       <c r="D722" s="7"/>
@@ -18604,7 +18619,7 @@
       <c r="W722" s="7"/>
     </row>
     <row r="723">
-      <c r="A723" s="1"/>
+      <c r="A723" s="2"/>
       <c r="B723" s="7"/>
       <c r="C723" s="7"/>
       <c r="D723" s="7"/>
@@ -18629,7 +18644,7 @@
       <c r="W723" s="7"/>
     </row>
     <row r="724">
-      <c r="A724" s="1"/>
+      <c r="A724" s="2"/>
       <c r="B724" s="7"/>
       <c r="C724" s="7"/>
       <c r="D724" s="7"/>
@@ -18654,7 +18669,7 @@
       <c r="W724" s="7"/>
     </row>
     <row r="725">
-      <c r="A725" s="1"/>
+      <c r="A725" s="2"/>
       <c r="B725" s="7"/>
       <c r="C725" s="7"/>
       <c r="D725" s="7"/>
@@ -18679,7 +18694,7 @@
       <c r="W725" s="7"/>
     </row>
     <row r="726">
-      <c r="A726" s="1"/>
+      <c r="A726" s="2"/>
       <c r="B726" s="7"/>
       <c r="C726" s="7"/>
       <c r="D726" s="7"/>
@@ -18704,7 +18719,7 @@
       <c r="W726" s="7"/>
     </row>
     <row r="727">
-      <c r="A727" s="1"/>
+      <c r="A727" s="2"/>
       <c r="B727" s="7"/>
       <c r="C727" s="7"/>
       <c r="D727" s="7"/>
@@ -18729,7 +18744,7 @@
       <c r="W727" s="7"/>
     </row>
     <row r="728">
-      <c r="A728" s="1"/>
+      <c r="A728" s="2"/>
       <c r="B728" s="7"/>
       <c r="C728" s="7"/>
       <c r="D728" s="7"/>
@@ -18754,7 +18769,7 @@
       <c r="W728" s="7"/>
     </row>
     <row r="729">
-      <c r="A729" s="1"/>
+      <c r="A729" s="2"/>
       <c r="B729" s="7"/>
       <c r="C729" s="7"/>
       <c r="D729" s="7"/>
@@ -18779,7 +18794,7 @@
       <c r="W729" s="7"/>
     </row>
     <row r="730">
-      <c r="A730" s="1"/>
+      <c r="A730" s="2"/>
       <c r="B730" s="7"/>
       <c r="C730" s="7"/>
       <c r="D730" s="7"/>
@@ -18804,7 +18819,7 @@
       <c r="W730" s="7"/>
     </row>
     <row r="731">
-      <c r="A731" s="1"/>
+      <c r="A731" s="2"/>
       <c r="B731" s="7"/>
       <c r="C731" s="7"/>
       <c r="D731" s="7"/>
@@ -18829,7 +18844,7 @@
       <c r="W731" s="7"/>
     </row>
     <row r="732">
-      <c r="A732" s="1"/>
+      <c r="A732" s="2"/>
       <c r="B732" s="7"/>
       <c r="C732" s="7"/>
       <c r="D732" s="7"/>
@@ -18854,7 +18869,7 @@
       <c r="W732" s="7"/>
     </row>
     <row r="733">
-      <c r="A733" s="1"/>
+      <c r="A733" s="2"/>
       <c r="B733" s="7"/>
       <c r="C733" s="7"/>
       <c r="D733" s="7"/>
@@ -18879,7 +18894,7 @@
       <c r="W733" s="7"/>
     </row>
     <row r="734">
-      <c r="A734" s="1"/>
+      <c r="A734" s="2"/>
       <c r="B734" s="7"/>
       <c r="C734" s="7"/>
       <c r="D734" s="7"/>
@@ -18904,7 +18919,7 @@
       <c r="W734" s="7"/>
     </row>
     <row r="735">
-      <c r="A735" s="1"/>
+      <c r="A735" s="2"/>
       <c r="B735" s="7"/>
       <c r="C735" s="7"/>
       <c r="D735" s="7"/>
@@ -18929,7 +18944,7 @@
       <c r="W735" s="7"/>
     </row>
     <row r="736">
-      <c r="A736" s="1"/>
+      <c r="A736" s="2"/>
       <c r="B736" s="7"/>
       <c r="C736" s="7"/>
       <c r="D736" s="7"/>
@@ -18954,7 +18969,7 @@
       <c r="W736" s="7"/>
     </row>
     <row r="737">
-      <c r="A737" s="1"/>
+      <c r="A737" s="2"/>
       <c r="B737" s="7"/>
       <c r="C737" s="7"/>
       <c r="D737" s="7"/>
@@ -18979,7 +18994,7 @@
       <c r="W737" s="7"/>
     </row>
     <row r="738">
-      <c r="A738" s="1"/>
+      <c r="A738" s="2"/>
       <c r="B738" s="7"/>
       <c r="C738" s="7"/>
       <c r="D738" s="7"/>
@@ -19004,7 +19019,7 @@
       <c r="W738" s="7"/>
     </row>
     <row r="739">
-      <c r="A739" s="1"/>
+      <c r="A739" s="2"/>
       <c r="B739" s="7"/>
       <c r="C739" s="7"/>
       <c r="D739" s="7"/>
@@ -19029,7 +19044,7 @@
       <c r="W739" s="7"/>
     </row>
     <row r="740">
-      <c r="A740" s="1"/>
+      <c r="A740" s="2"/>
       <c r="B740" s="7"/>
       <c r="C740" s="7"/>
       <c r="D740" s="7"/>
@@ -19054,7 +19069,7 @@
       <c r="W740" s="7"/>
     </row>
     <row r="741">
-      <c r="A741" s="1"/>
+      <c r="A741" s="2"/>
       <c r="B741" s="7"/>
       <c r="C741" s="7"/>
       <c r="D741" s="7"/>
@@ -19079,7 +19094,7 @@
       <c r="W741" s="7"/>
     </row>
     <row r="742">
-      <c r="A742" s="1"/>
+      <c r="A742" s="2"/>
       <c r="B742" s="7"/>
       <c r="C742" s="7"/>
       <c r="D742" s="7"/>
@@ -19104,7 +19119,7 @@
       <c r="W742" s="7"/>
     </row>
     <row r="743">
-      <c r="A743" s="1"/>
+      <c r="A743" s="2"/>
       <c r="B743" s="7"/>
       <c r="C743" s="7"/>
       <c r="D743" s="7"/>
@@ -19129,7 +19144,7 @@
       <c r="W743" s="7"/>
     </row>
     <row r="744">
-      <c r="A744" s="1"/>
+      <c r="A744" s="2"/>
       <c r="B744" s="7"/>
       <c r="C744" s="7"/>
       <c r="D744" s="7"/>
@@ -19154,7 +19169,7 @@
       <c r="W744" s="7"/>
     </row>
     <row r="745">
-      <c r="A745" s="1"/>
+      <c r="A745" s="2"/>
       <c r="B745" s="7"/>
       <c r="C745" s="7"/>
       <c r="D745" s="7"/>
@@ -19179,7 +19194,7 @@
       <c r="W745" s="7"/>
     </row>
     <row r="746">
-      <c r="A746" s="1"/>
+      <c r="A746" s="2"/>
       <c r="B746" s="7"/>
       <c r="C746" s="7"/>
       <c r="D746" s="7"/>
@@ -19204,7 +19219,7 @@
       <c r="W746" s="7"/>
     </row>
     <row r="747">
-      <c r="A747" s="1"/>
+      <c r="A747" s="2"/>
       <c r="B747" s="7"/>
       <c r="C747" s="7"/>
       <c r="D747" s="7"/>
@@ -19229,7 +19244,7 @@
       <c r="W747" s="7"/>
     </row>
     <row r="748">
-      <c r="A748" s="1"/>
+      <c r="A748" s="2"/>
       <c r="B748" s="7"/>
       <c r="C748" s="7"/>
       <c r="D748" s="7"/>
@@ -19254,7 +19269,7 @@
       <c r="W748" s="7"/>
     </row>
     <row r="749">
-      <c r="A749" s="1"/>
+      <c r="A749" s="2"/>
       <c r="B749" s="7"/>
       <c r="C749" s="7"/>
       <c r="D749" s="7"/>
@@ -19279,7 +19294,7 @@
       <c r="W749" s="7"/>
     </row>
     <row r="750">
-      <c r="A750" s="1"/>
+      <c r="A750" s="2"/>
       <c r="B750" s="7"/>
       <c r="C750" s="7"/>
       <c r="D750" s="7"/>
@@ -19304,7 +19319,7 @@
       <c r="W750" s="7"/>
     </row>
     <row r="751">
-      <c r="A751" s="1"/>
+      <c r="A751" s="2"/>
       <c r="B751" s="7"/>
       <c r="C751" s="7"/>
       <c r="D751" s="7"/>
@@ -19329,7 +19344,7 @@
       <c r="W751" s="7"/>
     </row>
     <row r="752">
-      <c r="A752" s="1"/>
+      <c r="A752" s="2"/>
       <c r="B752" s="7"/>
       <c r="C752" s="7"/>
       <c r="D752" s="7"/>
@@ -19354,7 +19369,7 @@
       <c r="W752" s="7"/>
     </row>
     <row r="753">
-      <c r="A753" s="1"/>
+      <c r="A753" s="2"/>
       <c r="B753" s="7"/>
       <c r="C753" s="7"/>
       <c r="D753" s="7"/>
@@ -19379,7 +19394,7 @@
       <c r="W753" s="7"/>
     </row>
     <row r="754">
-      <c r="A754" s="1"/>
+      <c r="A754" s="2"/>
       <c r="B754" s="7"/>
       <c r="C754" s="7"/>
       <c r="D754" s="7"/>
@@ -19404,7 +19419,7 @@
       <c r="W754" s="7"/>
     </row>
     <row r="755">
-      <c r="A755" s="1"/>
+      <c r="A755" s="2"/>
       <c r="B755" s="7"/>
       <c r="C755" s="7"/>
       <c r="D755" s="7"/>
@@ -19429,7 +19444,7 @@
       <c r="W755" s="7"/>
     </row>
     <row r="756">
-      <c r="A756" s="1"/>
+      <c r="A756" s="2"/>
       <c r="B756" s="7"/>
       <c r="C756" s="7"/>
       <c r="D756" s="7"/>
@@ -19454,7 +19469,7 @@
       <c r="W756" s="7"/>
     </row>
     <row r="757">
-      <c r="A757" s="1"/>
+      <c r="A757" s="2"/>
       <c r="B757" s="7"/>
       <c r="C757" s="7"/>
       <c r="D757" s="7"/>
@@ -19479,7 +19494,7 @@
       <c r="W757" s="7"/>
     </row>
     <row r="758">
-      <c r="A758" s="1"/>
+      <c r="A758" s="2"/>
       <c r="B758" s="7"/>
       <c r="C758" s="7"/>
       <c r="D758" s="7"/>
@@ -19504,7 +19519,7 @@
       <c r="W758" s="7"/>
     </row>
     <row r="759">
-      <c r="A759" s="1"/>
+      <c r="A759" s="2"/>
       <c r="B759" s="7"/>
       <c r="C759" s="7"/>
       <c r="D759" s="7"/>
@@ -19529,7 +19544,7 @@
       <c r="W759" s="7"/>
     </row>
     <row r="760">
-      <c r="A760" s="1"/>
+      <c r="A760" s="2"/>
       <c r="B760" s="7"/>
       <c r="C760" s="7"/>
       <c r="D760" s="7"/>
@@ -19554,7 +19569,7 @@
       <c r="W760" s="7"/>
     </row>
     <row r="761">
-      <c r="A761" s="1"/>
+      <c r="A761" s="2"/>
       <c r="B761" s="7"/>
       <c r="C761" s="7"/>
       <c r="D761" s="7"/>
@@ -19579,7 +19594,7 @@
       <c r="W761" s="7"/>
     </row>
     <row r="762">
-      <c r="A762" s="1"/>
+      <c r="A762" s="2"/>
       <c r="B762" s="7"/>
       <c r="C762" s="7"/>
       <c r="D762" s="7"/>
@@ -19604,7 +19619,7 @@
       <c r="W762" s="7"/>
     </row>
     <row r="763">
-      <c r="A763" s="1"/>
+      <c r="A763" s="2"/>
       <c r="B763" s="7"/>
       <c r="C763" s="7"/>
       <c r="D763" s="7"/>
@@ -19629,7 +19644,7 @@
       <c r="W763" s="7"/>
     </row>
     <row r="764">
-      <c r="A764" s="1"/>
+      <c r="A764" s="2"/>
       <c r="B764" s="7"/>
       <c r="C764" s="7"/>
       <c r="D764" s="7"/>
@@ -19654,7 +19669,7 @@
       <c r="W764" s="7"/>
     </row>
     <row r="765">
-      <c r="A765" s="1"/>
+      <c r="A765" s="2"/>
       <c r="B765" s="7"/>
       <c r="C765" s="7"/>
       <c r="D765" s="7"/>
@@ -19679,7 +19694,7 @@
       <c r="W765" s="7"/>
     </row>
     <row r="766">
-      <c r="A766" s="1"/>
+      <c r="A766" s="2"/>
       <c r="B766" s="7"/>
       <c r="C766" s="7"/>
       <c r="D766" s="7"/>
@@ -19704,7 +19719,7 @@
       <c r="W766" s="7"/>
     </row>
     <row r="767">
-      <c r="A767" s="1"/>
+      <c r="A767" s="2"/>
       <c r="B767" s="7"/>
       <c r="C767" s="7"/>
       <c r="D767" s="7"/>
@@ -19729,7 +19744,7 @@
       <c r="W767" s="7"/>
     </row>
     <row r="768">
-      <c r="A768" s="1"/>
+      <c r="A768" s="2"/>
       <c r="B768" s="7"/>
       <c r="C768" s="7"/>
       <c r="D768" s="7"/>
@@ -19754,7 +19769,7 @@
       <c r="W768" s="7"/>
     </row>
     <row r="769">
-      <c r="A769" s="1"/>
+      <c r="A769" s="2"/>
       <c r="B769" s="7"/>
       <c r="C769" s="7"/>
       <c r="D769" s="7"/>
@@ -19779,7 +19794,7 @@
       <c r="W769" s="7"/>
     </row>
     <row r="770">
-      <c r="A770" s="1"/>
+      <c r="A770" s="2"/>
       <c r="B770" s="7"/>
       <c r="C770" s="7"/>
       <c r="D770" s="7"/>
@@ -19804,7 +19819,7 @@
       <c r="W770" s="7"/>
     </row>
     <row r="771">
-      <c r="A771" s="1"/>
+      <c r="A771" s="2"/>
       <c r="B771" s="7"/>
       <c r="C771" s="7"/>
       <c r="D771" s="7"/>
@@ -19829,7 +19844,7 @@
       <c r="W771" s="7"/>
     </row>
     <row r="772">
-      <c r="A772" s="1"/>
+      <c r="A772" s="2"/>
       <c r="B772" s="7"/>
       <c r="C772" s="7"/>
       <c r="D772" s="7"/>
@@ -19854,7 +19869,7 @@
       <c r="W772" s="7"/>
     </row>
     <row r="773">
-      <c r="A773" s="1"/>
+      <c r="A773" s="2"/>
       <c r="B773" s="7"/>
       <c r="C773" s="7"/>
       <c r="D773" s="7"/>
@@ -19879,7 +19894,7 @@
       <c r="W773" s="7"/>
     </row>
     <row r="774">
-      <c r="A774" s="1"/>
+      <c r="A774" s="2"/>
       <c r="B774" s="7"/>
       <c r="C774" s="7"/>
       <c r="D774" s="7"/>
@@ -19904,7 +19919,7 @@
       <c r="W774" s="7"/>
     </row>
     <row r="775">
-      <c r="A775" s="1"/>
+      <c r="A775" s="2"/>
       <c r="B775" s="7"/>
       <c r="C775" s="7"/>
       <c r="D775" s="7"/>
@@ -19929,7 +19944,7 @@
       <c r="W775" s="7"/>
     </row>
     <row r="776">
-      <c r="A776" s="1"/>
+      <c r="A776" s="2"/>
       <c r="B776" s="7"/>
       <c r="C776" s="7"/>
       <c r="D776" s="7"/>
@@ -19954,7 +19969,7 @@
       <c r="W776" s="7"/>
     </row>
     <row r="777">
-      <c r="A777" s="1"/>
+      <c r="A777" s="2"/>
       <c r="B777" s="7"/>
       <c r="C777" s="7"/>
       <c r="D777" s="7"/>
@@ -19979,7 +19994,7 @@
       <c r="W777" s="7"/>
     </row>
     <row r="778">
-      <c r="A778" s="1"/>
+      <c r="A778" s="2"/>
       <c r="B778" s="7"/>
       <c r="C778" s="7"/>
       <c r="D778" s="7"/>
@@ -20004,7 +20019,7 @@
       <c r="W778" s="7"/>
     </row>
     <row r="779">
-      <c r="A779" s="1"/>
+      <c r="A779" s="2"/>
       <c r="B779" s="7"/>
       <c r="C779" s="7"/>
       <c r="D779" s="7"/>
@@ -20029,7 +20044,7 @@
       <c r="W779" s="7"/>
     </row>
     <row r="780">
-      <c r="A780" s="1"/>
+      <c r="A780" s="2"/>
       <c r="B780" s="7"/>
       <c r="C780" s="7"/>
       <c r="D780" s="7"/>
@@ -20054,7 +20069,7 @@
       <c r="W780" s="7"/>
     </row>
     <row r="781">
-      <c r="A781" s="1"/>
+      <c r="A781" s="2"/>
       <c r="B781" s="7"/>
       <c r="C781" s="7"/>
       <c r="D781" s="7"/>
@@ -20079,7 +20094,7 @@
       <c r="W781" s="7"/>
     </row>
     <row r="782">
-      <c r="A782" s="1"/>
+      <c r="A782" s="2"/>
       <c r="B782" s="7"/>
       <c r="C782" s="7"/>
       <c r="D782" s="7"/>
@@ -20104,7 +20119,7 @@
       <c r="W782" s="7"/>
     </row>
     <row r="783">
-      <c r="A783" s="1"/>
+      <c r="A783" s="2"/>
       <c r="B783" s="7"/>
       <c r="C783" s="7"/>
       <c r="D783" s="7"/>
@@ -20129,7 +20144,7 @@
       <c r="W783" s="7"/>
     </row>
     <row r="784">
-      <c r="A784" s="1"/>
+      <c r="A784" s="2"/>
       <c r="B784" s="7"/>
       <c r="C784" s="7"/>
       <c r="D784" s="7"/>
@@ -20154,7 +20169,7 @@
       <c r="W784" s="7"/>
     </row>
     <row r="785">
-      <c r="A785" s="1"/>
+      <c r="A785" s="2"/>
       <c r="B785" s="7"/>
       <c r="C785" s="7"/>
       <c r="D785" s="7"/>
@@ -20179,7 +20194,7 @@
       <c r="W785" s="7"/>
     </row>
     <row r="786">
-      <c r="A786" s="1"/>
+      <c r="A786" s="2"/>
       <c r="B786" s="7"/>
       <c r="C786" s="7"/>
       <c r="D786" s="7"/>
@@ -20204,7 +20219,7 @@
       <c r="W786" s="7"/>
     </row>
     <row r="787">
-      <c r="A787" s="1"/>
+      <c r="A787" s="2"/>
       <c r="B787" s="7"/>
       <c r="C787" s="7"/>
       <c r="D787" s="7"/>
@@ -20229,7 +20244,7 @@
       <c r="W787" s="7"/>
     </row>
     <row r="788">
-      <c r="A788" s="1"/>
+      <c r="A788" s="2"/>
       <c r="B788" s="7"/>
       <c r="C788" s="7"/>
       <c r="D788" s="7"/>
@@ -20254,7 +20269,7 @@
       <c r="W788" s="7"/>
     </row>
     <row r="789">
-      <c r="A789" s="1"/>
+      <c r="A789" s="2"/>
       <c r="B789" s="7"/>
       <c r="C789" s="7"/>
       <c r="D789" s="7"/>
@@ -20279,7 +20294,7 @@
       <c r="W789" s="7"/>
     </row>
     <row r="790">
-      <c r="A790" s="1"/>
+      <c r="A790" s="2"/>
       <c r="B790" s="7"/>
       <c r="C790" s="7"/>
       <c r="D790" s="7"/>
@@ -20304,7 +20319,7 @@
       <c r="W790" s="7"/>
     </row>
     <row r="791">
-      <c r="A791" s="1"/>
+      <c r="A791" s="2"/>
       <c r="B791" s="7"/>
       <c r="C791" s="7"/>
       <c r="D791" s="7"/>
@@ -20329,7 +20344,7 @@
       <c r="W791" s="7"/>
     </row>
     <row r="792">
-      <c r="A792" s="1"/>
+      <c r="A792" s="2"/>
       <c r="B792" s="7"/>
       <c r="C792" s="7"/>
       <c r="D792" s="7"/>
@@ -20354,7 +20369,7 @@
       <c r="W792" s="7"/>
     </row>
     <row r="793">
-      <c r="A793" s="1"/>
+      <c r="A793" s="2"/>
       <c r="B793" s="7"/>
       <c r="C793" s="7"/>
       <c r="D793" s="7"/>
@@ -20379,7 +20394,7 @@
       <c r="W793" s="7"/>
     </row>
     <row r="794">
-      <c r="A794" s="1"/>
+      <c r="A794" s="2"/>
       <c r="B794" s="7"/>
       <c r="C794" s="7"/>
       <c r="D794" s="7"/>
@@ -20404,7 +20419,7 @@
       <c r="W794" s="7"/>
     </row>
     <row r="795">
-      <c r="A795" s="1"/>
+      <c r="A795" s="2"/>
       <c r="B795" s="7"/>
       <c r="C795" s="7"/>
       <c r="D795" s="7"/>
@@ -20429,7 +20444,7 @@
       <c r="W795" s="7"/>
     </row>
     <row r="796">
-      <c r="A796" s="1"/>
+      <c r="A796" s="2"/>
       <c r="B796" s="7"/>
       <c r="C796" s="7"/>
       <c r="D796" s="7"/>
@@ -20454,7 +20469,7 @@
       <c r="W796" s="7"/>
     </row>
     <row r="797">
-      <c r="A797" s="1"/>
+      <c r="A797" s="2"/>
       <c r="B797" s="7"/>
       <c r="C797" s="7"/>
       <c r="D797" s="7"/>
@@ -20479,7 +20494,7 @@
       <c r="W797" s="7"/>
     </row>
     <row r="798">
-      <c r="A798" s="1"/>
+      <c r="A798" s="2"/>
       <c r="B798" s="7"/>
       <c r="C798" s="7"/>
       <c r="D798" s="7"/>
@@ -20504,7 +20519,7 @@
       <c r="W798" s="7"/>
     </row>
     <row r="799">
-      <c r="A799" s="1"/>
+      <c r="A799" s="2"/>
       <c r="B799" s="7"/>
       <c r="C799" s="7"/>
       <c r="D799" s="7"/>
@@ -20529,7 +20544,7 @@
       <c r="W799" s="7"/>
     </row>
     <row r="800">
-      <c r="A800" s="1"/>
+      <c r="A800" s="2"/>
       <c r="B800" s="7"/>
       <c r="C800" s="7"/>
       <c r="D800" s="7"/>
@@ -20554,7 +20569,7 @@
       <c r="W800" s="7"/>
     </row>
     <row r="801">
-      <c r="A801" s="1"/>
+      <c r="A801" s="2"/>
       <c r="B801" s="7"/>
       <c r="C801" s="7"/>
       <c r="D801" s="7"/>
@@ -20579,7 +20594,7 @@
       <c r="W801" s="7"/>
     </row>
     <row r="802">
-      <c r="A802" s="1"/>
+      <c r="A802" s="2"/>
       <c r="B802" s="7"/>
       <c r="C802" s="7"/>
       <c r="D802" s="7"/>
@@ -20604,7 +20619,7 @@
       <c r="W802" s="7"/>
     </row>
     <row r="803">
-      <c r="A803" s="1"/>
+      <c r="A803" s="2"/>
       <c r="B803" s="7"/>
       <c r="C803" s="7"/>
       <c r="D803" s="7"/>
@@ -20629,7 +20644,7 @@
       <c r="W803" s="7"/>
     </row>
     <row r="804">
-      <c r="A804" s="1"/>
+      <c r="A804" s="2"/>
       <c r="B804" s="7"/>
       <c r="C804" s="7"/>
       <c r="D804" s="7"/>
@@ -20654,7 +20669,7 @@
       <c r="W804" s="7"/>
     </row>
     <row r="805">
-      <c r="A805" s="1"/>
+      <c r="A805" s="2"/>
       <c r="B805" s="7"/>
       <c r="C805" s="7"/>
       <c r="D805" s="7"/>
@@ -20679,7 +20694,7 @@
       <c r="W805" s="7"/>
     </row>
     <row r="806">
-      <c r="A806" s="1"/>
+      <c r="A806" s="2"/>
       <c r="B806" s="7"/>
       <c r="C806" s="7"/>
       <c r="D806" s="7"/>
@@ -20704,7 +20719,7 @@
       <c r="W806" s="7"/>
     </row>
     <row r="807">
-      <c r="A807" s="1"/>
+      <c r="A807" s="2"/>
       <c r="B807" s="7"/>
       <c r="C807" s="7"/>
       <c r="D807" s="7"/>
@@ -20729,7 +20744,7 @@
       <c r="W807" s="7"/>
     </row>
     <row r="808">
-      <c r="A808" s="1"/>
+      <c r="A808" s="2"/>
       <c r="B808" s="7"/>
       <c r="C808" s="7"/>
       <c r="D808" s="7"/>
@@ -20754,7 +20769,7 @@
       <c r="W808" s="7"/>
     </row>
     <row r="809">
-      <c r="A809" s="1"/>
+      <c r="A809" s="2"/>
       <c r="B809" s="7"/>
       <c r="C809" s="7"/>
       <c r="D809" s="7"/>
@@ -20779,7 +20794,7 @@
       <c r="W809" s="7"/>
     </row>
     <row r="810">
-      <c r="A810" s="1"/>
+      <c r="A810" s="2"/>
       <c r="B810" s="7"/>
       <c r="C810" s="7"/>
       <c r="D810" s="7"/>
@@ -20804,7 +20819,7 @@
       <c r="W810" s="7"/>
     </row>
     <row r="811">
-      <c r="A811" s="1"/>
+      <c r="A811" s="2"/>
       <c r="B811" s="7"/>
       <c r="C811" s="7"/>
       <c r="D811" s="7"/>
@@ -20829,7 +20844,7 @@
       <c r="W811" s="7"/>
     </row>
     <row r="812">
-      <c r="A812" s="1"/>
+      <c r="A812" s="2"/>
       <c r="B812" s="7"/>
       <c r="C812" s="7"/>
       <c r="D812" s="7"/>
@@ -20854,7 +20869,7 @@
       <c r="W812" s="7"/>
     </row>
     <row r="813">
-      <c r="A813" s="1"/>
+      <c r="A813" s="2"/>
       <c r="B813" s="7"/>
       <c r="C813" s="7"/>
       <c r="D813" s="7"/>
@@ -20879,7 +20894,7 @@
       <c r="W813" s="7"/>
     </row>
     <row r="814">
-      <c r="A814" s="1"/>
+      <c r="A814" s="2"/>
       <c r="B814" s="7"/>
       <c r="C814" s="7"/>
       <c r="D814" s="7"/>
@@ -20904,7 +20919,7 @@
       <c r="W814" s="7"/>
     </row>
     <row r="815">
-      <c r="A815" s="1"/>
+      <c r="A815" s="2"/>
       <c r="B815" s="7"/>
       <c r="C815" s="7"/>
       <c r="D815" s="7"/>
@@ -20929,7 +20944,7 @@
       <c r="W815" s="7"/>
     </row>
     <row r="816">
-      <c r="A816" s="1"/>
+      <c r="A816" s="2"/>
       <c r="B816" s="7"/>
       <c r="C816" s="7"/>
       <c r="D816" s="7"/>
@@ -20954,7 +20969,7 @@
       <c r="W816" s="7"/>
     </row>
     <row r="817">
-      <c r="A817" s="1"/>
+      <c r="A817" s="2"/>
       <c r="B817" s="7"/>
       <c r="C817" s="7"/>
       <c r="D817" s="7"/>
@@ -20979,7 +20994,7 @@
       <c r="W817" s="7"/>
     </row>
     <row r="818">
-      <c r="A818" s="1"/>
+      <c r="A818" s="2"/>
       <c r="B818" s="7"/>
       <c r="C818" s="7"/>
       <c r="D818" s="7"/>
@@ -21004,7 +21019,7 @@
       <c r="W818" s="7"/>
     </row>
     <row r="819">
-      <c r="A819" s="1"/>
+      <c r="A819" s="2"/>
       <c r="B819" s="7"/>
       <c r="C819" s="7"/>
       <c r="D819" s="7"/>
@@ -21029,7 +21044,7 @@
       <c r="W819" s="7"/>
     </row>
     <row r="820">
-      <c r="A820" s="1"/>
+      <c r="A820" s="2"/>
       <c r="B820" s="7"/>
       <c r="C820" s="7"/>
       <c r="D820" s="7"/>
@@ -21054,7 +21069,7 @@
       <c r="W820" s="7"/>
     </row>
     <row r="821">
-      <c r="A821" s="1"/>
+      <c r="A821" s="2"/>
       <c r="B821" s="7"/>
       <c r="C821" s="7"/>
       <c r="D821" s="7"/>
@@ -21079,7 +21094,7 @@
       <c r="W821" s="7"/>
     </row>
     <row r="822">
-      <c r="A822" s="1"/>
+      <c r="A822" s="2"/>
       <c r="B822" s="7"/>
       <c r="C822" s="7"/>
       <c r="D822" s="7"/>
@@ -21104,7 +21119,7 @@
       <c r="W822" s="7"/>
     </row>
     <row r="823">
-      <c r="A823" s="1"/>
+      <c r="A823" s="2"/>
       <c r="B823" s="7"/>
       <c r="C823" s="7"/>
       <c r="D823" s="7"/>
@@ -21129,7 +21144,7 @@
       <c r="W823" s="7"/>
     </row>
     <row r="824">
-      <c r="A824" s="1"/>
+      <c r="A824" s="2"/>
       <c r="B824" s="7"/>
       <c r="C824" s="7"/>
       <c r="D824" s="7"/>
@@ -21154,7 +21169,7 @@
       <c r="W824" s="7"/>
     </row>
     <row r="825">
-      <c r="A825" s="1"/>
+      <c r="A825" s="2"/>
       <c r="B825" s="7"/>
       <c r="C825" s="7"/>
       <c r="D825" s="7"/>
@@ -21179,7 +21194,7 @@
       <c r="W825" s="7"/>
     </row>
     <row r="826">
-      <c r="A826" s="1"/>
+      <c r="A826" s="2"/>
       <c r="B826" s="7"/>
       <c r="C826" s="7"/>
       <c r="D826" s="7"/>
@@ -21204,7 +21219,7 @@
       <c r="W826" s="7"/>
     </row>
     <row r="827">
-      <c r="A827" s="1"/>
+      <c r="A827" s="2"/>
       <c r="B827" s="7"/>
       <c r="C827" s="7"/>
       <c r="D827" s="7"/>
@@ -21229,7 +21244,7 @@
       <c r="W827" s="7"/>
     </row>
     <row r="828">
-      <c r="A828" s="1"/>
+      <c r="A828" s="2"/>
       <c r="B828" s="7"/>
       <c r="C828" s="7"/>
       <c r="D828" s="7"/>
@@ -21254,7 +21269,7 @@
       <c r="W828" s="7"/>
     </row>
     <row r="829">
-      <c r="A829" s="1"/>
+      <c r="A829" s="2"/>
       <c r="B829" s="7"/>
       <c r="C829" s="7"/>
       <c r="D829" s="7"/>
@@ -21279,7 +21294,7 @@
       <c r="W829" s="7"/>
     </row>
     <row r="830">
-      <c r="A830" s="1"/>
+      <c r="A830" s="2"/>
       <c r="B830" s="7"/>
       <c r="C830" s="7"/>
       <c r="D830" s="7"/>
@@ -21304,7 +21319,7 @@
       <c r="W830" s="7"/>
     </row>
     <row r="831">
-      <c r="A831" s="1"/>
+      <c r="A831" s="2"/>
       <c r="B831" s="7"/>
       <c r="C831" s="7"/>
       <c r="D831" s="7"/>
@@ -21329,7 +21344,7 @@
       <c r="W831" s="7"/>
     </row>
     <row r="832">
-      <c r="A832" s="1"/>
+      <c r="A832" s="2"/>
       <c r="B832" s="7"/>
       <c r="C832" s="7"/>
       <c r="D832" s="7"/>
@@ -21354,7 +21369,7 @@
       <c r="W832" s="7"/>
     </row>
     <row r="833">
-      <c r="A833" s="1"/>
+      <c r="A833" s="2"/>
       <c r="B833" s="7"/>
       <c r="C833" s="7"/>
       <c r="D833" s="7"/>
@@ -21379,7 +21394,7 @@
       <c r="W833" s="7"/>
     </row>
     <row r="834">
-      <c r="A834" s="1"/>
+      <c r="A834" s="2"/>
       <c r="B834" s="7"/>
       <c r="C834" s="7"/>
       <c r="D834" s="7"/>
@@ -21404,7 +21419,7 @@
       <c r="W834" s="7"/>
     </row>
     <row r="835">
-      <c r="A835" s="1"/>
+      <c r="A835" s="2"/>
       <c r="B835" s="7"/>
       <c r="C835" s="7"/>
       <c r="D835" s="7"/>
@@ -21429,7 +21444,7 @@
       <c r="W835" s="7"/>
     </row>
     <row r="836">
-      <c r="A836" s="1"/>
+      <c r="A836" s="2"/>
       <c r="B836" s="7"/>
       <c r="C836" s="7"/>
       <c r="D836" s="7"/>
@@ -21454,7 +21469,7 @@
       <c r="W836" s="7"/>
     </row>
     <row r="837">
-      <c r="A837" s="1"/>
+      <c r="A837" s="2"/>
       <c r="B837" s="7"/>
       <c r="C837" s="7"/>
       <c r="D837" s="7"/>
@@ -21479,7 +21494,7 @@
       <c r="W837" s="7"/>
     </row>
     <row r="838">
-      <c r="A838" s="1"/>
+      <c r="A838" s="2"/>
       <c r="B838" s="7"/>
       <c r="C838" s="7"/>
       <c r="D838" s="7"/>
@@ -21504,7 +21519,7 @@
       <c r="W838" s="7"/>
     </row>
     <row r="839">
-      <c r="A839" s="1"/>
+      <c r="A839" s="2"/>
       <c r="B839" s="7"/>
       <c r="C839" s="7"/>
       <c r="D839" s="7"/>
@@ -21529,7 +21544,7 @@
       <c r="W839" s="7"/>
     </row>
     <row r="840">
-      <c r="A840" s="1"/>
+      <c r="A840" s="2"/>
       <c r="B840" s="7"/>
       <c r="C840" s="7"/>
       <c r="D840" s="7"/>
@@ -21554,7 +21569,7 @@
       <c r="W840" s="7"/>
     </row>
     <row r="841">
-      <c r="A841" s="1"/>
+      <c r="A841" s="2"/>
       <c r="B841" s="7"/>
       <c r="C841" s="7"/>
       <c r="D841" s="7"/>
@@ -21579,7 +21594,7 @@
       <c r="W841" s="7"/>
     </row>
     <row r="842">
-      <c r="A842" s="1"/>
+      <c r="A842" s="2"/>
       <c r="B842" s="7"/>
       <c r="C842" s="7"/>
       <c r="D842" s="7"/>
@@ -21604,7 +21619,7 @@
       <c r="W842" s="7"/>
     </row>
     <row r="843">
-      <c r="A843" s="1"/>
+      <c r="A843" s="2"/>
       <c r="B843" s="7"/>
       <c r="C843" s="7"/>
       <c r="D843" s="7"/>
@@ -21629,7 +21644,7 @@
       <c r="W843" s="7"/>
     </row>
     <row r="844">
-      <c r="A844" s="1"/>
+      <c r="A844" s="2"/>
       <c r="B844" s="7"/>
       <c r="C844" s="7"/>
       <c r="D844" s="7"/>
@@ -21654,7 +21669,7 @@
       <c r="W844" s="7"/>
     </row>
     <row r="845">
-      <c r="A845" s="1"/>
+      <c r="A845" s="2"/>
       <c r="B845" s="7"/>
       <c r="C845" s="7"/>
       <c r="D845" s="7"/>
@@ -21679,7 +21694,7 @@
       <c r="W845" s="7"/>
     </row>
     <row r="846">
-      <c r="A846" s="1"/>
+      <c r="A846" s="2"/>
       <c r="B846" s="7"/>
       <c r="C846" s="7"/>
       <c r="D846" s="7"/>
@@ -21704,7 +21719,7 @@
       <c r="W846" s="7"/>
     </row>
     <row r="847">
-      <c r="A847" s="1"/>
+      <c r="A847" s="2"/>
       <c r="B847" s="7"/>
       <c r="C847" s="7"/>
       <c r="D847" s="7"/>
@@ -21729,7 +21744,7 @@
       <c r="W847" s="7"/>
     </row>
     <row r="848">
-      <c r="A848" s="1"/>
+      <c r="A848" s="2"/>
       <c r="B848" s="7"/>
       <c r="C848" s="7"/>
       <c r="D848" s="7"/>
@@ -21754,7 +21769,7 @@
       <c r="W848" s="7"/>
     </row>
     <row r="849">
-      <c r="A849" s="1"/>
+      <c r="A849" s="2"/>
       <c r="B849" s="7"/>
       <c r="C849" s="7"/>
       <c r="D849" s="7"/>
@@ -21779,7 +21794,7 @@
       <c r="W849" s="7"/>
     </row>
     <row r="850">
-      <c r="A850" s="1"/>
+      <c r="A850" s="2"/>
       <c r="B850" s="7"/>
       <c r="C850" s="7"/>
       <c r="D850" s="7"/>
@@ -21804,7 +21819,7 @@
       <c r="W850" s="7"/>
     </row>
     <row r="851">
-      <c r="A851" s="1"/>
+      <c r="A851" s="2"/>
       <c r="B851" s="7"/>
       <c r="C851" s="7"/>
       <c r="D851" s="7"/>
@@ -21829,7 +21844,7 @@
       <c r="W851" s="7"/>
     </row>
     <row r="852">
-      <c r="A852" s="1"/>
+      <c r="A852" s="2"/>
       <c r="B852" s="7"/>
       <c r="C852" s="7"/>
       <c r="D852" s="7"/>
@@ -21854,7 +21869,7 @@
       <c r="W852" s="7"/>
     </row>
     <row r="853">
-      <c r="A853" s="1"/>
+      <c r="A853" s="2"/>
       <c r="B853" s="7"/>
       <c r="C853" s="7"/>
       <c r="D853" s="7"/>
@@ -21879,7 +21894,7 @@
       <c r="W853" s="7"/>
     </row>
     <row r="854">
-      <c r="A854" s="1"/>
+      <c r="A854" s="2"/>
       <c r="B854" s="7"/>
       <c r="C854" s="7"/>
       <c r="D854" s="7"/>
@@ -21904,7 +21919,7 @@
       <c r="W854" s="7"/>
     </row>
     <row r="855">
-      <c r="A855" s="1"/>
+      <c r="A855" s="2"/>
       <c r="B855" s="7"/>
       <c r="C855" s="7"/>
       <c r="D855" s="7"/>
@@ -21929,7 +21944,7 @@
       <c r="W855" s="7"/>
     </row>
     <row r="856">
-      <c r="A856" s="1"/>
+      <c r="A856" s="2"/>
       <c r="B856" s="7"/>
       <c r="C856" s="7"/>
       <c r="D856" s="7"/>
@@ -21954,7 +21969,7 @@
       <c r="W856" s="7"/>
     </row>
     <row r="857">
-      <c r="A857" s="1"/>
+      <c r="A857" s="2"/>
       <c r="B857" s="7"/>
       <c r="C857" s="7"/>
       <c r="D857" s="7"/>
@@ -21979,7 +21994,7 @@
       <c r="W857" s="7"/>
     </row>
     <row r="858">
-      <c r="A858" s="1"/>
+      <c r="A858" s="2"/>
       <c r="B858" s="7"/>
       <c r="C858" s="7"/>
       <c r="D858" s="7"/>
@@ -22004,7 +22019,7 @@
       <c r="W858" s="7"/>
     </row>
     <row r="859">
-      <c r="A859" s="1"/>
+      <c r="A859" s="2"/>
       <c r="B859" s="7"/>
       <c r="C859" s="7"/>
       <c r="D859" s="7"/>
@@ -22029,7 +22044,7 @@
       <c r="W859" s="7"/>
     </row>
     <row r="860">
-      <c r="A860" s="1"/>
+      <c r="A860" s="2"/>
       <c r="B860" s="7"/>
       <c r="C860" s="7"/>
       <c r="D860" s="7"/>
@@ -22054,7 +22069,7 @@
       <c r="W860" s="7"/>
     </row>
     <row r="861">
-      <c r="A861" s="1"/>
+      <c r="A861" s="2"/>
       <c r="B861" s="7"/>
       <c r="C861" s="7"/>
       <c r="D861" s="7"/>
@@ -22079,7 +22094,7 @@
       <c r="W861" s="7"/>
     </row>
     <row r="862">
-      <c r="A862" s="1"/>
+      <c r="A862" s="2"/>
       <c r="B862" s="7"/>
       <c r="C862" s="7"/>
       <c r="D862" s="7"/>
@@ -22104,7 +22119,7 @@
       <c r="W862" s="7"/>
     </row>
     <row r="863">
-      <c r="A863" s="1"/>
+      <c r="A863" s="2"/>
       <c r="B863" s="7"/>
       <c r="C863" s="7"/>
       <c r="D863" s="7"/>
@@ -22129,7 +22144,7 @@
       <c r="W863" s="7"/>
     </row>
     <row r="864">
-      <c r="A864" s="1"/>
+      <c r="A864" s="2"/>
       <c r="B864" s="7"/>
       <c r="C864" s="7"/>
       <c r="D864" s="7"/>
@@ -22154,7 +22169,7 @@
       <c r="W864" s="7"/>
     </row>
     <row r="865">
-      <c r="A865" s="1"/>
+      <c r="A865" s="2"/>
       <c r="B865" s="7"/>
       <c r="C865" s="7"/>
       <c r="D865" s="7"/>
@@ -22179,7 +22194,7 @@
       <c r="W865" s="7"/>
     </row>
     <row r="866">
-      <c r="A866" s="1"/>
+      <c r="A866" s="2"/>
       <c r="B866" s="7"/>
       <c r="C866" s="7"/>
       <c r="D866" s="7"/>
@@ -22204,7 +22219,7 @@
       <c r="W866" s="7"/>
     </row>
     <row r="867">
-      <c r="A867" s="1"/>
+      <c r="A867" s="2"/>
       <c r="B867" s="7"/>
       <c r="C867" s="7"/>
       <c r="D867" s="7"/>
@@ -22229,7 +22244,7 @@
       <c r="W867" s="7"/>
     </row>
     <row r="868">
-      <c r="A868" s="1"/>
+      <c r="A868" s="2"/>
       <c r="B868" s="7"/>
       <c r="C868" s="7"/>
       <c r="D868" s="7"/>
@@ -22254,7 +22269,7 @@
       <c r="W868" s="7"/>
     </row>
     <row r="869">
-      <c r="A869" s="1"/>
+      <c r="A869" s="2"/>
       <c r="B869" s="7"/>
       <c r="C869" s="7"/>
       <c r="D869" s="7"/>
@@ -22279,7 +22294,7 @@
       <c r="W869" s="7"/>
     </row>
     <row r="870">
-      <c r="A870" s="1"/>
+      <c r="A870" s="2"/>
       <c r="B870" s="7"/>
       <c r="C870" s="7"/>
       <c r="D870" s="7"/>
@@ -22304,7 +22319,7 @@
       <c r="W870" s="7"/>
     </row>
     <row r="871">
-      <c r="A871" s="1"/>
+      <c r="A871" s="2"/>
       <c r="B871" s="7"/>
       <c r="C871" s="7"/>
       <c r="D871" s="7"/>
@@ -22329,7 +22344,7 @@
       <c r="W871" s="7"/>
     </row>
     <row r="872">
-      <c r="A872" s="1"/>
+      <c r="A872" s="2"/>
       <c r="B872" s="7"/>
       <c r="C872" s="7"/>
       <c r="D872" s="7"/>
@@ -22354,7 +22369,7 @@
       <c r="W872" s="7"/>
     </row>
     <row r="873">
-      <c r="A873" s="1"/>
+      <c r="A873" s="2"/>
       <c r="B873" s="7"/>
       <c r="C873" s="7"/>
       <c r="D873" s="7"/>
@@ -22379,7 +22394,7 @@
       <c r="W873" s="7"/>
     </row>
     <row r="874">
-      <c r="A874" s="1"/>
+      <c r="A874" s="2"/>
       <c r="B874" s="7"/>
       <c r="C874" s="7"/>
       <c r="D874" s="7"/>
@@ -22404,7 +22419,7 @@
       <c r="W874" s="7"/>
     </row>
     <row r="875">
-      <c r="A875" s="1"/>
+      <c r="A875" s="2"/>
       <c r="B875" s="7"/>
       <c r="C875" s="7"/>
       <c r="D875" s="7"/>
@@ -22429,7 +22444,7 @@
       <c r="W875" s="7"/>
     </row>
     <row r="876">
-      <c r="A876" s="1"/>
+      <c r="A876" s="2"/>
       <c r="B876" s="7"/>
       <c r="C876" s="7"/>
       <c r="D876" s="7"/>
@@ -22454,7 +22469,7 @@
       <c r="W876" s="7"/>
     </row>
     <row r="877">
-      <c r="A877" s="1"/>
+      <c r="A877" s="2"/>
       <c r="B877" s="7"/>
       <c r="C877" s="7"/>
       <c r="D877" s="7"/>
@@ -22479,7 +22494,7 @@
       <c r="W877" s="7"/>
     </row>
     <row r="878">
-      <c r="A878" s="1"/>
+      <c r="A878" s="2"/>
       <c r="B878" s="7"/>
       <c r="C878" s="7"/>
       <c r="D878" s="7"/>
@@ -22504,7 +22519,7 @@
       <c r="W878" s="7"/>
     </row>
     <row r="879">
-      <c r="A879" s="1"/>
+      <c r="A879" s="2"/>
       <c r="B879" s="7"/>
       <c r="C879" s="7"/>
       <c r="D879" s="7"/>
@@ -22529,7 +22544,7 @@
       <c r="W879" s="7"/>
     </row>
     <row r="880">
-      <c r="A880" s="1"/>
+      <c r="A880" s="2"/>
       <c r="B880" s="7"/>
       <c r="C880" s="7"/>
       <c r="D880" s="7"/>
@@ -22554,7 +22569,7 @@
       <c r="W880" s="7"/>
     </row>
     <row r="881">
-      <c r="A881" s="1"/>
+      <c r="A881" s="2"/>
       <c r="B881" s="7"/>
       <c r="C881" s="7"/>
       <c r="D881" s="7"/>
@@ -22579,7 +22594,7 @@
       <c r="W881" s="7"/>
     </row>
     <row r="882">
-      <c r="A882" s="1"/>
+      <c r="A882" s="2"/>
       <c r="B882" s="7"/>
       <c r="C882" s="7"/>
       <c r="D882" s="7"/>
@@ -22604,7 +22619,7 @@
       <c r="W882" s="7"/>
     </row>
     <row r="883">
-      <c r="A883" s="1"/>
+      <c r="A883" s="2"/>
       <c r="B883" s="7"/>
       <c r="C883" s="7"/>
       <c r="D883" s="7"/>
@@ -22629,7 +22644,7 @@
       <c r="W883" s="7"/>
     </row>
     <row r="884">
-      <c r="A884" s="1"/>
+      <c r="A884" s="2"/>
       <c r="B884" s="7"/>
       <c r="C884" s="7"/>
       <c r="D884" s="7"/>
@@ -22654,7 +22669,7 @@
       <c r="W884" s="7"/>
     </row>
     <row r="885">
-      <c r="A885" s="1"/>
+      <c r="A885" s="2"/>
       <c r="B885" s="7"/>
       <c r="C885" s="7"/>
       <c r="D885" s="7"/>
@@ -22679,7 +22694,7 @@
       <c r="W885" s="7"/>
     </row>
     <row r="886">
-      <c r="A886" s="1"/>
+      <c r="A886" s="2"/>
       <c r="B886" s="7"/>
       <c r="C886" s="7"/>
       <c r="D886" s="7"/>
@@ -22704,7 +22719,7 @@
       <c r="W886" s="7"/>
     </row>
     <row r="887">
-      <c r="A887" s="1"/>
+      <c r="A887" s="2"/>
       <c r="B887" s="7"/>
       <c r="C887" s="7"/>
       <c r="D887" s="7"/>
@@ -22729,7 +22744,7 @@
       <c r="W887" s="7"/>
     </row>
     <row r="888">
-      <c r="A888" s="1"/>
+      <c r="A888" s="2"/>
       <c r="B888" s="7"/>
       <c r="C888" s="7"/>
       <c r="D888" s="7"/>
@@ -22754,7 +22769,7 @@
       <c r="W888" s="7"/>
     </row>
     <row r="889">
-      <c r="A889" s="1"/>
+      <c r="A889" s="2"/>
       <c r="B889" s="7"/>
       <c r="C889" s="7"/>
       <c r="D889" s="7"/>
@@ -22779,7 +22794,7 @@
       <c r="W889" s="7"/>
     </row>
     <row r="890">
-      <c r="A890" s="1"/>
+      <c r="A890" s="2"/>
       <c r="B890" s="7"/>
       <c r="C890" s="7"/>
       <c r="D890" s="7"/>
@@ -22804,7 +22819,7 @@
       <c r="W890" s="7"/>
     </row>
     <row r="891">
-      <c r="A891" s="1"/>
+      <c r="A891" s="2"/>
       <c r="B891" s="7"/>
       <c r="C891" s="7"/>
       <c r="D891" s="7"/>
@@ -22829,7 +22844,7 @@
       <c r="W891" s="7"/>
     </row>
     <row r="892">
-      <c r="A892" s="1"/>
+      <c r="A892" s="2"/>
       <c r="B892" s="7"/>
       <c r="C892" s="7"/>
       <c r="D892" s="7"/>
@@ -22854,7 +22869,7 @@
       <c r="W892" s="7"/>
     </row>
     <row r="893">
-      <c r="A893" s="1"/>
+      <c r="A893" s="2"/>
       <c r="B893" s="7"/>
       <c r="C893" s="7"/>
       <c r="D893" s="7"/>
@@ -22879,7 +22894,7 @@
       <c r="W893" s="7"/>
     </row>
     <row r="894">
-      <c r="A894" s="1"/>
+      <c r="A894" s="2"/>
       <c r="B894" s="7"/>
       <c r="C894" s="7"/>
       <c r="D894" s="7"/>
@@ -22904,7 +22919,7 @@
       <c r="W894" s="7"/>
     </row>
     <row r="895">
-      <c r="A895" s="1"/>
+      <c r="A895" s="2"/>
       <c r="B895" s="7"/>
       <c r="C895" s="7"/>
       <c r="D895" s="7"/>
@@ -22929,7 +22944,7 @@
       <c r="W895" s="7"/>
     </row>
     <row r="896">
-      <c r="A896" s="1"/>
+      <c r="A896" s="2"/>
       <c r="B896" s="7"/>
       <c r="C896" s="7"/>
       <c r="D896" s="7"/>
@@ -22954,7 +22969,7 @@
       <c r="W896" s="7"/>
     </row>
     <row r="897">
-      <c r="A897" s="1"/>
+      <c r="A897" s="2"/>
       <c r="B897" s="7"/>
       <c r="C897" s="7"/>
       <c r="D897" s="7"/>
@@ -22979,7 +22994,7 @@
       <c r="W897" s="7"/>
     </row>
     <row r="898">
-      <c r="A898" s="1"/>
+      <c r="A898" s="2"/>
       <c r="B898" s="7"/>
       <c r="C898" s="7"/>
       <c r="D898" s="7"/>
@@ -23004,7 +23019,7 @@
       <c r="W898" s="7"/>
     </row>
     <row r="899">
-      <c r="A899" s="1"/>
+      <c r="A899" s="2"/>
       <c r="B899" s="7"/>
       <c r="C899" s="7"/>
       <c r="D899" s="7"/>
@@ -23029,7 +23044,7 @@
       <c r="W899" s="7"/>
     </row>
     <row r="900">
-      <c r="A900" s="1"/>
+      <c r="A900" s="2"/>
       <c r="B900" s="7"/>
       <c r="C900" s="7"/>
       <c r="D900" s="7"/>
@@ -23054,7 +23069,7 @@
       <c r="W900" s="7"/>
     </row>
     <row r="901">
-      <c r="A901" s="1"/>
+      <c r="A901" s="2"/>
       <c r="B901" s="7"/>
       <c r="C901" s="7"/>
       <c r="D901" s="7"/>
@@ -23079,7 +23094,7 @@
       <c r="W901" s="7"/>
     </row>
     <row r="902">
-      <c r="A902" s="1"/>
+      <c r="A902" s="2"/>
       <c r="B902" s="7"/>
       <c r="C902" s="7"/>
       <c r="D902" s="7"/>
@@ -23104,7 +23119,7 @@
       <c r="W902" s="7"/>
     </row>
     <row r="903">
-      <c r="A903" s="1"/>
+      <c r="A903" s="2"/>
       <c r="B903" s="7"/>
       <c r="C903" s="7"/>
       <c r="D903" s="7"/>
@@ -23129,7 +23144,7 @@
       <c r="W903" s="7"/>
     </row>
     <row r="904">
-      <c r="A904" s="1"/>
+      <c r="A904" s="2"/>
       <c r="B904" s="7"/>
       <c r="C904" s="7"/>
       <c r="D904" s="7"/>
@@ -23154,7 +23169,7 @@
       <c r="W904" s="7"/>
     </row>
     <row r="905">
-      <c r="A905" s="1"/>
+      <c r="A905" s="2"/>
       <c r="B905" s="7"/>
       <c r="C905" s="7"/>
       <c r="D905" s="7"/>
@@ -23179,7 +23194,7 @@
       <c r="W905" s="7"/>
     </row>
     <row r="906">
-      <c r="A906" s="1"/>
+      <c r="A906" s="2"/>
       <c r="B906" s="7"/>
       <c r="C906" s="7"/>
       <c r="D906" s="7"/>
@@ -23204,7 +23219,7 @@
       <c r="W906" s="7"/>
     </row>
     <row r="907">
-      <c r="A907" s="1"/>
+      <c r="A907" s="2"/>
       <c r="B907" s="7"/>
       <c r="C907" s="7"/>
       <c r="D907" s="7"/>
@@ -23229,7 +23244,7 @@
       <c r="W907" s="7"/>
     </row>
     <row r="908">
-      <c r="A908" s="1"/>
+      <c r="A908" s="2"/>
       <c r="B908" s="7"/>
       <c r="C908" s="7"/>
       <c r="D908" s="7"/>
@@ -23254,7 +23269,7 @@
       <c r="W908" s="7"/>
     </row>
     <row r="909">
-      <c r="A909" s="1"/>
+      <c r="A909" s="2"/>
       <c r="B909" s="7"/>
       <c r="C909" s="7"/>
       <c r="D909" s="7"/>
@@ -23279,7 +23294,7 @@
       <c r="W909" s="7"/>
     </row>
     <row r="910">
-      <c r="A910" s="1"/>
+      <c r="A910" s="2"/>
       <c r="B910" s="7"/>
       <c r="C910" s="7"/>
       <c r="D910" s="7"/>
@@ -23304,7 +23319,7 @@
       <c r="W910" s="7"/>
     </row>
     <row r="911">
-      <c r="A911" s="1"/>
+      <c r="A911" s="2"/>
       <c r="B911" s="7"/>
       <c r="C911" s="7"/>
       <c r="D911" s="7"/>
@@ -23329,7 +23344,7 @@
       <c r="W911" s="7"/>
     </row>
     <row r="912">
-      <c r="A912" s="1"/>
+      <c r="A912" s="2"/>
       <c r="B912" s="7"/>
       <c r="C912" s="7"/>
       <c r="D912" s="7"/>
@@ -23354,7 +23369,7 @@
       <c r="W912" s="7"/>
     </row>
     <row r="913">
-      <c r="A913" s="1"/>
+      <c r="A913" s="2"/>
       <c r="B913" s="7"/>
       <c r="C913" s="7"/>
       <c r="D913" s="7"/>
@@ -23379,7 +23394,7 @@
       <c r="W913" s="7"/>
     </row>
     <row r="914">
-      <c r="A914" s="1"/>
+      <c r="A914" s="2"/>
       <c r="B914" s="7"/>
       <c r="C914" s="7"/>
       <c r="D914" s="7"/>
@@ -23404,7 +23419,7 @@
       <c r="W914" s="7"/>
     </row>
     <row r="915">
-      <c r="A915" s="1"/>
+      <c r="A915" s="2"/>
       <c r="B915" s="7"/>
       <c r="C915" s="7"/>
       <c r="D915" s="7"/>
@@ -23429,7 +23444,7 @@
       <c r="W915" s="7"/>
     </row>
     <row r="916">
-      <c r="A916" s="1"/>
+      <c r="A916" s="2"/>
       <c r="B916" s="7"/>
       <c r="C916" s="7"/>
       <c r="D916" s="7"/>
@@ -23454,7 +23469,7 @@
       <c r="W916" s="7"/>
     </row>
     <row r="917">
-      <c r="A917" s="1"/>
+      <c r="A917" s="2"/>
       <c r="B917" s="7"/>
       <c r="C917" s="7"/>
       <c r="D917" s="7"/>
@@ -23479,7 +23494,7 @@
       <c r="W917" s="7"/>
     </row>
     <row r="918">
-      <c r="A918" s="1"/>
+      <c r="A918" s="2"/>
       <c r="B918" s="7"/>
       <c r="C918" s="7"/>
       <c r="D918" s="7"/>
@@ -23504,7 +23519,7 @@
       <c r="W918" s="7"/>
     </row>
     <row r="919">
-      <c r="A919" s="1"/>
+      <c r="A919" s="2"/>
       <c r="B919" s="7"/>
       <c r="C919" s="7"/>
       <c r="D919" s="7"/>
@@ -23529,7 +23544,7 @@
       <c r="W919" s="7"/>
     </row>
     <row r="920">
-      <c r="A920" s="1"/>
+      <c r="A920" s="2"/>
       <c r="B920" s="7"/>
       <c r="C920" s="7"/>
       <c r="D920" s="7"/>
@@ -23554,7 +23569,7 @@
       <c r="W920" s="7"/>
     </row>
     <row r="921">
-      <c r="A921" s="1"/>
+      <c r="A921" s="2"/>
       <c r="B921" s="7"/>
       <c r="C921" s="7"/>
       <c r="D921" s="7"/>
@@ -23579,7 +23594,7 @@
       <c r="W921" s="7"/>
     </row>
     <row r="922">
-      <c r="A922" s="1"/>
+      <c r="A922" s="2"/>
       <c r="B922" s="7"/>
       <c r="C922" s="7"/>
       <c r="D922" s="7"/>
@@ -23604,7 +23619,7 @@
       <c r="W922" s="7"/>
     </row>
     <row r="923">
-      <c r="A923" s="1"/>
+      <c r="A923" s="2"/>
       <c r="B923" s="7"/>
       <c r="C923" s="7"/>
       <c r="D923" s="7"/>
@@ -23629,7 +23644,7 @@
       <c r="W923" s="7"/>
     </row>
     <row r="924">
-      <c r="A924" s="1"/>
+      <c r="A924" s="2"/>
       <c r="B924" s="7"/>
       <c r="C924" s="7"/>
       <c r="D924" s="7"/>
@@ -23654,7 +23669,7 @@
       <c r="W924" s="7"/>
     </row>
     <row r="925">
-      <c r="A925" s="1"/>
+      <c r="A925" s="2"/>
       <c r="B925" s="7"/>
       <c r="C925" s="7"/>
       <c r="D925" s="7"/>
@@ -23679,7 +23694,7 @@
       <c r="W925" s="7"/>
     </row>
     <row r="926">
-      <c r="A926" s="1"/>
+      <c r="A926" s="2"/>
       <c r="B926" s="7"/>
       <c r="C926" s="7"/>
       <c r="D926" s="7"/>
@@ -23704,7 +23719,7 @@
       <c r="W926" s="7"/>
     </row>
     <row r="927">
-      <c r="A927" s="1"/>
+      <c r="A927" s="2"/>
       <c r="B927" s="7"/>
       <c r="C927" s="7"/>
       <c r="D927" s="7"/>
@@ -23729,7 +23744,7 @@
       <c r="W927" s="7"/>
     </row>
     <row r="928">
-      <c r="A928" s="1"/>
+      <c r="A928" s="2"/>
       <c r="B928" s="7"/>
       <c r="C928" s="7"/>
       <c r="D928" s="7"/>
@@ -23754,7 +23769,7 @@
       <c r="W928" s="7"/>
     </row>
     <row r="929">
-      <c r="A929" s="1"/>
+      <c r="A929" s="2"/>
       <c r="B929" s="7"/>
       <c r="C929" s="7"/>
       <c r="D929" s="7"/>
@@ -23779,7 +23794,7 @@
       <c r="W929" s="7"/>
     </row>
     <row r="930">
-      <c r="A930" s="1"/>
+      <c r="A930" s="2"/>
       <c r="B930" s="7"/>
       <c r="C930" s="7"/>
       <c r="D930" s="7"/>
@@ -23804,7 +23819,7 @@
       <c r="W930" s="7"/>
     </row>
     <row r="931">
-      <c r="A931" s="1"/>
+      <c r="A931" s="2"/>
       <c r="B931" s="7"/>
       <c r="C931" s="7"/>
       <c r="D931" s="7"/>
@@ -23829,7 +23844,7 @@
       <c r="W931" s="7"/>
     </row>
     <row r="932">
-      <c r="A932" s="1"/>
+      <c r="A932" s="2"/>
       <c r="B932" s="7"/>
       <c r="C932" s="7"/>
       <c r="D932" s="7"/>
@@ -23854,7 +23869,7 @@
       <c r="W932" s="7"/>
     </row>
     <row r="933">
-      <c r="A933" s="1"/>
+      <c r="A933" s="2"/>
       <c r="B933" s="7"/>
       <c r="C933" s="7"/>
       <c r="D933" s="7"/>
@@ -23879,7 +23894,7 @@
       <c r="W933" s="7"/>
     </row>
     <row r="934">
-      <c r="A934" s="1"/>
+      <c r="A934" s="2"/>
       <c r="B934" s="7"/>
       <c r="C934" s="7"/>
       <c r="D934" s="7"/>
@@ -23904,7 +23919,7 @@
       <c r="W934" s="7"/>
     </row>
     <row r="935">
-      <c r="A935" s="1"/>
+      <c r="A935" s="2"/>
       <c r="B935" s="7"/>
       <c r="C935" s="7"/>
       <c r="D935" s="7"/>
@@ -23929,7 +23944,7 @@
       <c r="W935" s="7"/>
     </row>
     <row r="936">
-      <c r="A936" s="1"/>
+      <c r="A936" s="2"/>
       <c r="B936" s="7"/>
       <c r="C936" s="7"/>
       <c r="D936" s="7"/>
@@ -23954,7 +23969,7 @@
       <c r="W936" s="7"/>
     </row>
     <row r="937">
-      <c r="A937" s="1"/>
+      <c r="A937" s="2"/>
       <c r="B937" s="7"/>
       <c r="C937" s="7"/>
       <c r="D937" s="7"/>
@@ -23979,7 +23994,7 @@
       <c r="W937" s="7"/>
     </row>
     <row r="938">
-      <c r="A938" s="1"/>
+      <c r="A938" s="2"/>
       <c r="B938" s="7"/>
       <c r="C938" s="7"/>
       <c r="D938" s="7"/>
@@ -24004,7 +24019,7 @@
       <c r="W938" s="7"/>
     </row>
     <row r="939">
-      <c r="A939" s="1"/>
+      <c r="A939" s="2"/>
       <c r="B939" s="7"/>
       <c r="C939" s="7"/>
       <c r="D939" s="7"/>
@@ -24029,7 +24044,7 @@
       <c r="W939" s="7"/>
     </row>
     <row r="940">
-      <c r="A940" s="1"/>
+      <c r="A940" s="2"/>
       <c r="B940" s="7"/>
       <c r="C940" s="7"/>
       <c r="D940" s="7"/>
@@ -24054,7 +24069,7 @@
       <c r="W940" s="7"/>
     </row>
     <row r="941">
-      <c r="A941" s="1"/>
+      <c r="A941" s="2"/>
       <c r="B941" s="7"/>
       <c r="C941" s="7"/>
       <c r="D941" s="7"/>
@@ -24079,7 +24094,7 @@
       <c r="W941" s="7"/>
     </row>
     <row r="942">
-      <c r="A942" s="1"/>
+      <c r="A942" s="2"/>
       <c r="B942" s="7"/>
       <c r="C942" s="7"/>
       <c r="D942" s="7"/>
@@ -24104,7 +24119,7 @@
       <c r="W942" s="7"/>
     </row>
     <row r="943">
-      <c r="A943" s="1"/>
+      <c r="A943" s="2"/>
       <c r="B943" s="7"/>
       <c r="C943" s="7"/>
       <c r="D943" s="7"/>
@@ -24129,7 +24144,7 @@
       <c r="W943" s="7"/>
     </row>
     <row r="944">
-      <c r="A944" s="1"/>
+      <c r="A944" s="2"/>
       <c r="B944" s="7"/>
       <c r="C944" s="7"/>
       <c r="D944" s="7"/>
@@ -24154,7 +24169,7 @@
       <c r="W944" s="7"/>
     </row>
     <row r="945">
-      <c r="A945" s="1"/>
+      <c r="A945" s="2"/>
       <c r="B945" s="7"/>
       <c r="C945" s="7"/>
       <c r="D945" s="7"/>
@@ -24179,7 +24194,7 @@
       <c r="W945" s="7"/>
     </row>
     <row r="946">
-      <c r="A946" s="1"/>
+      <c r="A946" s="2"/>
       <c r="B946" s="7"/>
       <c r="C946" s="7"/>
       <c r="D946" s="7"/>
@@ -24204,7 +24219,7 @@
       <c r="W946" s="7"/>
     </row>
     <row r="947">
-      <c r="A947" s="1"/>
+      <c r="A947" s="2"/>
       <c r="B947" s="7"/>
       <c r="C947" s="7"/>
       <c r="D947" s="7"/>
@@ -24229,7 +24244,7 @@
       <c r="W947" s="7"/>
     </row>
     <row r="948">
-      <c r="A948" s="1"/>
+      <c r="A948" s="2"/>
       <c r="B948" s="7"/>
       <c r="C948" s="7"/>
       <c r="D948" s="7"/>
@@ -24254,7 +24269,7 @@
       <c r="W948" s="7"/>
     </row>
     <row r="949">
-      <c r="A949" s="1"/>
+      <c r="A949" s="2"/>
       <c r="B949" s="7"/>
       <c r="C949" s="7"/>
       <c r="D949" s="7"/>
@@ -24279,7 +24294,7 @@
       <c r="W949" s="7"/>
     </row>
     <row r="950">
-      <c r="A950" s="1"/>
+      <c r="A950" s="2"/>
       <c r="B950" s="7"/>
       <c r="C950" s="7"/>
       <c r="D950" s="7"/>
@@ -24304,7 +24319,7 @@
       <c r="W950" s="7"/>
     </row>
     <row r="951">
-      <c r="A951" s="1"/>
+      <c r="A951" s="2"/>
       <c r="B951" s="7"/>
       <c r="C951" s="7"/>
       <c r="D951" s="7"/>
@@ -24329,7 +24344,7 @@
       <c r="W951" s="7"/>
     </row>
     <row r="952">
-      <c r="A952" s="1"/>
+      <c r="A952" s="2"/>
       <c r="B952" s="7"/>
       <c r="C952" s="7"/>
       <c r="D952" s="7"/>
@@ -24354,7 +24369,7 @@
       <c r="W952" s="7"/>
     </row>
     <row r="953">
-      <c r="A953" s="1"/>
+      <c r="A953" s="2"/>
       <c r="B953" s="7"/>
       <c r="C953" s="7"/>
       <c r="D953" s="7"/>
@@ -24379,7 +24394,7 @@
       <c r="W953" s="7"/>
     </row>
     <row r="954">
-      <c r="A954" s="1"/>
+      <c r="A954" s="2"/>
       <c r="B954" s="7"/>
       <c r="C954" s="7"/>
       <c r="D954" s="7"/>
@@ -24404,7 +24419,7 @@
       <c r="W954" s="7"/>
     </row>
     <row r="955">
-      <c r="A955" s="1"/>
+      <c r="A955" s="2"/>
       <c r="B955" s="7"/>
       <c r="C955" s="7"/>
       <c r="D955" s="7"/>
@@ -24429,7 +24444,7 @@
       <c r="W955" s="7"/>
     </row>
     <row r="956">
-      <c r="A956" s="1"/>
+      <c r="A956" s="2"/>
       <c r="B956" s="7"/>
       <c r="C956" s="7"/>
       <c r="D956" s="7"/>
@@ -24454,7 +24469,7 @@
       <c r="W956" s="7"/>
     </row>
     <row r="957">
-      <c r="A957" s="1"/>
+      <c r="A957" s="2"/>
       <c r="B957" s="7"/>
       <c r="C957" s="7"/>
       <c r="D957" s="7"/>
@@ -24479,7 +24494,7 @@
       <c r="W957" s="7"/>
     </row>
     <row r="958">
-      <c r="A958" s="1"/>
+      <c r="A958" s="2"/>
       <c r="B958" s="7"/>
       <c r="C958" s="7"/>
       <c r="D958" s="7"/>
@@ -24504,7 +24519,7 @@
       <c r="W958" s="7"/>
     </row>
     <row r="959">
-      <c r="A959" s="1"/>
+      <c r="A959" s="2"/>
       <c r="B959" s="7"/>
       <c r="C959" s="7"/>
       <c r="D959" s="7"/>
@@ -24529,7 +24544,7 @@
       <c r="W959" s="7"/>
     </row>
     <row r="960">
-      <c r="A960" s="1"/>
+      <c r="A960" s="2"/>
       <c r="B960" s="7"/>
       <c r="C960" s="7"/>
       <c r="D960" s="7"/>
@@ -24554,7 +24569,7 @@
       <c r="W960" s="7"/>
     </row>
     <row r="961">
-      <c r="A961" s="1"/>
+      <c r="A961" s="2"/>
       <c r="B961" s="7"/>
       <c r="C961" s="7"/>
       <c r="D961" s="7"/>
@@ -24579,7 +24594,7 @@
       <c r="W961" s="7"/>
     </row>
     <row r="962">
-      <c r="A962" s="1"/>
+      <c r="A962" s="2"/>
       <c r="B962" s="7"/>
       <c r="C962" s="7"/>
       <c r="D962" s="7"/>
@@ -24604,7 +24619,7 @@
       <c r="W962" s="7"/>
     </row>
     <row r="963">
-      <c r="A963" s="1"/>
+      <c r="A963" s="2"/>
       <c r="B963" s="7"/>
       <c r="C963" s="7"/>
       <c r="D963" s="7"/>
@@ -24629,7 +24644,7 @@
       <c r="W963" s="7"/>
     </row>
     <row r="964">
-      <c r="A964" s="1"/>
+      <c r="A964" s="2"/>
       <c r="B964" s="7"/>
       <c r="C964" s="7"/>
       <c r="D964" s="7"/>
@@ -24654,7 +24669,7 @@
       <c r="W964" s="7"/>
     </row>
     <row r="965">
-      <c r="A965" s="1"/>
+      <c r="A965" s="2"/>
       <c r="B965" s="7"/>
       <c r="C965" s="7"/>
       <c r="D965" s="7"/>
@@ -24679,7 +24694,7 @@
       <c r="W965" s="7"/>
     </row>
     <row r="966">
-      <c r="A966" s="1"/>
+      <c r="A966" s="2"/>
       <c r="B966" s="7"/>
       <c r="C966" s="7"/>
       <c r="D966" s="7"/>
@@ -24704,7 +24719,7 @@
       <c r="W966" s="7"/>
     </row>
     <row r="967">
-      <c r="A967" s="1"/>
+      <c r="A967" s="2"/>
       <c r="B967" s="7"/>
       <c r="C967" s="7"/>
       <c r="D967" s="7"/>
@@ -24729,7 +24744,7 @@
       <c r="W967" s="7"/>
     </row>
     <row r="968">
-      <c r="A968" s="1"/>
+      <c r="A968" s="2"/>
       <c r="B968" s="7"/>
       <c r="C968" s="7"/>
       <c r="D968" s="7"/>
@@ -24754,7 +24769,7 @@
       <c r="W968" s="7"/>
     </row>
     <row r="969">
-      <c r="A969" s="1"/>
+      <c r="A969" s="2"/>
       <c r="B969" s="7"/>
       <c r="C969" s="7"/>
       <c r="D969" s="7"/>
@@ -24779,7 +24794,7 @@
       <c r="W969" s="7"/>
     </row>
     <row r="970">
-      <c r="A970" s="1"/>
+      <c r="A970" s="2"/>
       <c r="B970" s="7"/>
       <c r="C970" s="7"/>
       <c r="D970" s="7"/>
@@ -24804,7 +24819,7 @@
       <c r="W970" s="7"/>
     </row>
     <row r="971">
-      <c r="A971" s="1"/>
+      <c r="A971" s="2"/>
       <c r="B971" s="7"/>
       <c r="C971" s="7"/>
       <c r="D971" s="7"/>
@@ -24829,7 +24844,7 @@
       <c r="W971" s="7"/>
     </row>
     <row r="972">
-      <c r="A972" s="1"/>
+      <c r="A972" s="2"/>
       <c r="B972" s="7"/>
       <c r="C972" s="7"/>
       <c r="D972" s="7"/>
@@ -24854,7 +24869,7 @@
       <c r="W972" s="7"/>
     </row>
     <row r="973">
-      <c r="A973" s="1"/>
+      <c r="A973" s="2"/>
       <c r="B973" s="7"/>
       <c r="C973" s="7"/>
       <c r="D973" s="7"/>
@@ -24879,7 +24894,7 @@
       <c r="W973" s="7"/>
     </row>
     <row r="974">
-      <c r="A974" s="1"/>
+      <c r="A974" s="2"/>
       <c r="B974" s="7"/>
       <c r="C974" s="7"/>
       <c r="D974" s="7"/>
@@ -24904,7 +24919,7 @@
       <c r="W974" s="7"/>
     </row>
     <row r="975">
-      <c r="A975" s="1"/>
+      <c r="A975" s="2"/>
       <c r="B975" s="7"/>
       <c r="C975" s="7"/>
       <c r="D975" s="7"/>
@@ -24929,7 +24944,7 @@
       <c r="W975" s="7"/>
     </row>
     <row r="976">
-      <c r="A976" s="1"/>
+      <c r="A976" s="2"/>
       <c r="B976" s="7"/>
       <c r="C976" s="7"/>
       <c r="D976" s="7"/>
@@ -24954,7 +24969,7 @@
       <c r="W976" s="7"/>
     </row>
     <row r="977">
-      <c r="A977" s="1"/>
+      <c r="A977" s="2"/>
       <c r="B977" s="7"/>
       <c r="C977" s="7"/>
       <c r="D977" s="7"/>
@@ -24979,7 +24994,7 @@
       <c r="W977" s="7"/>
     </row>
     <row r="978">
-      <c r="A978" s="1"/>
+      <c r="A978" s="2"/>
       <c r="B978" s="7"/>
       <c r="C978" s="7"/>
       <c r="D978" s="7"/>
@@ -25004,7 +25019,7 @@
       <c r="W978" s="7"/>
     </row>
     <row r="979">
-      <c r="A979" s="1"/>
+      <c r="A979" s="2"/>
       <c r="B979" s="7"/>
       <c r="C979" s="7"/>
       <c r="D979" s="7"/>
@@ -25029,7 +25044,7 @@
       <c r="W979" s="7"/>
     </row>
     <row r="980">
-      <c r="A980" s="1"/>
+      <c r="A980" s="2"/>
       <c r="B980" s="7"/>
       <c r="C980" s="7"/>
       <c r="D980" s="7"/>
@@ -25054,7 +25069,7 @@
       <c r="W980" s="7"/>
     </row>
     <row r="981">
-      <c r="A981" s="1"/>
+      <c r="A981" s="2"/>
       <c r="B981" s="7"/>
       <c r="C981" s="7"/>
       <c r="D981" s="7"/>
@@ -25079,7 +25094,7 @@
       <c r="W981" s="7"/>
     </row>
     <row r="982">
-      <c r="A982" s="1"/>
+      <c r="A982" s="2"/>
       <c r="B982" s="7"/>
       <c r="C982" s="7"/>
       <c r="D982" s="7"/>
@@ -25104,7 +25119,7 @@
       <c r="W982" s="7"/>
     </row>
     <row r="983">
-      <c r="A983" s="1"/>
+      <c r="A983" s="2"/>
       <c r="B983" s="7"/>
       <c r="C983" s="7"/>
       <c r="D983" s="7"/>
@@ -25129,7 +25144,7 @@
       <c r="W983" s="7"/>
     </row>
     <row r="984">
-      <c r="A984" s="1"/>
+      <c r="A984" s="2"/>
       <c r="B984" s="7"/>
       <c r="C984" s="7"/>
       <c r="D984" s="7"/>
@@ -25154,7 +25169,7 @@
       <c r="W984" s="7"/>
     </row>
     <row r="985">
-      <c r="A985" s="1"/>
+      <c r="A985" s="2"/>
       <c r="B985" s="7"/>
       <c r="C985" s="7"/>
       <c r="D985" s="7"/>
@@ -25179,7 +25194,7 @@
       <c r="W985" s="7"/>
     </row>
     <row r="986">
-      <c r="A986" s="1"/>
+      <c r="A986" s="2"/>
       <c r="B986" s="7"/>
       <c r="C986" s="7"/>
       <c r="D986" s="7"/>
@@ -25204,7 +25219,7 @@
       <c r="W986" s="7"/>
     </row>
     <row r="987">
-      <c r="A987" s="1"/>
+      <c r="A987" s="2"/>
       <c r="B987" s="7"/>
       <c r="C987" s="7"/>
       <c r="D987" s="7"/>
@@ -25229,7 +25244,7 @@
       <c r="W987" s="7"/>
     </row>
     <row r="988">
-      <c r="A988" s="1"/>
+      <c r="A988" s="2"/>
       <c r="B988" s="7"/>
       <c r="C988" s="7"/>
       <c r="D988" s="7"/>
@@ -25254,7 +25269,7 @@
       <c r="W988" s="7"/>
     </row>
     <row r="989">
-      <c r="A989" s="1"/>
+      <c r="A989" s="2"/>
       <c r="B989" s="7"/>
       <c r="C989" s="7"/>
       <c r="D989" s="7"/>
@@ -25279,7 +25294,7 @@
       <c r="W989" s="7"/>
     </row>
     <row r="990">
-      <c r="A990" s="1"/>
+      <c r="A990" s="2"/>
       <c r="B990" s="7"/>
       <c r="C990" s="7"/>
       <c r="D990" s="7"/>
@@ -25304,7 +25319,7 @@
       <c r="W990" s="7"/>
     </row>
     <row r="991">
-      <c r="A991" s="1"/>
+      <c r="A991" s="2"/>
       <c r="B991" s="7"/>
       <c r="C991" s="7"/>
       <c r="D991" s="7"/>
@@ -25329,7 +25344,7 @@
       <c r="W991" s="7"/>
     </row>
     <row r="992">
-      <c r="A992" s="1"/>
+      <c r="A992" s="2"/>
       <c r="B992" s="7"/>
       <c r="C992" s="7"/>
       <c r="D992" s="7"/>
@@ -25354,7 +25369,7 @@
       <c r="W992" s="7"/>
     </row>
     <row r="993">
-      <c r="A993" s="1"/>
+      <c r="A993" s="2"/>
       <c r="B993" s="7"/>
       <c r="C993" s="7"/>
       <c r="D993" s="7"/>
@@ -25379,7 +25394,7 @@
       <c r="W993" s="7"/>
     </row>
     <row r="994">
-      <c r="A994" s="1"/>
+      <c r="A994" s="2"/>
       <c r="B994" s="7"/>
       <c r="C994" s="7"/>
       <c r="D994" s="7"/>
@@ -25404,7 +25419,7 @@
       <c r="W994" s="7"/>
     </row>
     <row r="995">
-      <c r="A995" s="1"/>
+      <c r="A995" s="2"/>
       <c r="B995" s="7"/>
       <c r="C995" s="7"/>
       <c r="D995" s="7"/>
@@ -25429,7 +25444,7 @@
       <c r="W995" s="7"/>
     </row>
     <row r="996">
-      <c r="A996" s="1"/>
+      <c r="A996" s="2"/>
       <c r="B996" s="7"/>
       <c r="C996" s="7"/>
       <c r="D996" s="7"/>
@@ -25454,7 +25469,7 @@
       <c r="W996" s="7"/>
     </row>
     <row r="997">
-      <c r="A997" s="1"/>
+      <c r="A997" s="2"/>
       <c r="B997" s="7"/>
       <c r="C997" s="7"/>
       <c r="D997" s="7"/>
@@ -25479,7 +25494,7 @@
       <c r="W997" s="7"/>
     </row>
     <row r="998">
-      <c r="A998" s="1"/>
+      <c r="A998" s="2"/>
       <c r="B998" s="7"/>
       <c r="C998" s="7"/>
       <c r="D998" s="7"/>
@@ -25504,7 +25519,7 @@
       <c r="W998" s="7"/>
     </row>
     <row r="999">
-      <c r="A999" s="1"/>
+      <c r="A999" s="2"/>
       <c r="B999" s="7"/>
       <c r="C999" s="7"/>
       <c r="D999" s="7"/>
@@ -25529,7 +25544,7 @@
       <c r="W999" s="7"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="1"/>
+      <c r="A1000" s="2"/>
       <c r="B1000" s="7"/>
       <c r="C1000" s="7"/>
       <c r="D1000" s="7"/>
@@ -25554,10 +25569,7 @@
       <c r="W1000" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H2:H4"/>
+  <mergeCells count="33">
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="K2:K4"/>
@@ -25566,17 +25578,31 @@
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="E5:E8"/>
     <mergeCell ref="F5:F8"/>
     <mergeCell ref="G5:G8"/>
     <mergeCell ref="H5:H8"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
     <mergeCell ref="I5:I8"/>
     <mergeCell ref="J5:J8"/>
     <mergeCell ref="K5:K8"/>
     <mergeCell ref="L5:L8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -25591,57 +25617,57 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
     </row>

--- a/Grade3-Homeworks.xlsx
+++ b/Grade3-Homeworks.xlsx
@@ -17,12 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Monday</t>
-  </si>
-  <si>
-    <t>Date</t>
   </si>
   <si>
     <t xml:space="preserve">Telugu </t>
@@ -31,10 +28,10 @@
     <t xml:space="preserve">Maths </t>
   </si>
   <si>
-    <t>Tuesday</t>
+    <t>Date</t>
   </si>
   <si>
-    <t>Languages</t>
+    <t>Tuesday</t>
   </si>
   <si>
     <t xml:space="preserve">English </t>
@@ -43,13 +40,37 @@
     <t xml:space="preserve">Programming </t>
   </si>
   <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Languages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Science </t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social </t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>KhatriHindiSanskrit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technology </t>
+  </si>
+  <si>
     <t>Telugu</t>
   </si>
   <si>
     <t>English</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
   </si>
   <si>
     <t>Devanagari - HindiSanskritKhatriMarathi</t>
@@ -58,43 +79,22 @@
     <t>Maths</t>
   </si>
   <si>
-    <t xml:space="preserve">Science </t>
-  </si>
-  <si>
     <t>Technology</t>
   </si>
   <si>
     <t>Programming</t>
   </si>
   <si>
-    <t>Thursday</t>
-  </si>
-  <si>
-    <t>Music</t>
-  </si>
-  <si>
     <t>CarnaticMusic</t>
   </si>
   <si>
-    <t xml:space="preserve">Social </t>
-  </si>
-  <si>
     <t>Science</t>
-  </si>
-  <si>
-    <t>Friday</t>
   </si>
   <si>
     <t>SocialStudies ( + LifeSkills)</t>
   </si>
   <si>
     <t>Overview</t>
-  </si>
-  <si>
-    <t>KhatriHindiSanskrit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technology </t>
   </si>
   <si>
     <t>HW: Complete 3rd class text book, work book, copy tracing book and get it verified by your parents</t>
@@ -130,6 +130,29 @@
   </si>
   <si>
     <t>HW: Make sure the website is updated with all the files for Grade 2 - All subjects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HW: Complete class 4 + class 5 AP Environment textbook + workboo
+</t>
+  </si>
+  <si>
+    <t>HW: Read the introduction again (Enlightened Education book - introduction)</t>
+  </si>
+  <si>
+    <t>HW: Complete class 4 + class 5 AP Environment textbook + workbook</t>
+  </si>
+  <si>
+    <t>HW: For 1 or 2 days, live without electricity;</t>
+  </si>
+  <si>
+    <t>HW: Play 'pillars' game
+Sthambhaala aata/Pillars game: Four players stand at and hold onto four different pillars, while a fifth player (the "thief" or IT) stands in the center. The four players try to quickly swap positions from one pillar to another without getting caught, while the central player tries to occupy an open pillar. Traditionally, it is a popular folk game played by children in rural Andhra Pradesh and Telangana, often during weddings under a marriage pandal (pelli pandiri).</t>
+  </si>
+  <si>
+    <t>HW: Read, write meanings, and answer exercises; Memorize all the sentences from the textbook. (Class 1 CBSE textbook)</t>
+  </si>
+  <si>
+    <t>HW: Practice these songs; Write down the raagam, thaalam, and swaras. (Practiced detecting swaras for songs - Keshava madhava; Animuthyaalandi sahajayoga songs)</t>
   </si>
 </sst>
 </file>
@@ -271,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -319,6 +342,9 @@
     </xf>
     <xf borderId="11" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,46 +563,48 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="3" max="12" width="19.38"/>
+    <col customWidth="1" min="3" max="10" width="19.38"/>
+    <col customWidth="1" min="11" max="11" width="22.88"/>
+    <col customWidth="1" min="12" max="12" width="21.88"/>
     <col hidden="1" min="13" max="23" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -844,7 +872,9 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12">
-      <c r="A12" s="2"/>
+      <c r="A12" s="20">
+        <v>46296.0</v>
+      </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -853,8 +883,12 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
+      <c r="J12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -869,18 +903,9 @@
       <c r="W12" s="7"/>
     </row>
     <row r="13">
-      <c r="A13" s="2"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="K13" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -894,18 +919,9 @@
       <c r="W13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="2"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="K14" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
@@ -919,18 +935,9 @@
       <c r="W14" s="7"/>
     </row>
     <row r="15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="K15" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -944,15 +951,21 @@
       <c r="W15" s="7"/>
     </row>
     <row r="16">
-      <c r="A16" s="2"/>
+      <c r="A16" s="20">
+        <v>46297.0</v>
+      </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
+      <c r="I16" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -25569,7 +25582,7 @@
       <c r="W1000" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="44">
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="K2:K4"/>
@@ -25581,12 +25594,10 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K5:K8"/>
+    <mergeCell ref="L5:L8"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="C5:C8"/>
@@ -25594,15 +25605,28 @@
     <mergeCell ref="F5:F8"/>
     <mergeCell ref="G5:G8"/>
     <mergeCell ref="H5:H8"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="L10:L11"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K5:K8"/>
-    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="L12:L15"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -25621,10 +25645,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -25632,43 +25656,43 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>

--- a/Grade3-Homeworks.xlsx
+++ b/Grade3-Homeworks.xlsx
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t xml:space="preserve">Maths </t>
-  </si>
-  <si>
-    <t>Date</t>
   </si>
   <si>
     <t>Tuesday</t>
@@ -65,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">Technology </t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
   <si>
     <t>Telugu</t>
@@ -162,7 +162,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -179,8 +179,13 @@
       <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <strike/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,6 +202,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7B7B7"/>
+        <bgColor rgb="FFB7B7B7"/>
       </patternFill>
     </fill>
     <fill>
@@ -294,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -324,11 +335,11 @@
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
@@ -345,6 +356,9 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,10 +585,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>16</v>
@@ -883,10 +897,10 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="9" t="s">
         <v>38</v>
       </c>
       <c r="L12" s="7"/>
@@ -903,7 +917,7 @@
       <c r="W12" s="7"/>
     </row>
     <row r="13">
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M13" s="7"/>
@@ -919,7 +933,7 @@
       <c r="W13" s="7"/>
     </row>
     <row r="14">
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="21" t="s">
         <v>40</v>
       </c>
       <c r="M14" s="7"/>
@@ -935,7 +949,7 @@
       <c r="W14" s="7"/>
     </row>
     <row r="15">
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="21" t="s">
         <v>41</v>
       </c>
       <c r="M15" s="7"/>
@@ -957,13 +971,13 @@
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="9" t="s">
         <v>43</v>
       </c>
       <c r="J16" s="7"/>
@@ -25609,8 +25623,16 @@
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="L10:L11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="I12:I15"/>
     <mergeCell ref="J12:J15"/>
-    <mergeCell ref="I12:I15"/>
     <mergeCell ref="L12:L15"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="B12:B15"/>
@@ -25619,14 +25641,6 @@
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="F12:F15"/>
     <mergeCell ref="G12:G15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="H10:H11"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -25653,46 +25667,46 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>

--- a/Grade3-Homeworks.xlsx
+++ b/Grade3-Homeworks.xlsx
@@ -17,15 +17,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+  <si>
+    <t>Date</t>
+  </si>
   <si>
     <t>Monday</t>
+  </si>
+  <si>
+    <t>Languages</t>
+  </si>
+  <si>
+    <t>Telugu</t>
+  </si>
+  <si>
+    <t>English</t>
   </si>
   <si>
     <t xml:space="preserve">Telugu </t>
   </si>
   <si>
+    <t>Devanagari - HindiSanskritKhatriMarathi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maths </t>
+  </si>
+  <si>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>Technology</t>
   </si>
   <si>
     <t>Tuesday</t>
@@ -34,19 +55,31 @@
     <t xml:space="preserve">English </t>
   </si>
   <si>
+    <t>Programming</t>
+  </si>
+  <si>
     <t xml:space="preserve">Programming </t>
+  </si>
+  <si>
+    <t>CarnaticMusic</t>
   </si>
   <si>
     <t>Wednesday</t>
   </si>
   <si>
-    <t>Languages</t>
+    <t>Science</t>
   </si>
   <si>
     <t xml:space="preserve">Science </t>
   </si>
   <si>
+    <t>SocialStudies ( + LifeSkills)</t>
+  </si>
+  <si>
     <t>Thursday</t>
+  </si>
+  <si>
+    <t>Overview</t>
   </si>
   <si>
     <t>Music</t>
@@ -64,40 +97,7 @@
     <t xml:space="preserve">Technology </t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Telugu</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Devanagari - HindiSanskritKhatriMarathi</t>
-  </si>
-  <si>
-    <t>Maths</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Programming</t>
-  </si>
-  <si>
-    <t>CarnaticMusic</t>
-  </si>
-  <si>
-    <t>Science</t>
-  </si>
-  <si>
-    <t>SocialStudies ( + LifeSkills)</t>
-  </si>
-  <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>HW: Complete 3rd class text book, work book, copy tracing book and get it verified by your parents</t>
+    <t>Complete 3rd class text book, work book, copy tracing book and get it verified by your parents</t>
   </si>
   <si>
     <t>Read 10th grade AP Telugu Textbook - Ramayanam - until the birth of Shri Rama
@@ -105,54 +105,81 @@
   </si>
   <si>
     <t>Read 10th grade AP Telugu Textbook - Ramayanam - until the birth of Shri Rama
-HW: Write all the meanings using AI</t>
+Write all the meanings using AI</t>
   </si>
   <si>
-    <t>HW: Complete Grade 3 AP Telugu textbook and workbook; Ask your parents to verify</t>
+    <t>Complete Grade 3 AP Telugu textbook and workbook; Ask your parents to verify</t>
   </si>
   <si>
-    <t>HW: Complete this book; Watch the movie ( 'Man who knew infinity' about an Indian Mathematician)</t>
+    <t>Complete this book; Watch the movie ( 'Man who knew infinity' about an Indian Mathematician)</t>
   </si>
   <si>
-    <t>HW: Read this and complete the exercises (Brehe's Grammar Anatomy open textbook)</t>
+    <t>Read this and complete the exercises (Brehe's Grammar Anatomy open textbook)</t>
   </si>
   <si>
-    <t>HW: Read 'The Hound of the Baskervilles' and watch movie</t>
+    <t>Read 'The Hound of the Baskervilles' and watch movie</t>
   </si>
   <si>
-    <t>HW: Read and understand all of these and solve word problems on Geometry</t>
+    <t>Read and understand all of these and solve word problems on Geometry</t>
   </si>
   <si>
-    <t>HW: Learn all of these operations and practice the exercises (Linux command line operations - AI notes)</t>
+    <t>Learn all of these operations and practice the exercises (Linux command line operations - AI notes)</t>
   </si>
   <si>
-    <t>HW: Read python book - Coder's apprentice and solve the exercises</t>
+    <t>Read python book - Coder's apprentice and solve the exercises</t>
   </si>
   <si>
-    <t>HW: Make sure the website is updated with all the files for Grade 2 - All subjects</t>
+    <t>Make sure the website is updated with all the files for Grade 2 - All subjects</t>
   </si>
   <si>
-    <t xml:space="preserve">HW: Complete class 4 + class 5 AP Environment textbook + workboo
+    <t xml:space="preserve">Complete class 4 + class 5 AP Environment textbook + workboo
 </t>
   </si>
   <si>
-    <t>HW: Read the introduction again (Enlightened Education book - introduction)</t>
+    <t>Read the introduction again (Enlightened Education book - introduction)</t>
   </si>
   <si>
-    <t>HW: Complete class 4 + class 5 AP Environment textbook + workbook</t>
+    <t>Complete class 4 + class 5 AP Environment textbook + workbook</t>
   </si>
   <si>
-    <t>HW: For 1 or 2 days, live without electricity;</t>
+    <t>For 1 or 2 days, live without electricity;</t>
   </si>
   <si>
-    <t>HW: Play 'pillars' game
+    <t>Play 'pillars' game
 Sthambhaala aata/Pillars game: Four players stand at and hold onto four different pillars, while a fifth player (the "thief" or IT) stands in the center. The four players try to quickly swap positions from one pillar to another without getting caught, while the central player tries to occupy an open pillar. Traditionally, it is a popular folk game played by children in rural Andhra Pradesh and Telangana, often during weddings under a marriage pandal (pelli pandiri).</t>
   </si>
   <si>
-    <t>HW: Read, write meanings, and answer exercises; Memorize all the sentences from the textbook. (Class 1 CBSE textbook)</t>
+    <t>Read, write meanings, and answer exercises; Memorize all the sentences from the textbook. (Class 1 CBSE textbook)</t>
   </si>
   <si>
-    <t>HW: Practice these songs; Write down the raagam, thaalam, and swaras. (Practiced detecting swaras for songs - Keshava madhava; Animuthyaalandi sahajayoga songs)</t>
+    <t>Practice these songs; Write down the raagam, thaalam, and swaras. (Practiced detecting swaras for songs - Keshava madhava; Animuthyaalandi sahajayoga songs)</t>
+  </si>
+  <si>
+    <t>Finish previous HWs</t>
+  </si>
+  <si>
+    <t>Listen to previous class videos again (on Geometry); Check previous homeworks</t>
+  </si>
+  <si>
+    <t>Read the story again (Read Ramayana until the death of Thataka.)</t>
+  </si>
+  <si>
+    <t>For 20 different radii, draw circles, measure perimeters and make a table of radii, perimeters and their ratios.</t>
+  </si>
+  <si>
+    <t>Complete/check previous HWs</t>
+  </si>
+  <si>
+    <t>Practice 20 times each ( 3 new song compositions - I am a drop; Shri Allah Shri Rama; Ankhon me basee)</t>
+  </si>
+  <si>
+    <t>Complete previous HWs</t>
+  </si>
+  <si>
+    <t>Complete previous HWs of textbook exercises</t>
+  </si>
+  <si>
+    <t>Read this! (William Blake's 'Marriage of Heaven and Hell')</t>
   </si>
 </sst>
 </file>
@@ -170,11 +197,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -305,31 +332,31 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -339,27 +366,28 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -584,53 +612,53 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>15</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>7</v>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="3">
@@ -996,12 +1024,18 @@
       <c r="W16" s="7"/>
     </row>
     <row r="17">
-      <c r="A17" s="2"/>
+      <c r="A17" s="20">
+        <v>46301.0</v>
+      </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
+      <c r="C17" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="F17" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -1021,18 +1055,12 @@
       <c r="W17" s="7"/>
     </row>
     <row r="18">
-      <c r="A18" s="2"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+      <c r="C18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>47</v>
+      </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
@@ -1046,7 +1074,9 @@
       <c r="W18" s="7"/>
     </row>
     <row r="19">
-      <c r="A19" s="2"/>
+      <c r="A19" s="20">
+        <v>46302.0</v>
+      </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -1054,7 +1084,9 @@
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
+      <c r="I19" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -1071,18 +1103,9 @@
       <c r="W19" s="7"/>
     </row>
     <row r="20">
-      <c r="A20" s="2"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
+      <c r="I20" s="9" t="s">
+        <v>49</v>
+      </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
@@ -1096,14 +1119,20 @@
       <c r="W20" s="7"/>
     </row>
     <row r="21">
-      <c r="A21" s="2"/>
+      <c r="A21" s="20">
+        <v>46308.0</v>
+      </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="9" t="s">
+        <v>50</v>
+      </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="H21" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1121,18 +1150,9 @@
       <c r="W21" s="7"/>
     </row>
     <row r="22">
-      <c r="A22" s="2"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="D22" s="21" t="s">
+        <v>52</v>
+      </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -1146,7 +1166,7 @@
       <c r="W22" s="7"/>
     </row>
     <row r="23">
-      <c r="A23" s="2"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -1171,7 +1191,7 @@
       <c r="W23" s="7"/>
     </row>
     <row r="24">
-      <c r="A24" s="2"/>
+      <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -1196,7 +1216,7 @@
       <c r="W24" s="7"/>
     </row>
     <row r="25">
-      <c r="A25" s="2"/>
+      <c r="A25" s="1"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -1221,7 +1241,7 @@
       <c r="W25" s="7"/>
     </row>
     <row r="26">
-      <c r="A26" s="2"/>
+      <c r="A26" s="1"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -1246,7 +1266,7 @@
       <c r="W26" s="7"/>
     </row>
     <row r="27">
-      <c r="A27" s="2"/>
+      <c r="A27" s="1"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -1271,7 +1291,7 @@
       <c r="W27" s="7"/>
     </row>
     <row r="28">
-      <c r="A28" s="2"/>
+      <c r="A28" s="1"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -1296,7 +1316,7 @@
       <c r="W28" s="7"/>
     </row>
     <row r="29">
-      <c r="A29" s="2"/>
+      <c r="A29" s="1"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1321,7 +1341,7 @@
       <c r="W29" s="7"/>
     </row>
     <row r="30">
-      <c r="A30" s="2"/>
+      <c r="A30" s="1"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -1346,7 +1366,7 @@
       <c r="W30" s="7"/>
     </row>
     <row r="31">
-      <c r="A31" s="2"/>
+      <c r="A31" s="1"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -1371,7 +1391,7 @@
       <c r="W31" s="7"/>
     </row>
     <row r="32">
-      <c r="A32" s="2"/>
+      <c r="A32" s="1"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -1396,7 +1416,7 @@
       <c r="W32" s="7"/>
     </row>
     <row r="33">
-      <c r="A33" s="2"/>
+      <c r="A33" s="1"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -1421,7 +1441,7 @@
       <c r="W33" s="7"/>
     </row>
     <row r="34">
-      <c r="A34" s="2"/>
+      <c r="A34" s="1"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -1446,7 +1466,7 @@
       <c r="W34" s="7"/>
     </row>
     <row r="35">
-      <c r="A35" s="2"/>
+      <c r="A35" s="1"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1471,7 +1491,7 @@
       <c r="W35" s="7"/>
     </row>
     <row r="36">
-      <c r="A36" s="2"/>
+      <c r="A36" s="1"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -1496,7 +1516,7 @@
       <c r="W36" s="7"/>
     </row>
     <row r="37">
-      <c r="A37" s="2"/>
+      <c r="A37" s="1"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -1521,7 +1541,7 @@
       <c r="W37" s="7"/>
     </row>
     <row r="38">
-      <c r="A38" s="2"/>
+      <c r="A38" s="1"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -1546,7 +1566,7 @@
       <c r="W38" s="7"/>
     </row>
     <row r="39">
-      <c r="A39" s="2"/>
+      <c r="A39" s="1"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -1571,7 +1591,7 @@
       <c r="W39" s="7"/>
     </row>
     <row r="40">
-      <c r="A40" s="2"/>
+      <c r="A40" s="1"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -1596,7 +1616,7 @@
       <c r="W40" s="7"/>
     </row>
     <row r="41">
-      <c r="A41" s="2"/>
+      <c r="A41" s="1"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1621,7 +1641,7 @@
       <c r="W41" s="7"/>
     </row>
     <row r="42">
-      <c r="A42" s="2"/>
+      <c r="A42" s="1"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -1646,7 +1666,7 @@
       <c r="W42" s="7"/>
     </row>
     <row r="43">
-      <c r="A43" s="2"/>
+      <c r="A43" s="1"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -1671,7 +1691,7 @@
       <c r="W43" s="7"/>
     </row>
     <row r="44">
-      <c r="A44" s="2"/>
+      <c r="A44" s="1"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -1696,7 +1716,7 @@
       <c r="W44" s="7"/>
     </row>
     <row r="45">
-      <c r="A45" s="2"/>
+      <c r="A45" s="1"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1721,7 +1741,7 @@
       <c r="W45" s="7"/>
     </row>
     <row r="46">
-      <c r="A46" s="2"/>
+      <c r="A46" s="1"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -1746,7 +1766,7 @@
       <c r="W46" s="7"/>
     </row>
     <row r="47">
-      <c r="A47" s="2"/>
+      <c r="A47" s="1"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -1771,7 +1791,7 @@
       <c r="W47" s="7"/>
     </row>
     <row r="48">
-      <c r="A48" s="2"/>
+      <c r="A48" s="1"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -1796,7 +1816,7 @@
       <c r="W48" s="7"/>
     </row>
     <row r="49">
-      <c r="A49" s="2"/>
+      <c r="A49" s="1"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -1821,7 +1841,7 @@
       <c r="W49" s="7"/>
     </row>
     <row r="50">
-      <c r="A50" s="2"/>
+      <c r="A50" s="1"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
@@ -1846,7 +1866,7 @@
       <c r="W50" s="7"/>
     </row>
     <row r="51">
-      <c r="A51" s="2"/>
+      <c r="A51" s="1"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -1871,7 +1891,7 @@
       <c r="W51" s="7"/>
     </row>
     <row r="52">
-      <c r="A52" s="2"/>
+      <c r="A52" s="1"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -1896,7 +1916,7 @@
       <c r="W52" s="7"/>
     </row>
     <row r="53">
-      <c r="A53" s="2"/>
+      <c r="A53" s="1"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -1921,7 +1941,7 @@
       <c r="W53" s="7"/>
     </row>
     <row r="54">
-      <c r="A54" s="2"/>
+      <c r="A54" s="1"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -1946,7 +1966,7 @@
       <c r="W54" s="7"/>
     </row>
     <row r="55">
-      <c r="A55" s="2"/>
+      <c r="A55" s="1"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -1971,7 +1991,7 @@
       <c r="W55" s="7"/>
     </row>
     <row r="56">
-      <c r="A56" s="2"/>
+      <c r="A56" s="1"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -1996,7 +2016,7 @@
       <c r="W56" s="7"/>
     </row>
     <row r="57">
-      <c r="A57" s="2"/>
+      <c r="A57" s="1"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -2021,7 +2041,7 @@
       <c r="W57" s="7"/>
     </row>
     <row r="58">
-      <c r="A58" s="2"/>
+      <c r="A58" s="1"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -2046,7 +2066,7 @@
       <c r="W58" s="7"/>
     </row>
     <row r="59">
-      <c r="A59" s="2"/>
+      <c r="A59" s="1"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -2071,7 +2091,7 @@
       <c r="W59" s="7"/>
     </row>
     <row r="60">
-      <c r="A60" s="2"/>
+      <c r="A60" s="1"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -2096,7 +2116,7 @@
       <c r="W60" s="7"/>
     </row>
     <row r="61">
-      <c r="A61" s="2"/>
+      <c r="A61" s="1"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -2121,7 +2141,7 @@
       <c r="W61" s="7"/>
     </row>
     <row r="62">
-      <c r="A62" s="2"/>
+      <c r="A62" s="1"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -2146,7 +2166,7 @@
       <c r="W62" s="7"/>
     </row>
     <row r="63">
-      <c r="A63" s="2"/>
+      <c r="A63" s="1"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -2171,7 +2191,7 @@
       <c r="W63" s="7"/>
     </row>
     <row r="64">
-      <c r="A64" s="2"/>
+      <c r="A64" s="1"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -2196,7 +2216,7 @@
       <c r="W64" s="7"/>
     </row>
     <row r="65">
-      <c r="A65" s="2"/>
+      <c r="A65" s="1"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -2221,7 +2241,7 @@
       <c r="W65" s="7"/>
     </row>
     <row r="66">
-      <c r="A66" s="2"/>
+      <c r="A66" s="1"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -2246,7 +2266,7 @@
       <c r="W66" s="7"/>
     </row>
     <row r="67">
-      <c r="A67" s="2"/>
+      <c r="A67" s="1"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -2271,7 +2291,7 @@
       <c r="W67" s="7"/>
     </row>
     <row r="68">
-      <c r="A68" s="2"/>
+      <c r="A68" s="1"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -2296,7 +2316,7 @@
       <c r="W68" s="7"/>
     </row>
     <row r="69">
-      <c r="A69" s="2"/>
+      <c r="A69" s="1"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -2321,7 +2341,7 @@
       <c r="W69" s="7"/>
     </row>
     <row r="70">
-      <c r="A70" s="2"/>
+      <c r="A70" s="1"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -2346,7 +2366,7 @@
       <c r="W70" s="7"/>
     </row>
     <row r="71">
-      <c r="A71" s="2"/>
+      <c r="A71" s="1"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -2371,7 +2391,7 @@
       <c r="W71" s="7"/>
     </row>
     <row r="72">
-      <c r="A72" s="2"/>
+      <c r="A72" s="1"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -2396,7 +2416,7 @@
       <c r="W72" s="7"/>
     </row>
     <row r="73">
-      <c r="A73" s="2"/>
+      <c r="A73" s="1"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -2421,7 +2441,7 @@
       <c r="W73" s="7"/>
     </row>
     <row r="74">
-      <c r="A74" s="2"/>
+      <c r="A74" s="1"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -2446,7 +2466,7 @@
       <c r="W74" s="7"/>
     </row>
     <row r="75">
-      <c r="A75" s="2"/>
+      <c r="A75" s="1"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
@@ -2471,7 +2491,7 @@
       <c r="W75" s="7"/>
     </row>
     <row r="76">
-      <c r="A76" s="2"/>
+      <c r="A76" s="1"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -2496,7 +2516,7 @@
       <c r="W76" s="7"/>
     </row>
     <row r="77">
-      <c r="A77" s="2"/>
+      <c r="A77" s="1"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -2521,7 +2541,7 @@
       <c r="W77" s="7"/>
     </row>
     <row r="78">
-      <c r="A78" s="2"/>
+      <c r="A78" s="1"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -2546,7 +2566,7 @@
       <c r="W78" s="7"/>
     </row>
     <row r="79">
-      <c r="A79" s="2"/>
+      <c r="A79" s="1"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -2571,7 +2591,7 @@
       <c r="W79" s="7"/>
     </row>
     <row r="80">
-      <c r="A80" s="2"/>
+      <c r="A80" s="1"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -2596,7 +2616,7 @@
       <c r="W80" s="7"/>
     </row>
     <row r="81">
-      <c r="A81" s="2"/>
+      <c r="A81" s="1"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -2621,7 +2641,7 @@
       <c r="W81" s="7"/>
     </row>
     <row r="82">
-      <c r="A82" s="2"/>
+      <c r="A82" s="1"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -2646,7 +2666,7 @@
       <c r="W82" s="7"/>
     </row>
     <row r="83">
-      <c r="A83" s="2"/>
+      <c r="A83" s="1"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -2671,7 +2691,7 @@
       <c r="W83" s="7"/>
     </row>
     <row r="84">
-      <c r="A84" s="2"/>
+      <c r="A84" s="1"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -2696,7 +2716,7 @@
       <c r="W84" s="7"/>
     </row>
     <row r="85">
-      <c r="A85" s="2"/>
+      <c r="A85" s="1"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
@@ -2721,7 +2741,7 @@
       <c r="W85" s="7"/>
     </row>
     <row r="86">
-      <c r="A86" s="2"/>
+      <c r="A86" s="1"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
@@ -2746,7 +2766,7 @@
       <c r="W86" s="7"/>
     </row>
     <row r="87">
-      <c r="A87" s="2"/>
+      <c r="A87" s="1"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
@@ -2771,7 +2791,7 @@
       <c r="W87" s="7"/>
     </row>
     <row r="88">
-      <c r="A88" s="2"/>
+      <c r="A88" s="1"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
@@ -2796,7 +2816,7 @@
       <c r="W88" s="7"/>
     </row>
     <row r="89">
-      <c r="A89" s="2"/>
+      <c r="A89" s="1"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
@@ -2821,7 +2841,7 @@
       <c r="W89" s="7"/>
     </row>
     <row r="90">
-      <c r="A90" s="2"/>
+      <c r="A90" s="1"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
@@ -2846,7 +2866,7 @@
       <c r="W90" s="7"/>
     </row>
     <row r="91">
-      <c r="A91" s="2"/>
+      <c r="A91" s="1"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -2871,7 +2891,7 @@
       <c r="W91" s="7"/>
     </row>
     <row r="92">
-      <c r="A92" s="2"/>
+      <c r="A92" s="1"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -2896,7 +2916,7 @@
       <c r="W92" s="7"/>
     </row>
     <row r="93">
-      <c r="A93" s="2"/>
+      <c r="A93" s="1"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -2921,7 +2941,7 @@
       <c r="W93" s="7"/>
     </row>
     <row r="94">
-      <c r="A94" s="2"/>
+      <c r="A94" s="1"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -2946,7 +2966,7 @@
       <c r="W94" s="7"/>
     </row>
     <row r="95">
-      <c r="A95" s="2"/>
+      <c r="A95" s="1"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -2971,7 +2991,7 @@
       <c r="W95" s="7"/>
     </row>
     <row r="96">
-      <c r="A96" s="2"/>
+      <c r="A96" s="1"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -2996,7 +3016,7 @@
       <c r="W96" s="7"/>
     </row>
     <row r="97">
-      <c r="A97" s="2"/>
+      <c r="A97" s="1"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
@@ -3021,7 +3041,7 @@
       <c r="W97" s="7"/>
     </row>
     <row r="98">
-      <c r="A98" s="2"/>
+      <c r="A98" s="1"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
@@ -3046,7 +3066,7 @@
       <c r="W98" s="7"/>
     </row>
     <row r="99">
-      <c r="A99" s="2"/>
+      <c r="A99" s="1"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
@@ -3071,7 +3091,7 @@
       <c r="W99" s="7"/>
     </row>
     <row r="100">
-      <c r="A100" s="2"/>
+      <c r="A100" s="1"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
@@ -3096,7 +3116,7 @@
       <c r="W100" s="7"/>
     </row>
     <row r="101">
-      <c r="A101" s="2"/>
+      <c r="A101" s="1"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
@@ -3121,7 +3141,7 @@
       <c r="W101" s="7"/>
     </row>
     <row r="102">
-      <c r="A102" s="2"/>
+      <c r="A102" s="1"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
@@ -3146,7 +3166,7 @@
       <c r="W102" s="7"/>
     </row>
     <row r="103">
-      <c r="A103" s="2"/>
+      <c r="A103" s="1"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
@@ -3171,7 +3191,7 @@
       <c r="W103" s="7"/>
     </row>
     <row r="104">
-      <c r="A104" s="2"/>
+      <c r="A104" s="1"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
@@ -3196,7 +3216,7 @@
       <c r="W104" s="7"/>
     </row>
     <row r="105">
-      <c r="A105" s="2"/>
+      <c r="A105" s="1"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
@@ -3221,7 +3241,7 @@
       <c r="W105" s="7"/>
     </row>
     <row r="106">
-      <c r="A106" s="2"/>
+      <c r="A106" s="1"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
@@ -3246,7 +3266,7 @@
       <c r="W106" s="7"/>
     </row>
     <row r="107">
-      <c r="A107" s="2"/>
+      <c r="A107" s="1"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
@@ -3271,7 +3291,7 @@
       <c r="W107" s="7"/>
     </row>
     <row r="108">
-      <c r="A108" s="2"/>
+      <c r="A108" s="1"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
@@ -3296,7 +3316,7 @@
       <c r="W108" s="7"/>
     </row>
     <row r="109">
-      <c r="A109" s="2"/>
+      <c r="A109" s="1"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
@@ -3321,7 +3341,7 @@
       <c r="W109" s="7"/>
     </row>
     <row r="110">
-      <c r="A110" s="2"/>
+      <c r="A110" s="1"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
@@ -3346,7 +3366,7 @@
       <c r="W110" s="7"/>
     </row>
     <row r="111">
-      <c r="A111" s="2"/>
+      <c r="A111" s="1"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
@@ -3371,7 +3391,7 @@
       <c r="W111" s="7"/>
     </row>
     <row r="112">
-      <c r="A112" s="2"/>
+      <c r="A112" s="1"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
@@ -3396,7 +3416,7 @@
       <c r="W112" s="7"/>
     </row>
     <row r="113">
-      <c r="A113" s="2"/>
+      <c r="A113" s="1"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
@@ -3421,7 +3441,7 @@
       <c r="W113" s="7"/>
     </row>
     <row r="114">
-      <c r="A114" s="2"/>
+      <c r="A114" s="1"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
@@ -3446,7 +3466,7 @@
       <c r="W114" s="7"/>
     </row>
     <row r="115">
-      <c r="A115" s="2"/>
+      <c r="A115" s="1"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
@@ -3471,7 +3491,7 @@
       <c r="W115" s="7"/>
     </row>
     <row r="116">
-      <c r="A116" s="2"/>
+      <c r="A116" s="1"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
@@ -3496,7 +3516,7 @@
       <c r="W116" s="7"/>
     </row>
     <row r="117">
-      <c r="A117" s="2"/>
+      <c r="A117" s="1"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
@@ -3521,7 +3541,7 @@
       <c r="W117" s="7"/>
     </row>
     <row r="118">
-      <c r="A118" s="2"/>
+      <c r="A118" s="1"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
@@ -3546,7 +3566,7 @@
       <c r="W118" s="7"/>
     </row>
     <row r="119">
-      <c r="A119" s="2"/>
+      <c r="A119" s="1"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
@@ -3571,7 +3591,7 @@
       <c r="W119" s="7"/>
     </row>
     <row r="120">
-      <c r="A120" s="2"/>
+      <c r="A120" s="1"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
@@ -3596,7 +3616,7 @@
       <c r="W120" s="7"/>
     </row>
     <row r="121">
-      <c r="A121" s="2"/>
+      <c r="A121" s="1"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
@@ -3621,7 +3641,7 @@
       <c r="W121" s="7"/>
     </row>
     <row r="122">
-      <c r="A122" s="2"/>
+      <c r="A122" s="1"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
@@ -3646,7 +3666,7 @@
       <c r="W122" s="7"/>
     </row>
     <row r="123">
-      <c r="A123" s="2"/>
+      <c r="A123" s="1"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
@@ -3671,7 +3691,7 @@
       <c r="W123" s="7"/>
     </row>
     <row r="124">
-      <c r="A124" s="2"/>
+      <c r="A124" s="1"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
@@ -3696,7 +3716,7 @@
       <c r="W124" s="7"/>
     </row>
     <row r="125">
-      <c r="A125" s="2"/>
+      <c r="A125" s="1"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
@@ -3721,7 +3741,7 @@
       <c r="W125" s="7"/>
     </row>
     <row r="126">
-      <c r="A126" s="2"/>
+      <c r="A126" s="1"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
@@ -3746,7 +3766,7 @@
       <c r="W126" s="7"/>
     </row>
     <row r="127">
-      <c r="A127" s="2"/>
+      <c r="A127" s="1"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
@@ -3771,7 +3791,7 @@
       <c r="W127" s="7"/>
     </row>
     <row r="128">
-      <c r="A128" s="2"/>
+      <c r="A128" s="1"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
@@ -3796,7 +3816,7 @@
       <c r="W128" s="7"/>
     </row>
     <row r="129">
-      <c r="A129" s="2"/>
+      <c r="A129" s="1"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
@@ -3821,7 +3841,7 @@
       <c r="W129" s="7"/>
     </row>
     <row r="130">
-      <c r="A130" s="2"/>
+      <c r="A130" s="1"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
@@ -3846,7 +3866,7 @@
       <c r="W130" s="7"/>
     </row>
     <row r="131">
-      <c r="A131" s="2"/>
+      <c r="A131" s="1"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
@@ -3871,7 +3891,7 @@
       <c r="W131" s="7"/>
     </row>
     <row r="132">
-      <c r="A132" s="2"/>
+      <c r="A132" s="1"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
@@ -3896,7 +3916,7 @@
       <c r="W132" s="7"/>
     </row>
     <row r="133">
-      <c r="A133" s="2"/>
+      <c r="A133" s="1"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
@@ -3921,7 +3941,7 @@
       <c r="W133" s="7"/>
     </row>
     <row r="134">
-      <c r="A134" s="2"/>
+      <c r="A134" s="1"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
@@ -3946,7 +3966,7 @@
       <c r="W134" s="7"/>
     </row>
     <row r="135">
-      <c r="A135" s="2"/>
+      <c r="A135" s="1"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -3971,7 +3991,7 @@
       <c r="W135" s="7"/>
     </row>
     <row r="136">
-      <c r="A136" s="2"/>
+      <c r="A136" s="1"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
@@ -3996,7 +4016,7 @@
       <c r="W136" s="7"/>
     </row>
     <row r="137">
-      <c r="A137" s="2"/>
+      <c r="A137" s="1"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -4021,7 +4041,7 @@
       <c r="W137" s="7"/>
     </row>
     <row r="138">
-      <c r="A138" s="2"/>
+      <c r="A138" s="1"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
@@ -4046,7 +4066,7 @@
       <c r="W138" s="7"/>
     </row>
     <row r="139">
-      <c r="A139" s="2"/>
+      <c r="A139" s="1"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -4071,7 +4091,7 @@
       <c r="W139" s="7"/>
     </row>
     <row r="140">
-      <c r="A140" s="2"/>
+      <c r="A140" s="1"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
@@ -4096,7 +4116,7 @@
       <c r="W140" s="7"/>
     </row>
     <row r="141">
-      <c r="A141" s="2"/>
+      <c r="A141" s="1"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -4121,7 +4141,7 @@
       <c r="W141" s="7"/>
     </row>
     <row r="142">
-      <c r="A142" s="2"/>
+      <c r="A142" s="1"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
@@ -4146,7 +4166,7 @@
       <c r="W142" s="7"/>
     </row>
     <row r="143">
-      <c r="A143" s="2"/>
+      <c r="A143" s="1"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -4171,7 +4191,7 @@
       <c r="W143" s="7"/>
     </row>
     <row r="144">
-      <c r="A144" s="2"/>
+      <c r="A144" s="1"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
@@ -4196,7 +4216,7 @@
       <c r="W144" s="7"/>
     </row>
     <row r="145">
-      <c r="A145" s="2"/>
+      <c r="A145" s="1"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -4221,7 +4241,7 @@
       <c r="W145" s="7"/>
     </row>
     <row r="146">
-      <c r="A146" s="2"/>
+      <c r="A146" s="1"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
@@ -4246,7 +4266,7 @@
       <c r="W146" s="7"/>
     </row>
     <row r="147">
-      <c r="A147" s="2"/>
+      <c r="A147" s="1"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -4271,7 +4291,7 @@
       <c r="W147" s="7"/>
     </row>
     <row r="148">
-      <c r="A148" s="2"/>
+      <c r="A148" s="1"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
@@ -4296,7 +4316,7 @@
       <c r="W148" s="7"/>
     </row>
     <row r="149">
-      <c r="A149" s="2"/>
+      <c r="A149" s="1"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -4321,7 +4341,7 @@
       <c r="W149" s="7"/>
     </row>
     <row r="150">
-      <c r="A150" s="2"/>
+      <c r="A150" s="1"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
@@ -4346,7 +4366,7 @@
       <c r="W150" s="7"/>
     </row>
     <row r="151">
-      <c r="A151" s="2"/>
+      <c r="A151" s="1"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
@@ -4371,7 +4391,7 @@
       <c r="W151" s="7"/>
     </row>
     <row r="152">
-      <c r="A152" s="2"/>
+      <c r="A152" s="1"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
@@ -4396,7 +4416,7 @@
       <c r="W152" s="7"/>
     </row>
     <row r="153">
-      <c r="A153" s="2"/>
+      <c r="A153" s="1"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
@@ -4421,7 +4441,7 @@
       <c r="W153" s="7"/>
     </row>
     <row r="154">
-      <c r="A154" s="2"/>
+      <c r="A154" s="1"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
@@ -4446,7 +4466,7 @@
       <c r="W154" s="7"/>
     </row>
     <row r="155">
-      <c r="A155" s="2"/>
+      <c r="A155" s="1"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -4471,7 +4491,7 @@
       <c r="W155" s="7"/>
     </row>
     <row r="156">
-      <c r="A156" s="2"/>
+      <c r="A156" s="1"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
@@ -4496,7 +4516,7 @@
       <c r="W156" s="7"/>
     </row>
     <row r="157">
-      <c r="A157" s="2"/>
+      <c r="A157" s="1"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
@@ -4521,7 +4541,7 @@
       <c r="W157" s="7"/>
     </row>
     <row r="158">
-      <c r="A158" s="2"/>
+      <c r="A158" s="1"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
@@ -4546,7 +4566,7 @@
       <c r="W158" s="7"/>
     </row>
     <row r="159">
-      <c r="A159" s="2"/>
+      <c r="A159" s="1"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -4571,7 +4591,7 @@
       <c r="W159" s="7"/>
     </row>
     <row r="160">
-      <c r="A160" s="2"/>
+      <c r="A160" s="1"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -4596,7 +4616,7 @@
       <c r="W160" s="7"/>
     </row>
     <row r="161">
-      <c r="A161" s="2"/>
+      <c r="A161" s="1"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -4621,7 +4641,7 @@
       <c r="W161" s="7"/>
     </row>
     <row r="162">
-      <c r="A162" s="2"/>
+      <c r="A162" s="1"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -4646,7 +4666,7 @@
       <c r="W162" s="7"/>
     </row>
     <row r="163">
-      <c r="A163" s="2"/>
+      <c r="A163" s="1"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
@@ -4671,7 +4691,7 @@
       <c r="W163" s="7"/>
     </row>
     <row r="164">
-      <c r="A164" s="2"/>
+      <c r="A164" s="1"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
@@ -4696,7 +4716,7 @@
       <c r="W164" s="7"/>
     </row>
     <row r="165">
-      <c r="A165" s="2"/>
+      <c r="A165" s="1"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
@@ -4721,7 +4741,7 @@
       <c r="W165" s="7"/>
     </row>
     <row r="166">
-      <c r="A166" s="2"/>
+      <c r="A166" s="1"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
@@ -4746,7 +4766,7 @@
       <c r="W166" s="7"/>
     </row>
     <row r="167">
-      <c r="A167" s="2"/>
+      <c r="A167" s="1"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -4771,7 +4791,7 @@
       <c r="W167" s="7"/>
     </row>
     <row r="168">
-      <c r="A168" s="2"/>
+      <c r="A168" s="1"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -4796,7 +4816,7 @@
       <c r="W168" s="7"/>
     </row>
     <row r="169">
-      <c r="A169" s="2"/>
+      <c r="A169" s="1"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -4821,7 +4841,7 @@
       <c r="W169" s="7"/>
     </row>
     <row r="170">
-      <c r="A170" s="2"/>
+      <c r="A170" s="1"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -4846,7 +4866,7 @@
       <c r="W170" s="7"/>
     </row>
     <row r="171">
-      <c r="A171" s="2"/>
+      <c r="A171" s="1"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -4871,7 +4891,7 @@
       <c r="W171" s="7"/>
     </row>
     <row r="172">
-      <c r="A172" s="2"/>
+      <c r="A172" s="1"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -4896,7 +4916,7 @@
       <c r="W172" s="7"/>
     </row>
     <row r="173">
-      <c r="A173" s="2"/>
+      <c r="A173" s="1"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -4921,7 +4941,7 @@
       <c r="W173" s="7"/>
     </row>
     <row r="174">
-      <c r="A174" s="2"/>
+      <c r="A174" s="1"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -4946,7 +4966,7 @@
       <c r="W174" s="7"/>
     </row>
     <row r="175">
-      <c r="A175" s="2"/>
+      <c r="A175" s="1"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -4971,7 +4991,7 @@
       <c r="W175" s="7"/>
     </row>
     <row r="176">
-      <c r="A176" s="2"/>
+      <c r="A176" s="1"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -4996,7 +5016,7 @@
       <c r="W176" s="7"/>
     </row>
     <row r="177">
-      <c r="A177" s="2"/>
+      <c r="A177" s="1"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -5021,7 +5041,7 @@
       <c r="W177" s="7"/>
     </row>
     <row r="178">
-      <c r="A178" s="2"/>
+      <c r="A178" s="1"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -5046,7 +5066,7 @@
       <c r="W178" s="7"/>
     </row>
     <row r="179">
-      <c r="A179" s="2"/>
+      <c r="A179" s="1"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -5071,7 +5091,7 @@
       <c r="W179" s="7"/>
     </row>
     <row r="180">
-      <c r="A180" s="2"/>
+      <c r="A180" s="1"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -5096,7 +5116,7 @@
       <c r="W180" s="7"/>
     </row>
     <row r="181">
-      <c r="A181" s="2"/>
+      <c r="A181" s="1"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -5121,7 +5141,7 @@
       <c r="W181" s="7"/>
     </row>
     <row r="182">
-      <c r="A182" s="2"/>
+      <c r="A182" s="1"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -5146,7 +5166,7 @@
       <c r="W182" s="7"/>
     </row>
     <row r="183">
-      <c r="A183" s="2"/>
+      <c r="A183" s="1"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -5171,7 +5191,7 @@
       <c r="W183" s="7"/>
     </row>
     <row r="184">
-      <c r="A184" s="2"/>
+      <c r="A184" s="1"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -5196,7 +5216,7 @@
       <c r="W184" s="7"/>
     </row>
     <row r="185">
-      <c r="A185" s="2"/>
+      <c r="A185" s="1"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -5221,7 +5241,7 @@
       <c r="W185" s="7"/>
     </row>
     <row r="186">
-      <c r="A186" s="2"/>
+      <c r="A186" s="1"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -5246,7 +5266,7 @@
       <c r="W186" s="7"/>
     </row>
     <row r="187">
-      <c r="A187" s="2"/>
+      <c r="A187" s="1"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -5271,7 +5291,7 @@
       <c r="W187" s="7"/>
     </row>
     <row r="188">
-      <c r="A188" s="2"/>
+      <c r="A188" s="1"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -5296,7 +5316,7 @@
       <c r="W188" s="7"/>
     </row>
     <row r="189">
-      <c r="A189" s="2"/>
+      <c r="A189" s="1"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -5321,7 +5341,7 @@
       <c r="W189" s="7"/>
     </row>
     <row r="190">
-      <c r="A190" s="2"/>
+      <c r="A190" s="1"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -5346,7 +5366,7 @@
       <c r="W190" s="7"/>
     </row>
     <row r="191">
-      <c r="A191" s="2"/>
+      <c r="A191" s="1"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -5371,7 +5391,7 @@
       <c r="W191" s="7"/>
     </row>
     <row r="192">
-      <c r="A192" s="2"/>
+      <c r="A192" s="1"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -5396,7 +5416,7 @@
       <c r="W192" s="7"/>
     </row>
     <row r="193">
-      <c r="A193" s="2"/>
+      <c r="A193" s="1"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
@@ -5421,7 +5441,7 @@
       <c r="W193" s="7"/>
     </row>
     <row r="194">
-      <c r="A194" s="2"/>
+      <c r="A194" s="1"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
@@ -5446,7 +5466,7 @@
       <c r="W194" s="7"/>
     </row>
     <row r="195">
-      <c r="A195" s="2"/>
+      <c r="A195" s="1"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
@@ -5471,7 +5491,7 @@
       <c r="W195" s="7"/>
     </row>
     <row r="196">
-      <c r="A196" s="2"/>
+      <c r="A196" s="1"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
@@ -5496,7 +5516,7 @@
       <c r="W196" s="7"/>
     </row>
     <row r="197">
-      <c r="A197" s="2"/>
+      <c r="A197" s="1"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
@@ -5521,7 +5541,7 @@
       <c r="W197" s="7"/>
     </row>
     <row r="198">
-      <c r="A198" s="2"/>
+      <c r="A198" s="1"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
@@ -5546,7 +5566,7 @@
       <c r="W198" s="7"/>
     </row>
     <row r="199">
-      <c r="A199" s="2"/>
+      <c r="A199" s="1"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
@@ -5571,7 +5591,7 @@
       <c r="W199" s="7"/>
     </row>
     <row r="200">
-      <c r="A200" s="2"/>
+      <c r="A200" s="1"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
@@ -5596,7 +5616,7 @@
       <c r="W200" s="7"/>
     </row>
     <row r="201">
-      <c r="A201" s="2"/>
+      <c r="A201" s="1"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
@@ -5621,7 +5641,7 @@
       <c r="W201" s="7"/>
     </row>
     <row r="202">
-      <c r="A202" s="2"/>
+      <c r="A202" s="1"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
@@ -5646,7 +5666,7 @@
       <c r="W202" s="7"/>
     </row>
     <row r="203">
-      <c r="A203" s="2"/>
+      <c r="A203" s="1"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
@@ -5671,7 +5691,7 @@
       <c r="W203" s="7"/>
     </row>
     <row r="204">
-      <c r="A204" s="2"/>
+      <c r="A204" s="1"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
@@ -5696,7 +5716,7 @@
       <c r="W204" s="7"/>
     </row>
     <row r="205">
-      <c r="A205" s="2"/>
+      <c r="A205" s="1"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -5721,7 +5741,7 @@
       <c r="W205" s="7"/>
     </row>
     <row r="206">
-      <c r="A206" s="2"/>
+      <c r="A206" s="1"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -5746,7 +5766,7 @@
       <c r="W206" s="7"/>
     </row>
     <row r="207">
-      <c r="A207" s="2"/>
+      <c r="A207" s="1"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
@@ -5771,7 +5791,7 @@
       <c r="W207" s="7"/>
     </row>
     <row r="208">
-      <c r="A208" s="2"/>
+      <c r="A208" s="1"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
@@ -5796,7 +5816,7 @@
       <c r="W208" s="7"/>
     </row>
     <row r="209">
-      <c r="A209" s="2"/>
+      <c r="A209" s="1"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
@@ -5821,7 +5841,7 @@
       <c r="W209" s="7"/>
     </row>
     <row r="210">
-      <c r="A210" s="2"/>
+      <c r="A210" s="1"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
@@ -5846,7 +5866,7 @@
       <c r="W210" s="7"/>
     </row>
     <row r="211">
-      <c r="A211" s="2"/>
+      <c r="A211" s="1"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
@@ -5871,7 +5891,7 @@
       <c r="W211" s="7"/>
     </row>
     <row r="212">
-      <c r="A212" s="2"/>
+      <c r="A212" s="1"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
@@ -5896,7 +5916,7 @@
       <c r="W212" s="7"/>
     </row>
     <row r="213">
-      <c r="A213" s="2"/>
+      <c r="A213" s="1"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
@@ -5921,7 +5941,7 @@
       <c r="W213" s="7"/>
     </row>
     <row r="214">
-      <c r="A214" s="2"/>
+      <c r="A214" s="1"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
@@ -5946,7 +5966,7 @@
       <c r="W214" s="7"/>
     </row>
     <row r="215">
-      <c r="A215" s="2"/>
+      <c r="A215" s="1"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
@@ -5971,7 +5991,7 @@
       <c r="W215" s="7"/>
     </row>
     <row r="216">
-      <c r="A216" s="2"/>
+      <c r="A216" s="1"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
@@ -5996,7 +6016,7 @@
       <c r="W216" s="7"/>
     </row>
     <row r="217">
-      <c r="A217" s="2"/>
+      <c r="A217" s="1"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -6021,7 +6041,7 @@
       <c r="W217" s="7"/>
     </row>
     <row r="218">
-      <c r="A218" s="2"/>
+      <c r="A218" s="1"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -6046,7 +6066,7 @@
       <c r="W218" s="7"/>
     </row>
     <row r="219">
-      <c r="A219" s="2"/>
+      <c r="A219" s="1"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
@@ -6071,7 +6091,7 @@
       <c r="W219" s="7"/>
     </row>
     <row r="220">
-      <c r="A220" s="2"/>
+      <c r="A220" s="1"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -6096,7 +6116,7 @@
       <c r="W220" s="7"/>
     </row>
     <row r="221">
-      <c r="A221" s="2"/>
+      <c r="A221" s="1"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
@@ -6121,7 +6141,7 @@
       <c r="W221" s="7"/>
     </row>
     <row r="222">
-      <c r="A222" s="2"/>
+      <c r="A222" s="1"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
@@ -6146,7 +6166,7 @@
       <c r="W222" s="7"/>
     </row>
     <row r="223">
-      <c r="A223" s="2"/>
+      <c r="A223" s="1"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
@@ -6171,7 +6191,7 @@
       <c r="W223" s="7"/>
     </row>
     <row r="224">
-      <c r="A224" s="2"/>
+      <c r="A224" s="1"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
@@ -6196,7 +6216,7 @@
       <c r="W224" s="7"/>
     </row>
     <row r="225">
-      <c r="A225" s="2"/>
+      <c r="A225" s="1"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
@@ -6221,7 +6241,7 @@
       <c r="W225" s="7"/>
     </row>
     <row r="226">
-      <c r="A226" s="2"/>
+      <c r="A226" s="1"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
@@ -6246,7 +6266,7 @@
       <c r="W226" s="7"/>
     </row>
     <row r="227">
-      <c r="A227" s="2"/>
+      <c r="A227" s="1"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
@@ -6271,7 +6291,7 @@
       <c r="W227" s="7"/>
     </row>
     <row r="228">
-      <c r="A228" s="2"/>
+      <c r="A228" s="1"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -6296,7 +6316,7 @@
       <c r="W228" s="7"/>
     </row>
     <row r="229">
-      <c r="A229" s="2"/>
+      <c r="A229" s="1"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
@@ -6321,7 +6341,7 @@
       <c r="W229" s="7"/>
     </row>
     <row r="230">
-      <c r="A230" s="2"/>
+      <c r="A230" s="1"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
@@ -6346,7 +6366,7 @@
       <c r="W230" s="7"/>
     </row>
     <row r="231">
-      <c r="A231" s="2"/>
+      <c r="A231" s="1"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
@@ -6371,7 +6391,7 @@
       <c r="W231" s="7"/>
     </row>
     <row r="232">
-      <c r="A232" s="2"/>
+      <c r="A232" s="1"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -6396,7 +6416,7 @@
       <c r="W232" s="7"/>
     </row>
     <row r="233">
-      <c r="A233" s="2"/>
+      <c r="A233" s="1"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
@@ -6421,7 +6441,7 @@
       <c r="W233" s="7"/>
     </row>
     <row r="234">
-      <c r="A234" s="2"/>
+      <c r="A234" s="1"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
@@ -6446,7 +6466,7 @@
       <c r="W234" s="7"/>
     </row>
     <row r="235">
-      <c r="A235" s="2"/>
+      <c r="A235" s="1"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
@@ -6471,7 +6491,7 @@
       <c r="W235" s="7"/>
     </row>
     <row r="236">
-      <c r="A236" s="2"/>
+      <c r="A236" s="1"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
@@ -6496,7 +6516,7 @@
       <c r="W236" s="7"/>
     </row>
     <row r="237">
-      <c r="A237" s="2"/>
+      <c r="A237" s="1"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
@@ -6521,7 +6541,7 @@
       <c r="W237" s="7"/>
     </row>
     <row r="238">
-      <c r="A238" s="2"/>
+      <c r="A238" s="1"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
@@ -6546,7 +6566,7 @@
       <c r="W238" s="7"/>
     </row>
     <row r="239">
-      <c r="A239" s="2"/>
+      <c r="A239" s="1"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
@@ -6571,7 +6591,7 @@
       <c r="W239" s="7"/>
     </row>
     <row r="240">
-      <c r="A240" s="2"/>
+      <c r="A240" s="1"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
@@ -6596,7 +6616,7 @@
       <c r="W240" s="7"/>
     </row>
     <row r="241">
-      <c r="A241" s="2"/>
+      <c r="A241" s="1"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
@@ -6621,7 +6641,7 @@
       <c r="W241" s="7"/>
     </row>
     <row r="242">
-      <c r="A242" s="2"/>
+      <c r="A242" s="1"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
@@ -6646,7 +6666,7 @@
       <c r="W242" s="7"/>
     </row>
     <row r="243">
-      <c r="A243" s="2"/>
+      <c r="A243" s="1"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
@@ -6671,7 +6691,7 @@
       <c r="W243" s="7"/>
     </row>
     <row r="244">
-      <c r="A244" s="2"/>
+      <c r="A244" s="1"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
@@ -6696,7 +6716,7 @@
       <c r="W244" s="7"/>
     </row>
     <row r="245">
-      <c r="A245" s="2"/>
+      <c r="A245" s="1"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
@@ -6721,7 +6741,7 @@
       <c r="W245" s="7"/>
     </row>
     <row r="246">
-      <c r="A246" s="2"/>
+      <c r="A246" s="1"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
@@ -6746,7 +6766,7 @@
       <c r="W246" s="7"/>
     </row>
     <row r="247">
-      <c r="A247" s="2"/>
+      <c r="A247" s="1"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
@@ -6771,7 +6791,7 @@
       <c r="W247" s="7"/>
     </row>
     <row r="248">
-      <c r="A248" s="2"/>
+      <c r="A248" s="1"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
@@ -6796,7 +6816,7 @@
       <c r="W248" s="7"/>
     </row>
     <row r="249">
-      <c r="A249" s="2"/>
+      <c r="A249" s="1"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
@@ -6821,7 +6841,7 @@
       <c r="W249" s="7"/>
     </row>
     <row r="250">
-      <c r="A250" s="2"/>
+      <c r="A250" s="1"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
@@ -6846,7 +6866,7 @@
       <c r="W250" s="7"/>
     </row>
     <row r="251">
-      <c r="A251" s="2"/>
+      <c r="A251" s="1"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
@@ -6871,7 +6891,7 @@
       <c r="W251" s="7"/>
     </row>
     <row r="252">
-      <c r="A252" s="2"/>
+      <c r="A252" s="1"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
@@ -6896,7 +6916,7 @@
       <c r="W252" s="7"/>
     </row>
     <row r="253">
-      <c r="A253" s="2"/>
+      <c r="A253" s="1"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
@@ -6921,7 +6941,7 @@
       <c r="W253" s="7"/>
     </row>
     <row r="254">
-      <c r="A254" s="2"/>
+      <c r="A254" s="1"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
@@ -6946,7 +6966,7 @@
       <c r="W254" s="7"/>
     </row>
     <row r="255">
-      <c r="A255" s="2"/>
+      <c r="A255" s="1"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
@@ -6971,7 +6991,7 @@
       <c r="W255" s="7"/>
     </row>
     <row r="256">
-      <c r="A256" s="2"/>
+      <c r="A256" s="1"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
@@ -6996,7 +7016,7 @@
       <c r="W256" s="7"/>
     </row>
     <row r="257">
-      <c r="A257" s="2"/>
+      <c r="A257" s="1"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
@@ -7021,7 +7041,7 @@
       <c r="W257" s="7"/>
     </row>
     <row r="258">
-      <c r="A258" s="2"/>
+      <c r="A258" s="1"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
@@ -7046,7 +7066,7 @@
       <c r="W258" s="7"/>
     </row>
     <row r="259">
-      <c r="A259" s="2"/>
+      <c r="A259" s="1"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
@@ -7071,7 +7091,7 @@
       <c r="W259" s="7"/>
     </row>
     <row r="260">
-      <c r="A260" s="2"/>
+      <c r="A260" s="1"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
@@ -7096,7 +7116,7 @@
       <c r="W260" s="7"/>
     </row>
     <row r="261">
-      <c r="A261" s="2"/>
+      <c r="A261" s="1"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
@@ -7121,7 +7141,7 @@
       <c r="W261" s="7"/>
     </row>
     <row r="262">
-      <c r="A262" s="2"/>
+      <c r="A262" s="1"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
@@ -7146,7 +7166,7 @@
       <c r="W262" s="7"/>
     </row>
     <row r="263">
-      <c r="A263" s="2"/>
+      <c r="A263" s="1"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
@@ -7171,7 +7191,7 @@
       <c r="W263" s="7"/>
     </row>
     <row r="264">
-      <c r="A264" s="2"/>
+      <c r="A264" s="1"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
@@ -7196,7 +7216,7 @@
       <c r="W264" s="7"/>
     </row>
     <row r="265">
-      <c r="A265" s="2"/>
+      <c r="A265" s="1"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
@@ -7221,7 +7241,7 @@
       <c r="W265" s="7"/>
     </row>
     <row r="266">
-      <c r="A266" s="2"/>
+      <c r="A266" s="1"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
@@ -7246,7 +7266,7 @@
       <c r="W266" s="7"/>
     </row>
     <row r="267">
-      <c r="A267" s="2"/>
+      <c r="A267" s="1"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
@@ -7271,7 +7291,7 @@
       <c r="W267" s="7"/>
     </row>
     <row r="268">
-      <c r="A268" s="2"/>
+      <c r="A268" s="1"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
@@ -7296,7 +7316,7 @@
       <c r="W268" s="7"/>
     </row>
     <row r="269">
-      <c r="A269" s="2"/>
+      <c r="A269" s="1"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
@@ -7321,7 +7341,7 @@
       <c r="W269" s="7"/>
     </row>
     <row r="270">
-      <c r="A270" s="2"/>
+      <c r="A270" s="1"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
@@ -7346,7 +7366,7 @@
       <c r="W270" s="7"/>
     </row>
     <row r="271">
-      <c r="A271" s="2"/>
+      <c r="A271" s="1"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
@@ -7371,7 +7391,7 @@
       <c r="W271" s="7"/>
     </row>
     <row r="272">
-      <c r="A272" s="2"/>
+      <c r="A272" s="1"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
@@ -7396,7 +7416,7 @@
       <c r="W272" s="7"/>
     </row>
     <row r="273">
-      <c r="A273" s="2"/>
+      <c r="A273" s="1"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
@@ -7421,7 +7441,7 @@
       <c r="W273" s="7"/>
     </row>
     <row r="274">
-      <c r="A274" s="2"/>
+      <c r="A274" s="1"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
@@ -7446,7 +7466,7 @@
       <c r="W274" s="7"/>
     </row>
     <row r="275">
-      <c r="A275" s="2"/>
+      <c r="A275" s="1"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
@@ -7471,7 +7491,7 @@
       <c r="W275" s="7"/>
     </row>
     <row r="276">
-      <c r="A276" s="2"/>
+      <c r="A276" s="1"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
@@ -7496,7 +7516,7 @@
       <c r="W276" s="7"/>
     </row>
     <row r="277">
-      <c r="A277" s="2"/>
+      <c r="A277" s="1"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
@@ -7521,7 +7541,7 @@
       <c r="W277" s="7"/>
     </row>
     <row r="278">
-      <c r="A278" s="2"/>
+      <c r="A278" s="1"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
@@ -7546,7 +7566,7 @@
       <c r="W278" s="7"/>
     </row>
     <row r="279">
-      <c r="A279" s="2"/>
+      <c r="A279" s="1"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
@@ -7571,7 +7591,7 @@
       <c r="W279" s="7"/>
     </row>
     <row r="280">
-      <c r="A280" s="2"/>
+      <c r="A280" s="1"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
@@ -7596,7 +7616,7 @@
       <c r="W280" s="7"/>
     </row>
     <row r="281">
-      <c r="A281" s="2"/>
+      <c r="A281" s="1"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
@@ -7621,7 +7641,7 @@
       <c r="W281" s="7"/>
     </row>
     <row r="282">
-      <c r="A282" s="2"/>
+      <c r="A282" s="1"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
@@ -7646,7 +7666,7 @@
       <c r="W282" s="7"/>
     </row>
     <row r="283">
-      <c r="A283" s="2"/>
+      <c r="A283" s="1"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
@@ -7671,7 +7691,7 @@
       <c r="W283" s="7"/>
     </row>
     <row r="284">
-      <c r="A284" s="2"/>
+      <c r="A284" s="1"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
@@ -7696,7 +7716,7 @@
       <c r="W284" s="7"/>
     </row>
     <row r="285">
-      <c r="A285" s="2"/>
+      <c r="A285" s="1"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
@@ -7721,7 +7741,7 @@
       <c r="W285" s="7"/>
     </row>
     <row r="286">
-      <c r="A286" s="2"/>
+      <c r="A286" s="1"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
@@ -7746,7 +7766,7 @@
       <c r="W286" s="7"/>
     </row>
     <row r="287">
-      <c r="A287" s="2"/>
+      <c r="A287" s="1"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
@@ -7771,7 +7791,7 @@
       <c r="W287" s="7"/>
     </row>
     <row r="288">
-      <c r="A288" s="2"/>
+      <c r="A288" s="1"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
@@ -7796,7 +7816,7 @@
       <c r="W288" s="7"/>
     </row>
     <row r="289">
-      <c r="A289" s="2"/>
+      <c r="A289" s="1"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
@@ -7821,7 +7841,7 @@
       <c r="W289" s="7"/>
     </row>
     <row r="290">
-      <c r="A290" s="2"/>
+      <c r="A290" s="1"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
@@ -7846,7 +7866,7 @@
       <c r="W290" s="7"/>
     </row>
     <row r="291">
-      <c r="A291" s="2"/>
+      <c r="A291" s="1"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
@@ -7871,7 +7891,7 @@
       <c r="W291" s="7"/>
     </row>
     <row r="292">
-      <c r="A292" s="2"/>
+      <c r="A292" s="1"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
@@ -7896,7 +7916,7 @@
       <c r="W292" s="7"/>
     </row>
     <row r="293">
-      <c r="A293" s="2"/>
+      <c r="A293" s="1"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
@@ -7921,7 +7941,7 @@
       <c r="W293" s="7"/>
     </row>
     <row r="294">
-      <c r="A294" s="2"/>
+      <c r="A294" s="1"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
@@ -7946,7 +7966,7 @@
       <c r="W294" s="7"/>
     </row>
     <row r="295">
-      <c r="A295" s="2"/>
+      <c r="A295" s="1"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
@@ -7971,7 +7991,7 @@
       <c r="W295" s="7"/>
     </row>
     <row r="296">
-      <c r="A296" s="2"/>
+      <c r="A296" s="1"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
@@ -7996,7 +8016,7 @@
       <c r="W296" s="7"/>
     </row>
     <row r="297">
-      <c r="A297" s="2"/>
+      <c r="A297" s="1"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
@@ -8021,7 +8041,7 @@
       <c r="W297" s="7"/>
     </row>
     <row r="298">
-      <c r="A298" s="2"/>
+      <c r="A298" s="1"/>
       <c r="B298" s="7"/>
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
@@ -8046,7 +8066,7 @@
       <c r="W298" s="7"/>
     </row>
     <row r="299">
-      <c r="A299" s="2"/>
+      <c r="A299" s="1"/>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
@@ -8071,7 +8091,7 @@
       <c r="W299" s="7"/>
     </row>
     <row r="300">
-      <c r="A300" s="2"/>
+      <c r="A300" s="1"/>
       <c r="B300" s="7"/>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
@@ -8096,7 +8116,7 @@
       <c r="W300" s="7"/>
     </row>
     <row r="301">
-      <c r="A301" s="2"/>
+      <c r="A301" s="1"/>
       <c r="B301" s="7"/>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
@@ -8121,7 +8141,7 @@
       <c r="W301" s="7"/>
     </row>
     <row r="302">
-      <c r="A302" s="2"/>
+      <c r="A302" s="1"/>
       <c r="B302" s="7"/>
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
@@ -8146,7 +8166,7 @@
       <c r="W302" s="7"/>
     </row>
     <row r="303">
-      <c r="A303" s="2"/>
+      <c r="A303" s="1"/>
       <c r="B303" s="7"/>
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
@@ -8171,7 +8191,7 @@
       <c r="W303" s="7"/>
     </row>
     <row r="304">
-      <c r="A304" s="2"/>
+      <c r="A304" s="1"/>
       <c r="B304" s="7"/>
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
@@ -8196,7 +8216,7 @@
       <c r="W304" s="7"/>
     </row>
     <row r="305">
-      <c r="A305" s="2"/>
+      <c r="A305" s="1"/>
       <c r="B305" s="7"/>
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
@@ -8221,7 +8241,7 @@
       <c r="W305" s="7"/>
     </row>
     <row r="306">
-      <c r="A306" s="2"/>
+      <c r="A306" s="1"/>
       <c r="B306" s="7"/>
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
@@ -8246,7 +8266,7 @@
       <c r="W306" s="7"/>
     </row>
     <row r="307">
-      <c r="A307" s="2"/>
+      <c r="A307" s="1"/>
       <c r="B307" s="7"/>
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
@@ -8271,7 +8291,7 @@
       <c r="W307" s="7"/>
     </row>
     <row r="308">
-      <c r="A308" s="2"/>
+      <c r="A308" s="1"/>
       <c r="B308" s="7"/>
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
@@ -8296,7 +8316,7 @@
       <c r="W308" s="7"/>
     </row>
     <row r="309">
-      <c r="A309" s="2"/>
+      <c r="A309" s="1"/>
       <c r="B309" s="7"/>
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
@@ -8321,7 +8341,7 @@
       <c r="W309" s="7"/>
     </row>
     <row r="310">
-      <c r="A310" s="2"/>
+      <c r="A310" s="1"/>
       <c r="B310" s="7"/>
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
@@ -8346,7 +8366,7 @@
       <c r="W310" s="7"/>
     </row>
     <row r="311">
-      <c r="A311" s="2"/>
+      <c r="A311" s="1"/>
       <c r="B311" s="7"/>
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
@@ -8371,7 +8391,7 @@
       <c r="W311" s="7"/>
     </row>
     <row r="312">
-      <c r="A312" s="2"/>
+      <c r="A312" s="1"/>
       <c r="B312" s="7"/>
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
@@ -8396,7 +8416,7 @@
       <c r="W312" s="7"/>
     </row>
     <row r="313">
-      <c r="A313" s="2"/>
+      <c r="A313" s="1"/>
       <c r="B313" s="7"/>
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
@@ -8421,7 +8441,7 @@
       <c r="W313" s="7"/>
     </row>
     <row r="314">
-      <c r="A314" s="2"/>
+      <c r="A314" s="1"/>
       <c r="B314" s="7"/>
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
@@ -8446,7 +8466,7 @@
       <c r="W314" s="7"/>
     </row>
     <row r="315">
-      <c r="A315" s="2"/>
+      <c r="A315" s="1"/>
       <c r="B315" s="7"/>
       <c r="C315" s="7"/>
       <c r="D315" s="7"/>
@@ -8471,7 +8491,7 @@
       <c r="W315" s="7"/>
     </row>
     <row r="316">
-      <c r="A316" s="2"/>
+      <c r="A316" s="1"/>
       <c r="B316" s="7"/>
       <c r="C316" s="7"/>
       <c r="D316" s="7"/>
@@ -8496,7 +8516,7 @@
       <c r="W316" s="7"/>
     </row>
     <row r="317">
-      <c r="A317" s="2"/>
+      <c r="A317" s="1"/>
       <c r="B317" s="7"/>
       <c r="C317" s="7"/>
       <c r="D317" s="7"/>
@@ -8521,7 +8541,7 @@
       <c r="W317" s="7"/>
     </row>
     <row r="318">
-      <c r="A318" s="2"/>
+      <c r="A318" s="1"/>
       <c r="B318" s="7"/>
       <c r="C318" s="7"/>
       <c r="D318" s="7"/>
@@ -8546,7 +8566,7 @@
       <c r="W318" s="7"/>
     </row>
     <row r="319">
-      <c r="A319" s="2"/>
+      <c r="A319" s="1"/>
       <c r="B319" s="7"/>
       <c r="C319" s="7"/>
       <c r="D319" s="7"/>
@@ -8571,7 +8591,7 @@
       <c r="W319" s="7"/>
     </row>
     <row r="320">
-      <c r="A320" s="2"/>
+      <c r="A320" s="1"/>
       <c r="B320" s="7"/>
       <c r="C320" s="7"/>
       <c r="D320" s="7"/>
@@ -8596,7 +8616,7 @@
       <c r="W320" s="7"/>
     </row>
     <row r="321">
-      <c r="A321" s="2"/>
+      <c r="A321" s="1"/>
       <c r="B321" s="7"/>
       <c r="C321" s="7"/>
       <c r="D321" s="7"/>
@@ -8621,7 +8641,7 @@
       <c r="W321" s="7"/>
     </row>
     <row r="322">
-      <c r="A322" s="2"/>
+      <c r="A322" s="1"/>
       <c r="B322" s="7"/>
       <c r="C322" s="7"/>
       <c r="D322" s="7"/>
@@ -8646,7 +8666,7 @@
       <c r="W322" s="7"/>
     </row>
     <row r="323">
-      <c r="A323" s="2"/>
+      <c r="A323" s="1"/>
       <c r="B323" s="7"/>
       <c r="C323" s="7"/>
       <c r="D323" s="7"/>
@@ -8671,7 +8691,7 @@
       <c r="W323" s="7"/>
     </row>
     <row r="324">
-      <c r="A324" s="2"/>
+      <c r="A324" s="1"/>
       <c r="B324" s="7"/>
       <c r="C324" s="7"/>
       <c r="D324" s="7"/>
@@ -8696,7 +8716,7 @@
       <c r="W324" s="7"/>
     </row>
     <row r="325">
-      <c r="A325" s="2"/>
+      <c r="A325" s="1"/>
       <c r="B325" s="7"/>
       <c r="C325" s="7"/>
       <c r="D325" s="7"/>
@@ -8721,7 +8741,7 @@
       <c r="W325" s="7"/>
     </row>
     <row r="326">
-      <c r="A326" s="2"/>
+      <c r="A326" s="1"/>
       <c r="B326" s="7"/>
       <c r="C326" s="7"/>
       <c r="D326" s="7"/>
@@ -8746,7 +8766,7 @@
       <c r="W326" s="7"/>
     </row>
     <row r="327">
-      <c r="A327" s="2"/>
+      <c r="A327" s="1"/>
       <c r="B327" s="7"/>
       <c r="C327" s="7"/>
       <c r="D327" s="7"/>
@@ -8771,7 +8791,7 @@
       <c r="W327" s="7"/>
     </row>
     <row r="328">
-      <c r="A328" s="2"/>
+      <c r="A328" s="1"/>
       <c r="B328" s="7"/>
       <c r="C328" s="7"/>
       <c r="D328" s="7"/>
@@ -8796,7 +8816,7 @@
       <c r="W328" s="7"/>
     </row>
     <row r="329">
-      <c r="A329" s="2"/>
+      <c r="A329" s="1"/>
       <c r="B329" s="7"/>
       <c r="C329" s="7"/>
       <c r="D329" s="7"/>
@@ -8821,7 +8841,7 @@
       <c r="W329" s="7"/>
     </row>
     <row r="330">
-      <c r="A330" s="2"/>
+      <c r="A330" s="1"/>
       <c r="B330" s="7"/>
       <c r="C330" s="7"/>
       <c r="D330" s="7"/>
@@ -8846,7 +8866,7 @@
       <c r="W330" s="7"/>
     </row>
     <row r="331">
-      <c r="A331" s="2"/>
+      <c r="A331" s="1"/>
       <c r="B331" s="7"/>
       <c r="C331" s="7"/>
       <c r="D331" s="7"/>
@@ -8871,7 +8891,7 @@
       <c r="W331" s="7"/>
     </row>
     <row r="332">
-      <c r="A332" s="2"/>
+      <c r="A332" s="1"/>
       <c r="B332" s="7"/>
       <c r="C332" s="7"/>
       <c r="D332" s="7"/>
@@ -8896,7 +8916,7 @@
       <c r="W332" s="7"/>
     </row>
     <row r="333">
-      <c r="A333" s="2"/>
+      <c r="A333" s="1"/>
       <c r="B333" s="7"/>
       <c r="C333" s="7"/>
       <c r="D333" s="7"/>
@@ -8921,7 +8941,7 @@
       <c r="W333" s="7"/>
     </row>
     <row r="334">
-      <c r="A334" s="2"/>
+      <c r="A334" s="1"/>
       <c r="B334" s="7"/>
       <c r="C334" s="7"/>
       <c r="D334" s="7"/>
@@ -8946,7 +8966,7 @@
       <c r="W334" s="7"/>
     </row>
     <row r="335">
-      <c r="A335" s="2"/>
+      <c r="A335" s="1"/>
       <c r="B335" s="7"/>
       <c r="C335" s="7"/>
       <c r="D335" s="7"/>
@@ -8971,7 +8991,7 @@
       <c r="W335" s="7"/>
     </row>
     <row r="336">
-      <c r="A336" s="2"/>
+      <c r="A336" s="1"/>
       <c r="B336" s="7"/>
       <c r="C336" s="7"/>
       <c r="D336" s="7"/>
@@ -8996,7 +9016,7 @@
       <c r="W336" s="7"/>
     </row>
     <row r="337">
-      <c r="A337" s="2"/>
+      <c r="A337" s="1"/>
       <c r="B337" s="7"/>
       <c r="C337" s="7"/>
       <c r="D337" s="7"/>
@@ -9021,7 +9041,7 @@
       <c r="W337" s="7"/>
     </row>
     <row r="338">
-      <c r="A338" s="2"/>
+      <c r="A338" s="1"/>
       <c r="B338" s="7"/>
       <c r="C338" s="7"/>
       <c r="D338" s="7"/>
@@ -9046,7 +9066,7 @@
       <c r="W338" s="7"/>
     </row>
     <row r="339">
-      <c r="A339" s="2"/>
+      <c r="A339" s="1"/>
       <c r="B339" s="7"/>
       <c r="C339" s="7"/>
       <c r="D339" s="7"/>
@@ -9071,7 +9091,7 @@
       <c r="W339" s="7"/>
     </row>
     <row r="340">
-      <c r="A340" s="2"/>
+      <c r="A340" s="1"/>
       <c r="B340" s="7"/>
       <c r="C340" s="7"/>
       <c r="D340" s="7"/>
@@ -9096,7 +9116,7 @@
       <c r="W340" s="7"/>
     </row>
     <row r="341">
-      <c r="A341" s="2"/>
+      <c r="A341" s="1"/>
       <c r="B341" s="7"/>
       <c r="C341" s="7"/>
       <c r="D341" s="7"/>
@@ -9121,7 +9141,7 @@
       <c r="W341" s="7"/>
     </row>
     <row r="342">
-      <c r="A342" s="2"/>
+      <c r="A342" s="1"/>
       <c r="B342" s="7"/>
       <c r="C342" s="7"/>
       <c r="D342" s="7"/>
@@ -9146,7 +9166,7 @@
       <c r="W342" s="7"/>
     </row>
     <row r="343">
-      <c r="A343" s="2"/>
+      <c r="A343" s="1"/>
       <c r="B343" s="7"/>
       <c r="C343" s="7"/>
       <c r="D343" s="7"/>
@@ -9171,7 +9191,7 @@
       <c r="W343" s="7"/>
     </row>
     <row r="344">
-      <c r="A344" s="2"/>
+      <c r="A344" s="1"/>
       <c r="B344" s="7"/>
       <c r="C344" s="7"/>
       <c r="D344" s="7"/>
@@ -9196,7 +9216,7 @@
       <c r="W344" s="7"/>
     </row>
     <row r="345">
-      <c r="A345" s="2"/>
+      <c r="A345" s="1"/>
       <c r="B345" s="7"/>
       <c r="C345" s="7"/>
       <c r="D345" s="7"/>
@@ -9221,7 +9241,7 @@
       <c r="W345" s="7"/>
     </row>
     <row r="346">
-      <c r="A346" s="2"/>
+      <c r="A346" s="1"/>
       <c r="B346" s="7"/>
       <c r="C346" s="7"/>
       <c r="D346" s="7"/>
@@ -9246,7 +9266,7 @@
       <c r="W346" s="7"/>
     </row>
     <row r="347">
-      <c r="A347" s="2"/>
+      <c r="A347" s="1"/>
       <c r="B347" s="7"/>
       <c r="C347" s="7"/>
       <c r="D347" s="7"/>
@@ -9271,7 +9291,7 @@
       <c r="W347" s="7"/>
     </row>
     <row r="348">
-      <c r="A348" s="2"/>
+      <c r="A348" s="1"/>
       <c r="B348" s="7"/>
       <c r="C348" s="7"/>
       <c r="D348" s="7"/>
@@ -9296,7 +9316,7 @@
       <c r="W348" s="7"/>
     </row>
     <row r="349">
-      <c r="A349" s="2"/>
+      <c r="A349" s="1"/>
       <c r="B349" s="7"/>
       <c r="C349" s="7"/>
       <c r="D349" s="7"/>
@@ -9321,7 +9341,7 @@
       <c r="W349" s="7"/>
     </row>
     <row r="350">
-      <c r="A350" s="2"/>
+      <c r="A350" s="1"/>
       <c r="B350" s="7"/>
       <c r="C350" s="7"/>
       <c r="D350" s="7"/>
@@ -9346,7 +9366,7 @@
       <c r="W350" s="7"/>
     </row>
     <row r="351">
-      <c r="A351" s="2"/>
+      <c r="A351" s="1"/>
       <c r="B351" s="7"/>
       <c r="C351" s="7"/>
       <c r="D351" s="7"/>
@@ -9371,7 +9391,7 @@
       <c r="W351" s="7"/>
     </row>
     <row r="352">
-      <c r="A352" s="2"/>
+      <c r="A352" s="1"/>
       <c r="B352" s="7"/>
       <c r="C352" s="7"/>
       <c r="D352" s="7"/>
@@ -9396,7 +9416,7 @@
       <c r="W352" s="7"/>
     </row>
     <row r="353">
-      <c r="A353" s="2"/>
+      <c r="A353" s="1"/>
       <c r="B353" s="7"/>
       <c r="C353" s="7"/>
       <c r="D353" s="7"/>
@@ -9421,7 +9441,7 @@
       <c r="W353" s="7"/>
     </row>
     <row r="354">
-      <c r="A354" s="2"/>
+      <c r="A354" s="1"/>
       <c r="B354" s="7"/>
       <c r="C354" s="7"/>
       <c r="D354" s="7"/>
@@ -9446,7 +9466,7 @@
       <c r="W354" s="7"/>
     </row>
     <row r="355">
-      <c r="A355" s="2"/>
+      <c r="A355" s="1"/>
       <c r="B355" s="7"/>
       <c r="C355" s="7"/>
       <c r="D355" s="7"/>
@@ -9471,7 +9491,7 @@
       <c r="W355" s="7"/>
     </row>
     <row r="356">
-      <c r="A356" s="2"/>
+      <c r="A356" s="1"/>
       <c r="B356" s="7"/>
       <c r="C356" s="7"/>
       <c r="D356" s="7"/>
@@ -9496,7 +9516,7 @@
       <c r="W356" s="7"/>
     </row>
     <row r="357">
-      <c r="A357" s="2"/>
+      <c r="A357" s="1"/>
       <c r="B357" s="7"/>
       <c r="C357" s="7"/>
       <c r="D357" s="7"/>
@@ -9521,7 +9541,7 @@
       <c r="W357" s="7"/>
     </row>
     <row r="358">
-      <c r="A358" s="2"/>
+      <c r="A358" s="1"/>
       <c r="B358" s="7"/>
       <c r="C358" s="7"/>
       <c r="D358" s="7"/>
@@ -9546,7 +9566,7 @@
       <c r="W358" s="7"/>
     </row>
     <row r="359">
-      <c r="A359" s="2"/>
+      <c r="A359" s="1"/>
       <c r="B359" s="7"/>
       <c r="C359" s="7"/>
       <c r="D359" s="7"/>
@@ -9571,7 +9591,7 @@
       <c r="W359" s="7"/>
     </row>
     <row r="360">
-      <c r="A360" s="2"/>
+      <c r="A360" s="1"/>
       <c r="B360" s="7"/>
       <c r="C360" s="7"/>
       <c r="D360" s="7"/>
@@ -9596,7 +9616,7 @@
       <c r="W360" s="7"/>
     </row>
     <row r="361">
-      <c r="A361" s="2"/>
+      <c r="A361" s="1"/>
       <c r="B361" s="7"/>
       <c r="C361" s="7"/>
       <c r="D361" s="7"/>
@@ -9621,7 +9641,7 @@
       <c r="W361" s="7"/>
     </row>
     <row r="362">
-      <c r="A362" s="2"/>
+      <c r="A362" s="1"/>
       <c r="B362" s="7"/>
       <c r="C362" s="7"/>
       <c r="D362" s="7"/>
@@ -9646,7 +9666,7 @@
       <c r="W362" s="7"/>
     </row>
     <row r="363">
-      <c r="A363" s="2"/>
+      <c r="A363" s="1"/>
       <c r="B363" s="7"/>
       <c r="C363" s="7"/>
       <c r="D363" s="7"/>
@@ -9671,7 +9691,7 @@
       <c r="W363" s="7"/>
     </row>
     <row r="364">
-      <c r="A364" s="2"/>
+      <c r="A364" s="1"/>
       <c r="B364" s="7"/>
       <c r="C364" s="7"/>
       <c r="D364" s="7"/>
@@ -9696,7 +9716,7 @@
       <c r="W364" s="7"/>
     </row>
     <row r="365">
-      <c r="A365" s="2"/>
+      <c r="A365" s="1"/>
       <c r="B365" s="7"/>
       <c r="C365" s="7"/>
       <c r="D365" s="7"/>
@@ -9721,7 +9741,7 @@
       <c r="W365" s="7"/>
     </row>
     <row r="366">
-      <c r="A366" s="2"/>
+      <c r="A366" s="1"/>
       <c r="B366" s="7"/>
       <c r="C366" s="7"/>
       <c r="D366" s="7"/>
@@ -9746,7 +9766,7 @@
       <c r="W366" s="7"/>
     </row>
     <row r="367">
-      <c r="A367" s="2"/>
+      <c r="A367" s="1"/>
       <c r="B367" s="7"/>
       <c r="C367" s="7"/>
       <c r="D367" s="7"/>
@@ -9771,7 +9791,7 @@
       <c r="W367" s="7"/>
     </row>
     <row r="368">
-      <c r="A368" s="2"/>
+      <c r="A368" s="1"/>
       <c r="B368" s="7"/>
       <c r="C368" s="7"/>
       <c r="D368" s="7"/>
@@ -9796,7 +9816,7 @@
       <c r="W368" s="7"/>
     </row>
     <row r="369">
-      <c r="A369" s="2"/>
+      <c r="A369" s="1"/>
       <c r="B369" s="7"/>
       <c r="C369" s="7"/>
       <c r="D369" s="7"/>
@@ -9821,7 +9841,7 @@
       <c r="W369" s="7"/>
     </row>
     <row r="370">
-      <c r="A370" s="2"/>
+      <c r="A370" s="1"/>
       <c r="B370" s="7"/>
       <c r="C370" s="7"/>
       <c r="D370" s="7"/>
@@ -9846,7 +9866,7 @@
       <c r="W370" s="7"/>
     </row>
     <row r="371">
-      <c r="A371" s="2"/>
+      <c r="A371" s="1"/>
       <c r="B371" s="7"/>
       <c r="C371" s="7"/>
       <c r="D371" s="7"/>
@@ -9871,7 +9891,7 @@
       <c r="W371" s="7"/>
     </row>
     <row r="372">
-      <c r="A372" s="2"/>
+      <c r="A372" s="1"/>
       <c r="B372" s="7"/>
       <c r="C372" s="7"/>
       <c r="D372" s="7"/>
@@ -9896,7 +9916,7 @@
       <c r="W372" s="7"/>
     </row>
     <row r="373">
-      <c r="A373" s="2"/>
+      <c r="A373" s="1"/>
       <c r="B373" s="7"/>
       <c r="C373" s="7"/>
       <c r="D373" s="7"/>
@@ -9921,7 +9941,7 @@
       <c r="W373" s="7"/>
     </row>
     <row r="374">
-      <c r="A374" s="2"/>
+      <c r="A374" s="1"/>
       <c r="B374" s="7"/>
       <c r="C374" s="7"/>
       <c r="D374" s="7"/>
@@ -9946,7 +9966,7 @@
       <c r="W374" s="7"/>
     </row>
     <row r="375">
-      <c r="A375" s="2"/>
+      <c r="A375" s="1"/>
       <c r="B375" s="7"/>
       <c r="C375" s="7"/>
       <c r="D375" s="7"/>
@@ -9971,7 +9991,7 @@
       <c r="W375" s="7"/>
     </row>
     <row r="376">
-      <c r="A376" s="2"/>
+      <c r="A376" s="1"/>
       <c r="B376" s="7"/>
       <c r="C376" s="7"/>
       <c r="D376" s="7"/>
@@ -9996,7 +10016,7 @@
       <c r="W376" s="7"/>
     </row>
     <row r="377">
-      <c r="A377" s="2"/>
+      <c r="A377" s="1"/>
       <c r="B377" s="7"/>
       <c r="C377" s="7"/>
       <c r="D377" s="7"/>
@@ -10021,7 +10041,7 @@
       <c r="W377" s="7"/>
     </row>
     <row r="378">
-      <c r="A378" s="2"/>
+      <c r="A378" s="1"/>
       <c r="B378" s="7"/>
       <c r="C378" s="7"/>
       <c r="D378" s="7"/>
@@ -10046,7 +10066,7 @@
       <c r="W378" s="7"/>
     </row>
     <row r="379">
-      <c r="A379" s="2"/>
+      <c r="A379" s="1"/>
       <c r="B379" s="7"/>
       <c r="C379" s="7"/>
       <c r="D379" s="7"/>
@@ -10071,7 +10091,7 @@
       <c r="W379" s="7"/>
     </row>
     <row r="380">
-      <c r="A380" s="2"/>
+      <c r="A380" s="1"/>
       <c r="B380" s="7"/>
       <c r="C380" s="7"/>
       <c r="D380" s="7"/>
@@ -10096,7 +10116,7 @@
       <c r="W380" s="7"/>
     </row>
     <row r="381">
-      <c r="A381" s="2"/>
+      <c r="A381" s="1"/>
       <c r="B381" s="7"/>
       <c r="C381" s="7"/>
       <c r="D381" s="7"/>
@@ -10121,7 +10141,7 @@
       <c r="W381" s="7"/>
     </row>
     <row r="382">
-      <c r="A382" s="2"/>
+      <c r="A382" s="1"/>
       <c r="B382" s="7"/>
       <c r="C382" s="7"/>
       <c r="D382" s="7"/>
@@ -10146,7 +10166,7 @@
       <c r="W382" s="7"/>
     </row>
     <row r="383">
-      <c r="A383" s="2"/>
+      <c r="A383" s="1"/>
       <c r="B383" s="7"/>
       <c r="C383" s="7"/>
       <c r="D383" s="7"/>
@@ -10171,7 +10191,7 @@
       <c r="W383" s="7"/>
     </row>
     <row r="384">
-      <c r="A384" s="2"/>
+      <c r="A384" s="1"/>
       <c r="B384" s="7"/>
       <c r="C384" s="7"/>
       <c r="D384" s="7"/>
@@ -10196,7 +10216,7 @@
       <c r="W384" s="7"/>
     </row>
     <row r="385">
-      <c r="A385" s="2"/>
+      <c r="A385" s="1"/>
       <c r="B385" s="7"/>
       <c r="C385" s="7"/>
       <c r="D385" s="7"/>
@@ -10221,7 +10241,7 @@
       <c r="W385" s="7"/>
     </row>
     <row r="386">
-      <c r="A386" s="2"/>
+      <c r="A386" s="1"/>
       <c r="B386" s="7"/>
       <c r="C386" s="7"/>
       <c r="D386" s="7"/>
@@ -10246,7 +10266,7 @@
       <c r="W386" s="7"/>
     </row>
     <row r="387">
-      <c r="A387" s="2"/>
+      <c r="A387" s="1"/>
       <c r="B387" s="7"/>
       <c r="C387" s="7"/>
       <c r="D387" s="7"/>
@@ -10271,7 +10291,7 @@
       <c r="W387" s="7"/>
     </row>
     <row r="388">
-      <c r="A388" s="2"/>
+      <c r="A388" s="1"/>
       <c r="B388" s="7"/>
       <c r="C388" s="7"/>
       <c r="D388" s="7"/>
@@ -10296,7 +10316,7 @@
       <c r="W388" s="7"/>
     </row>
     <row r="389">
-      <c r="A389" s="2"/>
+      <c r="A389" s="1"/>
       <c r="B389" s="7"/>
       <c r="C389" s="7"/>
       <c r="D389" s="7"/>
@@ -10321,7 +10341,7 @@
       <c r="W389" s="7"/>
     </row>
     <row r="390">
-      <c r="A390" s="2"/>
+      <c r="A390" s="1"/>
       <c r="B390" s="7"/>
       <c r="C390" s="7"/>
       <c r="D390" s="7"/>
@@ -10346,7 +10366,7 @@
       <c r="W390" s="7"/>
     </row>
     <row r="391">
-      <c r="A391" s="2"/>
+      <c r="A391" s="1"/>
       <c r="B391" s="7"/>
       <c r="C391" s="7"/>
       <c r="D391" s="7"/>
@@ -10371,7 +10391,7 @@
       <c r="W391" s="7"/>
     </row>
     <row r="392">
-      <c r="A392" s="2"/>
+      <c r="A392" s="1"/>
       <c r="B392" s="7"/>
       <c r="C392" s="7"/>
       <c r="D392" s="7"/>
@@ -10396,7 +10416,7 @@
       <c r="W392" s="7"/>
     </row>
     <row r="393">
-      <c r="A393" s="2"/>
+      <c r="A393" s="1"/>
       <c r="B393" s="7"/>
       <c r="C393" s="7"/>
       <c r="D393" s="7"/>
@@ -10421,7 +10441,7 @@
       <c r="W393" s="7"/>
     </row>
     <row r="394">
-      <c r="A394" s="2"/>
+      <c r="A394" s="1"/>
       <c r="B394" s="7"/>
       <c r="C394" s="7"/>
       <c r="D394" s="7"/>
@@ -10446,7 +10466,7 @@
       <c r="W394" s="7"/>
     </row>
     <row r="395">
-      <c r="A395" s="2"/>
+      <c r="A395" s="1"/>
       <c r="B395" s="7"/>
       <c r="C395" s="7"/>
       <c r="D395" s="7"/>
@@ -10471,7 +10491,7 @@
       <c r="W395" s="7"/>
     </row>
     <row r="396">
-      <c r="A396" s="2"/>
+      <c r="A396" s="1"/>
       <c r="B396" s="7"/>
       <c r="C396" s="7"/>
       <c r="D396" s="7"/>
@@ -10496,7 +10516,7 @@
       <c r="W396" s="7"/>
     </row>
     <row r="397">
-      <c r="A397" s="2"/>
+      <c r="A397" s="1"/>
       <c r="B397" s="7"/>
       <c r="C397" s="7"/>
       <c r="D397" s="7"/>
@@ -10521,7 +10541,7 @@
       <c r="W397" s="7"/>
     </row>
     <row r="398">
-      <c r="A398" s="2"/>
+      <c r="A398" s="1"/>
       <c r="B398" s="7"/>
       <c r="C398" s="7"/>
       <c r="D398" s="7"/>
@@ -10546,7 +10566,7 @@
       <c r="W398" s="7"/>
     </row>
     <row r="399">
-      <c r="A399" s="2"/>
+      <c r="A399" s="1"/>
       <c r="B399" s="7"/>
       <c r="C399" s="7"/>
       <c r="D399" s="7"/>
@@ -10571,7 +10591,7 @@
       <c r="W399" s="7"/>
     </row>
     <row r="400">
-      <c r="A400" s="2"/>
+      <c r="A400" s="1"/>
       <c r="B400" s="7"/>
       <c r="C400" s="7"/>
       <c r="D400" s="7"/>
@@ -10596,7 +10616,7 @@
       <c r="W400" s="7"/>
     </row>
     <row r="401">
-      <c r="A401" s="2"/>
+      <c r="A401" s="1"/>
       <c r="B401" s="7"/>
       <c r="C401" s="7"/>
       <c r="D401" s="7"/>
@@ -10621,7 +10641,7 @@
       <c r="W401" s="7"/>
     </row>
     <row r="402">
-      <c r="A402" s="2"/>
+      <c r="A402" s="1"/>
       <c r="B402" s="7"/>
       <c r="C402" s="7"/>
       <c r="D402" s="7"/>
@@ -10646,7 +10666,7 @@
       <c r="W402" s="7"/>
     </row>
     <row r="403">
-      <c r="A403" s="2"/>
+      <c r="A403" s="1"/>
       <c r="B403" s="7"/>
       <c r="C403" s="7"/>
       <c r="D403" s="7"/>
@@ -10671,7 +10691,7 @@
       <c r="W403" s="7"/>
     </row>
     <row r="404">
-      <c r="A404" s="2"/>
+      <c r="A404" s="1"/>
       <c r="B404" s="7"/>
       <c r="C404" s="7"/>
       <c r="D404" s="7"/>
@@ -10696,7 +10716,7 @@
       <c r="W404" s="7"/>
     </row>
     <row r="405">
-      <c r="A405" s="2"/>
+      <c r="A405" s="1"/>
       <c r="B405" s="7"/>
       <c r="C405" s="7"/>
       <c r="D405" s="7"/>
@@ -10721,7 +10741,7 @@
       <c r="W405" s="7"/>
     </row>
     <row r="406">
-      <c r="A406" s="2"/>
+      <c r="A406" s="1"/>
       <c r="B406" s="7"/>
       <c r="C406" s="7"/>
       <c r="D406" s="7"/>
@@ -10746,7 +10766,7 @@
       <c r="W406" s="7"/>
     </row>
     <row r="407">
-      <c r="A407" s="2"/>
+      <c r="A407" s="1"/>
       <c r="B407" s="7"/>
       <c r="C407" s="7"/>
       <c r="D407" s="7"/>
@@ -10771,7 +10791,7 @@
       <c r="W407" s="7"/>
     </row>
     <row r="408">
-      <c r="A408" s="2"/>
+      <c r="A408" s="1"/>
       <c r="B408" s="7"/>
       <c r="C408" s="7"/>
       <c r="D408" s="7"/>
@@ -10796,7 +10816,7 @@
       <c r="W408" s="7"/>
     </row>
     <row r="409">
-      <c r="A409" s="2"/>
+      <c r="A409" s="1"/>
       <c r="B409" s="7"/>
       <c r="C409" s="7"/>
       <c r="D409" s="7"/>
@@ -10821,7 +10841,7 @@
       <c r="W409" s="7"/>
     </row>
     <row r="410">
-      <c r="A410" s="2"/>
+      <c r="A410" s="1"/>
       <c r="B410" s="7"/>
       <c r="C410" s="7"/>
       <c r="D410" s="7"/>
@@ -10846,7 +10866,7 @@
       <c r="W410" s="7"/>
     </row>
     <row r="411">
-      <c r="A411" s="2"/>
+      <c r="A411" s="1"/>
       <c r="B411" s="7"/>
       <c r="C411" s="7"/>
       <c r="D411" s="7"/>
@@ -10871,7 +10891,7 @@
       <c r="W411" s="7"/>
     </row>
     <row r="412">
-      <c r="A412" s="2"/>
+      <c r="A412" s="1"/>
       <c r="B412" s="7"/>
       <c r="C412" s="7"/>
       <c r="D412" s="7"/>
@@ -10896,7 +10916,7 @@
       <c r="W412" s="7"/>
     </row>
     <row r="413">
-      <c r="A413" s="2"/>
+      <c r="A413" s="1"/>
       <c r="B413" s="7"/>
       <c r="C413" s="7"/>
       <c r="D413" s="7"/>
@@ -10921,7 +10941,7 @@
       <c r="W413" s="7"/>
     </row>
     <row r="414">
-      <c r="A414" s="2"/>
+      <c r="A414" s="1"/>
       <c r="B414" s="7"/>
       <c r="C414" s="7"/>
       <c r="D414" s="7"/>
@@ -10946,7 +10966,7 @@
       <c r="W414" s="7"/>
     </row>
     <row r="415">
-      <c r="A415" s="2"/>
+      <c r="A415" s="1"/>
       <c r="B415" s="7"/>
       <c r="C415" s="7"/>
       <c r="D415" s="7"/>
@@ -10971,7 +10991,7 @@
       <c r="W415" s="7"/>
     </row>
     <row r="416">
-      <c r="A416" s="2"/>
+      <c r="A416" s="1"/>
       <c r="B416" s="7"/>
       <c r="C416" s="7"/>
       <c r="D416" s="7"/>
@@ -10996,7 +11016,7 @@
       <c r="W416" s="7"/>
     </row>
     <row r="417">
-      <c r="A417" s="2"/>
+      <c r="A417" s="1"/>
       <c r="B417" s="7"/>
       <c r="C417" s="7"/>
       <c r="D417" s="7"/>
@@ -11021,7 +11041,7 @@
       <c r="W417" s="7"/>
     </row>
     <row r="418">
-      <c r="A418" s="2"/>
+      <c r="A418" s="1"/>
       <c r="B418" s="7"/>
       <c r="C418" s="7"/>
       <c r="D418" s="7"/>
@@ -11046,7 +11066,7 @@
       <c r="W418" s="7"/>
     </row>
     <row r="419">
-      <c r="A419" s="2"/>
+      <c r="A419" s="1"/>
       <c r="B419" s="7"/>
       <c r="C419" s="7"/>
       <c r="D419" s="7"/>
@@ -11071,7 +11091,7 @@
       <c r="W419" s="7"/>
     </row>
     <row r="420">
-      <c r="A420" s="2"/>
+      <c r="A420" s="1"/>
       <c r="B420" s="7"/>
       <c r="C420" s="7"/>
       <c r="D420" s="7"/>
@@ -11096,7 +11116,7 @@
       <c r="W420" s="7"/>
     </row>
     <row r="421">
-      <c r="A421" s="2"/>
+      <c r="A421" s="1"/>
       <c r="B421" s="7"/>
       <c r="C421" s="7"/>
       <c r="D421" s="7"/>
@@ -11121,7 +11141,7 @@
       <c r="W421" s="7"/>
     </row>
     <row r="422">
-      <c r="A422" s="2"/>
+      <c r="A422" s="1"/>
       <c r="B422" s="7"/>
       <c r="C422" s="7"/>
       <c r="D422" s="7"/>
@@ -11146,7 +11166,7 @@
       <c r="W422" s="7"/>
     </row>
     <row r="423">
-      <c r="A423" s="2"/>
+      <c r="A423" s="1"/>
       <c r="B423" s="7"/>
       <c r="C423" s="7"/>
       <c r="D423" s="7"/>
@@ -11171,7 +11191,7 @@
       <c r="W423" s="7"/>
     </row>
     <row r="424">
-      <c r="A424" s="2"/>
+      <c r="A424" s="1"/>
       <c r="B424" s="7"/>
       <c r="C424" s="7"/>
       <c r="D424" s="7"/>
@@ -11196,7 +11216,7 @@
       <c r="W424" s="7"/>
     </row>
     <row r="425">
-      <c r="A425" s="2"/>
+      <c r="A425" s="1"/>
       <c r="B425" s="7"/>
       <c r="C425" s="7"/>
       <c r="D425" s="7"/>
@@ -11221,7 +11241,7 @@
       <c r="W425" s="7"/>
     </row>
     <row r="426">
-      <c r="A426" s="2"/>
+      <c r="A426" s="1"/>
       <c r="B426" s="7"/>
       <c r="C426" s="7"/>
       <c r="D426" s="7"/>
@@ -11246,7 +11266,7 @@
       <c r="W426" s="7"/>
     </row>
     <row r="427">
-      <c r="A427" s="2"/>
+      <c r="A427" s="1"/>
       <c r="B427" s="7"/>
       <c r="C427" s="7"/>
       <c r="D427" s="7"/>
@@ -11271,7 +11291,7 @@
       <c r="W427" s="7"/>
     </row>
     <row r="428">
-      <c r="A428" s="2"/>
+      <c r="A428" s="1"/>
       <c r="B428" s="7"/>
       <c r="C428" s="7"/>
       <c r="D428" s="7"/>
@@ -11296,7 +11316,7 @@
       <c r="W428" s="7"/>
     </row>
     <row r="429">
-      <c r="A429" s="2"/>
+      <c r="A429" s="1"/>
       <c r="B429" s="7"/>
       <c r="C429" s="7"/>
       <c r="D429" s="7"/>
@@ -11321,7 +11341,7 @@
       <c r="W429" s="7"/>
     </row>
     <row r="430">
-      <c r="A430" s="2"/>
+      <c r="A430" s="1"/>
       <c r="B430" s="7"/>
       <c r="C430" s="7"/>
       <c r="D430" s="7"/>
@@ -11346,7 +11366,7 @@
       <c r="W430" s="7"/>
     </row>
     <row r="431">
-      <c r="A431" s="2"/>
+      <c r="A431" s="1"/>
       <c r="B431" s="7"/>
       <c r="C431" s="7"/>
       <c r="D431" s="7"/>
@@ -11371,7 +11391,7 @@
       <c r="W431" s="7"/>
     </row>
     <row r="432">
-      <c r="A432" s="2"/>
+      <c r="A432" s="1"/>
       <c r="B432" s="7"/>
       <c r="C432" s="7"/>
       <c r="D432" s="7"/>
@@ -11396,7 +11416,7 @@
       <c r="W432" s="7"/>
     </row>
     <row r="433">
-      <c r="A433" s="2"/>
+      <c r="A433" s="1"/>
       <c r="B433" s="7"/>
       <c r="C433" s="7"/>
       <c r="D433" s="7"/>
@@ -11421,7 +11441,7 @@
       <c r="W433" s="7"/>
     </row>
     <row r="434">
-      <c r="A434" s="2"/>
+      <c r="A434" s="1"/>
       <c r="B434" s="7"/>
       <c r="C434" s="7"/>
       <c r="D434" s="7"/>
@@ -11446,7 +11466,7 @@
       <c r="W434" s="7"/>
     </row>
     <row r="435">
-      <c r="A435" s="2"/>
+      <c r="A435" s="1"/>
       <c r="B435" s="7"/>
       <c r="C435" s="7"/>
       <c r="D435" s="7"/>
@@ -11471,7 +11491,7 @@
       <c r="W435" s="7"/>
     </row>
     <row r="436">
-      <c r="A436" s="2"/>
+      <c r="A436" s="1"/>
       <c r="B436" s="7"/>
       <c r="C436" s="7"/>
       <c r="D436" s="7"/>
@@ -11496,7 +11516,7 @@
       <c r="W436" s="7"/>
     </row>
     <row r="437">
-      <c r="A437" s="2"/>
+      <c r="A437" s="1"/>
       <c r="B437" s="7"/>
       <c r="C437" s="7"/>
       <c r="D437" s="7"/>
@@ -11521,7 +11541,7 @@
       <c r="W437" s="7"/>
     </row>
     <row r="438">
-      <c r="A438" s="2"/>
+      <c r="A438" s="1"/>
       <c r="B438" s="7"/>
       <c r="C438" s="7"/>
       <c r="D438" s="7"/>
@@ -11546,7 +11566,7 @@
       <c r="W438" s="7"/>
     </row>
     <row r="439">
-      <c r="A439" s="2"/>
+      <c r="A439" s="1"/>
       <c r="B439" s="7"/>
       <c r="C439" s="7"/>
       <c r="D439" s="7"/>
@@ -11571,7 +11591,7 @@
       <c r="W439" s="7"/>
     </row>
     <row r="440">
-      <c r="A440" s="2"/>
+      <c r="A440" s="1"/>
       <c r="B440" s="7"/>
       <c r="C440" s="7"/>
       <c r="D440" s="7"/>
@@ -11596,7 +11616,7 @@
       <c r="W440" s="7"/>
     </row>
     <row r="441">
-      <c r="A441" s="2"/>
+      <c r="A441" s="1"/>
       <c r="B441" s="7"/>
       <c r="C441" s="7"/>
       <c r="D441" s="7"/>
@@ -11621,7 +11641,7 @@
       <c r="W441" s="7"/>
     </row>
     <row r="442">
-      <c r="A442" s="2"/>
+      <c r="A442" s="1"/>
       <c r="B442" s="7"/>
       <c r="C442" s="7"/>
       <c r="D442" s="7"/>
@@ -11646,7 +11666,7 @@
       <c r="W442" s="7"/>
     </row>
     <row r="443">
-      <c r="A443" s="2"/>
+      <c r="A443" s="1"/>
       <c r="B443" s="7"/>
       <c r="C443" s="7"/>
       <c r="D443" s="7"/>
@@ -11671,7 +11691,7 @@
       <c r="W443" s="7"/>
     </row>
     <row r="444">
-      <c r="A444" s="2"/>
+      <c r="A444" s="1"/>
       <c r="B444" s="7"/>
       <c r="C444" s="7"/>
       <c r="D444" s="7"/>
@@ -11696,7 +11716,7 @@
       <c r="W444" s="7"/>
     </row>
     <row r="445">
-      <c r="A445" s="2"/>
+      <c r="A445" s="1"/>
       <c r="B445" s="7"/>
       <c r="C445" s="7"/>
       <c r="D445" s="7"/>
@@ -11721,7 +11741,7 @@
       <c r="W445" s="7"/>
     </row>
     <row r="446">
-      <c r="A446" s="2"/>
+      <c r="A446" s="1"/>
       <c r="B446" s="7"/>
       <c r="C446" s="7"/>
       <c r="D446" s="7"/>
@@ -11746,7 +11766,7 @@
       <c r="W446" s="7"/>
     </row>
     <row r="447">
-      <c r="A447" s="2"/>
+      <c r="A447" s="1"/>
       <c r="B447" s="7"/>
       <c r="C447" s="7"/>
       <c r="D447" s="7"/>
@@ -11771,7 +11791,7 @@
       <c r="W447" s="7"/>
     </row>
     <row r="448">
-      <c r="A448" s="2"/>
+      <c r="A448" s="1"/>
       <c r="B448" s="7"/>
       <c r="C448" s="7"/>
       <c r="D448" s="7"/>
@@ -11796,7 +11816,7 @@
       <c r="W448" s="7"/>
     </row>
     <row r="449">
-      <c r="A449" s="2"/>
+      <c r="A449" s="1"/>
       <c r="B449" s="7"/>
       <c r="C449" s="7"/>
       <c r="D449" s="7"/>
@@ -11821,7 +11841,7 @@
       <c r="W449" s="7"/>
     </row>
     <row r="450">
-      <c r="A450" s="2"/>
+      <c r="A450" s="1"/>
       <c r="B450" s="7"/>
       <c r="C450" s="7"/>
       <c r="D450" s="7"/>
@@ -11846,7 +11866,7 @@
       <c r="W450" s="7"/>
     </row>
     <row r="451">
-      <c r="A451" s="2"/>
+      <c r="A451" s="1"/>
       <c r="B451" s="7"/>
       <c r="C451" s="7"/>
       <c r="D451" s="7"/>
@@ -11871,7 +11891,7 @@
       <c r="W451" s="7"/>
     </row>
     <row r="452">
-      <c r="A452" s="2"/>
+      <c r="A452" s="1"/>
       <c r="B452" s="7"/>
       <c r="C452" s="7"/>
       <c r="D452" s="7"/>
@@ -11896,7 +11916,7 @@
       <c r="W452" s="7"/>
     </row>
     <row r="453">
-      <c r="A453" s="2"/>
+      <c r="A453" s="1"/>
       <c r="B453" s="7"/>
       <c r="C453" s="7"/>
       <c r="D453" s="7"/>
@@ -11921,7 +11941,7 @@
       <c r="W453" s="7"/>
     </row>
     <row r="454">
-      <c r="A454" s="2"/>
+      <c r="A454" s="1"/>
       <c r="B454" s="7"/>
       <c r="C454" s="7"/>
       <c r="D454" s="7"/>
@@ -11946,7 +11966,7 @@
       <c r="W454" s="7"/>
     </row>
     <row r="455">
-      <c r="A455" s="2"/>
+      <c r="A455" s="1"/>
       <c r="B455" s="7"/>
       <c r="C455" s="7"/>
       <c r="D455" s="7"/>
@@ -11971,7 +11991,7 @@
       <c r="W455" s="7"/>
     </row>
     <row r="456">
-      <c r="A456" s="2"/>
+      <c r="A456" s="1"/>
       <c r="B456" s="7"/>
       <c r="C456" s="7"/>
       <c r="D456" s="7"/>
@@ -11996,7 +12016,7 @@
       <c r="W456" s="7"/>
     </row>
     <row r="457">
-      <c r="A457" s="2"/>
+      <c r="A457" s="1"/>
       <c r="B457" s="7"/>
       <c r="C457" s="7"/>
       <c r="D457" s="7"/>
@@ -12021,7 +12041,7 @@
       <c r="W457" s="7"/>
     </row>
     <row r="458">
-      <c r="A458" s="2"/>
+      <c r="A458" s="1"/>
       <c r="B458" s="7"/>
       <c r="C458" s="7"/>
       <c r="D458" s="7"/>
@@ -12046,7 +12066,7 @@
       <c r="W458" s="7"/>
     </row>
     <row r="459">
-      <c r="A459" s="2"/>
+      <c r="A459" s="1"/>
       <c r="B459" s="7"/>
       <c r="C459" s="7"/>
       <c r="D459" s="7"/>
@@ -12071,7 +12091,7 @@
       <c r="W459" s="7"/>
     </row>
     <row r="460">
-      <c r="A460" s="2"/>
+      <c r="A460" s="1"/>
       <c r="B460" s="7"/>
       <c r="C460" s="7"/>
       <c r="D460" s="7"/>
@@ -12096,7 +12116,7 @@
       <c r="W460" s="7"/>
     </row>
     <row r="461">
-      <c r="A461" s="2"/>
+      <c r="A461" s="1"/>
       <c r="B461" s="7"/>
       <c r="C461" s="7"/>
       <c r="D461" s="7"/>
@@ -12121,7 +12141,7 @@
       <c r="W461" s="7"/>
     </row>
     <row r="462">
-      <c r="A462" s="2"/>
+      <c r="A462" s="1"/>
       <c r="B462" s="7"/>
       <c r="C462" s="7"/>
       <c r="D462" s="7"/>
@@ -12146,7 +12166,7 @@
       <c r="W462" s="7"/>
     </row>
     <row r="463">
-      <c r="A463" s="2"/>
+      <c r="A463" s="1"/>
       <c r="B463" s="7"/>
       <c r="C463" s="7"/>
       <c r="D463" s="7"/>
@@ -12171,7 +12191,7 @@
       <c r="W463" s="7"/>
     </row>
     <row r="464">
-      <c r="A464" s="2"/>
+      <c r="A464" s="1"/>
       <c r="B464" s="7"/>
       <c r="C464" s="7"/>
       <c r="D464" s="7"/>
@@ -12196,7 +12216,7 @@
       <c r="W464" s="7"/>
     </row>
     <row r="465">
-      <c r="A465" s="2"/>
+      <c r="A465" s="1"/>
       <c r="B465" s="7"/>
       <c r="C465" s="7"/>
       <c r="D465" s="7"/>
@@ -12221,7 +12241,7 @@
       <c r="W465" s="7"/>
     </row>
     <row r="466">
-      <c r="A466" s="2"/>
+      <c r="A466" s="1"/>
       <c r="B466" s="7"/>
       <c r="C466" s="7"/>
       <c r="D466" s="7"/>
@@ -12246,7 +12266,7 @@
       <c r="W466" s="7"/>
     </row>
     <row r="467">
-      <c r="A467" s="2"/>
+      <c r="A467" s="1"/>
       <c r="B467" s="7"/>
       <c r="C467" s="7"/>
       <c r="D467" s="7"/>
@@ -12271,7 +12291,7 @@
       <c r="W467" s="7"/>
     </row>
     <row r="468">
-      <c r="A468" s="2"/>
+      <c r="A468" s="1"/>
       <c r="B468" s="7"/>
       <c r="C468" s="7"/>
       <c r="D468" s="7"/>
@@ -12296,7 +12316,7 @@
       <c r="W468" s="7"/>
     </row>
     <row r="469">
-      <c r="A469" s="2"/>
+      <c r="A469" s="1"/>
       <c r="B469" s="7"/>
       <c r="C469" s="7"/>
       <c r="D469" s="7"/>
@@ -12321,7 +12341,7 @@
       <c r="W469" s="7"/>
     </row>
     <row r="470">
-      <c r="A470" s="2"/>
+      <c r="A470" s="1"/>
       <c r="B470" s="7"/>
       <c r="C470" s="7"/>
       <c r="D470" s="7"/>
@@ -12346,7 +12366,7 @@
       <c r="W470" s="7"/>
     </row>
     <row r="471">
-      <c r="A471" s="2"/>
+      <c r="A471" s="1"/>
       <c r="B471" s="7"/>
       <c r="C471" s="7"/>
       <c r="D471" s="7"/>
@@ -12371,7 +12391,7 @@
       <c r="W471" s="7"/>
     </row>
     <row r="472">
-      <c r="A472" s="2"/>
+      <c r="A472" s="1"/>
       <c r="B472" s="7"/>
       <c r="C472" s="7"/>
       <c r="D472" s="7"/>
@@ -12396,7 +12416,7 @@
       <c r="W472" s="7"/>
     </row>
     <row r="473">
-      <c r="A473" s="2"/>
+      <c r="A473" s="1"/>
       <c r="B473" s="7"/>
       <c r="C473" s="7"/>
       <c r="D473" s="7"/>
@@ -12421,7 +12441,7 @@
       <c r="W473" s="7"/>
     </row>
     <row r="474">
-      <c r="A474" s="2"/>
+      <c r="A474" s="1"/>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
       <c r="D474" s="7"/>
@@ -12446,7 +12466,7 @@
       <c r="W474" s="7"/>
     </row>
     <row r="475">
-      <c r="A475" s="2"/>
+      <c r="A475" s="1"/>
       <c r="B475" s="7"/>
       <c r="C475" s="7"/>
       <c r="D475" s="7"/>
@@ -12471,7 +12491,7 @@
       <c r="W475" s="7"/>
     </row>
     <row r="476">
-      <c r="A476" s="2"/>
+      <c r="A476" s="1"/>
       <c r="B476" s="7"/>
       <c r="C476" s="7"/>
       <c r="D476" s="7"/>
@@ -12496,7 +12516,7 @@
       <c r="W476" s="7"/>
     </row>
     <row r="477">
-      <c r="A477" s="2"/>
+      <c r="A477" s="1"/>
       <c r="B477" s="7"/>
       <c r="C477" s="7"/>
       <c r="D477" s="7"/>
@@ -12521,7 +12541,7 @@
       <c r="W477" s="7"/>
     </row>
     <row r="478">
-      <c r="A478" s="2"/>
+      <c r="A478" s="1"/>
       <c r="B478" s="7"/>
       <c r="C478" s="7"/>
       <c r="D478" s="7"/>
@@ -12546,7 +12566,7 @@
       <c r="W478" s="7"/>
     </row>
     <row r="479">
-      <c r="A479" s="2"/>
+      <c r="A479" s="1"/>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
       <c r="D479" s="7"/>
@@ -12571,7 +12591,7 @@
       <c r="W479" s="7"/>
     </row>
     <row r="480">
-      <c r="A480" s="2"/>
+      <c r="A480" s="1"/>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
       <c r="D480" s="7"/>
@@ -12596,7 +12616,7 @@
       <c r="W480" s="7"/>
     </row>
     <row r="481">
-      <c r="A481" s="2"/>
+      <c r="A481" s="1"/>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
       <c r="D481" s="7"/>
@@ -12621,7 +12641,7 @@
       <c r="W481" s="7"/>
     </row>
     <row r="482">
-      <c r="A482" s="2"/>
+      <c r="A482" s="1"/>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
       <c r="D482" s="7"/>
@@ -12646,7 +12666,7 @@
       <c r="W482" s="7"/>
     </row>
     <row r="483">
-      <c r="A483" s="2"/>
+      <c r="A483" s="1"/>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
       <c r="D483" s="7"/>
@@ -12671,7 +12691,7 @@
       <c r="W483" s="7"/>
     </row>
     <row r="484">
-      <c r="A484" s="2"/>
+      <c r="A484" s="1"/>
       <c r="B484" s="7"/>
       <c r="C484" s="7"/>
       <c r="D484" s="7"/>
@@ -12696,7 +12716,7 @@
       <c r="W484" s="7"/>
     </row>
     <row r="485">
-      <c r="A485" s="2"/>
+      <c r="A485" s="1"/>
       <c r="B485" s="7"/>
       <c r="C485" s="7"/>
       <c r="D485" s="7"/>
@@ -12721,7 +12741,7 @@
       <c r="W485" s="7"/>
     </row>
     <row r="486">
-      <c r="A486" s="2"/>
+      <c r="A486" s="1"/>
       <c r="B486" s="7"/>
       <c r="C486" s="7"/>
       <c r="D486" s="7"/>
@@ -12746,7 +12766,7 @@
       <c r="W486" s="7"/>
     </row>
     <row r="487">
-      <c r="A487" s="2"/>
+      <c r="A487" s="1"/>
       <c r="B487" s="7"/>
       <c r="C487" s="7"/>
       <c r="D487" s="7"/>
@@ -12771,7 +12791,7 @@
       <c r="W487" s="7"/>
     </row>
     <row r="488">
-      <c r="A488" s="2"/>
+      <c r="A488" s="1"/>
       <c r="B488" s="7"/>
       <c r="C488" s="7"/>
       <c r="D488" s="7"/>
@@ -12796,7 +12816,7 @@
       <c r="W488" s="7"/>
     </row>
     <row r="489">
-      <c r="A489" s="2"/>
+      <c r="A489" s="1"/>
       <c r="B489" s="7"/>
       <c r="C489" s="7"/>
       <c r="D489" s="7"/>
@@ -12821,7 +12841,7 @@
       <c r="W489" s="7"/>
     </row>
     <row r="490">
-      <c r="A490" s="2"/>
+      <c r="A490" s="1"/>
       <c r="B490" s="7"/>
       <c r="C490" s="7"/>
       <c r="D490" s="7"/>
@@ -12846,7 +12866,7 @@
       <c r="W490" s="7"/>
     </row>
     <row r="491">
-      <c r="A491" s="2"/>
+      <c r="A491" s="1"/>
       <c r="B491" s="7"/>
       <c r="C491" s="7"/>
       <c r="D491" s="7"/>
@@ -12871,7 +12891,7 @@
       <c r="W491" s="7"/>
     </row>
     <row r="492">
-      <c r="A492" s="2"/>
+      <c r="A492" s="1"/>
       <c r="B492" s="7"/>
       <c r="C492" s="7"/>
       <c r="D492" s="7"/>
@@ -12896,7 +12916,7 @@
       <c r="W492" s="7"/>
     </row>
     <row r="493">
-      <c r="A493" s="2"/>
+      <c r="A493" s="1"/>
       <c r="B493" s="7"/>
       <c r="C493" s="7"/>
       <c r="D493" s="7"/>
@@ -12921,7 +12941,7 @@
       <c r="W493" s="7"/>
     </row>
     <row r="494">
-      <c r="A494" s="2"/>
+      <c r="A494" s="1"/>
       <c r="B494" s="7"/>
       <c r="C494" s="7"/>
       <c r="D494" s="7"/>
@@ -12946,7 +12966,7 @@
       <c r="W494" s="7"/>
     </row>
     <row r="495">
-      <c r="A495" s="2"/>
+      <c r="A495" s="1"/>
       <c r="B495" s="7"/>
       <c r="C495" s="7"/>
       <c r="D495" s="7"/>
@@ -12971,7 +12991,7 @@
       <c r="W495" s="7"/>
     </row>
     <row r="496">
-      <c r="A496" s="2"/>
+      <c r="A496" s="1"/>
       <c r="B496" s="7"/>
       <c r="C496" s="7"/>
       <c r="D496" s="7"/>
@@ -12996,7 +13016,7 @@
       <c r="W496" s="7"/>
     </row>
     <row r="497">
-      <c r="A497" s="2"/>
+      <c r="A497" s="1"/>
       <c r="B497" s="7"/>
       <c r="C497" s="7"/>
       <c r="D497" s="7"/>
@@ -13021,7 +13041,7 @@
       <c r="W497" s="7"/>
     </row>
     <row r="498">
-      <c r="A498" s="2"/>
+      <c r="A498" s="1"/>
       <c r="B498" s="7"/>
       <c r="C498" s="7"/>
       <c r="D498" s="7"/>
@@ -13046,7 +13066,7 @@
       <c r="W498" s="7"/>
     </row>
     <row r="499">
-      <c r="A499" s="2"/>
+      <c r="A499" s="1"/>
       <c r="B499" s="7"/>
       <c r="C499" s="7"/>
       <c r="D499" s="7"/>
@@ -13071,7 +13091,7 @@
       <c r="W499" s="7"/>
     </row>
     <row r="500">
-      <c r="A500" s="2"/>
+      <c r="A500" s="1"/>
       <c r="B500" s="7"/>
       <c r="C500" s="7"/>
       <c r="D500" s="7"/>
@@ -13096,7 +13116,7 @@
       <c r="W500" s="7"/>
     </row>
     <row r="501">
-      <c r="A501" s="2"/>
+      <c r="A501" s="1"/>
       <c r="B501" s="7"/>
       <c r="C501" s="7"/>
       <c r="D501" s="7"/>
@@ -13121,7 +13141,7 @@
       <c r="W501" s="7"/>
     </row>
     <row r="502">
-      <c r="A502" s="2"/>
+      <c r="A502" s="1"/>
       <c r="B502" s="7"/>
       <c r="C502" s="7"/>
       <c r="D502" s="7"/>
@@ -13146,7 +13166,7 @@
       <c r="W502" s="7"/>
     </row>
     <row r="503">
-      <c r="A503" s="2"/>
+      <c r="A503" s="1"/>
       <c r="B503" s="7"/>
       <c r="C503" s="7"/>
       <c r="D503" s="7"/>
@@ -13171,7 +13191,7 @@
       <c r="W503" s="7"/>
     </row>
     <row r="504">
-      <c r="A504" s="2"/>
+      <c r="A504" s="1"/>
       <c r="B504" s="7"/>
       <c r="C504" s="7"/>
       <c r="D504" s="7"/>
@@ -13196,7 +13216,7 @@
       <c r="W504" s="7"/>
     </row>
     <row r="505">
-      <c r="A505" s="2"/>
+      <c r="A505" s="1"/>
       <c r="B505" s="7"/>
       <c r="C505" s="7"/>
       <c r="D505" s="7"/>
@@ -13221,7 +13241,7 @@
       <c r="W505" s="7"/>
     </row>
     <row r="506">
-      <c r="A506" s="2"/>
+      <c r="A506" s="1"/>
       <c r="B506" s="7"/>
       <c r="C506" s="7"/>
       <c r="D506" s="7"/>
@@ -13246,7 +13266,7 @@
       <c r="W506" s="7"/>
     </row>
     <row r="507">
-      <c r="A507" s="2"/>
+      <c r="A507" s="1"/>
       <c r="B507" s="7"/>
       <c r="C507" s="7"/>
       <c r="D507" s="7"/>
@@ -13271,7 +13291,7 @@
       <c r="W507" s="7"/>
     </row>
     <row r="508">
-      <c r="A508" s="2"/>
+      <c r="A508" s="1"/>
       <c r="B508" s="7"/>
       <c r="C508" s="7"/>
       <c r="D508" s="7"/>
@@ -13296,7 +13316,7 @@
       <c r="W508" s="7"/>
     </row>
     <row r="509">
-      <c r="A509" s="2"/>
+      <c r="A509" s="1"/>
       <c r="B509" s="7"/>
       <c r="C509" s="7"/>
       <c r="D509" s="7"/>
@@ -13321,7 +13341,7 @@
       <c r="W509" s="7"/>
     </row>
     <row r="510">
-      <c r="A510" s="2"/>
+      <c r="A510" s="1"/>
       <c r="B510" s="7"/>
       <c r="C510" s="7"/>
       <c r="D510" s="7"/>
@@ -13346,7 +13366,7 @@
       <c r="W510" s="7"/>
     </row>
     <row r="511">
-      <c r="A511" s="2"/>
+      <c r="A511" s="1"/>
       <c r="B511" s="7"/>
       <c r="C511" s="7"/>
       <c r="D511" s="7"/>
@@ -13371,7 +13391,7 @@
       <c r="W511" s="7"/>
     </row>
     <row r="512">
-      <c r="A512" s="2"/>
+      <c r="A512" s="1"/>
       <c r="B512" s="7"/>
       <c r="C512" s="7"/>
       <c r="D512" s="7"/>
@@ -13396,7 +13416,7 @@
       <c r="W512" s="7"/>
     </row>
     <row r="513">
-      <c r="A513" s="2"/>
+      <c r="A513" s="1"/>
       <c r="B513" s="7"/>
       <c r="C513" s="7"/>
       <c r="D513" s="7"/>
@@ -13421,7 +13441,7 @@
       <c r="W513" s="7"/>
     </row>
     <row r="514">
-      <c r="A514" s="2"/>
+      <c r="A514" s="1"/>
       <c r="B514" s="7"/>
       <c r="C514" s="7"/>
       <c r="D514" s="7"/>
@@ -13446,7 +13466,7 @@
       <c r="W514" s="7"/>
     </row>
     <row r="515">
-      <c r="A515" s="2"/>
+      <c r="A515" s="1"/>
       <c r="B515" s="7"/>
       <c r="C515" s="7"/>
       <c r="D515" s="7"/>
@@ -13471,7 +13491,7 @@
       <c r="W515" s="7"/>
     </row>
     <row r="516">
-      <c r="A516" s="2"/>
+      <c r="A516" s="1"/>
       <c r="B516" s="7"/>
       <c r="C516" s="7"/>
       <c r="D516" s="7"/>
@@ -13496,7 +13516,7 @@
       <c r="W516" s="7"/>
     </row>
     <row r="517">
-      <c r="A517" s="2"/>
+      <c r="A517" s="1"/>
       <c r="B517" s="7"/>
       <c r="C517" s="7"/>
       <c r="D517" s="7"/>
@@ -13521,7 +13541,7 @@
       <c r="W517" s="7"/>
     </row>
     <row r="518">
-      <c r="A518" s="2"/>
+      <c r="A518" s="1"/>
       <c r="B518" s="7"/>
       <c r="C518" s="7"/>
       <c r="D518" s="7"/>
@@ -13546,7 +13566,7 @@
       <c r="W518" s="7"/>
     </row>
     <row r="519">
-      <c r="A519" s="2"/>
+      <c r="A519" s="1"/>
       <c r="B519" s="7"/>
       <c r="C519" s="7"/>
       <c r="D519" s="7"/>
@@ -13571,7 +13591,7 @@
       <c r="W519" s="7"/>
     </row>
     <row r="520">
-      <c r="A520" s="2"/>
+      <c r="A520" s="1"/>
       <c r="B520" s="7"/>
       <c r="C520" s="7"/>
       <c r="D520" s="7"/>
@@ -13596,7 +13616,7 @@
       <c r="W520" s="7"/>
     </row>
     <row r="521">
-      <c r="A521" s="2"/>
+      <c r="A521" s="1"/>
       <c r="B521" s="7"/>
       <c r="C521" s="7"/>
       <c r="D521" s="7"/>
@@ -13621,7 +13641,7 @@
       <c r="W521" s="7"/>
     </row>
     <row r="522">
-      <c r="A522" s="2"/>
+      <c r="A522" s="1"/>
       <c r="B522" s="7"/>
       <c r="C522" s="7"/>
       <c r="D522" s="7"/>
@@ -13646,7 +13666,7 @@
       <c r="W522" s="7"/>
     </row>
     <row r="523">
-      <c r="A523" s="2"/>
+      <c r="A523" s="1"/>
       <c r="B523" s="7"/>
       <c r="C523" s="7"/>
       <c r="D523" s="7"/>
@@ -13671,7 +13691,7 @@
       <c r="W523" s="7"/>
     </row>
     <row r="524">
-      <c r="A524" s="2"/>
+      <c r="A524" s="1"/>
       <c r="B524" s="7"/>
       <c r="C524" s="7"/>
       <c r="D524" s="7"/>
@@ -13696,7 +13716,7 @@
       <c r="W524" s="7"/>
     </row>
     <row r="525">
-      <c r="A525" s="2"/>
+      <c r="A525" s="1"/>
       <c r="B525" s="7"/>
       <c r="C525" s="7"/>
       <c r="D525" s="7"/>
@@ -13721,7 +13741,7 @@
       <c r="W525" s="7"/>
     </row>
     <row r="526">
-      <c r="A526" s="2"/>
+      <c r="A526" s="1"/>
       <c r="B526" s="7"/>
       <c r="C526" s="7"/>
       <c r="D526" s="7"/>
@@ -13746,7 +13766,7 @@
       <c r="W526" s="7"/>
     </row>
     <row r="527">
-      <c r="A527" s="2"/>
+      <c r="A527" s="1"/>
       <c r="B527" s="7"/>
       <c r="C527" s="7"/>
       <c r="D527" s="7"/>
@@ -13771,7 +13791,7 @@
       <c r="W527" s="7"/>
     </row>
     <row r="528">
-      <c r="A528" s="2"/>
+      <c r="A528" s="1"/>
       <c r="B528" s="7"/>
       <c r="C528" s="7"/>
       <c r="D528" s="7"/>
@@ -13796,7 +13816,7 @@
       <c r="W528" s="7"/>
     </row>
     <row r="529">
-      <c r="A529" s="2"/>
+      <c r="A529" s="1"/>
       <c r="B529" s="7"/>
       <c r="C529" s="7"/>
       <c r="D529" s="7"/>
@@ -13821,7 +13841,7 @@
       <c r="W529" s="7"/>
     </row>
     <row r="530">
-      <c r="A530" s="2"/>
+      <c r="A530" s="1"/>
       <c r="B530" s="7"/>
       <c r="C530" s="7"/>
       <c r="D530" s="7"/>
@@ -13846,7 +13866,7 @@
       <c r="W530" s="7"/>
     </row>
     <row r="531">
-      <c r="A531" s="2"/>
+      <c r="A531" s="1"/>
       <c r="B531" s="7"/>
       <c r="C531" s="7"/>
       <c r="D531" s="7"/>
@@ -13871,7 +13891,7 @@
       <c r="W531" s="7"/>
     </row>
     <row r="532">
-      <c r="A532" s="2"/>
+      <c r="A532" s="1"/>
       <c r="B532" s="7"/>
       <c r="C532" s="7"/>
       <c r="D532" s="7"/>
@@ -13896,7 +13916,7 @@
       <c r="W532" s="7"/>
     </row>
     <row r="533">
-      <c r="A533" s="2"/>
+      <c r="A533" s="1"/>
       <c r="B533" s="7"/>
       <c r="C533" s="7"/>
       <c r="D533" s="7"/>
@@ -13921,7 +13941,7 @@
       <c r="W533" s="7"/>
     </row>
     <row r="534">
-      <c r="A534" s="2"/>
+      <c r="A534" s="1"/>
       <c r="B534" s="7"/>
       <c r="C534" s="7"/>
       <c r="D534" s="7"/>
@@ -13946,7 +13966,7 @@
       <c r="W534" s="7"/>
     </row>
     <row r="535">
-      <c r="A535" s="2"/>
+      <c r="A535" s="1"/>
       <c r="B535" s="7"/>
       <c r="C535" s="7"/>
       <c r="D535" s="7"/>
@@ -13971,7 +13991,7 @@
       <c r="W535" s="7"/>
     </row>
     <row r="536">
-      <c r="A536" s="2"/>
+      <c r="A536" s="1"/>
       <c r="B536" s="7"/>
       <c r="C536" s="7"/>
       <c r="D536" s="7"/>
@@ -13996,7 +14016,7 @@
       <c r="W536" s="7"/>
     </row>
     <row r="537">
-      <c r="A537" s="2"/>
+      <c r="A537" s="1"/>
       <c r="B537" s="7"/>
       <c r="C537" s="7"/>
       <c r="D537" s="7"/>
@@ -14021,7 +14041,7 @@
       <c r="W537" s="7"/>
     </row>
     <row r="538">
-      <c r="A538" s="2"/>
+      <c r="A538" s="1"/>
       <c r="B538" s="7"/>
       <c r="C538" s="7"/>
       <c r="D538" s="7"/>
@@ -14046,7 +14066,7 @@
       <c r="W538" s="7"/>
     </row>
     <row r="539">
-      <c r="A539" s="2"/>
+      <c r="A539" s="1"/>
       <c r="B539" s="7"/>
       <c r="C539" s="7"/>
       <c r="D539" s="7"/>
@@ -14071,7 +14091,7 @@
       <c r="W539" s="7"/>
     </row>
     <row r="540">
-      <c r="A540" s="2"/>
+      <c r="A540" s="1"/>
       <c r="B540" s="7"/>
       <c r="C540" s="7"/>
       <c r="D540" s="7"/>
@@ -14096,7 +14116,7 @@
       <c r="W540" s="7"/>
     </row>
     <row r="541">
-      <c r="A541" s="2"/>
+      <c r="A541" s="1"/>
       <c r="B541" s="7"/>
       <c r="C541" s="7"/>
       <c r="D541" s="7"/>
@@ -14121,7 +14141,7 @@
       <c r="W541" s="7"/>
     </row>
     <row r="542">
-      <c r="A542" s="2"/>
+      <c r="A542" s="1"/>
       <c r="B542" s="7"/>
       <c r="C542" s="7"/>
       <c r="D542" s="7"/>
@@ -14146,7 +14166,7 @@
       <c r="W542" s="7"/>
     </row>
     <row r="543">
-      <c r="A543" s="2"/>
+      <c r="A543" s="1"/>
       <c r="B543" s="7"/>
       <c r="C543" s="7"/>
       <c r="D543" s="7"/>
@@ -14171,7 +14191,7 @@
       <c r="W543" s="7"/>
     </row>
     <row r="544">
-      <c r="A544" s="2"/>
+      <c r="A544" s="1"/>
       <c r="B544" s="7"/>
       <c r="C544" s="7"/>
       <c r="D544" s="7"/>
@@ -14196,7 +14216,7 @@
       <c r="W544" s="7"/>
     </row>
     <row r="545">
-      <c r="A545" s="2"/>
+      <c r="A545" s="1"/>
       <c r="B545" s="7"/>
       <c r="C545" s="7"/>
       <c r="D545" s="7"/>
@@ -14221,7 +14241,7 @@
       <c r="W545" s="7"/>
     </row>
     <row r="546">
-      <c r="A546" s="2"/>
+      <c r="A546" s="1"/>
       <c r="B546" s="7"/>
       <c r="C546" s="7"/>
       <c r="D546" s="7"/>
@@ -14246,7 +14266,7 @@
       <c r="W546" s="7"/>
     </row>
     <row r="547">
-      <c r="A547" s="2"/>
+      <c r="A547" s="1"/>
       <c r="B547" s="7"/>
       <c r="C547" s="7"/>
       <c r="D547" s="7"/>
@@ -14271,7 +14291,7 @@
       <c r="W547" s="7"/>
     </row>
     <row r="548">
-      <c r="A548" s="2"/>
+      <c r="A548" s="1"/>
       <c r="B548" s="7"/>
       <c r="C548" s="7"/>
       <c r="D548" s="7"/>
@@ -14296,7 +14316,7 @@
       <c r="W548" s="7"/>
     </row>
     <row r="549">
-      <c r="A549" s="2"/>
+      <c r="A549" s="1"/>
       <c r="B549" s="7"/>
       <c r="C549" s="7"/>
       <c r="D549" s="7"/>
@@ -14321,7 +14341,7 @@
       <c r="W549" s="7"/>
     </row>
     <row r="550">
-      <c r="A550" s="2"/>
+      <c r="A550" s="1"/>
       <c r="B550" s="7"/>
       <c r="C550" s="7"/>
       <c r="D550" s="7"/>
@@ -14346,7 +14366,7 @@
       <c r="W550" s="7"/>
     </row>
     <row r="551">
-      <c r="A551" s="2"/>
+      <c r="A551" s="1"/>
       <c r="B551" s="7"/>
       <c r="C551" s="7"/>
       <c r="D551" s="7"/>
@@ -14371,7 +14391,7 @@
       <c r="W551" s="7"/>
     </row>
     <row r="552">
-      <c r="A552" s="2"/>
+      <c r="A552" s="1"/>
       <c r="B552" s="7"/>
       <c r="C552" s="7"/>
       <c r="D552" s="7"/>
@@ -14396,7 +14416,7 @@
       <c r="W552" s="7"/>
     </row>
     <row r="553">
-      <c r="A553" s="2"/>
+      <c r="A553" s="1"/>
       <c r="B553" s="7"/>
       <c r="C553" s="7"/>
       <c r="D553" s="7"/>
@@ -14421,7 +14441,7 @@
       <c r="W553" s="7"/>
     </row>
     <row r="554">
-      <c r="A554" s="2"/>
+      <c r="A554" s="1"/>
       <c r="B554" s="7"/>
       <c r="C554" s="7"/>
       <c r="D554" s="7"/>
@@ -14446,7 +14466,7 @@
       <c r="W554" s="7"/>
     </row>
     <row r="555">
-      <c r="A555" s="2"/>
+      <c r="A555" s="1"/>
       <c r="B555" s="7"/>
       <c r="C555" s="7"/>
       <c r="D555" s="7"/>
@@ -14471,7 +14491,7 @@
       <c r="W555" s="7"/>
     </row>
     <row r="556">
-      <c r="A556" s="2"/>
+      <c r="A556" s="1"/>
       <c r="B556" s="7"/>
       <c r="C556" s="7"/>
       <c r="D556" s="7"/>
@@ -14496,7 +14516,7 @@
       <c r="W556" s="7"/>
     </row>
     <row r="557">
-      <c r="A557" s="2"/>
+      <c r="A557" s="1"/>
       <c r="B557" s="7"/>
       <c r="C557" s="7"/>
       <c r="D557" s="7"/>
@@ -14521,7 +14541,7 @@
       <c r="W557" s="7"/>
     </row>
     <row r="558">
-      <c r="A558" s="2"/>
+      <c r="A558" s="1"/>
       <c r="B558" s="7"/>
       <c r="C558" s="7"/>
       <c r="D558" s="7"/>
@@ -14546,7 +14566,7 @@
       <c r="W558" s="7"/>
     </row>
     <row r="559">
-      <c r="A559" s="2"/>
+      <c r="A559" s="1"/>
       <c r="B559" s="7"/>
       <c r="C559" s="7"/>
       <c r="D559" s="7"/>
@@ -14571,7 +14591,7 @@
       <c r="W559" s="7"/>
     </row>
     <row r="560">
-      <c r="A560" s="2"/>
+      <c r="A560" s="1"/>
       <c r="B560" s="7"/>
       <c r="C560" s="7"/>
       <c r="D560" s="7"/>
@@ -14596,7 +14616,7 @@
       <c r="W560" s="7"/>
     </row>
     <row r="561">
-      <c r="A561" s="2"/>
+      <c r="A561" s="1"/>
       <c r="B561" s="7"/>
       <c r="C561" s="7"/>
       <c r="D561" s="7"/>
@@ -14621,7 +14641,7 @@
       <c r="W561" s="7"/>
     </row>
     <row r="562">
-      <c r="A562" s="2"/>
+      <c r="A562" s="1"/>
       <c r="B562" s="7"/>
       <c r="C562" s="7"/>
       <c r="D562" s="7"/>
@@ -14646,7 +14666,7 @@
       <c r="W562" s="7"/>
     </row>
     <row r="563">
-      <c r="A563" s="2"/>
+      <c r="A563" s="1"/>
       <c r="B563" s="7"/>
       <c r="C563" s="7"/>
       <c r="D563" s="7"/>
@@ -14671,7 +14691,7 @@
       <c r="W563" s="7"/>
     </row>
     <row r="564">
-      <c r="A564" s="2"/>
+      <c r="A564" s="1"/>
       <c r="B564" s="7"/>
       <c r="C564" s="7"/>
       <c r="D564" s="7"/>
@@ -14696,7 +14716,7 @@
       <c r="W564" s="7"/>
     </row>
     <row r="565">
-      <c r="A565" s="2"/>
+      <c r="A565" s="1"/>
       <c r="B565" s="7"/>
       <c r="C565" s="7"/>
       <c r="D565" s="7"/>
@@ -14721,7 +14741,7 @@
       <c r="W565" s="7"/>
     </row>
     <row r="566">
-      <c r="A566" s="2"/>
+      <c r="A566" s="1"/>
       <c r="B566" s="7"/>
       <c r="C566" s="7"/>
       <c r="D566" s="7"/>
@@ -14746,7 +14766,7 @@
       <c r="W566" s="7"/>
     </row>
     <row r="567">
-      <c r="A567" s="2"/>
+      <c r="A567" s="1"/>
       <c r="B567" s="7"/>
       <c r="C567" s="7"/>
       <c r="D567" s="7"/>
@@ -14771,7 +14791,7 @@
       <c r="W567" s="7"/>
     </row>
     <row r="568">
-      <c r="A568" s="2"/>
+      <c r="A568" s="1"/>
       <c r="B568" s="7"/>
       <c r="C568" s="7"/>
       <c r="D568" s="7"/>
@@ -14796,7 +14816,7 @@
       <c r="W568" s="7"/>
     </row>
     <row r="569">
-      <c r="A569" s="2"/>
+      <c r="A569" s="1"/>
       <c r="B569" s="7"/>
       <c r="C569" s="7"/>
       <c r="D569" s="7"/>
@@ -14821,7 +14841,7 @@
       <c r="W569" s="7"/>
     </row>
     <row r="570">
-      <c r="A570" s="2"/>
+      <c r="A570" s="1"/>
       <c r="B570" s="7"/>
       <c r="C570" s="7"/>
       <c r="D570" s="7"/>
@@ -14846,7 +14866,7 @@
       <c r="W570" s="7"/>
     </row>
     <row r="571">
-      <c r="A571" s="2"/>
+      <c r="A571" s="1"/>
       <c r="B571" s="7"/>
       <c r="C571" s="7"/>
       <c r="D571" s="7"/>
@@ -14871,7 +14891,7 @@
       <c r="W571" s="7"/>
     </row>
     <row r="572">
-      <c r="A572" s="2"/>
+      <c r="A572" s="1"/>
       <c r="B572" s="7"/>
       <c r="C572" s="7"/>
       <c r="D572" s="7"/>
@@ -14896,7 +14916,7 @@
       <c r="W572" s="7"/>
     </row>
     <row r="573">
-      <c r="A573" s="2"/>
+      <c r="A573" s="1"/>
       <c r="B573" s="7"/>
       <c r="C573" s="7"/>
       <c r="D573" s="7"/>
@@ -14921,7 +14941,7 @@
       <c r="W573" s="7"/>
     </row>
     <row r="574">
-      <c r="A574" s="2"/>
+      <c r="A574" s="1"/>
       <c r="B574" s="7"/>
       <c r="C574" s="7"/>
       <c r="D574" s="7"/>
@@ -14946,7 +14966,7 @@
       <c r="W574" s="7"/>
     </row>
     <row r="575">
-      <c r="A575" s="2"/>
+      <c r="A575" s="1"/>
       <c r="B575" s="7"/>
       <c r="C575" s="7"/>
       <c r="D575" s="7"/>
@@ -14971,7 +14991,7 @@
       <c r="W575" s="7"/>
     </row>
     <row r="576">
-      <c r="A576" s="2"/>
+      <c r="A576" s="1"/>
       <c r="B576" s="7"/>
       <c r="C576" s="7"/>
       <c r="D576" s="7"/>
@@ -14996,7 +15016,7 @@
       <c r="W576" s="7"/>
     </row>
     <row r="577">
-      <c r="A577" s="2"/>
+      <c r="A577" s="1"/>
       <c r="B577" s="7"/>
       <c r="C577" s="7"/>
       <c r="D577" s="7"/>
@@ -15021,7 +15041,7 @@
       <c r="W577" s="7"/>
     </row>
     <row r="578">
-      <c r="A578" s="2"/>
+      <c r="A578" s="1"/>
       <c r="B578" s="7"/>
       <c r="C578" s="7"/>
       <c r="D578" s="7"/>
@@ -15046,7 +15066,7 @@
       <c r="W578" s="7"/>
     </row>
     <row r="579">
-      <c r="A579" s="2"/>
+      <c r="A579" s="1"/>
       <c r="B579" s="7"/>
       <c r="C579" s="7"/>
       <c r="D579" s="7"/>
@@ -15071,7 +15091,7 @@
       <c r="W579" s="7"/>
     </row>
     <row r="580">
-      <c r="A580" s="2"/>
+      <c r="A580" s="1"/>
       <c r="B580" s="7"/>
       <c r="C580" s="7"/>
       <c r="D580" s="7"/>
@@ -15096,7 +15116,7 @@
       <c r="W580" s="7"/>
     </row>
     <row r="581">
-      <c r="A581" s="2"/>
+      <c r="A581" s="1"/>
       <c r="B581" s="7"/>
       <c r="C581" s="7"/>
       <c r="D581" s="7"/>
@@ -15121,7 +15141,7 @@
       <c r="W581" s="7"/>
     </row>
     <row r="582">
-      <c r="A582" s="2"/>
+      <c r="A582" s="1"/>
       <c r="B582" s="7"/>
       <c r="C582" s="7"/>
       <c r="D582" s="7"/>
@@ -15146,7 +15166,7 @@
       <c r="W582" s="7"/>
     </row>
     <row r="583">
-      <c r="A583" s="2"/>
+      <c r="A583" s="1"/>
       <c r="B583" s="7"/>
       <c r="C583" s="7"/>
       <c r="D583" s="7"/>
@@ -15171,7 +15191,7 @@
       <c r="W583" s="7"/>
     </row>
     <row r="584">
-      <c r="A584" s="2"/>
+      <c r="A584" s="1"/>
       <c r="B584" s="7"/>
       <c r="C584" s="7"/>
       <c r="D584" s="7"/>
@@ -15196,7 +15216,7 @@
       <c r="W584" s="7"/>
     </row>
     <row r="585">
-      <c r="A585" s="2"/>
+      <c r="A585" s="1"/>
       <c r="B585" s="7"/>
       <c r="C585" s="7"/>
       <c r="D585" s="7"/>
@@ -15221,7 +15241,7 @@
       <c r="W585" s="7"/>
     </row>
     <row r="586">
-      <c r="A586" s="2"/>
+      <c r="A586" s="1"/>
       <c r="B586" s="7"/>
       <c r="C586" s="7"/>
       <c r="D586" s="7"/>
@@ -15246,7 +15266,7 @@
       <c r="W586" s="7"/>
     </row>
     <row r="587">
-      <c r="A587" s="2"/>
+      <c r="A587" s="1"/>
       <c r="B587" s="7"/>
       <c r="C587" s="7"/>
       <c r="D587" s="7"/>
@@ -15271,7 +15291,7 @@
       <c r="W587" s="7"/>
     </row>
     <row r="588">
-      <c r="A588" s="2"/>
+      <c r="A588" s="1"/>
       <c r="B588" s="7"/>
       <c r="C588" s="7"/>
       <c r="D588" s="7"/>
@@ -15296,7 +15316,7 @@
       <c r="W588" s="7"/>
     </row>
     <row r="589">
-      <c r="A589" s="2"/>
+      <c r="A589" s="1"/>
       <c r="B589" s="7"/>
       <c r="C589" s="7"/>
       <c r="D589" s="7"/>
@@ -15321,7 +15341,7 @@
       <c r="W589" s="7"/>
     </row>
     <row r="590">
-      <c r="A590" s="2"/>
+      <c r="A590" s="1"/>
       <c r="B590" s="7"/>
       <c r="C590" s="7"/>
       <c r="D590" s="7"/>
@@ -15346,7 +15366,7 @@
       <c r="W590" s="7"/>
     </row>
     <row r="591">
-      <c r="A591" s="2"/>
+      <c r="A591" s="1"/>
       <c r="B591" s="7"/>
       <c r="C591" s="7"/>
       <c r="D591" s="7"/>
@@ -15371,7 +15391,7 @@
       <c r="W591" s="7"/>
     </row>
     <row r="592">
-      <c r="A592" s="2"/>
+      <c r="A592" s="1"/>
       <c r="B592" s="7"/>
       <c r="C592" s="7"/>
       <c r="D592" s="7"/>
@@ -15396,7 +15416,7 @@
       <c r="W592" s="7"/>
     </row>
     <row r="593">
-      <c r="A593" s="2"/>
+      <c r="A593" s="1"/>
       <c r="B593" s="7"/>
       <c r="C593" s="7"/>
       <c r="D593" s="7"/>
@@ -15421,7 +15441,7 @@
       <c r="W593" s="7"/>
     </row>
     <row r="594">
-      <c r="A594" s="2"/>
+      <c r="A594" s="1"/>
       <c r="B594" s="7"/>
       <c r="C594" s="7"/>
       <c r="D594" s="7"/>
@@ -15446,7 +15466,7 @@
       <c r="W594" s="7"/>
     </row>
     <row r="595">
-      <c r="A595" s="2"/>
+      <c r="A595" s="1"/>
       <c r="B595" s="7"/>
       <c r="C595" s="7"/>
       <c r="D595" s="7"/>
@@ -15471,7 +15491,7 @@
       <c r="W595" s="7"/>
     </row>
     <row r="596">
-      <c r="A596" s="2"/>
+      <c r="A596" s="1"/>
       <c r="B596" s="7"/>
       <c r="C596" s="7"/>
       <c r="D596" s="7"/>
@@ -15496,7 +15516,7 @@
       <c r="W596" s="7"/>
     </row>
     <row r="597">
-      <c r="A597" s="2"/>
+      <c r="A597" s="1"/>
       <c r="B597" s="7"/>
       <c r="C597" s="7"/>
       <c r="D597" s="7"/>
@@ -15521,7 +15541,7 @@
       <c r="W597" s="7"/>
     </row>
     <row r="598">
-      <c r="A598" s="2"/>
+      <c r="A598" s="1"/>
       <c r="B598" s="7"/>
       <c r="C598" s="7"/>
       <c r="D598" s="7"/>
@@ -15546,7 +15566,7 @@
       <c r="W598" s="7"/>
     </row>
     <row r="599">
-      <c r="A599" s="2"/>
+      <c r="A599" s="1"/>
       <c r="B599" s="7"/>
       <c r="C599" s="7"/>
       <c r="D599" s="7"/>
@@ -15571,7 +15591,7 @@
       <c r="W599" s="7"/>
     </row>
     <row r="600">
-      <c r="A600" s="2"/>
+      <c r="A600" s="1"/>
       <c r="B600" s="7"/>
       <c r="C600" s="7"/>
       <c r="D600" s="7"/>
@@ -15596,7 +15616,7 @@
       <c r="W600" s="7"/>
     </row>
     <row r="601">
-      <c r="A601" s="2"/>
+      <c r="A601" s="1"/>
       <c r="B601" s="7"/>
       <c r="C601" s="7"/>
       <c r="D601" s="7"/>
@@ -15621,7 +15641,7 @@
       <c r="W601" s="7"/>
     </row>
     <row r="602">
-      <c r="A602" s="2"/>
+      <c r="A602" s="1"/>
       <c r="B602" s="7"/>
       <c r="C602" s="7"/>
       <c r="D602" s="7"/>
@@ -15646,7 +15666,7 @@
       <c r="W602" s="7"/>
     </row>
     <row r="603">
-      <c r="A603" s="2"/>
+      <c r="A603" s="1"/>
       <c r="B603" s="7"/>
       <c r="C603" s="7"/>
       <c r="D603" s="7"/>
@@ -15671,7 +15691,7 @@
       <c r="W603" s="7"/>
     </row>
     <row r="604">
-      <c r="A604" s="2"/>
+      <c r="A604" s="1"/>
       <c r="B604" s="7"/>
       <c r="C604" s="7"/>
       <c r="D604" s="7"/>
@@ -15696,7 +15716,7 @@
       <c r="W604" s="7"/>
     </row>
     <row r="605">
-      <c r="A605" s="2"/>
+      <c r="A605" s="1"/>
       <c r="B605" s="7"/>
       <c r="C605" s="7"/>
       <c r="D605" s="7"/>
@@ -15721,7 +15741,7 @@
       <c r="W605" s="7"/>
     </row>
     <row r="606">
-      <c r="A606" s="2"/>
+      <c r="A606" s="1"/>
       <c r="B606" s="7"/>
       <c r="C606" s="7"/>
       <c r="D606" s="7"/>
@@ -15746,7 +15766,7 @@
       <c r="W606" s="7"/>
     </row>
     <row r="607">
-      <c r="A607" s="2"/>
+      <c r="A607" s="1"/>
       <c r="B607" s="7"/>
       <c r="C607" s="7"/>
       <c r="D607" s="7"/>
@@ -15771,7 +15791,7 @@
       <c r="W607" s="7"/>
     </row>
     <row r="608">
-      <c r="A608" s="2"/>
+      <c r="A608" s="1"/>
       <c r="B608" s="7"/>
       <c r="C608" s="7"/>
       <c r="D608" s="7"/>
@@ -15796,7 +15816,7 @@
       <c r="W608" s="7"/>
     </row>
     <row r="609">
-      <c r="A609" s="2"/>
+      <c r="A609" s="1"/>
       <c r="B609" s="7"/>
       <c r="C609" s="7"/>
       <c r="D609" s="7"/>
@@ -15821,7 +15841,7 @@
       <c r="W609" s="7"/>
     </row>
     <row r="610">
-      <c r="A610" s="2"/>
+      <c r="A610" s="1"/>
       <c r="B610" s="7"/>
       <c r="C610" s="7"/>
       <c r="D610" s="7"/>
@@ -15846,7 +15866,7 @@
       <c r="W610" s="7"/>
     </row>
     <row r="611">
-      <c r="A611" s="2"/>
+      <c r="A611" s="1"/>
       <c r="B611" s="7"/>
       <c r="C611" s="7"/>
       <c r="D611" s="7"/>
@@ -15871,7 +15891,7 @@
       <c r="W611" s="7"/>
     </row>
     <row r="612">
-      <c r="A612" s="2"/>
+      <c r="A612" s="1"/>
       <c r="B612" s="7"/>
       <c r="C612" s="7"/>
       <c r="D612" s="7"/>
@@ -15896,7 +15916,7 @@
       <c r="W612" s="7"/>
     </row>
     <row r="613">
-      <c r="A613" s="2"/>
+      <c r="A613" s="1"/>
       <c r="B613" s="7"/>
       <c r="C613" s="7"/>
       <c r="D613" s="7"/>
@@ -15921,7 +15941,7 @@
       <c r="W613" s="7"/>
     </row>
     <row r="614">
-      <c r="A614" s="2"/>
+      <c r="A614" s="1"/>
       <c r="B614" s="7"/>
       <c r="C614" s="7"/>
       <c r="D614" s="7"/>
@@ -15946,7 +15966,7 @@
       <c r="W614" s="7"/>
     </row>
     <row r="615">
-      <c r="A615" s="2"/>
+      <c r="A615" s="1"/>
       <c r="B615" s="7"/>
       <c r="C615" s="7"/>
       <c r="D615" s="7"/>
@@ -15971,7 +15991,7 @@
       <c r="W615" s="7"/>
     </row>
     <row r="616">
-      <c r="A616" s="2"/>
+      <c r="A616" s="1"/>
       <c r="B616" s="7"/>
       <c r="C616" s="7"/>
       <c r="D616" s="7"/>
@@ -15996,7 +16016,7 @@
       <c r="W616" s="7"/>
     </row>
     <row r="617">
-      <c r="A617" s="2"/>
+      <c r="A617" s="1"/>
       <c r="B617" s="7"/>
       <c r="C617" s="7"/>
       <c r="D617" s="7"/>
@@ -16021,7 +16041,7 @@
       <c r="W617" s="7"/>
     </row>
     <row r="618">
-      <c r="A618" s="2"/>
+      <c r="A618" s="1"/>
       <c r="B618" s="7"/>
       <c r="C618" s="7"/>
       <c r="D618" s="7"/>
@@ -16046,7 +16066,7 @@
       <c r="W618" s="7"/>
     </row>
     <row r="619">
-      <c r="A619" s="2"/>
+      <c r="A619" s="1"/>
       <c r="B619" s="7"/>
       <c r="C619" s="7"/>
       <c r="D619" s="7"/>
@@ -16071,7 +16091,7 @@
       <c r="W619" s="7"/>
     </row>
     <row r="620">
-      <c r="A620" s="2"/>
+      <c r="A620" s="1"/>
       <c r="B620" s="7"/>
       <c r="C620" s="7"/>
       <c r="D620" s="7"/>
@@ -16096,7 +16116,7 @@
       <c r="W620" s="7"/>
     </row>
     <row r="621">
-      <c r="A621" s="2"/>
+      <c r="A621" s="1"/>
       <c r="B621" s="7"/>
       <c r="C621" s="7"/>
       <c r="D621" s="7"/>
@@ -16121,7 +16141,7 @@
       <c r="W621" s="7"/>
     </row>
     <row r="622">
-      <c r="A622" s="2"/>
+      <c r="A622" s="1"/>
       <c r="B622" s="7"/>
       <c r="C622" s="7"/>
       <c r="D622" s="7"/>
@@ -16146,7 +16166,7 @@
       <c r="W622" s="7"/>
     </row>
     <row r="623">
-      <c r="A623" s="2"/>
+      <c r="A623" s="1"/>
       <c r="B623" s="7"/>
       <c r="C623" s="7"/>
       <c r="D623" s="7"/>
@@ -16171,7 +16191,7 @@
       <c r="W623" s="7"/>
     </row>
     <row r="624">
-      <c r="A624" s="2"/>
+      <c r="A624" s="1"/>
       <c r="B624" s="7"/>
       <c r="C624" s="7"/>
       <c r="D624" s="7"/>
@@ -16196,7 +16216,7 @@
       <c r="W624" s="7"/>
     </row>
     <row r="625">
-      <c r="A625" s="2"/>
+      <c r="A625" s="1"/>
       <c r="B625" s="7"/>
       <c r="C625" s="7"/>
       <c r="D625" s="7"/>
@@ -16221,7 +16241,7 @@
       <c r="W625" s="7"/>
     </row>
     <row r="626">
-      <c r="A626" s="2"/>
+      <c r="A626" s="1"/>
       <c r="B626" s="7"/>
       <c r="C626" s="7"/>
       <c r="D626" s="7"/>
@@ -16246,7 +16266,7 @@
       <c r="W626" s="7"/>
     </row>
     <row r="627">
-      <c r="A627" s="2"/>
+      <c r="A627" s="1"/>
       <c r="B627" s="7"/>
       <c r="C627" s="7"/>
       <c r="D627" s="7"/>
@@ -16271,7 +16291,7 @@
       <c r="W627" s="7"/>
     </row>
     <row r="628">
-      <c r="A628" s="2"/>
+      <c r="A628" s="1"/>
       <c r="B628" s="7"/>
       <c r="C628" s="7"/>
       <c r="D628" s="7"/>
@@ -16296,7 +16316,7 @@
       <c r="W628" s="7"/>
     </row>
     <row r="629">
-      <c r="A629" s="2"/>
+      <c r="A629" s="1"/>
       <c r="B629" s="7"/>
       <c r="C629" s="7"/>
       <c r="D629" s="7"/>
@@ -16321,7 +16341,7 @@
       <c r="W629" s="7"/>
     </row>
     <row r="630">
-      <c r="A630" s="2"/>
+      <c r="A630" s="1"/>
       <c r="B630" s="7"/>
       <c r="C630" s="7"/>
       <c r="D630" s="7"/>
@@ -16346,7 +16366,7 @@
       <c r="W630" s="7"/>
     </row>
     <row r="631">
-      <c r="A631" s="2"/>
+      <c r="A631" s="1"/>
       <c r="B631" s="7"/>
       <c r="C631" s="7"/>
       <c r="D631" s="7"/>
@@ -16371,7 +16391,7 @@
       <c r="W631" s="7"/>
     </row>
     <row r="632">
-      <c r="A632" s="2"/>
+      <c r="A632" s="1"/>
       <c r="B632" s="7"/>
       <c r="C632" s="7"/>
       <c r="D632" s="7"/>
@@ -16396,7 +16416,7 @@
       <c r="W632" s="7"/>
     </row>
     <row r="633">
-      <c r="A633" s="2"/>
+      <c r="A633" s="1"/>
       <c r="B633" s="7"/>
       <c r="C633" s="7"/>
       <c r="D633" s="7"/>
@@ -16421,7 +16441,7 @@
       <c r="W633" s="7"/>
     </row>
     <row r="634">
-      <c r="A634" s="2"/>
+      <c r="A634" s="1"/>
       <c r="B634" s="7"/>
       <c r="C634" s="7"/>
       <c r="D634" s="7"/>
@@ -16446,7 +16466,7 @@
       <c r="W634" s="7"/>
     </row>
     <row r="635">
-      <c r="A635" s="2"/>
+      <c r="A635" s="1"/>
       <c r="B635" s="7"/>
       <c r="C635" s="7"/>
       <c r="D635" s="7"/>
@@ -16471,7 +16491,7 @@
       <c r="W635" s="7"/>
     </row>
     <row r="636">
-      <c r="A636" s="2"/>
+      <c r="A636" s="1"/>
       <c r="B636" s="7"/>
       <c r="C636" s="7"/>
       <c r="D636" s="7"/>
@@ -16496,7 +16516,7 @@
       <c r="W636" s="7"/>
     </row>
     <row r="637">
-      <c r="A637" s="2"/>
+      <c r="A637" s="1"/>
       <c r="B637" s="7"/>
       <c r="C637" s="7"/>
       <c r="D637" s="7"/>
@@ -16521,7 +16541,7 @@
       <c r="W637" s="7"/>
     </row>
     <row r="638">
-      <c r="A638" s="2"/>
+      <c r="A638" s="1"/>
       <c r="B638" s="7"/>
       <c r="C638" s="7"/>
       <c r="D638" s="7"/>
@@ -16546,7 +16566,7 @@
       <c r="W638" s="7"/>
     </row>
     <row r="639">
-      <c r="A639" s="2"/>
+      <c r="A639" s="1"/>
       <c r="B639" s="7"/>
       <c r="C639" s="7"/>
       <c r="D639" s="7"/>
@@ -16571,7 +16591,7 @@
       <c r="W639" s="7"/>
     </row>
     <row r="640">
-      <c r="A640" s="2"/>
+      <c r="A640" s="1"/>
       <c r="B640" s="7"/>
       <c r="C640" s="7"/>
       <c r="D640" s="7"/>
@@ -16596,7 +16616,7 @@
       <c r="W640" s="7"/>
     </row>
     <row r="641">
-      <c r="A641" s="2"/>
+      <c r="A641" s="1"/>
       <c r="B641" s="7"/>
       <c r="C641" s="7"/>
       <c r="D641" s="7"/>
@@ -16621,7 +16641,7 @@
       <c r="W641" s="7"/>
     </row>
     <row r="642">
-      <c r="A642" s="2"/>
+      <c r="A642" s="1"/>
       <c r="B642" s="7"/>
       <c r="C642" s="7"/>
       <c r="D642" s="7"/>
@@ -16646,7 +16666,7 @@
       <c r="W642" s="7"/>
     </row>
     <row r="643">
-      <c r="A643" s="2"/>
+      <c r="A643" s="1"/>
       <c r="B643" s="7"/>
       <c r="C643" s="7"/>
       <c r="D643" s="7"/>
@@ -16671,7 +16691,7 @@
       <c r="W643" s="7"/>
     </row>
     <row r="644">
-      <c r="A644" s="2"/>
+      <c r="A644" s="1"/>
       <c r="B644" s="7"/>
       <c r="C644" s="7"/>
       <c r="D644" s="7"/>
@@ -16696,7 +16716,7 @@
       <c r="W644" s="7"/>
     </row>
     <row r="645">
-      <c r="A645" s="2"/>
+      <c r="A645" s="1"/>
       <c r="B645" s="7"/>
       <c r="C645" s="7"/>
       <c r="D645" s="7"/>
@@ -16721,7 +16741,7 @@
       <c r="W645" s="7"/>
     </row>
     <row r="646">
-      <c r="A646" s="2"/>
+      <c r="A646" s="1"/>
       <c r="B646" s="7"/>
       <c r="C646" s="7"/>
       <c r="D646" s="7"/>
@@ -16746,7 +16766,7 @@
       <c r="W646" s="7"/>
     </row>
     <row r="647">
-      <c r="A647" s="2"/>
+      <c r="A647" s="1"/>
       <c r="B647" s="7"/>
       <c r="C647" s="7"/>
       <c r="D647" s="7"/>
@@ -16771,7 +16791,7 @@
       <c r="W647" s="7"/>
     </row>
     <row r="648">
-      <c r="A648" s="2"/>
+      <c r="A648" s="1"/>
       <c r="B648" s="7"/>
       <c r="C648" s="7"/>
       <c r="D648" s="7"/>
@@ -16796,7 +16816,7 @@
       <c r="W648" s="7"/>
     </row>
     <row r="649">
-      <c r="A649" s="2"/>
+      <c r="A649" s="1"/>
       <c r="B649" s="7"/>
       <c r="C649" s="7"/>
       <c r="D649" s="7"/>
@@ -16821,7 +16841,7 @@
       <c r="W649" s="7"/>
     </row>
     <row r="650">
-      <c r="A650" s="2"/>
+      <c r="A650" s="1"/>
       <c r="B650" s="7"/>
       <c r="C650" s="7"/>
       <c r="D650" s="7"/>
@@ -16846,7 +16866,7 @@
       <c r="W650" s="7"/>
     </row>
     <row r="651">
-      <c r="A651" s="2"/>
+      <c r="A651" s="1"/>
       <c r="B651" s="7"/>
       <c r="C651" s="7"/>
       <c r="D651" s="7"/>
@@ -16871,7 +16891,7 @@
       <c r="W651" s="7"/>
     </row>
     <row r="652">
-      <c r="A652" s="2"/>
+      <c r="A652" s="1"/>
       <c r="B652" s="7"/>
       <c r="C652" s="7"/>
       <c r="D652" s="7"/>
@@ -16896,7 +16916,7 @@
       <c r="W652" s="7"/>
     </row>
     <row r="653">
-      <c r="A653" s="2"/>
+      <c r="A653" s="1"/>
       <c r="B653" s="7"/>
       <c r="C653" s="7"/>
       <c r="D653" s="7"/>
@@ -16921,7 +16941,7 @@
       <c r="W653" s="7"/>
     </row>
     <row r="654">
-      <c r="A654" s="2"/>
+      <c r="A654" s="1"/>
       <c r="B654" s="7"/>
       <c r="C654" s="7"/>
       <c r="D654" s="7"/>
@@ -16946,7 +16966,7 @@
       <c r="W654" s="7"/>
     </row>
     <row r="655">
-      <c r="A655" s="2"/>
+      <c r="A655" s="1"/>
       <c r="B655" s="7"/>
       <c r="C655" s="7"/>
       <c r="D655" s="7"/>
@@ -16971,7 +16991,7 @@
       <c r="W655" s="7"/>
     </row>
     <row r="656">
-      <c r="A656" s="2"/>
+      <c r="A656" s="1"/>
       <c r="B656" s="7"/>
       <c r="C656" s="7"/>
       <c r="D656" s="7"/>
@@ -16996,7 +17016,7 @@
       <c r="W656" s="7"/>
     </row>
     <row r="657">
-      <c r="A657" s="2"/>
+      <c r="A657" s="1"/>
       <c r="B657" s="7"/>
       <c r="C657" s="7"/>
       <c r="D657" s="7"/>
@@ -17021,7 +17041,7 @@
       <c r="W657" s="7"/>
     </row>
     <row r="658">
-      <c r="A658" s="2"/>
+      <c r="A658" s="1"/>
       <c r="B658" s="7"/>
       <c r="C658" s="7"/>
       <c r="D658" s="7"/>
@@ -17046,7 +17066,7 @@
       <c r="W658" s="7"/>
     </row>
     <row r="659">
-      <c r="A659" s="2"/>
+      <c r="A659" s="1"/>
       <c r="B659" s="7"/>
       <c r="C659" s="7"/>
       <c r="D659" s="7"/>
@@ -17071,7 +17091,7 @@
       <c r="W659" s="7"/>
     </row>
     <row r="660">
-      <c r="A660" s="2"/>
+      <c r="A660" s="1"/>
       <c r="B660" s="7"/>
       <c r="C660" s="7"/>
       <c r="D660" s="7"/>
@@ -17096,7 +17116,7 @@
       <c r="W660" s="7"/>
     </row>
     <row r="661">
-      <c r="A661" s="2"/>
+      <c r="A661" s="1"/>
       <c r="B661" s="7"/>
       <c r="C661" s="7"/>
       <c r="D661" s="7"/>
@@ -17121,7 +17141,7 @@
       <c r="W661" s="7"/>
     </row>
     <row r="662">
-      <c r="A662" s="2"/>
+      <c r="A662" s="1"/>
       <c r="B662" s="7"/>
       <c r="C662" s="7"/>
       <c r="D662" s="7"/>
@@ -17146,7 +17166,7 @@
       <c r="W662" s="7"/>
     </row>
     <row r="663">
-      <c r="A663" s="2"/>
+      <c r="A663" s="1"/>
       <c r="B663" s="7"/>
       <c r="C663" s="7"/>
       <c r="D663" s="7"/>
@@ -17171,7 +17191,7 @@
       <c r="W663" s="7"/>
     </row>
     <row r="664">
-      <c r="A664" s="2"/>
+      <c r="A664" s="1"/>
       <c r="B664" s="7"/>
       <c r="C664" s="7"/>
       <c r="D664" s="7"/>
@@ -17196,7 +17216,7 @@
       <c r="W664" s="7"/>
     </row>
     <row r="665">
-      <c r="A665" s="2"/>
+      <c r="A665" s="1"/>
       <c r="B665" s="7"/>
       <c r="C665" s="7"/>
       <c r="D665" s="7"/>
@@ -17221,7 +17241,7 @@
       <c r="W665" s="7"/>
     </row>
     <row r="666">
-      <c r="A666" s="2"/>
+      <c r="A666" s="1"/>
       <c r="B666" s="7"/>
       <c r="C666" s="7"/>
       <c r="D666" s="7"/>
@@ -17246,7 +17266,7 @@
       <c r="W666" s="7"/>
     </row>
     <row r="667">
-      <c r="A667" s="2"/>
+      <c r="A667" s="1"/>
       <c r="B667" s="7"/>
       <c r="C667" s="7"/>
       <c r="D667" s="7"/>
@@ -17271,7 +17291,7 @@
       <c r="W667" s="7"/>
     </row>
     <row r="668">
-      <c r="A668" s="2"/>
+      <c r="A668" s="1"/>
       <c r="B668" s="7"/>
       <c r="C668" s="7"/>
       <c r="D668" s="7"/>
@@ -17296,7 +17316,7 @@
       <c r="W668" s="7"/>
     </row>
     <row r="669">
-      <c r="A669" s="2"/>
+      <c r="A669" s="1"/>
       <c r="B669" s="7"/>
       <c r="C669" s="7"/>
       <c r="D669" s="7"/>
@@ -17321,7 +17341,7 @@
       <c r="W669" s="7"/>
     </row>
     <row r="670">
-      <c r="A670" s="2"/>
+      <c r="A670" s="1"/>
       <c r="B670" s="7"/>
       <c r="C670" s="7"/>
       <c r="D670" s="7"/>
@@ -17346,7 +17366,7 @@
       <c r="W670" s="7"/>
     </row>
     <row r="671">
-      <c r="A671" s="2"/>
+      <c r="A671" s="1"/>
       <c r="B671" s="7"/>
       <c r="C671" s="7"/>
       <c r="D671" s="7"/>
@@ -17371,7 +17391,7 @@
       <c r="W671" s="7"/>
     </row>
     <row r="672">
-      <c r="A672" s="2"/>
+      <c r="A672" s="1"/>
       <c r="B672" s="7"/>
       <c r="C672" s="7"/>
       <c r="D672" s="7"/>
@@ -17396,7 +17416,7 @@
       <c r="W672" s="7"/>
     </row>
     <row r="673">
-      <c r="A673" s="2"/>
+      <c r="A673" s="1"/>
       <c r="B673" s="7"/>
       <c r="C673" s="7"/>
       <c r="D673" s="7"/>
@@ -17421,7 +17441,7 @@
       <c r="W673" s="7"/>
     </row>
     <row r="674">
-      <c r="A674" s="2"/>
+      <c r="A674" s="1"/>
       <c r="B674" s="7"/>
       <c r="C674" s="7"/>
       <c r="D674" s="7"/>
@@ -17446,7 +17466,7 @@
       <c r="W674" s="7"/>
     </row>
     <row r="675">
-      <c r="A675" s="2"/>
+      <c r="A675" s="1"/>
       <c r="B675" s="7"/>
       <c r="C675" s="7"/>
       <c r="D675" s="7"/>
@@ -17471,7 +17491,7 @@
       <c r="W675" s="7"/>
     </row>
     <row r="676">
-      <c r="A676" s="2"/>
+      <c r="A676" s="1"/>
       <c r="B676" s="7"/>
       <c r="C676" s="7"/>
       <c r="D676" s="7"/>
@@ -17496,7 +17516,7 @@
       <c r="W676" s="7"/>
     </row>
     <row r="677">
-      <c r="A677" s="2"/>
+      <c r="A677" s="1"/>
       <c r="B677" s="7"/>
       <c r="C677" s="7"/>
       <c r="D677" s="7"/>
@@ -17521,7 +17541,7 @@
       <c r="W677" s="7"/>
     </row>
     <row r="678">
-      <c r="A678" s="2"/>
+      <c r="A678" s="1"/>
       <c r="B678" s="7"/>
       <c r="C678" s="7"/>
       <c r="D678" s="7"/>
@@ -17546,7 +17566,7 @@
       <c r="W678" s="7"/>
     </row>
     <row r="679">
-      <c r="A679" s="2"/>
+      <c r="A679" s="1"/>
       <c r="B679" s="7"/>
       <c r="C679" s="7"/>
       <c r="D679" s="7"/>
@@ -17571,7 +17591,7 @@
       <c r="W679" s="7"/>
     </row>
     <row r="680">
-      <c r="A680" s="2"/>
+      <c r="A680" s="1"/>
       <c r="B680" s="7"/>
       <c r="C680" s="7"/>
       <c r="D680" s="7"/>
@@ -17596,7 +17616,7 @@
       <c r="W680" s="7"/>
     </row>
     <row r="681">
-      <c r="A681" s="2"/>
+      <c r="A681" s="1"/>
       <c r="B681" s="7"/>
       <c r="C681" s="7"/>
       <c r="D681" s="7"/>
@@ -17621,7 +17641,7 @@
       <c r="W681" s="7"/>
     </row>
     <row r="682">
-      <c r="A682" s="2"/>
+      <c r="A682" s="1"/>
       <c r="B682" s="7"/>
       <c r="C682" s="7"/>
       <c r="D682" s="7"/>
@@ -17646,7 +17666,7 @@
       <c r="W682" s="7"/>
     </row>
     <row r="683">
-      <c r="A683" s="2"/>
+      <c r="A683" s="1"/>
       <c r="B683" s="7"/>
       <c r="C683" s="7"/>
       <c r="D683" s="7"/>
@@ -17671,7 +17691,7 @@
       <c r="W683" s="7"/>
     </row>
     <row r="684">
-      <c r="A684" s="2"/>
+      <c r="A684" s="1"/>
       <c r="B684" s="7"/>
       <c r="C684" s="7"/>
       <c r="D684" s="7"/>
@@ -17696,7 +17716,7 @@
       <c r="W684" s="7"/>
     </row>
     <row r="685">
-      <c r="A685" s="2"/>
+      <c r="A685" s="1"/>
       <c r="B685" s="7"/>
       <c r="C685" s="7"/>
       <c r="D685" s="7"/>
@@ -17721,7 +17741,7 @@
       <c r="W685" s="7"/>
     </row>
     <row r="686">
-      <c r="A686" s="2"/>
+      <c r="A686" s="1"/>
       <c r="B686" s="7"/>
       <c r="C686" s="7"/>
       <c r="D686" s="7"/>
@@ -17746,7 +17766,7 @@
       <c r="W686" s="7"/>
     </row>
     <row r="687">
-      <c r="A687" s="2"/>
+      <c r="A687" s="1"/>
       <c r="B687" s="7"/>
       <c r="C687" s="7"/>
       <c r="D687" s="7"/>
@@ -17771,7 +17791,7 @@
       <c r="W687" s="7"/>
     </row>
     <row r="688">
-      <c r="A688" s="2"/>
+      <c r="A688" s="1"/>
       <c r="B688" s="7"/>
       <c r="C688" s="7"/>
       <c r="D688" s="7"/>
@@ -17796,7 +17816,7 @@
       <c r="W688" s="7"/>
     </row>
     <row r="689">
-      <c r="A689" s="2"/>
+      <c r="A689" s="1"/>
       <c r="B689" s="7"/>
       <c r="C689" s="7"/>
       <c r="D689" s="7"/>
@@ -17821,7 +17841,7 @@
       <c r="W689" s="7"/>
     </row>
     <row r="690">
-      <c r="A690" s="2"/>
+      <c r="A690" s="1"/>
       <c r="B690" s="7"/>
       <c r="C690" s="7"/>
       <c r="D690" s="7"/>
@@ -17846,7 +17866,7 @@
       <c r="W690" s="7"/>
     </row>
     <row r="691">
-      <c r="A691" s="2"/>
+      <c r="A691" s="1"/>
       <c r="B691" s="7"/>
       <c r="C691" s="7"/>
       <c r="D691" s="7"/>
@@ -17871,7 +17891,7 @@
       <c r="W691" s="7"/>
     </row>
     <row r="692">
-      <c r="A692" s="2"/>
+      <c r="A692" s="1"/>
       <c r="B692" s="7"/>
       <c r="C692" s="7"/>
       <c r="D692" s="7"/>
@@ -17896,7 +17916,7 @@
       <c r="W692" s="7"/>
     </row>
     <row r="693">
-      <c r="A693" s="2"/>
+      <c r="A693" s="1"/>
       <c r="B693" s="7"/>
       <c r="C693" s="7"/>
       <c r="D693" s="7"/>
@@ -17921,7 +17941,7 @@
       <c r="W693" s="7"/>
     </row>
     <row r="694">
-      <c r="A694" s="2"/>
+      <c r="A694" s="1"/>
       <c r="B694" s="7"/>
       <c r="C694" s="7"/>
       <c r="D694" s="7"/>
@@ -17946,7 +17966,7 @@
       <c r="W694" s="7"/>
     </row>
     <row r="695">
-      <c r="A695" s="2"/>
+      <c r="A695" s="1"/>
       <c r="B695" s="7"/>
       <c r="C695" s="7"/>
       <c r="D695" s="7"/>
@@ -17971,7 +17991,7 @@
       <c r="W695" s="7"/>
     </row>
     <row r="696">
-      <c r="A696" s="2"/>
+      <c r="A696" s="1"/>
       <c r="B696" s="7"/>
       <c r="C696" s="7"/>
       <c r="D696" s="7"/>
@@ -17996,7 +18016,7 @@
       <c r="W696" s="7"/>
     </row>
     <row r="697">
-      <c r="A697" s="2"/>
+      <c r="A697" s="1"/>
       <c r="B697" s="7"/>
       <c r="C697" s="7"/>
       <c r="D697" s="7"/>
@@ -18021,7 +18041,7 @@
       <c r="W697" s="7"/>
     </row>
     <row r="698">
-      <c r="A698" s="2"/>
+      <c r="A698" s="1"/>
       <c r="B698" s="7"/>
       <c r="C698" s="7"/>
       <c r="D698" s="7"/>
@@ -18046,7 +18066,7 @@
       <c r="W698" s="7"/>
     </row>
     <row r="699">
-      <c r="A699" s="2"/>
+      <c r="A699" s="1"/>
       <c r="B699" s="7"/>
       <c r="C699" s="7"/>
       <c r="D699" s="7"/>
@@ -18071,7 +18091,7 @@
       <c r="W699" s="7"/>
     </row>
     <row r="700">
-      <c r="A700" s="2"/>
+      <c r="A700" s="1"/>
       <c r="B700" s="7"/>
       <c r="C700" s="7"/>
       <c r="D700" s="7"/>
@@ -18096,7 +18116,7 @@
       <c r="W700" s="7"/>
     </row>
     <row r="701">
-      <c r="A701" s="2"/>
+      <c r="A701" s="1"/>
       <c r="B701" s="7"/>
       <c r="C701" s="7"/>
       <c r="D701" s="7"/>
@@ -18121,7 +18141,7 @@
       <c r="W701" s="7"/>
     </row>
     <row r="702">
-      <c r="A702" s="2"/>
+      <c r="A702" s="1"/>
       <c r="B702" s="7"/>
       <c r="C702" s="7"/>
       <c r="D702" s="7"/>
@@ -18146,7 +18166,7 @@
       <c r="W702" s="7"/>
     </row>
     <row r="703">
-      <c r="A703" s="2"/>
+      <c r="A703" s="1"/>
       <c r="B703" s="7"/>
       <c r="C703" s="7"/>
       <c r="D703" s="7"/>
@@ -18171,7 +18191,7 @@
       <c r="W703" s="7"/>
     </row>
     <row r="704">
-      <c r="A704" s="2"/>
+      <c r="A704" s="1"/>
       <c r="B704" s="7"/>
       <c r="C704" s="7"/>
       <c r="D704" s="7"/>
@@ -18196,7 +18216,7 @@
       <c r="W704" s="7"/>
     </row>
     <row r="705">
-      <c r="A705" s="2"/>
+      <c r="A705" s="1"/>
       <c r="B705" s="7"/>
       <c r="C705" s="7"/>
       <c r="D705" s="7"/>
@@ -18221,7 +18241,7 @@
       <c r="W705" s="7"/>
     </row>
     <row r="706">
-      <c r="A706" s="2"/>
+      <c r="A706" s="1"/>
       <c r="B706" s="7"/>
       <c r="C706" s="7"/>
       <c r="D706" s="7"/>
@@ -18246,7 +18266,7 @@
       <c r="W706" s="7"/>
     </row>
     <row r="707">
-      <c r="A707" s="2"/>
+      <c r="A707" s="1"/>
       <c r="B707" s="7"/>
       <c r="C707" s="7"/>
       <c r="D707" s="7"/>
@@ -18271,7 +18291,7 @@
       <c r="W707" s="7"/>
     </row>
     <row r="708">
-      <c r="A708" s="2"/>
+      <c r="A708" s="1"/>
       <c r="B708" s="7"/>
       <c r="C708" s="7"/>
       <c r="D708" s="7"/>
@@ -18296,7 +18316,7 @@
       <c r="W708" s="7"/>
     </row>
     <row r="709">
-      <c r="A709" s="2"/>
+      <c r="A709" s="1"/>
       <c r="B709" s="7"/>
       <c r="C709" s="7"/>
       <c r="D709" s="7"/>
@@ -18321,7 +18341,7 @@
       <c r="W709" s="7"/>
     </row>
     <row r="710">
-      <c r="A710" s="2"/>
+      <c r="A710" s="1"/>
       <c r="B710" s="7"/>
       <c r="C710" s="7"/>
       <c r="D710" s="7"/>
@@ -18346,7 +18366,7 @@
       <c r="W710" s="7"/>
     </row>
     <row r="711">
-      <c r="A711" s="2"/>
+      <c r="A711" s="1"/>
       <c r="B711" s="7"/>
       <c r="C711" s="7"/>
       <c r="D711" s="7"/>
@@ -18371,7 +18391,7 @@
       <c r="W711" s="7"/>
     </row>
     <row r="712">
-      <c r="A712" s="2"/>
+      <c r="A712" s="1"/>
       <c r="B712" s="7"/>
       <c r="C712" s="7"/>
       <c r="D712" s="7"/>
@@ -18396,7 +18416,7 @@
       <c r="W712" s="7"/>
     </row>
     <row r="713">
-      <c r="A713" s="2"/>
+      <c r="A713" s="1"/>
       <c r="B713" s="7"/>
       <c r="C713" s="7"/>
       <c r="D713" s="7"/>
@@ -18421,7 +18441,7 @@
       <c r="W713" s="7"/>
     </row>
     <row r="714">
-      <c r="A714" s="2"/>
+      <c r="A714" s="1"/>
       <c r="B714" s="7"/>
       <c r="C714" s="7"/>
       <c r="D714" s="7"/>
@@ -18446,7 +18466,7 @@
       <c r="W714" s="7"/>
     </row>
     <row r="715">
-      <c r="A715" s="2"/>
+      <c r="A715" s="1"/>
       <c r="B715" s="7"/>
       <c r="C715" s="7"/>
       <c r="D715" s="7"/>
@@ -18471,7 +18491,7 @@
       <c r="W715" s="7"/>
     </row>
     <row r="716">
-      <c r="A716" s="2"/>
+      <c r="A716" s="1"/>
       <c r="B716" s="7"/>
       <c r="C716" s="7"/>
       <c r="D716" s="7"/>
@@ -18496,7 +18516,7 @@
       <c r="W716" s="7"/>
     </row>
     <row r="717">
-      <c r="A717" s="2"/>
+      <c r="A717" s="1"/>
       <c r="B717" s="7"/>
       <c r="C717" s="7"/>
       <c r="D717" s="7"/>
@@ -18521,7 +18541,7 @@
       <c r="W717" s="7"/>
     </row>
     <row r="718">
-      <c r="A718" s="2"/>
+      <c r="A718" s="1"/>
       <c r="B718" s="7"/>
       <c r="C718" s="7"/>
       <c r="D718" s="7"/>
@@ -18546,7 +18566,7 @@
       <c r="W718" s="7"/>
     </row>
     <row r="719">
-      <c r="A719" s="2"/>
+      <c r="A719" s="1"/>
       <c r="B719" s="7"/>
       <c r="C719" s="7"/>
       <c r="D719" s="7"/>
@@ -18571,7 +18591,7 @@
       <c r="W719" s="7"/>
     </row>
     <row r="720">
-      <c r="A720" s="2"/>
+      <c r="A720" s="1"/>
       <c r="B720" s="7"/>
       <c r="C720" s="7"/>
       <c r="D720" s="7"/>
@@ -18596,7 +18616,7 @@
       <c r="W720" s="7"/>
     </row>
     <row r="721">
-      <c r="A721" s="2"/>
+      <c r="A721" s="1"/>
       <c r="B721" s="7"/>
       <c r="C721" s="7"/>
       <c r="D721" s="7"/>
@@ -18621,7 +18641,7 @@
       <c r="W721" s="7"/>
     </row>
     <row r="722">
-      <c r="A722" s="2"/>
+      <c r="A722" s="1"/>
       <c r="B722" s="7"/>
       <c r="C722" s="7"/>
       <c r="D722" s="7"/>
@@ -18646,7 +18666,7 @@
       <c r="W722" s="7"/>
     </row>
     <row r="723">
-      <c r="A723" s="2"/>
+      <c r="A723" s="1"/>
       <c r="B723" s="7"/>
       <c r="C723" s="7"/>
       <c r="D723" s="7"/>
@@ -18671,7 +18691,7 @@
       <c r="W723" s="7"/>
     </row>
     <row r="724">
-      <c r="A724" s="2"/>
+      <c r="A724" s="1"/>
       <c r="B724" s="7"/>
       <c r="C724" s="7"/>
       <c r="D724" s="7"/>
@@ -18696,7 +18716,7 @@
       <c r="W724" s="7"/>
     </row>
     <row r="725">
-      <c r="A725" s="2"/>
+      <c r="A725" s="1"/>
       <c r="B725" s="7"/>
       <c r="C725" s="7"/>
       <c r="D725" s="7"/>
@@ -18721,7 +18741,7 @@
       <c r="W725" s="7"/>
     </row>
     <row r="726">
-      <c r="A726" s="2"/>
+      <c r="A726" s="1"/>
       <c r="B726" s="7"/>
       <c r="C726" s="7"/>
       <c r="D726" s="7"/>
@@ -18746,7 +18766,7 @@
       <c r="W726" s="7"/>
     </row>
     <row r="727">
-      <c r="A727" s="2"/>
+      <c r="A727" s="1"/>
       <c r="B727" s="7"/>
       <c r="C727" s="7"/>
       <c r="D727" s="7"/>
@@ -18771,7 +18791,7 @@
       <c r="W727" s="7"/>
     </row>
     <row r="728">
-      <c r="A728" s="2"/>
+      <c r="A728" s="1"/>
       <c r="B728" s="7"/>
       <c r="C728" s="7"/>
       <c r="D728" s="7"/>
@@ -18796,7 +18816,7 @@
       <c r="W728" s="7"/>
     </row>
     <row r="729">
-      <c r="A729" s="2"/>
+      <c r="A729" s="1"/>
       <c r="B729" s="7"/>
       <c r="C729" s="7"/>
       <c r="D729" s="7"/>
@@ -18821,7 +18841,7 @@
       <c r="W729" s="7"/>
     </row>
     <row r="730">
-      <c r="A730" s="2"/>
+      <c r="A730" s="1"/>
       <c r="B730" s="7"/>
       <c r="C730" s="7"/>
       <c r="D730" s="7"/>
@@ -18846,7 +18866,7 @@
       <c r="W730" s="7"/>
     </row>
     <row r="731">
-      <c r="A731" s="2"/>
+      <c r="A731" s="1"/>
       <c r="B731" s="7"/>
       <c r="C731" s="7"/>
       <c r="D731" s="7"/>
@@ -18871,7 +18891,7 @@
       <c r="W731" s="7"/>
     </row>
     <row r="732">
-      <c r="A732" s="2"/>
+      <c r="A732" s="1"/>
       <c r="B732" s="7"/>
       <c r="C732" s="7"/>
       <c r="D732" s="7"/>
@@ -18896,7 +18916,7 @@
       <c r="W732" s="7"/>
     </row>
     <row r="733">
-      <c r="A733" s="2"/>
+      <c r="A733" s="1"/>
       <c r="B733" s="7"/>
       <c r="C733" s="7"/>
       <c r="D733" s="7"/>
@@ -18921,7 +18941,7 @@
       <c r="W733" s="7"/>
     </row>
     <row r="734">
-      <c r="A734" s="2"/>
+      <c r="A734" s="1"/>
       <c r="B734" s="7"/>
       <c r="C734" s="7"/>
       <c r="D734" s="7"/>
@@ -18946,7 +18966,7 @@
       <c r="W734" s="7"/>
     </row>
     <row r="735">
-      <c r="A735" s="2"/>
+      <c r="A735" s="1"/>
       <c r="B735" s="7"/>
       <c r="C735" s="7"/>
       <c r="D735" s="7"/>
@@ -18971,7 +18991,7 @@
       <c r="W735" s="7"/>
     </row>
     <row r="736">
-      <c r="A736" s="2"/>
+      <c r="A736" s="1"/>
       <c r="B736" s="7"/>
       <c r="C736" s="7"/>
       <c r="D736" s="7"/>
@@ -18996,7 +19016,7 @@
       <c r="W736" s="7"/>
     </row>
     <row r="737">
-      <c r="A737" s="2"/>
+      <c r="A737" s="1"/>
       <c r="B737" s="7"/>
       <c r="C737" s="7"/>
       <c r="D737" s="7"/>
@@ -19021,7 +19041,7 @@
       <c r="W737" s="7"/>
     </row>
     <row r="738">
-      <c r="A738" s="2"/>
+      <c r="A738" s="1"/>
       <c r="B738" s="7"/>
       <c r="C738" s="7"/>
       <c r="D738" s="7"/>
@@ -19046,7 +19066,7 @@
       <c r="W738" s="7"/>
     </row>
     <row r="739">
-      <c r="A739" s="2"/>
+      <c r="A739" s="1"/>
       <c r="B739" s="7"/>
       <c r="C739" s="7"/>
       <c r="D739" s="7"/>
@@ -19071,7 +19091,7 @@
       <c r="W739" s="7"/>
     </row>
     <row r="740">
-      <c r="A740" s="2"/>
+      <c r="A740" s="1"/>
       <c r="B740" s="7"/>
       <c r="C740" s="7"/>
       <c r="D740" s="7"/>
@@ -19096,7 +19116,7 @@
       <c r="W740" s="7"/>
     </row>
     <row r="741">
-      <c r="A741" s="2"/>
+      <c r="A741" s="1"/>
       <c r="B741" s="7"/>
       <c r="C741" s="7"/>
       <c r="D741" s="7"/>
@@ -19121,7 +19141,7 @@
       <c r="W741" s="7"/>
     </row>
     <row r="742">
-      <c r="A742" s="2"/>
+      <c r="A742" s="1"/>
       <c r="B742" s="7"/>
       <c r="C742" s="7"/>
       <c r="D742" s="7"/>
@@ -19146,7 +19166,7 @@
       <c r="W742" s="7"/>
     </row>
     <row r="743">
-      <c r="A743" s="2"/>
+      <c r="A743" s="1"/>
       <c r="B743" s="7"/>
       <c r="C743" s="7"/>
       <c r="D743" s="7"/>
@@ -19171,7 +19191,7 @@
       <c r="W743" s="7"/>
     </row>
     <row r="744">
-      <c r="A744" s="2"/>
+      <c r="A744" s="1"/>
       <c r="B744" s="7"/>
       <c r="C744" s="7"/>
       <c r="D744" s="7"/>
@@ -19196,7 +19216,7 @@
       <c r="W744" s="7"/>
     </row>
     <row r="745">
-      <c r="A745" s="2"/>
+      <c r="A745" s="1"/>
       <c r="B745" s="7"/>
       <c r="C745" s="7"/>
       <c r="D745" s="7"/>
@@ -19221,7 +19241,7 @@
       <c r="W745" s="7"/>
     </row>
     <row r="746">
-      <c r="A746" s="2"/>
+      <c r="A746" s="1"/>
       <c r="B746" s="7"/>
       <c r="C746" s="7"/>
       <c r="D746" s="7"/>
@@ -19246,7 +19266,7 @@
       <c r="W746" s="7"/>
     </row>
     <row r="747">
-      <c r="A747" s="2"/>
+      <c r="A747" s="1"/>
       <c r="B747" s="7"/>
       <c r="C747" s="7"/>
       <c r="D747" s="7"/>
@@ -19271,7 +19291,7 @@
       <c r="W747" s="7"/>
     </row>
     <row r="748">
-      <c r="A748" s="2"/>
+      <c r="A748" s="1"/>
       <c r="B748" s="7"/>
       <c r="C748" s="7"/>
       <c r="D748" s="7"/>
@@ -19296,7 +19316,7 @@
       <c r="W748" s="7"/>
     </row>
     <row r="749">
-      <c r="A749" s="2"/>
+      <c r="A749" s="1"/>
       <c r="B749" s="7"/>
       <c r="C749" s="7"/>
       <c r="D749" s="7"/>
@@ -19321,7 +19341,7 @@
       <c r="W749" s="7"/>
     </row>
     <row r="750">
-      <c r="A750" s="2"/>
+      <c r="A750" s="1"/>
       <c r="B750" s="7"/>
       <c r="C750" s="7"/>
       <c r="D750" s="7"/>
@@ -19346,7 +19366,7 @@
       <c r="W750" s="7"/>
     </row>
     <row r="751">
-      <c r="A751" s="2"/>
+      <c r="A751" s="1"/>
       <c r="B751" s="7"/>
       <c r="C751" s="7"/>
       <c r="D751" s="7"/>
@@ -19371,7 +19391,7 @@
       <c r="W751" s="7"/>
     </row>
     <row r="752">
-      <c r="A752" s="2"/>
+      <c r="A752" s="1"/>
       <c r="B752" s="7"/>
       <c r="C752" s="7"/>
       <c r="D752" s="7"/>
@@ -19396,7 +19416,7 @@
       <c r="W752" s="7"/>
     </row>
     <row r="753">
-      <c r="A753" s="2"/>
+      <c r="A753" s="1"/>
       <c r="B753" s="7"/>
       <c r="C753" s="7"/>
       <c r="D753" s="7"/>
@@ -19421,7 +19441,7 @@
       <c r="W753" s="7"/>
     </row>
     <row r="754">
-      <c r="A754" s="2"/>
+      <c r="A754" s="1"/>
       <c r="B754" s="7"/>
       <c r="C754" s="7"/>
       <c r="D754" s="7"/>
@@ -19446,7 +19466,7 @@
       <c r="W754" s="7"/>
     </row>
     <row r="755">
-      <c r="A755" s="2"/>
+      <c r="A755" s="1"/>
       <c r="B755" s="7"/>
       <c r="C755" s="7"/>
       <c r="D755" s="7"/>
@@ -19471,7 +19491,7 @@
       <c r="W755" s="7"/>
     </row>
     <row r="756">
-      <c r="A756" s="2"/>
+      <c r="A756" s="1"/>
       <c r="B756" s="7"/>
       <c r="C756" s="7"/>
       <c r="D756" s="7"/>
@@ -19496,7 +19516,7 @@
       <c r="W756" s="7"/>
     </row>
     <row r="757">
-      <c r="A757" s="2"/>
+      <c r="A757" s="1"/>
       <c r="B757" s="7"/>
       <c r="C757" s="7"/>
       <c r="D757" s="7"/>
@@ -19521,7 +19541,7 @@
       <c r="W757" s="7"/>
     </row>
     <row r="758">
-      <c r="A758" s="2"/>
+      <c r="A758" s="1"/>
       <c r="B758" s="7"/>
       <c r="C758" s="7"/>
       <c r="D758" s="7"/>
@@ -19546,7 +19566,7 @@
       <c r="W758" s="7"/>
     </row>
     <row r="759">
-      <c r="A759" s="2"/>
+      <c r="A759" s="1"/>
       <c r="B759" s="7"/>
       <c r="C759" s="7"/>
       <c r="D759" s="7"/>
@@ -19571,7 +19591,7 @@
       <c r="W759" s="7"/>
     </row>
     <row r="760">
-      <c r="A760" s="2"/>
+      <c r="A760" s="1"/>
       <c r="B760" s="7"/>
       <c r="C760" s="7"/>
       <c r="D760" s="7"/>
@@ -19596,7 +19616,7 @@
       <c r="W760" s="7"/>
     </row>
     <row r="761">
-      <c r="A761" s="2"/>
+      <c r="A761" s="1"/>
       <c r="B761" s="7"/>
       <c r="C761" s="7"/>
       <c r="D761" s="7"/>
@@ -19621,7 +19641,7 @@
       <c r="W761" s="7"/>
     </row>
     <row r="762">
-      <c r="A762" s="2"/>
+      <c r="A762" s="1"/>
       <c r="B762" s="7"/>
       <c r="C762" s="7"/>
       <c r="D762" s="7"/>
@@ -19646,7 +19666,7 @@
       <c r="W762" s="7"/>
     </row>
     <row r="763">
-      <c r="A763" s="2"/>
+      <c r="A763" s="1"/>
       <c r="B763" s="7"/>
       <c r="C763" s="7"/>
       <c r="D763" s="7"/>
@@ -19671,7 +19691,7 @@
       <c r="W763" s="7"/>
     </row>
     <row r="764">
-      <c r="A764" s="2"/>
+      <c r="A764" s="1"/>
       <c r="B764" s="7"/>
       <c r="C764" s="7"/>
       <c r="D764" s="7"/>
@@ -19696,7 +19716,7 @@
       <c r="W764" s="7"/>
     </row>
     <row r="765">
-      <c r="A765" s="2"/>
+      <c r="A765" s="1"/>
       <c r="B765" s="7"/>
       <c r="C765" s="7"/>
       <c r="D765" s="7"/>
@@ -19721,7 +19741,7 @@
       <c r="W765" s="7"/>
     </row>
     <row r="766">
-      <c r="A766" s="2"/>
+      <c r="A766" s="1"/>
       <c r="B766" s="7"/>
       <c r="C766" s="7"/>
       <c r="D766" s="7"/>
@@ -19746,7 +19766,7 @@
       <c r="W766" s="7"/>
     </row>
     <row r="767">
-      <c r="A767" s="2"/>
+      <c r="A767" s="1"/>
       <c r="B767" s="7"/>
       <c r="C767" s="7"/>
       <c r="D767" s="7"/>
@@ -19771,7 +19791,7 @@
       <c r="W767" s="7"/>
     </row>
     <row r="768">
-      <c r="A768" s="2"/>
+      <c r="A768" s="1"/>
       <c r="B768" s="7"/>
       <c r="C768" s="7"/>
       <c r="D768" s="7"/>
@@ -19796,7 +19816,7 @@
       <c r="W768" s="7"/>
     </row>
     <row r="769">
-      <c r="A769" s="2"/>
+      <c r="A769" s="1"/>
       <c r="B769" s="7"/>
       <c r="C769" s="7"/>
       <c r="D769" s="7"/>
@@ -19821,7 +19841,7 @@
       <c r="W769" s="7"/>
     </row>
     <row r="770">
-      <c r="A770" s="2"/>
+      <c r="A770" s="1"/>
       <c r="B770" s="7"/>
       <c r="C770" s="7"/>
       <c r="D770" s="7"/>
@@ -19846,7 +19866,7 @@
       <c r="W770" s="7"/>
     </row>
     <row r="771">
-      <c r="A771" s="2"/>
+      <c r="A771" s="1"/>
       <c r="B771" s="7"/>
       <c r="C771" s="7"/>
       <c r="D771" s="7"/>
@@ -19871,7 +19891,7 @@
       <c r="W771" s="7"/>
     </row>
     <row r="772">
-      <c r="A772" s="2"/>
+      <c r="A772" s="1"/>
       <c r="B772" s="7"/>
       <c r="C772" s="7"/>
       <c r="D772" s="7"/>
@@ -19896,7 +19916,7 @@
       <c r="W772" s="7"/>
     </row>
     <row r="773">
-      <c r="A773" s="2"/>
+      <c r="A773" s="1"/>
       <c r="B773" s="7"/>
       <c r="C773" s="7"/>
       <c r="D773" s="7"/>
@@ -19921,7 +19941,7 @@
       <c r="W773" s="7"/>
     </row>
     <row r="774">
-      <c r="A774" s="2"/>
+      <c r="A774" s="1"/>
       <c r="B774" s="7"/>
       <c r="C774" s="7"/>
       <c r="D774" s="7"/>
@@ -19946,7 +19966,7 @@
       <c r="W774" s="7"/>
     </row>
     <row r="775">
-      <c r="A775" s="2"/>
+      <c r="A775" s="1"/>
       <c r="B775" s="7"/>
       <c r="C775" s="7"/>
       <c r="D775" s="7"/>
@@ -19971,7 +19991,7 @@
       <c r="W775" s="7"/>
     </row>
     <row r="776">
-      <c r="A776" s="2"/>
+      <c r="A776" s="1"/>
       <c r="B776" s="7"/>
       <c r="C776" s="7"/>
       <c r="D776" s="7"/>
@@ -19996,7 +20016,7 @@
       <c r="W776" s="7"/>
     </row>
     <row r="777">
-      <c r="A777" s="2"/>
+      <c r="A777" s="1"/>
       <c r="B777" s="7"/>
       <c r="C777" s="7"/>
       <c r="D777" s="7"/>
@@ -20021,7 +20041,7 @@
       <c r="W777" s="7"/>
     </row>
     <row r="778">
-      <c r="A778" s="2"/>
+      <c r="A778" s="1"/>
       <c r="B778" s="7"/>
       <c r="C778" s="7"/>
       <c r="D778" s="7"/>
@@ -20046,7 +20066,7 @@
       <c r="W778" s="7"/>
     </row>
     <row r="779">
-      <c r="A779" s="2"/>
+      <c r="A779" s="1"/>
       <c r="B779" s="7"/>
       <c r="C779" s="7"/>
       <c r="D779" s="7"/>
@@ -20071,7 +20091,7 @@
       <c r="W779" s="7"/>
     </row>
     <row r="780">
-      <c r="A780" s="2"/>
+      <c r="A780" s="1"/>
       <c r="B780" s="7"/>
       <c r="C780" s="7"/>
       <c r="D780" s="7"/>
@@ -20096,7 +20116,7 @@
       <c r="W780" s="7"/>
     </row>
     <row r="781">
-      <c r="A781" s="2"/>
+      <c r="A781" s="1"/>
       <c r="B781" s="7"/>
       <c r="C781" s="7"/>
       <c r="D781" s="7"/>
@@ -20121,7 +20141,7 @@
       <c r="W781" s="7"/>
     </row>
     <row r="782">
-      <c r="A782" s="2"/>
+      <c r="A782" s="1"/>
       <c r="B782" s="7"/>
       <c r="C782" s="7"/>
       <c r="D782" s="7"/>
@@ -20146,7 +20166,7 @@
       <c r="W782" s="7"/>
     </row>
     <row r="783">
-      <c r="A783" s="2"/>
+      <c r="A783" s="1"/>
       <c r="B783" s="7"/>
       <c r="C783" s="7"/>
       <c r="D783" s="7"/>
@@ -20171,7 +20191,7 @@
       <c r="W783" s="7"/>
     </row>
     <row r="784">
-      <c r="A784" s="2"/>
+      <c r="A784" s="1"/>
       <c r="B784" s="7"/>
       <c r="C784" s="7"/>
       <c r="D784" s="7"/>
@@ -20196,7 +20216,7 @@
       <c r="W784" s="7"/>
     </row>
     <row r="785">
-      <c r="A785" s="2"/>
+      <c r="A785" s="1"/>
       <c r="B785" s="7"/>
       <c r="C785" s="7"/>
       <c r="D785" s="7"/>
@@ -20221,7 +20241,7 @@
       <c r="W785" s="7"/>
     </row>
     <row r="786">
-      <c r="A786" s="2"/>
+      <c r="A786" s="1"/>
       <c r="B786" s="7"/>
       <c r="C786" s="7"/>
       <c r="D786" s="7"/>
@@ -20246,7 +20266,7 @@
       <c r="W786" s="7"/>
     </row>
     <row r="787">
-      <c r="A787" s="2"/>
+      <c r="A787" s="1"/>
       <c r="B787" s="7"/>
       <c r="C787" s="7"/>
       <c r="D787" s="7"/>
@@ -20271,7 +20291,7 @@
       <c r="W787" s="7"/>
     </row>
     <row r="788">
-      <c r="A788" s="2"/>
+      <c r="A788" s="1"/>
       <c r="B788" s="7"/>
       <c r="C788" s="7"/>
       <c r="D788" s="7"/>
@@ -20296,7 +20316,7 @@
       <c r="W788" s="7"/>
     </row>
     <row r="789">
-      <c r="A789" s="2"/>
+      <c r="A789" s="1"/>
       <c r="B789" s="7"/>
       <c r="C789" s="7"/>
       <c r="D789" s="7"/>
@@ -20321,7 +20341,7 @@
       <c r="W789" s="7"/>
     </row>
     <row r="790">
-      <c r="A790" s="2"/>
+      <c r="A790" s="1"/>
       <c r="B790" s="7"/>
       <c r="C790" s="7"/>
       <c r="D790" s="7"/>
@@ -20346,7 +20366,7 @@
       <c r="W790" s="7"/>
     </row>
     <row r="791">
-      <c r="A791" s="2"/>
+      <c r="A791" s="1"/>
       <c r="B791" s="7"/>
       <c r="C791" s="7"/>
       <c r="D791" s="7"/>
@@ -20371,7 +20391,7 @@
       <c r="W791" s="7"/>
     </row>
     <row r="792">
-      <c r="A792" s="2"/>
+      <c r="A792" s="1"/>
       <c r="B792" s="7"/>
       <c r="C792" s="7"/>
       <c r="D792" s="7"/>
@@ -20396,7 +20416,7 @@
       <c r="W792" s="7"/>
     </row>
     <row r="793">
-      <c r="A793" s="2"/>
+      <c r="A793" s="1"/>
       <c r="B793" s="7"/>
       <c r="C793" s="7"/>
       <c r="D793" s="7"/>
@@ -20421,7 +20441,7 @@
       <c r="W793" s="7"/>
     </row>
     <row r="794">
-      <c r="A794" s="2"/>
+      <c r="A794" s="1"/>
       <c r="B794" s="7"/>
       <c r="C794" s="7"/>
       <c r="D794" s="7"/>
@@ -20446,7 +20466,7 @@
       <c r="W794" s="7"/>
     </row>
     <row r="795">
-      <c r="A795" s="2"/>
+      <c r="A795" s="1"/>
       <c r="B795" s="7"/>
       <c r="C795" s="7"/>
       <c r="D795" s="7"/>
@@ -20471,7 +20491,7 @@
       <c r="W795" s="7"/>
     </row>
     <row r="796">
-      <c r="A796" s="2"/>
+      <c r="A796" s="1"/>
       <c r="B796" s="7"/>
       <c r="C796" s="7"/>
       <c r="D796" s="7"/>
@@ -20496,7 +20516,7 @@
       <c r="W796" s="7"/>
     </row>
     <row r="797">
-      <c r="A797" s="2"/>
+      <c r="A797" s="1"/>
       <c r="B797" s="7"/>
       <c r="C797" s="7"/>
       <c r="D797" s="7"/>
@@ -20521,7 +20541,7 @@
       <c r="W797" s="7"/>
     </row>
     <row r="798">
-      <c r="A798" s="2"/>
+      <c r="A798" s="1"/>
       <c r="B798" s="7"/>
       <c r="C798" s="7"/>
       <c r="D798" s="7"/>
@@ -20546,7 +20566,7 @@
       <c r="W798" s="7"/>
     </row>
     <row r="799">
-      <c r="A799" s="2"/>
+      <c r="A799" s="1"/>
       <c r="B799" s="7"/>
       <c r="C799" s="7"/>
       <c r="D799" s="7"/>
@@ -20571,7 +20591,7 @@
       <c r="W799" s="7"/>
     </row>
     <row r="800">
-      <c r="A800" s="2"/>
+      <c r="A800" s="1"/>
       <c r="B800" s="7"/>
       <c r="C800" s="7"/>
       <c r="D800" s="7"/>
@@ -20596,7 +20616,7 @@
       <c r="W800" s="7"/>
     </row>
     <row r="801">
-      <c r="A801" s="2"/>
+      <c r="A801" s="1"/>
       <c r="B801" s="7"/>
       <c r="C801" s="7"/>
       <c r="D801" s="7"/>
@@ -20621,7 +20641,7 @@
       <c r="W801" s="7"/>
     </row>
     <row r="802">
-      <c r="A802" s="2"/>
+      <c r="A802" s="1"/>
       <c r="B802" s="7"/>
       <c r="C802" s="7"/>
       <c r="D802" s="7"/>
@@ -20646,7 +20666,7 @@
       <c r="W802" s="7"/>
     </row>
     <row r="803">
-      <c r="A803" s="2"/>
+      <c r="A803" s="1"/>
       <c r="B803" s="7"/>
       <c r="C803" s="7"/>
       <c r="D803" s="7"/>
@@ -20671,7 +20691,7 @@
       <c r="W803" s="7"/>
     </row>
     <row r="804">
-      <c r="A804" s="2"/>
+      <c r="A804" s="1"/>
       <c r="B804" s="7"/>
       <c r="C804" s="7"/>
       <c r="D804" s="7"/>
@@ -20696,7 +20716,7 @@
       <c r="W804" s="7"/>
     </row>
     <row r="805">
-      <c r="A805" s="2"/>
+      <c r="A805" s="1"/>
       <c r="B805" s="7"/>
       <c r="C805" s="7"/>
       <c r="D805" s="7"/>
@@ -20721,7 +20741,7 @@
       <c r="W805" s="7"/>
     </row>
     <row r="806">
-      <c r="A806" s="2"/>
+      <c r="A806" s="1"/>
       <c r="B806" s="7"/>
       <c r="C806" s="7"/>
       <c r="D806" s="7"/>
@@ -20746,7 +20766,7 @@
       <c r="W806" s="7"/>
     </row>
     <row r="807">
-      <c r="A807" s="2"/>
+      <c r="A807" s="1"/>
       <c r="B807" s="7"/>
       <c r="C807" s="7"/>
       <c r="D807" s="7"/>
@@ -20771,7 +20791,7 @@
       <c r="W807" s="7"/>
     </row>
     <row r="808">
-      <c r="A808" s="2"/>
+      <c r="A808" s="1"/>
       <c r="B808" s="7"/>
       <c r="C808" s="7"/>
       <c r="D808" s="7"/>
@@ -20796,7 +20816,7 @@
       <c r="W808" s="7"/>
     </row>
     <row r="809">
-      <c r="A809" s="2"/>
+      <c r="A809" s="1"/>
       <c r="B809" s="7"/>
       <c r="C809" s="7"/>
       <c r="D809" s="7"/>
@@ -20821,7 +20841,7 @@
       <c r="W809" s="7"/>
     </row>
     <row r="810">
-      <c r="A810" s="2"/>
+      <c r="A810" s="1"/>
       <c r="B810" s="7"/>
       <c r="C810" s="7"/>
       <c r="D810" s="7"/>
@@ -20846,7 +20866,7 @@
       <c r="W810" s="7"/>
     </row>
     <row r="811">
-      <c r="A811" s="2"/>
+      <c r="A811" s="1"/>
       <c r="B811" s="7"/>
       <c r="C811" s="7"/>
       <c r="D811" s="7"/>
@@ -20871,7 +20891,7 @@
       <c r="W811" s="7"/>
     </row>
     <row r="812">
-      <c r="A812" s="2"/>
+      <c r="A812" s="1"/>
       <c r="B812" s="7"/>
       <c r="C812" s="7"/>
       <c r="D812" s="7"/>
@@ -20896,7 +20916,7 @@
       <c r="W812" s="7"/>
     </row>
     <row r="813">
-      <c r="A813" s="2"/>
+      <c r="A813" s="1"/>
       <c r="B813" s="7"/>
       <c r="C813" s="7"/>
       <c r="D813" s="7"/>
@@ -20921,7 +20941,7 @@
       <c r="W813" s="7"/>
     </row>
     <row r="814">
-      <c r="A814" s="2"/>
+      <c r="A814" s="1"/>
       <c r="B814" s="7"/>
       <c r="C814" s="7"/>
       <c r="D814" s="7"/>
@@ -20946,7 +20966,7 @@
       <c r="W814" s="7"/>
     </row>
     <row r="815">
-      <c r="A815" s="2"/>
+      <c r="A815" s="1"/>
       <c r="B815" s="7"/>
       <c r="C815" s="7"/>
       <c r="D815" s="7"/>
@@ -20971,7 +20991,7 @@
       <c r="W815" s="7"/>
     </row>
     <row r="816">
-      <c r="A816" s="2"/>
+      <c r="A816" s="1"/>
       <c r="B816" s="7"/>
       <c r="C816" s="7"/>
       <c r="D816" s="7"/>
@@ -20996,7 +21016,7 @@
       <c r="W816" s="7"/>
     </row>
     <row r="817">
-      <c r="A817" s="2"/>
+      <c r="A817" s="1"/>
       <c r="B817" s="7"/>
       <c r="C817" s="7"/>
       <c r="D817" s="7"/>
@@ -21021,7 +21041,7 @@
       <c r="W817" s="7"/>
     </row>
     <row r="818">
-      <c r="A818" s="2"/>
+      <c r="A818" s="1"/>
       <c r="B818" s="7"/>
       <c r="C818" s="7"/>
       <c r="D818" s="7"/>
@@ -21046,7 +21066,7 @@
       <c r="W818" s="7"/>
     </row>
     <row r="819">
-      <c r="A819" s="2"/>
+      <c r="A819" s="1"/>
       <c r="B819" s="7"/>
       <c r="C819" s="7"/>
       <c r="D819" s="7"/>
@@ -21071,7 +21091,7 @@
       <c r="W819" s="7"/>
     </row>
     <row r="820">
-      <c r="A820" s="2"/>
+      <c r="A820" s="1"/>
       <c r="B820" s="7"/>
       <c r="C820" s="7"/>
       <c r="D820" s="7"/>
@@ -21096,7 +21116,7 @@
       <c r="W820" s="7"/>
     </row>
     <row r="821">
-      <c r="A821" s="2"/>
+      <c r="A821" s="1"/>
       <c r="B821" s="7"/>
       <c r="C821" s="7"/>
       <c r="D821" s="7"/>
@@ -21121,7 +21141,7 @@
       <c r="W821" s="7"/>
     </row>
     <row r="822">
-      <c r="A822" s="2"/>
+      <c r="A822" s="1"/>
       <c r="B822" s="7"/>
       <c r="C822" s="7"/>
       <c r="D822" s="7"/>
@@ -21146,7 +21166,7 @@
       <c r="W822" s="7"/>
     </row>
     <row r="823">
-      <c r="A823" s="2"/>
+      <c r="A823" s="1"/>
       <c r="B823" s="7"/>
       <c r="C823" s="7"/>
       <c r="D823" s="7"/>
@@ -21171,7 +21191,7 @@
       <c r="W823" s="7"/>
     </row>
     <row r="824">
-      <c r="A824" s="2"/>
+      <c r="A824" s="1"/>
       <c r="B824" s="7"/>
       <c r="C824" s="7"/>
       <c r="D824" s="7"/>
@@ -21196,7 +21216,7 @@
       <c r="W824" s="7"/>
     </row>
     <row r="825">
-      <c r="A825" s="2"/>
+      <c r="A825" s="1"/>
       <c r="B825" s="7"/>
       <c r="C825" s="7"/>
       <c r="D825" s="7"/>
@@ -21221,7 +21241,7 @@
       <c r="W825" s="7"/>
     </row>
     <row r="826">
-      <c r="A826" s="2"/>
+      <c r="A826" s="1"/>
       <c r="B826" s="7"/>
       <c r="C826" s="7"/>
       <c r="D826" s="7"/>
@@ -21246,7 +21266,7 @@
       <c r="W826" s="7"/>
     </row>
     <row r="827">
-      <c r="A827" s="2"/>
+      <c r="A827" s="1"/>
       <c r="B827" s="7"/>
       <c r="C827" s="7"/>
       <c r="D827" s="7"/>
@@ -21271,7 +21291,7 @@
       <c r="W827" s="7"/>
     </row>
     <row r="828">
-      <c r="A828" s="2"/>
+      <c r="A828" s="1"/>
       <c r="B828" s="7"/>
       <c r="C828" s="7"/>
       <c r="D828" s="7"/>
@@ -21296,7 +21316,7 @@
       <c r="W828" s="7"/>
     </row>
     <row r="829">
-      <c r="A829" s="2"/>
+      <c r="A829" s="1"/>
       <c r="B829" s="7"/>
       <c r="C829" s="7"/>
       <c r="D829" s="7"/>
@@ -21321,7 +21341,7 @@
       <c r="W829" s="7"/>
     </row>
     <row r="830">
-      <c r="A830" s="2"/>
+      <c r="A830" s="1"/>
       <c r="B830" s="7"/>
       <c r="C830" s="7"/>
       <c r="D830" s="7"/>
@@ -21346,7 +21366,7 @@
       <c r="W830" s="7"/>
     </row>
     <row r="831">
-      <c r="A831" s="2"/>
+      <c r="A831" s="1"/>
       <c r="B831" s="7"/>
       <c r="C831" s="7"/>
       <c r="D831" s="7"/>
@@ -21371,7 +21391,7 @@
       <c r="W831" s="7"/>
     </row>
     <row r="832">
-      <c r="A832" s="2"/>
+      <c r="A832" s="1"/>
       <c r="B832" s="7"/>
       <c r="C832" s="7"/>
       <c r="D832" s="7"/>
@@ -21396,7 +21416,7 @@
       <c r="W832" s="7"/>
     </row>
     <row r="833">
-      <c r="A833" s="2"/>
+      <c r="A833" s="1"/>
       <c r="B833" s="7"/>
       <c r="C833" s="7"/>
       <c r="D833" s="7"/>
@@ -21421,7 +21441,7 @@
       <c r="W833" s="7"/>
     </row>
     <row r="834">
-      <c r="A834" s="2"/>
+      <c r="A834" s="1"/>
       <c r="B834" s="7"/>
       <c r="C834" s="7"/>
       <c r="D834" s="7"/>
@@ -21446,7 +21466,7 @@
       <c r="W834" s="7"/>
     </row>
     <row r="835">
-      <c r="A835" s="2"/>
+      <c r="A835" s="1"/>
       <c r="B835" s="7"/>
       <c r="C835" s="7"/>
       <c r="D835" s="7"/>
@@ -21471,7 +21491,7 @@
       <c r="W835" s="7"/>
     </row>
     <row r="836">
-      <c r="A836" s="2"/>
+      <c r="A836" s="1"/>
       <c r="B836" s="7"/>
       <c r="C836" s="7"/>
       <c r="D836" s="7"/>
@@ -21496,7 +21516,7 @@
       <c r="W836" s="7"/>
     </row>
     <row r="837">
-      <c r="A837" s="2"/>
+      <c r="A837" s="1"/>
       <c r="B837" s="7"/>
       <c r="C837" s="7"/>
       <c r="D837" s="7"/>
@@ -21521,7 +21541,7 @@
       <c r="W837" s="7"/>
     </row>
     <row r="838">
-      <c r="A838" s="2"/>
+      <c r="A838" s="1"/>
       <c r="B838" s="7"/>
       <c r="C838" s="7"/>
       <c r="D838" s="7"/>
@@ -21546,7 +21566,7 @@
       <c r="W838" s="7"/>
     </row>
     <row r="839">
-      <c r="A839" s="2"/>
+      <c r="A839" s="1"/>
       <c r="B839" s="7"/>
       <c r="C839" s="7"/>
       <c r="D839" s="7"/>
@@ -21571,7 +21591,7 @@
       <c r="W839" s="7"/>
     </row>
     <row r="840">
-      <c r="A840" s="2"/>
+      <c r="A840" s="1"/>
       <c r="B840" s="7"/>
       <c r="C840" s="7"/>
       <c r="D840" s="7"/>
@@ -21596,7 +21616,7 @@
       <c r="W840" s="7"/>
     </row>
     <row r="841">
-      <c r="A841" s="2"/>
+      <c r="A841" s="1"/>
       <c r="B841" s="7"/>
       <c r="C841" s="7"/>
       <c r="D841" s="7"/>
@@ -21621,7 +21641,7 @@
       <c r="W841" s="7"/>
     </row>
     <row r="842">
-      <c r="A842" s="2"/>
+      <c r="A842" s="1"/>
       <c r="B842" s="7"/>
       <c r="C842" s="7"/>
       <c r="D842" s="7"/>
@@ -21646,7 +21666,7 @@
       <c r="W842" s="7"/>
     </row>
     <row r="843">
-      <c r="A843" s="2"/>
+      <c r="A843" s="1"/>
       <c r="B843" s="7"/>
       <c r="C843" s="7"/>
       <c r="D843" s="7"/>
@@ -21671,7 +21691,7 @@
       <c r="W843" s="7"/>
     </row>
     <row r="844">
-      <c r="A844" s="2"/>
+      <c r="A844" s="1"/>
       <c r="B844" s="7"/>
       <c r="C844" s="7"/>
       <c r="D844" s="7"/>
@@ -21696,7 +21716,7 @@
       <c r="W844" s="7"/>
     </row>
     <row r="845">
-      <c r="A845" s="2"/>
+      <c r="A845" s="1"/>
       <c r="B845" s="7"/>
       <c r="C845" s="7"/>
       <c r="D845" s="7"/>
@@ -21721,7 +21741,7 @@
       <c r="W845" s="7"/>
     </row>
     <row r="846">
-      <c r="A846" s="2"/>
+      <c r="A846" s="1"/>
       <c r="B846" s="7"/>
       <c r="C846" s="7"/>
       <c r="D846" s="7"/>
@@ -21746,7 +21766,7 @@
       <c r="W846" s="7"/>
     </row>
     <row r="847">
-      <c r="A847" s="2"/>
+      <c r="A847" s="1"/>
       <c r="B847" s="7"/>
       <c r="C847" s="7"/>
       <c r="D847" s="7"/>
@@ -21771,7 +21791,7 @@
       <c r="W847" s="7"/>
     </row>
     <row r="848">
-      <c r="A848" s="2"/>
+      <c r="A848" s="1"/>
       <c r="B848" s="7"/>
       <c r="C848" s="7"/>
       <c r="D848" s="7"/>
@@ -21796,7 +21816,7 @@
       <c r="W848" s="7"/>
     </row>
     <row r="849">
-      <c r="A849" s="2"/>
+      <c r="A849" s="1"/>
       <c r="B849" s="7"/>
       <c r="C849" s="7"/>
       <c r="D849" s="7"/>
@@ -21821,7 +21841,7 @@
       <c r="W849" s="7"/>
     </row>
     <row r="850">
-      <c r="A850" s="2"/>
+      <c r="A850" s="1"/>
       <c r="B850" s="7"/>
       <c r="C850" s="7"/>
       <c r="D850" s="7"/>
@@ -21846,7 +21866,7 @@
       <c r="W850" s="7"/>
     </row>
     <row r="851">
-      <c r="A851" s="2"/>
+      <c r="A851" s="1"/>
       <c r="B851" s="7"/>
       <c r="C851" s="7"/>
       <c r="D851" s="7"/>
@@ -21871,7 +21891,7 @@
       <c r="W851" s="7"/>
     </row>
     <row r="852">
-      <c r="A852" s="2"/>
+      <c r="A852" s="1"/>
       <c r="B852" s="7"/>
       <c r="C852" s="7"/>
       <c r="D852" s="7"/>
@@ -21896,7 +21916,7 @@
       <c r="W852" s="7"/>
     </row>
     <row r="853">
-      <c r="A853" s="2"/>
+      <c r="A853" s="1"/>
       <c r="B853" s="7"/>
       <c r="C853" s="7"/>
       <c r="D853" s="7"/>
@@ -21921,7 +21941,7 @@
       <c r="W853" s="7"/>
     </row>
     <row r="854">
-      <c r="A854" s="2"/>
+      <c r="A854" s="1"/>
       <c r="B854" s="7"/>
       <c r="C854" s="7"/>
       <c r="D854" s="7"/>
@@ -21946,7 +21966,7 @@
       <c r="W854" s="7"/>
     </row>
     <row r="855">
-      <c r="A855" s="2"/>
+      <c r="A855" s="1"/>
       <c r="B855" s="7"/>
       <c r="C855" s="7"/>
       <c r="D855" s="7"/>
@@ -21971,7 +21991,7 @@
       <c r="W855" s="7"/>
     </row>
     <row r="856">
-      <c r="A856" s="2"/>
+      <c r="A856" s="1"/>
       <c r="B856" s="7"/>
       <c r="C856" s="7"/>
       <c r="D856" s="7"/>
@@ -21996,7 +22016,7 @@
       <c r="W856" s="7"/>
     </row>
     <row r="857">
-      <c r="A857" s="2"/>
+      <c r="A857" s="1"/>
       <c r="B857" s="7"/>
       <c r="C857" s="7"/>
       <c r="D857" s="7"/>
@@ -22021,7 +22041,7 @@
       <c r="W857" s="7"/>
     </row>
     <row r="858">
-      <c r="A858" s="2"/>
+      <c r="A858" s="1"/>
       <c r="B858" s="7"/>
       <c r="C858" s="7"/>
       <c r="D858" s="7"/>
@@ -22046,7 +22066,7 @@
       <c r="W858" s="7"/>
     </row>
     <row r="859">
-      <c r="A859" s="2"/>
+      <c r="A859" s="1"/>
       <c r="B859" s="7"/>
       <c r="C859" s="7"/>
       <c r="D859" s="7"/>
@@ -22071,7 +22091,7 @@
       <c r="W859" s="7"/>
     </row>
     <row r="860">
-      <c r="A860" s="2"/>
+      <c r="A860" s="1"/>
       <c r="B860" s="7"/>
       <c r="C860" s="7"/>
       <c r="D860" s="7"/>
@@ -22096,7 +22116,7 @@
       <c r="W860" s="7"/>
     </row>
     <row r="861">
-      <c r="A861" s="2"/>
+      <c r="A861" s="1"/>
       <c r="B861" s="7"/>
       <c r="C861" s="7"/>
       <c r="D861" s="7"/>
@@ -22121,7 +22141,7 @@
       <c r="W861" s="7"/>
     </row>
     <row r="862">
-      <c r="A862" s="2"/>
+      <c r="A862" s="1"/>
       <c r="B862" s="7"/>
       <c r="C862" s="7"/>
       <c r="D862" s="7"/>
@@ -22146,7 +22166,7 @@
       <c r="W862" s="7"/>
     </row>
     <row r="863">
-      <c r="A863" s="2"/>
+      <c r="A863" s="1"/>
       <c r="B863" s="7"/>
       <c r="C863" s="7"/>
       <c r="D863" s="7"/>
@@ -22171,7 +22191,7 @@
       <c r="W863" s="7"/>
     </row>
     <row r="864">
-      <c r="A864" s="2"/>
+      <c r="A864" s="1"/>
       <c r="B864" s="7"/>
       <c r="C864" s="7"/>
       <c r="D864" s="7"/>
@@ -22196,7 +22216,7 @@
       <c r="W864" s="7"/>
     </row>
     <row r="865">
-      <c r="A865" s="2"/>
+      <c r="A865" s="1"/>
       <c r="B865" s="7"/>
       <c r="C865" s="7"/>
       <c r="D865" s="7"/>
@@ -22221,7 +22241,7 @@
       <c r="W865" s="7"/>
     </row>
     <row r="866">
-      <c r="A866" s="2"/>
+      <c r="A866" s="1"/>
       <c r="B866" s="7"/>
       <c r="C866" s="7"/>
       <c r="D866" s="7"/>
@@ -22246,7 +22266,7 @@
       <c r="W866" s="7"/>
     </row>
     <row r="867">
-      <c r="A867" s="2"/>
+      <c r="A867" s="1"/>
       <c r="B867" s="7"/>
       <c r="C867" s="7"/>
       <c r="D867" s="7"/>
@@ -22271,7 +22291,7 @@
       <c r="W867" s="7"/>
     </row>
     <row r="868">
-      <c r="A868" s="2"/>
+      <c r="A868" s="1"/>
       <c r="B868" s="7"/>
       <c r="C868" s="7"/>
       <c r="D868" s="7"/>
@@ -22296,7 +22316,7 @@
       <c r="W868" s="7"/>
     </row>
     <row r="869">
-      <c r="A869" s="2"/>
+      <c r="A869" s="1"/>
       <c r="B869" s="7"/>
       <c r="C869" s="7"/>
       <c r="D869" s="7"/>
@@ -22321,7 +22341,7 @@
       <c r="W869" s="7"/>
     </row>
     <row r="870">
-      <c r="A870" s="2"/>
+      <c r="A870" s="1"/>
       <c r="B870" s="7"/>
       <c r="C870" s="7"/>
       <c r="D870" s="7"/>
@@ -22346,7 +22366,7 @@
       <c r="W870" s="7"/>
     </row>
     <row r="871">
-      <c r="A871" s="2"/>
+      <c r="A871" s="1"/>
       <c r="B871" s="7"/>
       <c r="C871" s="7"/>
       <c r="D871" s="7"/>
@@ -22371,7 +22391,7 @@
       <c r="W871" s="7"/>
     </row>
     <row r="872">
-      <c r="A872" s="2"/>
+      <c r="A872" s="1"/>
       <c r="B872" s="7"/>
       <c r="C872" s="7"/>
       <c r="D872" s="7"/>
@@ -22396,7 +22416,7 @@
       <c r="W872" s="7"/>
     </row>
     <row r="873">
-      <c r="A873" s="2"/>
+      <c r="A873" s="1"/>
       <c r="B873" s="7"/>
       <c r="C873" s="7"/>
       <c r="D873" s="7"/>
@@ -22421,7 +22441,7 @@
       <c r="W873" s="7"/>
     </row>
     <row r="874">
-      <c r="A874" s="2"/>
+      <c r="A874" s="1"/>
       <c r="B874" s="7"/>
       <c r="C874" s="7"/>
       <c r="D874" s="7"/>
@@ -22446,7 +22466,7 @@
       <c r="W874" s="7"/>
     </row>
     <row r="875">
-      <c r="A875" s="2"/>
+      <c r="A875" s="1"/>
       <c r="B875" s="7"/>
       <c r="C875" s="7"/>
       <c r="D875" s="7"/>
@@ -22471,7 +22491,7 @@
       <c r="W875" s="7"/>
     </row>
     <row r="876">
-      <c r="A876" s="2"/>
+      <c r="A876" s="1"/>
       <c r="B876" s="7"/>
       <c r="C876" s="7"/>
       <c r="D876" s="7"/>
@@ -22496,7 +22516,7 @@
       <c r="W876" s="7"/>
     </row>
     <row r="877">
-      <c r="A877" s="2"/>
+      <c r="A877" s="1"/>
       <c r="B877" s="7"/>
       <c r="C877" s="7"/>
       <c r="D877" s="7"/>
@@ -22521,7 +22541,7 @@
       <c r="W877" s="7"/>
     </row>
     <row r="878">
-      <c r="A878" s="2"/>
+      <c r="A878" s="1"/>
       <c r="B878" s="7"/>
       <c r="C878" s="7"/>
       <c r="D878" s="7"/>
@@ -22546,7 +22566,7 @@
       <c r="W878" s="7"/>
     </row>
     <row r="879">
-      <c r="A879" s="2"/>
+      <c r="A879" s="1"/>
       <c r="B879" s="7"/>
       <c r="C879" s="7"/>
       <c r="D879" s="7"/>
@@ -22571,7 +22591,7 @@
       <c r="W879" s="7"/>
     </row>
     <row r="880">
-      <c r="A880" s="2"/>
+      <c r="A880" s="1"/>
       <c r="B880" s="7"/>
       <c r="C880" s="7"/>
       <c r="D880" s="7"/>
@@ -22596,7 +22616,7 @@
       <c r="W880" s="7"/>
     </row>
     <row r="881">
-      <c r="A881" s="2"/>
+      <c r="A881" s="1"/>
       <c r="B881" s="7"/>
       <c r="C881" s="7"/>
       <c r="D881" s="7"/>
@@ -22621,7 +22641,7 @@
       <c r="W881" s="7"/>
     </row>
     <row r="882">
-      <c r="A882" s="2"/>
+      <c r="A882" s="1"/>
       <c r="B882" s="7"/>
       <c r="C882" s="7"/>
       <c r="D882" s="7"/>
@@ -22646,7 +22666,7 @@
       <c r="W882" s="7"/>
     </row>
     <row r="883">
-      <c r="A883" s="2"/>
+      <c r="A883" s="1"/>
       <c r="B883" s="7"/>
       <c r="C883" s="7"/>
       <c r="D883" s="7"/>
@@ -22671,7 +22691,7 @@
       <c r="W883" s="7"/>
     </row>
     <row r="884">
-      <c r="A884" s="2"/>
+      <c r="A884" s="1"/>
       <c r="B884" s="7"/>
       <c r="C884" s="7"/>
       <c r="D884" s="7"/>
@@ -22696,7 +22716,7 @@
       <c r="W884" s="7"/>
     </row>
     <row r="885">
-      <c r="A885" s="2"/>
+      <c r="A885" s="1"/>
       <c r="B885" s="7"/>
       <c r="C885" s="7"/>
       <c r="D885" s="7"/>
@@ -22721,7 +22741,7 @@
       <c r="W885" s="7"/>
     </row>
     <row r="886">
-      <c r="A886" s="2"/>
+      <c r="A886" s="1"/>
       <c r="B886" s="7"/>
       <c r="C886" s="7"/>
       <c r="D886" s="7"/>
@@ -22746,7 +22766,7 @@
       <c r="W886" s="7"/>
     </row>
     <row r="887">
-      <c r="A887" s="2"/>
+      <c r="A887" s="1"/>
       <c r="B887" s="7"/>
       <c r="C887" s="7"/>
       <c r="D887" s="7"/>
@@ -22771,7 +22791,7 @@
       <c r="W887" s="7"/>
     </row>
     <row r="888">
-      <c r="A888" s="2"/>
+      <c r="A888" s="1"/>
       <c r="B888" s="7"/>
       <c r="C888" s="7"/>
       <c r="D888" s="7"/>
@@ -22796,7 +22816,7 @@
       <c r="W888" s="7"/>
     </row>
     <row r="889">
-      <c r="A889" s="2"/>
+      <c r="A889" s="1"/>
       <c r="B889" s="7"/>
       <c r="C889" s="7"/>
       <c r="D889" s="7"/>
@@ -22821,7 +22841,7 @@
       <c r="W889" s="7"/>
     </row>
     <row r="890">
-      <c r="A890" s="2"/>
+      <c r="A890" s="1"/>
       <c r="B890" s="7"/>
       <c r="C890" s="7"/>
       <c r="D890" s="7"/>
@@ -22846,7 +22866,7 @@
       <c r="W890" s="7"/>
     </row>
     <row r="891">
-      <c r="A891" s="2"/>
+      <c r="A891" s="1"/>
       <c r="B891" s="7"/>
       <c r="C891" s="7"/>
       <c r="D891" s="7"/>
@@ -22871,7 +22891,7 @@
       <c r="W891" s="7"/>
     </row>
     <row r="892">
-      <c r="A892" s="2"/>
+      <c r="A892" s="1"/>
       <c r="B892" s="7"/>
       <c r="C892" s="7"/>
       <c r="D892" s="7"/>
@@ -22896,7 +22916,7 @@
       <c r="W892" s="7"/>
     </row>
     <row r="893">
-      <c r="A893" s="2"/>
+      <c r="A893" s="1"/>
       <c r="B893" s="7"/>
       <c r="C893" s="7"/>
       <c r="D893" s="7"/>
@@ -22921,7 +22941,7 @@
       <c r="W893" s="7"/>
     </row>
     <row r="894">
-      <c r="A894" s="2"/>
+      <c r="A894" s="1"/>
       <c r="B894" s="7"/>
       <c r="C894" s="7"/>
       <c r="D894" s="7"/>
@@ -22946,7 +22966,7 @@
       <c r="W894" s="7"/>
     </row>
     <row r="895">
-      <c r="A895" s="2"/>
+      <c r="A895" s="1"/>
       <c r="B895" s="7"/>
       <c r="C895" s="7"/>
       <c r="D895" s="7"/>
@@ -22971,7 +22991,7 @@
       <c r="W895" s="7"/>
     </row>
     <row r="896">
-      <c r="A896" s="2"/>
+      <c r="A896" s="1"/>
       <c r="B896" s="7"/>
       <c r="C896" s="7"/>
       <c r="D896" s="7"/>
@@ -22996,7 +23016,7 @@
       <c r="W896" s="7"/>
     </row>
     <row r="897">
-      <c r="A897" s="2"/>
+      <c r="A897" s="1"/>
       <c r="B897" s="7"/>
       <c r="C897" s="7"/>
       <c r="D897" s="7"/>
@@ -23021,7 +23041,7 @@
       <c r="W897" s="7"/>
     </row>
     <row r="898">
-      <c r="A898" s="2"/>
+      <c r="A898" s="1"/>
       <c r="B898" s="7"/>
       <c r="C898" s="7"/>
       <c r="D898" s="7"/>
@@ -23046,7 +23066,7 @@
       <c r="W898" s="7"/>
     </row>
     <row r="899">
-      <c r="A899" s="2"/>
+      <c r="A899" s="1"/>
       <c r="B899" s="7"/>
       <c r="C899" s="7"/>
       <c r="D899" s="7"/>
@@ -23071,7 +23091,7 @@
       <c r="W899" s="7"/>
     </row>
     <row r="900">
-      <c r="A900" s="2"/>
+      <c r="A900" s="1"/>
       <c r="B900" s="7"/>
       <c r="C900" s="7"/>
       <c r="D900" s="7"/>
@@ -23096,7 +23116,7 @@
       <c r="W900" s="7"/>
     </row>
     <row r="901">
-      <c r="A901" s="2"/>
+      <c r="A901" s="1"/>
       <c r="B901" s="7"/>
       <c r="C901" s="7"/>
       <c r="D901" s="7"/>
@@ -23121,7 +23141,7 @@
       <c r="W901" s="7"/>
     </row>
     <row r="902">
-      <c r="A902" s="2"/>
+      <c r="A902" s="1"/>
       <c r="B902" s="7"/>
       <c r="C902" s="7"/>
       <c r="D902" s="7"/>
@@ -23146,7 +23166,7 @@
       <c r="W902" s="7"/>
     </row>
     <row r="903">
-      <c r="A903" s="2"/>
+      <c r="A903" s="1"/>
       <c r="B903" s="7"/>
       <c r="C903" s="7"/>
       <c r="D903" s="7"/>
@@ -23171,7 +23191,7 @@
       <c r="W903" s="7"/>
     </row>
     <row r="904">
-      <c r="A904" s="2"/>
+      <c r="A904" s="1"/>
       <c r="B904" s="7"/>
       <c r="C904" s="7"/>
       <c r="D904" s="7"/>
@@ -23196,7 +23216,7 @@
       <c r="W904" s="7"/>
     </row>
     <row r="905">
-      <c r="A905" s="2"/>
+      <c r="A905" s="1"/>
       <c r="B905" s="7"/>
       <c r="C905" s="7"/>
       <c r="D905" s="7"/>
@@ -23221,7 +23241,7 @@
       <c r="W905" s="7"/>
     </row>
     <row r="906">
-      <c r="A906" s="2"/>
+      <c r="A906" s="1"/>
       <c r="B906" s="7"/>
       <c r="C906" s="7"/>
       <c r="D906" s="7"/>
@@ -23246,7 +23266,7 @@
       <c r="W906" s="7"/>
     </row>
     <row r="907">
-      <c r="A907" s="2"/>
+      <c r="A907" s="1"/>
       <c r="B907" s="7"/>
       <c r="C907" s="7"/>
       <c r="D907" s="7"/>
@@ -23271,7 +23291,7 @@
       <c r="W907" s="7"/>
     </row>
     <row r="908">
-      <c r="A908" s="2"/>
+      <c r="A908" s="1"/>
       <c r="B908" s="7"/>
       <c r="C908" s="7"/>
       <c r="D908" s="7"/>
@@ -23296,7 +23316,7 @@
       <c r="W908" s="7"/>
     </row>
     <row r="909">
-      <c r="A909" s="2"/>
+      <c r="A909" s="1"/>
       <c r="B909" s="7"/>
       <c r="C909" s="7"/>
       <c r="D909" s="7"/>
@@ -23321,7 +23341,7 @@
       <c r="W909" s="7"/>
     </row>
     <row r="910">
-      <c r="A910" s="2"/>
+      <c r="A910" s="1"/>
       <c r="B910" s="7"/>
       <c r="C910" s="7"/>
       <c r="D910" s="7"/>
@@ -23346,7 +23366,7 @@
       <c r="W910" s="7"/>
     </row>
     <row r="911">
-      <c r="A911" s="2"/>
+      <c r="A911" s="1"/>
       <c r="B911" s="7"/>
       <c r="C911" s="7"/>
       <c r="D911" s="7"/>
@@ -23371,7 +23391,7 @@
       <c r="W911" s="7"/>
     </row>
     <row r="912">
-      <c r="A912" s="2"/>
+      <c r="A912" s="1"/>
       <c r="B912" s="7"/>
       <c r="C912" s="7"/>
       <c r="D912" s="7"/>
@@ -23396,7 +23416,7 @@
       <c r="W912" s="7"/>
     </row>
     <row r="913">
-      <c r="A913" s="2"/>
+      <c r="A913" s="1"/>
       <c r="B913" s="7"/>
       <c r="C913" s="7"/>
       <c r="D913" s="7"/>
@@ -23421,7 +23441,7 @@
       <c r="W913" s="7"/>
     </row>
     <row r="914">
-      <c r="A914" s="2"/>
+      <c r="A914" s="1"/>
       <c r="B914" s="7"/>
       <c r="C914" s="7"/>
       <c r="D914" s="7"/>
@@ -23446,7 +23466,7 @@
       <c r="W914" s="7"/>
     </row>
     <row r="915">
-      <c r="A915" s="2"/>
+      <c r="A915" s="1"/>
       <c r="B915" s="7"/>
       <c r="C915" s="7"/>
       <c r="D915" s="7"/>
@@ -23471,7 +23491,7 @@
       <c r="W915" s="7"/>
     </row>
     <row r="916">
-      <c r="A916" s="2"/>
+      <c r="A916" s="1"/>
       <c r="B916" s="7"/>
       <c r="C916" s="7"/>
       <c r="D916" s="7"/>
@@ -23496,7 +23516,7 @@
       <c r="W916" s="7"/>
     </row>
     <row r="917">
-      <c r="A917" s="2"/>
+      <c r="A917" s="1"/>
       <c r="B917" s="7"/>
       <c r="C917" s="7"/>
       <c r="D917" s="7"/>
@@ -23521,7 +23541,7 @@
       <c r="W917" s="7"/>
     </row>
     <row r="918">
-      <c r="A918" s="2"/>
+      <c r="A918" s="1"/>
       <c r="B918" s="7"/>
       <c r="C918" s="7"/>
       <c r="D918" s="7"/>
@@ -23546,7 +23566,7 @@
       <c r="W918" s="7"/>
     </row>
     <row r="919">
-      <c r="A919" s="2"/>
+      <c r="A919" s="1"/>
       <c r="B919" s="7"/>
       <c r="C919" s="7"/>
       <c r="D919" s="7"/>
@@ -23571,7 +23591,7 @@
       <c r="W919" s="7"/>
     </row>
     <row r="920">
-      <c r="A920" s="2"/>
+      <c r="A920" s="1"/>
       <c r="B920" s="7"/>
       <c r="C920" s="7"/>
       <c r="D920" s="7"/>
@@ -23596,7 +23616,7 @@
       <c r="W920" s="7"/>
     </row>
     <row r="921">
-      <c r="A921" s="2"/>
+      <c r="A921" s="1"/>
       <c r="B921" s="7"/>
       <c r="C921" s="7"/>
       <c r="D921" s="7"/>
@@ -23621,7 +23641,7 @@
       <c r="W921" s="7"/>
     </row>
     <row r="922">
-      <c r="A922" s="2"/>
+      <c r="A922" s="1"/>
       <c r="B922" s="7"/>
       <c r="C922" s="7"/>
       <c r="D922" s="7"/>
@@ -23646,7 +23666,7 @@
       <c r="W922" s="7"/>
     </row>
     <row r="923">
-      <c r="A923" s="2"/>
+      <c r="A923" s="1"/>
       <c r="B923" s="7"/>
       <c r="C923" s="7"/>
       <c r="D923" s="7"/>
@@ -23671,7 +23691,7 @@
       <c r="W923" s="7"/>
     </row>
     <row r="924">
-      <c r="A924" s="2"/>
+      <c r="A924" s="1"/>
       <c r="B924" s="7"/>
       <c r="C924" s="7"/>
       <c r="D924" s="7"/>
@@ -23696,7 +23716,7 @@
       <c r="W924" s="7"/>
     </row>
     <row r="925">
-      <c r="A925" s="2"/>
+      <c r="A925" s="1"/>
       <c r="B925" s="7"/>
       <c r="C925" s="7"/>
       <c r="D925" s="7"/>
@@ -23721,7 +23741,7 @@
       <c r="W925" s="7"/>
     </row>
     <row r="926">
-      <c r="A926" s="2"/>
+      <c r="A926" s="1"/>
       <c r="B926" s="7"/>
       <c r="C926" s="7"/>
       <c r="D926" s="7"/>
@@ -23746,7 +23766,7 @@
       <c r="W926" s="7"/>
     </row>
     <row r="927">
-      <c r="A927" s="2"/>
+      <c r="A927" s="1"/>
       <c r="B927" s="7"/>
       <c r="C927" s="7"/>
       <c r="D927" s="7"/>
@@ -23771,7 +23791,7 @@
       <c r="W927" s="7"/>
     </row>
     <row r="928">
-      <c r="A928" s="2"/>
+      <c r="A928" s="1"/>
       <c r="B928" s="7"/>
       <c r="C928" s="7"/>
       <c r="D928" s="7"/>
@@ -23796,7 +23816,7 @@
       <c r="W928" s="7"/>
     </row>
     <row r="929">
-      <c r="A929" s="2"/>
+      <c r="A929" s="1"/>
       <c r="B929" s="7"/>
       <c r="C929" s="7"/>
       <c r="D929" s="7"/>
@@ -23821,7 +23841,7 @@
       <c r="W929" s="7"/>
     </row>
     <row r="930">
-      <c r="A930" s="2"/>
+      <c r="A930" s="1"/>
       <c r="B930" s="7"/>
       <c r="C930" s="7"/>
       <c r="D930" s="7"/>
@@ -23846,7 +23866,7 @@
       <c r="W930" s="7"/>
     </row>
     <row r="931">
-      <c r="A931" s="2"/>
+      <c r="A931" s="1"/>
       <c r="B931" s="7"/>
       <c r="C931" s="7"/>
       <c r="D931" s="7"/>
@@ -23871,7 +23891,7 @@
       <c r="W931" s="7"/>
     </row>
     <row r="932">
-      <c r="A932" s="2"/>
+      <c r="A932" s="1"/>
       <c r="B932" s="7"/>
       <c r="C932" s="7"/>
       <c r="D932" s="7"/>
@@ -23896,7 +23916,7 @@
       <c r="W932" s="7"/>
     </row>
     <row r="933">
-      <c r="A933" s="2"/>
+      <c r="A933" s="1"/>
       <c r="B933" s="7"/>
       <c r="C933" s="7"/>
       <c r="D933" s="7"/>
@@ -23921,7 +23941,7 @@
       <c r="W933" s="7"/>
     </row>
     <row r="934">
-      <c r="A934" s="2"/>
+      <c r="A934" s="1"/>
       <c r="B934" s="7"/>
       <c r="C934" s="7"/>
       <c r="D934" s="7"/>
@@ -23946,7 +23966,7 @@
       <c r="W934" s="7"/>
     </row>
     <row r="935">
-      <c r="A935" s="2"/>
+      <c r="A935" s="1"/>
       <c r="B935" s="7"/>
       <c r="C935" s="7"/>
       <c r="D935" s="7"/>
@@ -23971,7 +23991,7 @@
       <c r="W935" s="7"/>
     </row>
     <row r="936">
-      <c r="A936" s="2"/>
+      <c r="A936" s="1"/>
       <c r="B936" s="7"/>
       <c r="C936" s="7"/>
       <c r="D936" s="7"/>
@@ -23996,7 +24016,7 @@
       <c r="W936" s="7"/>
     </row>
     <row r="937">
-      <c r="A937" s="2"/>
+      <c r="A937" s="1"/>
       <c r="B937" s="7"/>
       <c r="C937" s="7"/>
       <c r="D937" s="7"/>
@@ -24021,7 +24041,7 @@
       <c r="W937" s="7"/>
     </row>
     <row r="938">
-      <c r="A938" s="2"/>
+      <c r="A938" s="1"/>
       <c r="B938" s="7"/>
       <c r="C938" s="7"/>
       <c r="D938" s="7"/>
@@ -24046,7 +24066,7 @@
       <c r="W938" s="7"/>
     </row>
     <row r="939">
-      <c r="A939" s="2"/>
+      <c r="A939" s="1"/>
       <c r="B939" s="7"/>
       <c r="C939" s="7"/>
       <c r="D939" s="7"/>
@@ -24071,7 +24091,7 @@
       <c r="W939" s="7"/>
     </row>
     <row r="940">
-      <c r="A940" s="2"/>
+      <c r="A940" s="1"/>
       <c r="B940" s="7"/>
       <c r="C940" s="7"/>
       <c r="D940" s="7"/>
@@ -24096,7 +24116,7 @@
       <c r="W940" s="7"/>
     </row>
     <row r="941">
-      <c r="A941" s="2"/>
+      <c r="A941" s="1"/>
       <c r="B941" s="7"/>
       <c r="C941" s="7"/>
       <c r="D941" s="7"/>
@@ -24121,7 +24141,7 @@
       <c r="W941" s="7"/>
     </row>
     <row r="942">
-      <c r="A942" s="2"/>
+      <c r="A942" s="1"/>
       <c r="B942" s="7"/>
       <c r="C942" s="7"/>
       <c r="D942" s="7"/>
@@ -24146,7 +24166,7 @@
       <c r="W942" s="7"/>
     </row>
     <row r="943">
-      <c r="A943" s="2"/>
+      <c r="A943" s="1"/>
       <c r="B943" s="7"/>
       <c r="C943" s="7"/>
       <c r="D943" s="7"/>
@@ -24171,7 +24191,7 @@
       <c r="W943" s="7"/>
     </row>
     <row r="944">
-      <c r="A944" s="2"/>
+      <c r="A944" s="1"/>
       <c r="B944" s="7"/>
       <c r="C944" s="7"/>
       <c r="D944" s="7"/>
@@ -24196,7 +24216,7 @@
       <c r="W944" s="7"/>
     </row>
     <row r="945">
-      <c r="A945" s="2"/>
+      <c r="A945" s="1"/>
       <c r="B945" s="7"/>
       <c r="C945" s="7"/>
       <c r="D945" s="7"/>
@@ -24221,7 +24241,7 @@
       <c r="W945" s="7"/>
     </row>
     <row r="946">
-      <c r="A946" s="2"/>
+      <c r="A946" s="1"/>
       <c r="B946" s="7"/>
       <c r="C946" s="7"/>
       <c r="D946" s="7"/>
@@ -24246,7 +24266,7 @@
       <c r="W946" s="7"/>
     </row>
     <row r="947">
-      <c r="A947" s="2"/>
+      <c r="A947" s="1"/>
       <c r="B947" s="7"/>
       <c r="C947" s="7"/>
       <c r="D947" s="7"/>
@@ -24271,7 +24291,7 @@
       <c r="W947" s="7"/>
     </row>
     <row r="948">
-      <c r="A948" s="2"/>
+      <c r="A948" s="1"/>
       <c r="B948" s="7"/>
       <c r="C948" s="7"/>
       <c r="D948" s="7"/>
@@ -24296,7 +24316,7 @@
       <c r="W948" s="7"/>
     </row>
     <row r="949">
-      <c r="A949" s="2"/>
+      <c r="A949" s="1"/>
       <c r="B949" s="7"/>
       <c r="C949" s="7"/>
       <c r="D949" s="7"/>
@@ -24321,7 +24341,7 @@
       <c r="W949" s="7"/>
     </row>
     <row r="950">
-      <c r="A950" s="2"/>
+      <c r="A950" s="1"/>
       <c r="B950" s="7"/>
       <c r="C950" s="7"/>
       <c r="D950" s="7"/>
@@ -24346,7 +24366,7 @@
       <c r="W950" s="7"/>
     </row>
     <row r="951">
-      <c r="A951" s="2"/>
+      <c r="A951" s="1"/>
       <c r="B951" s="7"/>
       <c r="C951" s="7"/>
       <c r="D951" s="7"/>
@@ -24371,7 +24391,7 @@
       <c r="W951" s="7"/>
     </row>
     <row r="952">
-      <c r="A952" s="2"/>
+      <c r="A952" s="1"/>
       <c r="B952" s="7"/>
       <c r="C952" s="7"/>
       <c r="D952" s="7"/>
@@ -24396,7 +24416,7 @@
       <c r="W952" s="7"/>
     </row>
     <row r="953">
-      <c r="A953" s="2"/>
+      <c r="A953" s="1"/>
       <c r="B953" s="7"/>
       <c r="C953" s="7"/>
       <c r="D953" s="7"/>
@@ -24421,7 +24441,7 @@
       <c r="W953" s="7"/>
     </row>
     <row r="954">
-      <c r="A954" s="2"/>
+      <c r="A954" s="1"/>
       <c r="B954" s="7"/>
       <c r="C954" s="7"/>
       <c r="D954" s="7"/>
@@ -24446,7 +24466,7 @@
       <c r="W954" s="7"/>
     </row>
     <row r="955">
-      <c r="A955" s="2"/>
+      <c r="A955" s="1"/>
       <c r="B955" s="7"/>
       <c r="C955" s="7"/>
       <c r="D955" s="7"/>
@@ -24471,7 +24491,7 @@
       <c r="W955" s="7"/>
     </row>
     <row r="956">
-      <c r="A956" s="2"/>
+      <c r="A956" s="1"/>
       <c r="B956" s="7"/>
       <c r="C956" s="7"/>
       <c r="D956" s="7"/>
@@ -24496,7 +24516,7 @@
       <c r="W956" s="7"/>
     </row>
     <row r="957">
-      <c r="A957" s="2"/>
+      <c r="A957" s="1"/>
       <c r="B957" s="7"/>
       <c r="C957" s="7"/>
       <c r="D957" s="7"/>
@@ -24521,7 +24541,7 @@
       <c r="W957" s="7"/>
     </row>
     <row r="958">
-      <c r="A958" s="2"/>
+      <c r="A958" s="1"/>
       <c r="B958" s="7"/>
       <c r="C958" s="7"/>
       <c r="D958" s="7"/>
@@ -24546,7 +24566,7 @@
       <c r="W958" s="7"/>
     </row>
     <row r="959">
-      <c r="A959" s="2"/>
+      <c r="A959" s="1"/>
       <c r="B959" s="7"/>
       <c r="C959" s="7"/>
       <c r="D959" s="7"/>
@@ -24571,7 +24591,7 @@
       <c r="W959" s="7"/>
     </row>
     <row r="960">
-      <c r="A960" s="2"/>
+      <c r="A960" s="1"/>
       <c r="B960" s="7"/>
       <c r="C960" s="7"/>
       <c r="D960" s="7"/>
@@ -24596,7 +24616,7 @@
       <c r="W960" s="7"/>
     </row>
     <row r="961">
-      <c r="A961" s="2"/>
+      <c r="A961" s="1"/>
       <c r="B961" s="7"/>
       <c r="C961" s="7"/>
       <c r="D961" s="7"/>
@@ -24621,7 +24641,7 @@
       <c r="W961" s="7"/>
     </row>
     <row r="962">
-      <c r="A962" s="2"/>
+      <c r="A962" s="1"/>
       <c r="B962" s="7"/>
       <c r="C962" s="7"/>
       <c r="D962" s="7"/>
@@ -24646,7 +24666,7 @@
       <c r="W962" s="7"/>
     </row>
     <row r="963">
-      <c r="A963" s="2"/>
+      <c r="A963" s="1"/>
       <c r="B963" s="7"/>
       <c r="C963" s="7"/>
       <c r="D963" s="7"/>
@@ -24671,7 +24691,7 @@
       <c r="W963" s="7"/>
     </row>
     <row r="964">
-      <c r="A964" s="2"/>
+      <c r="A964" s="1"/>
       <c r="B964" s="7"/>
       <c r="C964" s="7"/>
       <c r="D964" s="7"/>
@@ -24696,7 +24716,7 @@
       <c r="W964" s="7"/>
     </row>
     <row r="965">
-      <c r="A965" s="2"/>
+      <c r="A965" s="1"/>
       <c r="B965" s="7"/>
       <c r="C965" s="7"/>
       <c r="D965" s="7"/>
@@ -24721,7 +24741,7 @@
       <c r="W965" s="7"/>
     </row>
     <row r="966">
-      <c r="A966" s="2"/>
+      <c r="A966" s="1"/>
       <c r="B966" s="7"/>
       <c r="C966" s="7"/>
       <c r="D966" s="7"/>
@@ -24746,7 +24766,7 @@
       <c r="W966" s="7"/>
     </row>
     <row r="967">
-      <c r="A967" s="2"/>
+      <c r="A967" s="1"/>
       <c r="B967" s="7"/>
       <c r="C967" s="7"/>
       <c r="D967" s="7"/>
@@ -24771,7 +24791,7 @@
       <c r="W967" s="7"/>
     </row>
     <row r="968">
-      <c r="A968" s="2"/>
+      <c r="A968" s="1"/>
       <c r="B968" s="7"/>
       <c r="C968" s="7"/>
       <c r="D968" s="7"/>
@@ -24796,7 +24816,7 @@
       <c r="W968" s="7"/>
     </row>
     <row r="969">
-      <c r="A969" s="2"/>
+      <c r="A969" s="1"/>
       <c r="B969" s="7"/>
       <c r="C969" s="7"/>
       <c r="D969" s="7"/>
@@ -24821,7 +24841,7 @@
       <c r="W969" s="7"/>
     </row>
     <row r="970">
-      <c r="A970" s="2"/>
+      <c r="A970" s="1"/>
       <c r="B970" s="7"/>
       <c r="C970" s="7"/>
       <c r="D970" s="7"/>
@@ -24846,7 +24866,7 @@
       <c r="W970" s="7"/>
     </row>
     <row r="971">
-      <c r="A971" s="2"/>
+      <c r="A971" s="1"/>
       <c r="B971" s="7"/>
       <c r="C971" s="7"/>
       <c r="D971" s="7"/>
@@ -24871,7 +24891,7 @@
       <c r="W971" s="7"/>
     </row>
     <row r="972">
-      <c r="A972" s="2"/>
+      <c r="A972" s="1"/>
       <c r="B972" s="7"/>
       <c r="C972" s="7"/>
       <c r="D972" s="7"/>
@@ -24896,7 +24916,7 @@
       <c r="W972" s="7"/>
     </row>
     <row r="973">
-      <c r="A973" s="2"/>
+      <c r="A973" s="1"/>
       <c r="B973" s="7"/>
       <c r="C973" s="7"/>
       <c r="D973" s="7"/>
@@ -24921,7 +24941,7 @@
       <c r="W973" s="7"/>
     </row>
     <row r="974">
-      <c r="A974" s="2"/>
+      <c r="A974" s="1"/>
       <c r="B974" s="7"/>
       <c r="C974" s="7"/>
       <c r="D974" s="7"/>
@@ -24946,7 +24966,7 @@
       <c r="W974" s="7"/>
     </row>
     <row r="975">
-      <c r="A975" s="2"/>
+      <c r="A975" s="1"/>
       <c r="B975" s="7"/>
       <c r="C975" s="7"/>
       <c r="D975" s="7"/>
@@ -24971,7 +24991,7 @@
       <c r="W975" s="7"/>
     </row>
     <row r="976">
-      <c r="A976" s="2"/>
+      <c r="A976" s="1"/>
       <c r="B976" s="7"/>
       <c r="C976" s="7"/>
       <c r="D976" s="7"/>
@@ -24996,7 +25016,7 @@
       <c r="W976" s="7"/>
     </row>
     <row r="977">
-      <c r="A977" s="2"/>
+      <c r="A977" s="1"/>
       <c r="B977" s="7"/>
       <c r="C977" s="7"/>
       <c r="D977" s="7"/>
@@ -25021,7 +25041,7 @@
       <c r="W977" s="7"/>
     </row>
     <row r="978">
-      <c r="A978" s="2"/>
+      <c r="A978" s="1"/>
       <c r="B978" s="7"/>
       <c r="C978" s="7"/>
       <c r="D978" s="7"/>
@@ -25046,7 +25066,7 @@
       <c r="W978" s="7"/>
     </row>
     <row r="979">
-      <c r="A979" s="2"/>
+      <c r="A979" s="1"/>
       <c r="B979" s="7"/>
       <c r="C979" s="7"/>
       <c r="D979" s="7"/>
@@ -25071,7 +25091,7 @@
       <c r="W979" s="7"/>
     </row>
     <row r="980">
-      <c r="A980" s="2"/>
+      <c r="A980" s="1"/>
       <c r="B980" s="7"/>
       <c r="C980" s="7"/>
       <c r="D980" s="7"/>
@@ -25096,7 +25116,7 @@
       <c r="W980" s="7"/>
     </row>
     <row r="981">
-      <c r="A981" s="2"/>
+      <c r="A981" s="1"/>
       <c r="B981" s="7"/>
       <c r="C981" s="7"/>
       <c r="D981" s="7"/>
@@ -25121,7 +25141,7 @@
       <c r="W981" s="7"/>
     </row>
     <row r="982">
-      <c r="A982" s="2"/>
+      <c r="A982" s="1"/>
       <c r="B982" s="7"/>
       <c r="C982" s="7"/>
       <c r="D982" s="7"/>
@@ -25146,7 +25166,7 @@
       <c r="W982" s="7"/>
     </row>
     <row r="983">
-      <c r="A983" s="2"/>
+      <c r="A983" s="1"/>
       <c r="B983" s="7"/>
       <c r="C983" s="7"/>
       <c r="D983" s="7"/>
@@ -25171,7 +25191,7 @@
       <c r="W983" s="7"/>
     </row>
     <row r="984">
-      <c r="A984" s="2"/>
+      <c r="A984" s="1"/>
       <c r="B984" s="7"/>
       <c r="C984" s="7"/>
       <c r="D984" s="7"/>
@@ -25196,7 +25216,7 @@
       <c r="W984" s="7"/>
     </row>
     <row r="985">
-      <c r="A985" s="2"/>
+      <c r="A985" s="1"/>
       <c r="B985" s="7"/>
       <c r="C985" s="7"/>
       <c r="D985" s="7"/>
@@ -25221,7 +25241,7 @@
       <c r="W985" s="7"/>
     </row>
     <row r="986">
-      <c r="A986" s="2"/>
+      <c r="A986" s="1"/>
       <c r="B986" s="7"/>
       <c r="C986" s="7"/>
       <c r="D986" s="7"/>
@@ -25246,7 +25266,7 @@
       <c r="W986" s="7"/>
     </row>
     <row r="987">
-      <c r="A987" s="2"/>
+      <c r="A987" s="1"/>
       <c r="B987" s="7"/>
       <c r="C987" s="7"/>
       <c r="D987" s="7"/>
@@ -25271,7 +25291,7 @@
       <c r="W987" s="7"/>
     </row>
     <row r="988">
-      <c r="A988" s="2"/>
+      <c r="A988" s="1"/>
       <c r="B988" s="7"/>
       <c r="C988" s="7"/>
       <c r="D988" s="7"/>
@@ -25296,7 +25316,7 @@
       <c r="W988" s="7"/>
     </row>
     <row r="989">
-      <c r="A989" s="2"/>
+      <c r="A989" s="1"/>
       <c r="B989" s="7"/>
       <c r="C989" s="7"/>
       <c r="D989" s="7"/>
@@ -25321,7 +25341,7 @@
       <c r="W989" s="7"/>
     </row>
     <row r="990">
-      <c r="A990" s="2"/>
+      <c r="A990" s="1"/>
       <c r="B990" s="7"/>
       <c r="C990" s="7"/>
       <c r="D990" s="7"/>
@@ -25346,7 +25366,7 @@
       <c r="W990" s="7"/>
     </row>
     <row r="991">
-      <c r="A991" s="2"/>
+      <c r="A991" s="1"/>
       <c r="B991" s="7"/>
       <c r="C991" s="7"/>
       <c r="D991" s="7"/>
@@ -25371,7 +25391,7 @@
       <c r="W991" s="7"/>
     </row>
     <row r="992">
-      <c r="A992" s="2"/>
+      <c r="A992" s="1"/>
       <c r="B992" s="7"/>
       <c r="C992" s="7"/>
       <c r="D992" s="7"/>
@@ -25396,7 +25416,7 @@
       <c r="W992" s="7"/>
     </row>
     <row r="993">
-      <c r="A993" s="2"/>
+      <c r="A993" s="1"/>
       <c r="B993" s="7"/>
       <c r="C993" s="7"/>
       <c r="D993" s="7"/>
@@ -25421,7 +25441,7 @@
       <c r="W993" s="7"/>
     </row>
     <row r="994">
-      <c r="A994" s="2"/>
+      <c r="A994" s="1"/>
       <c r="B994" s="7"/>
       <c r="C994" s="7"/>
       <c r="D994" s="7"/>
@@ -25446,7 +25466,7 @@
       <c r="W994" s="7"/>
     </row>
     <row r="995">
-      <c r="A995" s="2"/>
+      <c r="A995" s="1"/>
       <c r="B995" s="7"/>
       <c r="C995" s="7"/>
       <c r="D995" s="7"/>
@@ -25471,7 +25491,7 @@
       <c r="W995" s="7"/>
     </row>
     <row r="996">
-      <c r="A996" s="2"/>
+      <c r="A996" s="1"/>
       <c r="B996" s="7"/>
       <c r="C996" s="7"/>
       <c r="D996" s="7"/>
@@ -25496,7 +25516,7 @@
       <c r="W996" s="7"/>
     </row>
     <row r="997">
-      <c r="A997" s="2"/>
+      <c r="A997" s="1"/>
       <c r="B997" s="7"/>
       <c r="C997" s="7"/>
       <c r="D997" s="7"/>
@@ -25521,7 +25541,7 @@
       <c r="W997" s="7"/>
     </row>
     <row r="998">
-      <c r="A998" s="2"/>
+      <c r="A998" s="1"/>
       <c r="B998" s="7"/>
       <c r="C998" s="7"/>
       <c r="D998" s="7"/>
@@ -25546,7 +25566,7 @@
       <c r="W998" s="7"/>
     </row>
     <row r="999">
-      <c r="A999" s="2"/>
+      <c r="A999" s="1"/>
       <c r="B999" s="7"/>
       <c r="C999" s="7"/>
       <c r="D999" s="7"/>
@@ -25571,7 +25591,7 @@
       <c r="W999" s="7"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="2"/>
+      <c r="A1000" s="1"/>
       <c r="B1000" s="7"/>
       <c r="C1000" s="7"/>
       <c r="D1000" s="7"/>
@@ -25596,7 +25616,45 @@
       <c r="W1000" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="76">
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="L12:L15"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:I22"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="K2:K4"/>
@@ -25619,10 +25677,6 @@
     <mergeCell ref="F5:F8"/>
     <mergeCell ref="G5:G8"/>
     <mergeCell ref="H5:H8"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="L10:L11"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
@@ -25630,17 +25684,15 @@
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="J12:J15"/>
-    <mergeCell ref="L12:L15"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="J17:J18"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -25655,58 +25707,58 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
       </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
       </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>

--- a/Grade3-Homeworks.xlsx
+++ b/Grade3-Homeworks.xlsx
@@ -17,36 +17,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
-  <si>
-    <t>Date</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>Monday</t>
-  </si>
-  <si>
-    <t>Languages</t>
-  </si>
-  <si>
-    <t>Telugu</t>
-  </si>
-  <si>
-    <t>English</t>
   </si>
   <si>
     <t xml:space="preserve">Telugu </t>
   </si>
   <si>
-    <t>Devanagari - HindiSanskritKhatriMarathi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maths </t>
   </si>
   <si>
-    <t>Maths</t>
-  </si>
-  <si>
-    <t>Technology</t>
+    <t>Date</t>
   </si>
   <si>
     <t>Tuesday</t>
@@ -55,31 +37,19 @@
     <t xml:space="preserve">English </t>
   </si>
   <si>
-    <t>Programming</t>
-  </si>
-  <si>
     <t xml:space="preserve">Programming </t>
-  </si>
-  <si>
-    <t>CarnaticMusic</t>
   </si>
   <si>
     <t>Wednesday</t>
   </si>
   <si>
-    <t>Science</t>
+    <t>Languages</t>
   </si>
   <si>
     <t xml:space="preserve">Science </t>
   </si>
   <si>
-    <t>SocialStudies ( + LifeSkills)</t>
-  </si>
-  <si>
     <t>Thursday</t>
-  </si>
-  <si>
-    <t>Overview</t>
   </si>
   <si>
     <t>Music</t>
@@ -97,11 +67,41 @@
     <t xml:space="preserve">Technology </t>
   </si>
   <si>
+    <t>Telugu</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Devanagari - HindiSanskritKhatriMarathi</t>
+  </si>
+  <si>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Programming</t>
+  </si>
+  <si>
+    <t>CarnaticMusic</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>SocialStudies ( + LifeSkills)</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
     <t>Complete 3rd class text book, work book, copy tracing book and get it verified by your parents</t>
   </si>
   <si>
     <t>Read 10th grade AP Telugu Textbook - Ramayanam - until the birth of Shri Rama
-HW: Read all of it again</t>
+HW- Read all of it again</t>
   </si>
   <si>
     <t>Read 10th grade AP Telugu Textbook - Ramayanam - until the birth of Shri Rama
@@ -181,13 +181,23 @@
   <si>
     <t>Read this! (William Blake's 'Marriage of Heaven and Hell')</t>
   </si>
+  <si>
+    <t>Complete AI Exercises - Linux command line</t>
+  </si>
+  <si>
+    <t>Read Chandamama 1948-1 telugu book - AI companion Notes and see how much we need to enhance or change the prompts to make it useful</t>
+  </si>
+  <si>
+    <t>Read all of this; Prepare a list of good principles mentioned in the book; For each idea, mention if we are following this well in home school or if we need to improve. (Social: Enlightened Education - Introduction, Salutation, Vision)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -197,11 +207,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -332,31 +342,31 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -366,28 +376,33 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -612,53 +627,53 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="H1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3">
@@ -1166,13 +1181,17 @@
       <c r="W22" s="7"/>
     </row>
     <row r="23">
-      <c r="A23" s="22"/>
+      <c r="A23" s="22">
+        <v>46309.0</v>
+      </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
+      <c r="G23" s="9" t="s">
+        <v>53</v>
+      </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
@@ -1191,18 +1210,9 @@
       <c r="W23" s="7"/>
     </row>
     <row r="24">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
+      <c r="G24" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
@@ -1216,7 +1226,9 @@
       <c r="W24" s="7"/>
     </row>
     <row r="25">
-      <c r="A25" s="1"/>
+      <c r="A25" s="23">
+        <v>46310.0</v>
+      </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -1226,7 +1238,9 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
+      <c r="K25" s="9" t="s">
+        <v>55</v>
+      </c>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -1241,18 +1255,9 @@
       <c r="W25" s="7"/>
     </row>
     <row r="26">
-      <c r="A26" s="1"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
+      <c r="K26" s="9" t="s">
+        <v>50</v>
+      </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
@@ -1266,7 +1271,7 @@
       <c r="W26" s="7"/>
     </row>
     <row r="27">
-      <c r="A27" s="1"/>
+      <c r="A27" s="2"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -1291,7 +1296,7 @@
       <c r="W27" s="7"/>
     </row>
     <row r="28">
-      <c r="A28" s="1"/>
+      <c r="A28" s="2"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -1316,7 +1321,7 @@
       <c r="W28" s="7"/>
     </row>
     <row r="29">
-      <c r="A29" s="1"/>
+      <c r="A29" s="2"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1341,7 +1346,7 @@
       <c r="W29" s="7"/>
     </row>
     <row r="30">
-      <c r="A30" s="1"/>
+      <c r="A30" s="2"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -1366,7 +1371,7 @@
       <c r="W30" s="7"/>
     </row>
     <row r="31">
-      <c r="A31" s="1"/>
+      <c r="A31" s="2"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -1391,7 +1396,7 @@
       <c r="W31" s="7"/>
     </row>
     <row r="32">
-      <c r="A32" s="1"/>
+      <c r="A32" s="2"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -1416,7 +1421,7 @@
       <c r="W32" s="7"/>
     </row>
     <row r="33">
-      <c r="A33" s="1"/>
+      <c r="A33" s="2"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -1441,7 +1446,7 @@
       <c r="W33" s="7"/>
     </row>
     <row r="34">
-      <c r="A34" s="1"/>
+      <c r="A34" s="2"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -1466,7 +1471,7 @@
       <c r="W34" s="7"/>
     </row>
     <row r="35">
-      <c r="A35" s="1"/>
+      <c r="A35" s="2"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1491,7 +1496,7 @@
       <c r="W35" s="7"/>
     </row>
     <row r="36">
-      <c r="A36" s="1"/>
+      <c r="A36" s="2"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -1516,7 +1521,7 @@
       <c r="W36" s="7"/>
     </row>
     <row r="37">
-      <c r="A37" s="1"/>
+      <c r="A37" s="2"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -1541,7 +1546,7 @@
       <c r="W37" s="7"/>
     </row>
     <row r="38">
-      <c r="A38" s="1"/>
+      <c r="A38" s="2"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -1566,7 +1571,7 @@
       <c r="W38" s="7"/>
     </row>
     <row r="39">
-      <c r="A39" s="1"/>
+      <c r="A39" s="2"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -1591,7 +1596,7 @@
       <c r="W39" s="7"/>
     </row>
     <row r="40">
-      <c r="A40" s="1"/>
+      <c r="A40" s="2"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -1616,7 +1621,7 @@
       <c r="W40" s="7"/>
     </row>
     <row r="41">
-      <c r="A41" s="1"/>
+      <c r="A41" s="2"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1641,7 +1646,7 @@
       <c r="W41" s="7"/>
     </row>
     <row r="42">
-      <c r="A42" s="1"/>
+      <c r="A42" s="2"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -1666,7 +1671,7 @@
       <c r="W42" s="7"/>
     </row>
     <row r="43">
-      <c r="A43" s="1"/>
+      <c r="A43" s="2"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -1691,7 +1696,7 @@
       <c r="W43" s="7"/>
     </row>
     <row r="44">
-      <c r="A44" s="1"/>
+      <c r="A44" s="2"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -1716,7 +1721,7 @@
       <c r="W44" s="7"/>
     </row>
     <row r="45">
-      <c r="A45" s="1"/>
+      <c r="A45" s="2"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1741,7 +1746,7 @@
       <c r="W45" s="7"/>
     </row>
     <row r="46">
-      <c r="A46" s="1"/>
+      <c r="A46" s="2"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -1766,7 +1771,7 @@
       <c r="W46" s="7"/>
     </row>
     <row r="47">
-      <c r="A47" s="1"/>
+      <c r="A47" s="2"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -1791,7 +1796,7 @@
       <c r="W47" s="7"/>
     </row>
     <row r="48">
-      <c r="A48" s="1"/>
+      <c r="A48" s="2"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -1816,7 +1821,7 @@
       <c r="W48" s="7"/>
     </row>
     <row r="49">
-      <c r="A49" s="1"/>
+      <c r="A49" s="2"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -1841,7 +1846,7 @@
       <c r="W49" s="7"/>
     </row>
     <row r="50">
-      <c r="A50" s="1"/>
+      <c r="A50" s="2"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
@@ -1866,7 +1871,7 @@
       <c r="W50" s="7"/>
     </row>
     <row r="51">
-      <c r="A51" s="1"/>
+      <c r="A51" s="2"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -1891,7 +1896,7 @@
       <c r="W51" s="7"/>
     </row>
     <row r="52">
-      <c r="A52" s="1"/>
+      <c r="A52" s="2"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -1916,7 +1921,7 @@
       <c r="W52" s="7"/>
     </row>
     <row r="53">
-      <c r="A53" s="1"/>
+      <c r="A53" s="2"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -1941,7 +1946,7 @@
       <c r="W53" s="7"/>
     </row>
     <row r="54">
-      <c r="A54" s="1"/>
+      <c r="A54" s="2"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -1966,7 +1971,7 @@
       <c r="W54" s="7"/>
     </row>
     <row r="55">
-      <c r="A55" s="1"/>
+      <c r="A55" s="2"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -1991,7 +1996,7 @@
       <c r="W55" s="7"/>
     </row>
     <row r="56">
-      <c r="A56" s="1"/>
+      <c r="A56" s="2"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -2016,7 +2021,7 @@
       <c r="W56" s="7"/>
     </row>
     <row r="57">
-      <c r="A57" s="1"/>
+      <c r="A57" s="2"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -2041,7 +2046,7 @@
       <c r="W57" s="7"/>
     </row>
     <row r="58">
-      <c r="A58" s="1"/>
+      <c r="A58" s="2"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -2066,7 +2071,7 @@
       <c r="W58" s="7"/>
     </row>
     <row r="59">
-      <c r="A59" s="1"/>
+      <c r="A59" s="2"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -2091,7 +2096,7 @@
       <c r="W59" s="7"/>
     </row>
     <row r="60">
-      <c r="A60" s="1"/>
+      <c r="A60" s="2"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -2116,7 +2121,7 @@
       <c r="W60" s="7"/>
     </row>
     <row r="61">
-      <c r="A61" s="1"/>
+      <c r="A61" s="2"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -2141,7 +2146,7 @@
       <c r="W61" s="7"/>
     </row>
     <row r="62">
-      <c r="A62" s="1"/>
+      <c r="A62" s="2"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -2166,7 +2171,7 @@
       <c r="W62" s="7"/>
     </row>
     <row r="63">
-      <c r="A63" s="1"/>
+      <c r="A63" s="2"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -2191,7 +2196,7 @@
       <c r="W63" s="7"/>
     </row>
     <row r="64">
-      <c r="A64" s="1"/>
+      <c r="A64" s="2"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -2216,7 +2221,7 @@
       <c r="W64" s="7"/>
     </row>
     <row r="65">
-      <c r="A65" s="1"/>
+      <c r="A65" s="2"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -2241,7 +2246,7 @@
       <c r="W65" s="7"/>
     </row>
     <row r="66">
-      <c r="A66" s="1"/>
+      <c r="A66" s="2"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -2266,7 +2271,7 @@
       <c r="W66" s="7"/>
     </row>
     <row r="67">
-      <c r="A67" s="1"/>
+      <c r="A67" s="2"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -2291,7 +2296,7 @@
       <c r="W67" s="7"/>
     </row>
     <row r="68">
-      <c r="A68" s="1"/>
+      <c r="A68" s="2"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -2316,7 +2321,7 @@
       <c r="W68" s="7"/>
     </row>
     <row r="69">
-      <c r="A69" s="1"/>
+      <c r="A69" s="2"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -2341,7 +2346,7 @@
       <c r="W69" s="7"/>
     </row>
     <row r="70">
-      <c r="A70" s="1"/>
+      <c r="A70" s="2"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -2366,7 +2371,7 @@
       <c r="W70" s="7"/>
     </row>
     <row r="71">
-      <c r="A71" s="1"/>
+      <c r="A71" s="2"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -2391,7 +2396,7 @@
       <c r="W71" s="7"/>
     </row>
     <row r="72">
-      <c r="A72" s="1"/>
+      <c r="A72" s="2"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -2416,7 +2421,7 @@
       <c r="W72" s="7"/>
     </row>
     <row r="73">
-      <c r="A73" s="1"/>
+      <c r="A73" s="2"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -2441,7 +2446,7 @@
       <c r="W73" s="7"/>
     </row>
     <row r="74">
-      <c r="A74" s="1"/>
+      <c r="A74" s="2"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -2466,7 +2471,7 @@
       <c r="W74" s="7"/>
     </row>
     <row r="75">
-      <c r="A75" s="1"/>
+      <c r="A75" s="2"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
@@ -2491,7 +2496,7 @@
       <c r="W75" s="7"/>
     </row>
     <row r="76">
-      <c r="A76" s="1"/>
+      <c r="A76" s="2"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -2516,7 +2521,7 @@
       <c r="W76" s="7"/>
     </row>
     <row r="77">
-      <c r="A77" s="1"/>
+      <c r="A77" s="2"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -2541,7 +2546,7 @@
       <c r="W77" s="7"/>
     </row>
     <row r="78">
-      <c r="A78" s="1"/>
+      <c r="A78" s="2"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -2566,7 +2571,7 @@
       <c r="W78" s="7"/>
     </row>
     <row r="79">
-      <c r="A79" s="1"/>
+      <c r="A79" s="2"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -2591,7 +2596,7 @@
       <c r="W79" s="7"/>
     </row>
     <row r="80">
-      <c r="A80" s="1"/>
+      <c r="A80" s="2"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -2616,7 +2621,7 @@
       <c r="W80" s="7"/>
     </row>
     <row r="81">
-      <c r="A81" s="1"/>
+      <c r="A81" s="2"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -2641,7 +2646,7 @@
       <c r="W81" s="7"/>
     </row>
     <row r="82">
-      <c r="A82" s="1"/>
+      <c r="A82" s="2"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -2666,7 +2671,7 @@
       <c r="W82" s="7"/>
     </row>
     <row r="83">
-      <c r="A83" s="1"/>
+      <c r="A83" s="2"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -2691,7 +2696,7 @@
       <c r="W83" s="7"/>
     </row>
     <row r="84">
-      <c r="A84" s="1"/>
+      <c r="A84" s="2"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -2716,7 +2721,7 @@
       <c r="W84" s="7"/>
     </row>
     <row r="85">
-      <c r="A85" s="1"/>
+      <c r="A85" s="2"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
@@ -2741,7 +2746,7 @@
       <c r="W85" s="7"/>
     </row>
     <row r="86">
-      <c r="A86" s="1"/>
+      <c r="A86" s="2"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
@@ -2766,7 +2771,7 @@
       <c r="W86" s="7"/>
     </row>
     <row r="87">
-      <c r="A87" s="1"/>
+      <c r="A87" s="2"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
@@ -2791,7 +2796,7 @@
       <c r="W87" s="7"/>
     </row>
     <row r="88">
-      <c r="A88" s="1"/>
+      <c r="A88" s="2"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
@@ -2816,7 +2821,7 @@
       <c r="W88" s="7"/>
     </row>
     <row r="89">
-      <c r="A89" s="1"/>
+      <c r="A89" s="2"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
@@ -2841,7 +2846,7 @@
       <c r="W89" s="7"/>
     </row>
     <row r="90">
-      <c r="A90" s="1"/>
+      <c r="A90" s="2"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
@@ -2866,7 +2871,7 @@
       <c r="W90" s="7"/>
     </row>
     <row r="91">
-      <c r="A91" s="1"/>
+      <c r="A91" s="2"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -2891,7 +2896,7 @@
       <c r="W91" s="7"/>
     </row>
     <row r="92">
-      <c r="A92" s="1"/>
+      <c r="A92" s="2"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -2916,7 +2921,7 @@
       <c r="W92" s="7"/>
     </row>
     <row r="93">
-      <c r="A93" s="1"/>
+      <c r="A93" s="2"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -2941,7 +2946,7 @@
       <c r="W93" s="7"/>
     </row>
     <row r="94">
-      <c r="A94" s="1"/>
+      <c r="A94" s="2"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -2966,7 +2971,7 @@
       <c r="W94" s="7"/>
     </row>
     <row r="95">
-      <c r="A95" s="1"/>
+      <c r="A95" s="2"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -2991,7 +2996,7 @@
       <c r="W95" s="7"/>
     </row>
     <row r="96">
-      <c r="A96" s="1"/>
+      <c r="A96" s="2"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -3016,7 +3021,7 @@
       <c r="W96" s="7"/>
     </row>
     <row r="97">
-      <c r="A97" s="1"/>
+      <c r="A97" s="2"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
@@ -3041,7 +3046,7 @@
       <c r="W97" s="7"/>
     </row>
     <row r="98">
-      <c r="A98" s="1"/>
+      <c r="A98" s="2"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
@@ -3066,7 +3071,7 @@
       <c r="W98" s="7"/>
     </row>
     <row r="99">
-      <c r="A99" s="1"/>
+      <c r="A99" s="2"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
@@ -3091,7 +3096,7 @@
       <c r="W99" s="7"/>
     </row>
     <row r="100">
-      <c r="A100" s="1"/>
+      <c r="A100" s="2"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
@@ -3116,7 +3121,7 @@
       <c r="W100" s="7"/>
     </row>
     <row r="101">
-      <c r="A101" s="1"/>
+      <c r="A101" s="2"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
@@ -3141,7 +3146,7 @@
       <c r="W101" s="7"/>
     </row>
     <row r="102">
-      <c r="A102" s="1"/>
+      <c r="A102" s="2"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
@@ -3166,7 +3171,7 @@
       <c r="W102" s="7"/>
     </row>
     <row r="103">
-      <c r="A103" s="1"/>
+      <c r="A103" s="2"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
@@ -3191,7 +3196,7 @@
       <c r="W103" s="7"/>
     </row>
     <row r="104">
-      <c r="A104" s="1"/>
+      <c r="A104" s="2"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
@@ -3216,7 +3221,7 @@
       <c r="W104" s="7"/>
     </row>
     <row r="105">
-      <c r="A105" s="1"/>
+      <c r="A105" s="2"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
@@ -3241,7 +3246,7 @@
       <c r="W105" s="7"/>
     </row>
     <row r="106">
-      <c r="A106" s="1"/>
+      <c r="A106" s="2"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
@@ -3266,7 +3271,7 @@
       <c r="W106" s="7"/>
     </row>
     <row r="107">
-      <c r="A107" s="1"/>
+      <c r="A107" s="2"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
@@ -3291,7 +3296,7 @@
       <c r="W107" s="7"/>
     </row>
     <row r="108">
-      <c r="A108" s="1"/>
+      <c r="A108" s="2"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
@@ -3316,7 +3321,7 @@
       <c r="W108" s="7"/>
     </row>
     <row r="109">
-      <c r="A109" s="1"/>
+      <c r="A109" s="2"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
@@ -3341,7 +3346,7 @@
       <c r="W109" s="7"/>
     </row>
     <row r="110">
-      <c r="A110" s="1"/>
+      <c r="A110" s="2"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
@@ -3366,7 +3371,7 @@
       <c r="W110" s="7"/>
     </row>
     <row r="111">
-      <c r="A111" s="1"/>
+      <c r="A111" s="2"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
@@ -3391,7 +3396,7 @@
       <c r="W111" s="7"/>
     </row>
     <row r="112">
-      <c r="A112" s="1"/>
+      <c r="A112" s="2"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
@@ -3416,7 +3421,7 @@
       <c r="W112" s="7"/>
     </row>
     <row r="113">
-      <c r="A113" s="1"/>
+      <c r="A113" s="2"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
@@ -3441,7 +3446,7 @@
       <c r="W113" s="7"/>
     </row>
     <row r="114">
-      <c r="A114" s="1"/>
+      <c r="A114" s="2"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
@@ -3466,7 +3471,7 @@
       <c r="W114" s="7"/>
     </row>
     <row r="115">
-      <c r="A115" s="1"/>
+      <c r="A115" s="2"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
@@ -3491,7 +3496,7 @@
       <c r="W115" s="7"/>
     </row>
     <row r="116">
-      <c r="A116" s="1"/>
+      <c r="A116" s="2"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
@@ -3516,7 +3521,7 @@
       <c r="W116" s="7"/>
     </row>
     <row r="117">
-      <c r="A117" s="1"/>
+      <c r="A117" s="2"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
@@ -3541,7 +3546,7 @@
       <c r="W117" s="7"/>
     </row>
     <row r="118">
-      <c r="A118" s="1"/>
+      <c r="A118" s="2"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
@@ -3566,7 +3571,7 @@
       <c r="W118" s="7"/>
     </row>
     <row r="119">
-      <c r="A119" s="1"/>
+      <c r="A119" s="2"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
@@ -3591,7 +3596,7 @@
       <c r="W119" s="7"/>
     </row>
     <row r="120">
-      <c r="A120" s="1"/>
+      <c r="A120" s="2"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
@@ -3616,7 +3621,7 @@
       <c r="W120" s="7"/>
     </row>
     <row r="121">
-      <c r="A121" s="1"/>
+      <c r="A121" s="2"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
@@ -3641,7 +3646,7 @@
       <c r="W121" s="7"/>
     </row>
     <row r="122">
-      <c r="A122" s="1"/>
+      <c r="A122" s="2"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
@@ -3666,7 +3671,7 @@
       <c r="W122" s="7"/>
     </row>
     <row r="123">
-      <c r="A123" s="1"/>
+      <c r="A123" s="2"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
@@ -3691,7 +3696,7 @@
       <c r="W123" s="7"/>
     </row>
     <row r="124">
-      <c r="A124" s="1"/>
+      <c r="A124" s="2"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
@@ -3716,7 +3721,7 @@
       <c r="W124" s="7"/>
     </row>
     <row r="125">
-      <c r="A125" s="1"/>
+      <c r="A125" s="2"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
@@ -3741,7 +3746,7 @@
       <c r="W125" s="7"/>
     </row>
     <row r="126">
-      <c r="A126" s="1"/>
+      <c r="A126" s="2"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
@@ -3766,7 +3771,7 @@
       <c r="W126" s="7"/>
     </row>
     <row r="127">
-      <c r="A127" s="1"/>
+      <c r="A127" s="2"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
@@ -3791,7 +3796,7 @@
       <c r="W127" s="7"/>
     </row>
     <row r="128">
-      <c r="A128" s="1"/>
+      <c r="A128" s="2"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
@@ -3816,7 +3821,7 @@
       <c r="W128" s="7"/>
     </row>
     <row r="129">
-      <c r="A129" s="1"/>
+      <c r="A129" s="2"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
@@ -3841,7 +3846,7 @@
       <c r="W129" s="7"/>
     </row>
     <row r="130">
-      <c r="A130" s="1"/>
+      <c r="A130" s="2"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
@@ -3866,7 +3871,7 @@
       <c r="W130" s="7"/>
     </row>
     <row r="131">
-      <c r="A131" s="1"/>
+      <c r="A131" s="2"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
@@ -3891,7 +3896,7 @@
       <c r="W131" s="7"/>
     </row>
     <row r="132">
-      <c r="A132" s="1"/>
+      <c r="A132" s="2"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
@@ -3916,7 +3921,7 @@
       <c r="W132" s="7"/>
     </row>
     <row r="133">
-      <c r="A133" s="1"/>
+      <c r="A133" s="2"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
@@ -3941,7 +3946,7 @@
       <c r="W133" s="7"/>
     </row>
     <row r="134">
-      <c r="A134" s="1"/>
+      <c r="A134" s="2"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
@@ -3966,7 +3971,7 @@
       <c r="W134" s="7"/>
     </row>
     <row r="135">
-      <c r="A135" s="1"/>
+      <c r="A135" s="2"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -3991,7 +3996,7 @@
       <c r="W135" s="7"/>
     </row>
     <row r="136">
-      <c r="A136" s="1"/>
+      <c r="A136" s="2"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
@@ -4016,7 +4021,7 @@
       <c r="W136" s="7"/>
     </row>
     <row r="137">
-      <c r="A137" s="1"/>
+      <c r="A137" s="2"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -4041,7 +4046,7 @@
       <c r="W137" s="7"/>
     </row>
     <row r="138">
-      <c r="A138" s="1"/>
+      <c r="A138" s="2"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
@@ -4066,7 +4071,7 @@
       <c r="W138" s="7"/>
     </row>
     <row r="139">
-      <c r="A139" s="1"/>
+      <c r="A139" s="2"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -4091,7 +4096,7 @@
       <c r="W139" s="7"/>
     </row>
     <row r="140">
-      <c r="A140" s="1"/>
+      <c r="A140" s="2"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
@@ -4116,7 +4121,7 @@
       <c r="W140" s="7"/>
     </row>
     <row r="141">
-      <c r="A141" s="1"/>
+      <c r="A141" s="2"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -4141,7 +4146,7 @@
       <c r="W141" s="7"/>
     </row>
     <row r="142">
-      <c r="A142" s="1"/>
+      <c r="A142" s="2"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
@@ -4166,7 +4171,7 @@
       <c r="W142" s="7"/>
     </row>
     <row r="143">
-      <c r="A143" s="1"/>
+      <c r="A143" s="2"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -4191,7 +4196,7 @@
       <c r="W143" s="7"/>
     </row>
     <row r="144">
-      <c r="A144" s="1"/>
+      <c r="A144" s="2"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
@@ -4216,7 +4221,7 @@
       <c r="W144" s="7"/>
     </row>
     <row r="145">
-      <c r="A145" s="1"/>
+      <c r="A145" s="2"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -4241,7 +4246,7 @@
       <c r="W145" s="7"/>
     </row>
     <row r="146">
-      <c r="A146" s="1"/>
+      <c r="A146" s="2"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
@@ -4266,7 +4271,7 @@
       <c r="W146" s="7"/>
     </row>
     <row r="147">
-      <c r="A147" s="1"/>
+      <c r="A147" s="2"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -4291,7 +4296,7 @@
       <c r="W147" s="7"/>
     </row>
     <row r="148">
-      <c r="A148" s="1"/>
+      <c r="A148" s="2"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
@@ -4316,7 +4321,7 @@
       <c r="W148" s="7"/>
     </row>
     <row r="149">
-      <c r="A149" s="1"/>
+      <c r="A149" s="2"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -4341,7 +4346,7 @@
       <c r="W149" s="7"/>
     </row>
     <row r="150">
-      <c r="A150" s="1"/>
+      <c r="A150" s="2"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
@@ -4366,7 +4371,7 @@
       <c r="W150" s="7"/>
     </row>
     <row r="151">
-      <c r="A151" s="1"/>
+      <c r="A151" s="2"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
@@ -4391,7 +4396,7 @@
       <c r="W151" s="7"/>
     </row>
     <row r="152">
-      <c r="A152" s="1"/>
+      <c r="A152" s="2"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
@@ -4416,7 +4421,7 @@
       <c r="W152" s="7"/>
     </row>
     <row r="153">
-      <c r="A153" s="1"/>
+      <c r="A153" s="2"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
@@ -4441,7 +4446,7 @@
       <c r="W153" s="7"/>
     </row>
     <row r="154">
-      <c r="A154" s="1"/>
+      <c r="A154" s="2"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
@@ -4466,7 +4471,7 @@
       <c r="W154" s="7"/>
     </row>
     <row r="155">
-      <c r="A155" s="1"/>
+      <c r="A155" s="2"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -4491,7 +4496,7 @@
       <c r="W155" s="7"/>
     </row>
     <row r="156">
-      <c r="A156" s="1"/>
+      <c r="A156" s="2"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
@@ -4516,7 +4521,7 @@
       <c r="W156" s="7"/>
     </row>
     <row r="157">
-      <c r="A157" s="1"/>
+      <c r="A157" s="2"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
@@ -4541,7 +4546,7 @@
       <c r="W157" s="7"/>
     </row>
     <row r="158">
-      <c r="A158" s="1"/>
+      <c r="A158" s="2"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
@@ -4566,7 +4571,7 @@
       <c r="W158" s="7"/>
     </row>
     <row r="159">
-      <c r="A159" s="1"/>
+      <c r="A159" s="2"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -4591,7 +4596,7 @@
       <c r="W159" s="7"/>
     </row>
     <row r="160">
-      <c r="A160" s="1"/>
+      <c r="A160" s="2"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -4616,7 +4621,7 @@
       <c r="W160" s="7"/>
     </row>
     <row r="161">
-      <c r="A161" s="1"/>
+      <c r="A161" s="2"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -4641,7 +4646,7 @@
       <c r="W161" s="7"/>
     </row>
     <row r="162">
-      <c r="A162" s="1"/>
+      <c r="A162" s="2"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -4666,7 +4671,7 @@
       <c r="W162" s="7"/>
     </row>
     <row r="163">
-      <c r="A163" s="1"/>
+      <c r="A163" s="2"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
@@ -4691,7 +4696,7 @@
       <c r="W163" s="7"/>
     </row>
     <row r="164">
-      <c r="A164" s="1"/>
+      <c r="A164" s="2"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
@@ -4716,7 +4721,7 @@
       <c r="W164" s="7"/>
     </row>
     <row r="165">
-      <c r="A165" s="1"/>
+      <c r="A165" s="2"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
@@ -4741,7 +4746,7 @@
       <c r="W165" s="7"/>
     </row>
     <row r="166">
-      <c r="A166" s="1"/>
+      <c r="A166" s="2"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
@@ -4766,7 +4771,7 @@
       <c r="W166" s="7"/>
     </row>
     <row r="167">
-      <c r="A167" s="1"/>
+      <c r="A167" s="2"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -4791,7 +4796,7 @@
       <c r="W167" s="7"/>
     </row>
     <row r="168">
-      <c r="A168" s="1"/>
+      <c r="A168" s="2"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -4816,7 +4821,7 @@
       <c r="W168" s="7"/>
     </row>
     <row r="169">
-      <c r="A169" s="1"/>
+      <c r="A169" s="2"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -4841,7 +4846,7 @@
       <c r="W169" s="7"/>
     </row>
     <row r="170">
-      <c r="A170" s="1"/>
+      <c r="A170" s="2"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -4866,7 +4871,7 @@
       <c r="W170" s="7"/>
     </row>
     <row r="171">
-      <c r="A171" s="1"/>
+      <c r="A171" s="2"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -4891,7 +4896,7 @@
       <c r="W171" s="7"/>
     </row>
     <row r="172">
-      <c r="A172" s="1"/>
+      <c r="A172" s="2"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -4916,7 +4921,7 @@
       <c r="W172" s="7"/>
     </row>
     <row r="173">
-      <c r="A173" s="1"/>
+      <c r="A173" s="2"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -4941,7 +4946,7 @@
       <c r="W173" s="7"/>
     </row>
     <row r="174">
-      <c r="A174" s="1"/>
+      <c r="A174" s="2"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -4966,7 +4971,7 @@
       <c r="W174" s="7"/>
     </row>
     <row r="175">
-      <c r="A175" s="1"/>
+      <c r="A175" s="2"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -4991,7 +4996,7 @@
       <c r="W175" s="7"/>
     </row>
     <row r="176">
-      <c r="A176" s="1"/>
+      <c r="A176" s="2"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -5016,7 +5021,7 @@
       <c r="W176" s="7"/>
     </row>
     <row r="177">
-      <c r="A177" s="1"/>
+      <c r="A177" s="2"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -5041,7 +5046,7 @@
       <c r="W177" s="7"/>
     </row>
     <row r="178">
-      <c r="A178" s="1"/>
+      <c r="A178" s="2"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -5066,7 +5071,7 @@
       <c r="W178" s="7"/>
     </row>
     <row r="179">
-      <c r="A179" s="1"/>
+      <c r="A179" s="2"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -5091,7 +5096,7 @@
       <c r="W179" s="7"/>
     </row>
     <row r="180">
-      <c r="A180" s="1"/>
+      <c r="A180" s="2"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -5116,7 +5121,7 @@
       <c r="W180" s="7"/>
     </row>
     <row r="181">
-      <c r="A181" s="1"/>
+      <c r="A181" s="2"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -5141,7 +5146,7 @@
       <c r="W181" s="7"/>
     </row>
     <row r="182">
-      <c r="A182" s="1"/>
+      <c r="A182" s="2"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -5166,7 +5171,7 @@
       <c r="W182" s="7"/>
     </row>
     <row r="183">
-      <c r="A183" s="1"/>
+      <c r="A183" s="2"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -5191,7 +5196,7 @@
       <c r="W183" s="7"/>
     </row>
     <row r="184">
-      <c r="A184" s="1"/>
+      <c r="A184" s="2"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -5216,7 +5221,7 @@
       <c r="W184" s="7"/>
     </row>
     <row r="185">
-      <c r="A185" s="1"/>
+      <c r="A185" s="2"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -5241,7 +5246,7 @@
       <c r="W185" s="7"/>
     </row>
     <row r="186">
-      <c r="A186" s="1"/>
+      <c r="A186" s="2"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -5266,7 +5271,7 @@
       <c r="W186" s="7"/>
     </row>
     <row r="187">
-      <c r="A187" s="1"/>
+      <c r="A187" s="2"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -5291,7 +5296,7 @@
       <c r="W187" s="7"/>
     </row>
     <row r="188">
-      <c r="A188" s="1"/>
+      <c r="A188" s="2"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -5316,7 +5321,7 @@
       <c r="W188" s="7"/>
     </row>
     <row r="189">
-      <c r="A189" s="1"/>
+      <c r="A189" s="2"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -5341,7 +5346,7 @@
       <c r="W189" s="7"/>
     </row>
     <row r="190">
-      <c r="A190" s="1"/>
+      <c r="A190" s="2"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -5366,7 +5371,7 @@
       <c r="W190" s="7"/>
     </row>
     <row r="191">
-      <c r="A191" s="1"/>
+      <c r="A191" s="2"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -5391,7 +5396,7 @@
       <c r="W191" s="7"/>
     </row>
     <row r="192">
-      <c r="A192" s="1"/>
+      <c r="A192" s="2"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -5416,7 +5421,7 @@
       <c r="W192" s="7"/>
     </row>
     <row r="193">
-      <c r="A193" s="1"/>
+      <c r="A193" s="2"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
@@ -5441,7 +5446,7 @@
       <c r="W193" s="7"/>
     </row>
     <row r="194">
-      <c r="A194" s="1"/>
+      <c r="A194" s="2"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
@@ -5466,7 +5471,7 @@
       <c r="W194" s="7"/>
     </row>
     <row r="195">
-      <c r="A195" s="1"/>
+      <c r="A195" s="2"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
@@ -5491,7 +5496,7 @@
       <c r="W195" s="7"/>
     </row>
     <row r="196">
-      <c r="A196" s="1"/>
+      <c r="A196" s="2"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
@@ -5516,7 +5521,7 @@
       <c r="W196" s="7"/>
     </row>
     <row r="197">
-      <c r="A197" s="1"/>
+      <c r="A197" s="2"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
@@ -5541,7 +5546,7 @@
       <c r="W197" s="7"/>
     </row>
     <row r="198">
-      <c r="A198" s="1"/>
+      <c r="A198" s="2"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
@@ -5566,7 +5571,7 @@
       <c r="W198" s="7"/>
     </row>
     <row r="199">
-      <c r="A199" s="1"/>
+      <c r="A199" s="2"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
@@ -5591,7 +5596,7 @@
       <c r="W199" s="7"/>
     </row>
     <row r="200">
-      <c r="A200" s="1"/>
+      <c r="A200" s="2"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
@@ -5616,7 +5621,7 @@
       <c r="W200" s="7"/>
     </row>
     <row r="201">
-      <c r="A201" s="1"/>
+      <c r="A201" s="2"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
@@ -5641,7 +5646,7 @@
       <c r="W201" s="7"/>
     </row>
     <row r="202">
-      <c r="A202" s="1"/>
+      <c r="A202" s="2"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
@@ -5666,7 +5671,7 @@
       <c r="W202" s="7"/>
     </row>
     <row r="203">
-      <c r="A203" s="1"/>
+      <c r="A203" s="2"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
@@ -5691,7 +5696,7 @@
       <c r="W203" s="7"/>
     </row>
     <row r="204">
-      <c r="A204" s="1"/>
+      <c r="A204" s="2"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
@@ -5716,7 +5721,7 @@
       <c r="W204" s="7"/>
     </row>
     <row r="205">
-      <c r="A205" s="1"/>
+      <c r="A205" s="2"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -5741,7 +5746,7 @@
       <c r="W205" s="7"/>
     </row>
     <row r="206">
-      <c r="A206" s="1"/>
+      <c r="A206" s="2"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -5766,7 +5771,7 @@
       <c r="W206" s="7"/>
     </row>
     <row r="207">
-      <c r="A207" s="1"/>
+      <c r="A207" s="2"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
@@ -5791,7 +5796,7 @@
       <c r="W207" s="7"/>
     </row>
     <row r="208">
-      <c r="A208" s="1"/>
+      <c r="A208" s="2"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
@@ -5816,7 +5821,7 @@
       <c r="W208" s="7"/>
     </row>
     <row r="209">
-      <c r="A209" s="1"/>
+      <c r="A209" s="2"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
@@ -5841,7 +5846,7 @@
       <c r="W209" s="7"/>
     </row>
     <row r="210">
-      <c r="A210" s="1"/>
+      <c r="A210" s="2"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
@@ -5866,7 +5871,7 @@
       <c r="W210" s="7"/>
     </row>
     <row r="211">
-      <c r="A211" s="1"/>
+      <c r="A211" s="2"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
@@ -5891,7 +5896,7 @@
       <c r="W211" s="7"/>
     </row>
     <row r="212">
-      <c r="A212" s="1"/>
+      <c r="A212" s="2"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
@@ -5916,7 +5921,7 @@
       <c r="W212" s="7"/>
     </row>
     <row r="213">
-      <c r="A213" s="1"/>
+      <c r="A213" s="2"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
@@ -5941,7 +5946,7 @@
       <c r="W213" s="7"/>
     </row>
     <row r="214">
-      <c r="A214" s="1"/>
+      <c r="A214" s="2"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
@@ -5966,7 +5971,7 @@
       <c r="W214" s="7"/>
     </row>
     <row r="215">
-      <c r="A215" s="1"/>
+      <c r="A215" s="2"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
@@ -5991,7 +5996,7 @@
       <c r="W215" s="7"/>
     </row>
     <row r="216">
-      <c r="A216" s="1"/>
+      <c r="A216" s="2"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
@@ -6016,7 +6021,7 @@
       <c r="W216" s="7"/>
     </row>
     <row r="217">
-      <c r="A217" s="1"/>
+      <c r="A217" s="2"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -6041,7 +6046,7 @@
       <c r="W217" s="7"/>
     </row>
     <row r="218">
-      <c r="A218" s="1"/>
+      <c r="A218" s="2"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -6066,7 +6071,7 @@
       <c r="W218" s="7"/>
     </row>
     <row r="219">
-      <c r="A219" s="1"/>
+      <c r="A219" s="2"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
@@ -6091,7 +6096,7 @@
       <c r="W219" s="7"/>
     </row>
     <row r="220">
-      <c r="A220" s="1"/>
+      <c r="A220" s="2"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -6116,7 +6121,7 @@
       <c r="W220" s="7"/>
     </row>
     <row r="221">
-      <c r="A221" s="1"/>
+      <c r="A221" s="2"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
@@ -6141,7 +6146,7 @@
       <c r="W221" s="7"/>
     </row>
     <row r="222">
-      <c r="A222" s="1"/>
+      <c r="A222" s="2"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
@@ -6166,7 +6171,7 @@
       <c r="W222" s="7"/>
     </row>
     <row r="223">
-      <c r="A223" s="1"/>
+      <c r="A223" s="2"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
@@ -6191,7 +6196,7 @@
       <c r="W223" s="7"/>
     </row>
     <row r="224">
-      <c r="A224" s="1"/>
+      <c r="A224" s="2"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
@@ -6216,7 +6221,7 @@
       <c r="W224" s="7"/>
     </row>
     <row r="225">
-      <c r="A225" s="1"/>
+      <c r="A225" s="2"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
@@ -6241,7 +6246,7 @@
       <c r="W225" s="7"/>
     </row>
     <row r="226">
-      <c r="A226" s="1"/>
+      <c r="A226" s="2"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
@@ -6266,7 +6271,7 @@
       <c r="W226" s="7"/>
     </row>
     <row r="227">
-      <c r="A227" s="1"/>
+      <c r="A227" s="2"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
@@ -6291,7 +6296,7 @@
       <c r="W227" s="7"/>
     </row>
     <row r="228">
-      <c r="A228" s="1"/>
+      <c r="A228" s="2"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -6316,7 +6321,7 @@
       <c r="W228" s="7"/>
     </row>
     <row r="229">
-      <c r="A229" s="1"/>
+      <c r="A229" s="2"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
@@ -6341,7 +6346,7 @@
       <c r="W229" s="7"/>
     </row>
     <row r="230">
-      <c r="A230" s="1"/>
+      <c r="A230" s="2"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
@@ -6366,7 +6371,7 @@
       <c r="W230" s="7"/>
     </row>
     <row r="231">
-      <c r="A231" s="1"/>
+      <c r="A231" s="2"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
@@ -6391,7 +6396,7 @@
       <c r="W231" s="7"/>
     </row>
     <row r="232">
-      <c r="A232" s="1"/>
+      <c r="A232" s="2"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -6416,7 +6421,7 @@
       <c r="W232" s="7"/>
     </row>
     <row r="233">
-      <c r="A233" s="1"/>
+      <c r="A233" s="2"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
@@ -6441,7 +6446,7 @@
       <c r="W233" s="7"/>
     </row>
     <row r="234">
-      <c r="A234" s="1"/>
+      <c r="A234" s="2"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
@@ -6466,7 +6471,7 @@
       <c r="W234" s="7"/>
     </row>
     <row r="235">
-      <c r="A235" s="1"/>
+      <c r="A235" s="2"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
@@ -6491,7 +6496,7 @@
       <c r="W235" s="7"/>
     </row>
     <row r="236">
-      <c r="A236" s="1"/>
+      <c r="A236" s="2"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
@@ -6516,7 +6521,7 @@
       <c r="W236" s="7"/>
     </row>
     <row r="237">
-      <c r="A237" s="1"/>
+      <c r="A237" s="2"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
@@ -6541,7 +6546,7 @@
       <c r="W237" s="7"/>
     </row>
     <row r="238">
-      <c r="A238" s="1"/>
+      <c r="A238" s="2"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
@@ -6566,7 +6571,7 @@
       <c r="W238" s="7"/>
     </row>
     <row r="239">
-      <c r="A239" s="1"/>
+      <c r="A239" s="2"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
@@ -6591,7 +6596,7 @@
       <c r="W239" s="7"/>
     </row>
     <row r="240">
-      <c r="A240" s="1"/>
+      <c r="A240" s="2"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
@@ -6616,7 +6621,7 @@
       <c r="W240" s="7"/>
     </row>
     <row r="241">
-      <c r="A241" s="1"/>
+      <c r="A241" s="2"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
@@ -6641,7 +6646,7 @@
       <c r="W241" s="7"/>
     </row>
     <row r="242">
-      <c r="A242" s="1"/>
+      <c r="A242" s="2"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
@@ -6666,7 +6671,7 @@
       <c r="W242" s="7"/>
     </row>
     <row r="243">
-      <c r="A243" s="1"/>
+      <c r="A243" s="2"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
@@ -6691,7 +6696,7 @@
       <c r="W243" s="7"/>
     </row>
     <row r="244">
-      <c r="A244" s="1"/>
+      <c r="A244" s="2"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
@@ -6716,7 +6721,7 @@
       <c r="W244" s="7"/>
     </row>
     <row r="245">
-      <c r="A245" s="1"/>
+      <c r="A245" s="2"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
@@ -6741,7 +6746,7 @@
       <c r="W245" s="7"/>
     </row>
     <row r="246">
-      <c r="A246" s="1"/>
+      <c r="A246" s="2"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
@@ -6766,7 +6771,7 @@
       <c r="W246" s="7"/>
     </row>
     <row r="247">
-      <c r="A247" s="1"/>
+      <c r="A247" s="2"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
@@ -6791,7 +6796,7 @@
       <c r="W247" s="7"/>
     </row>
     <row r="248">
-      <c r="A248" s="1"/>
+      <c r="A248" s="2"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
@@ -6816,7 +6821,7 @@
       <c r="W248" s="7"/>
     </row>
     <row r="249">
-      <c r="A249" s="1"/>
+      <c r="A249" s="2"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
@@ -6841,7 +6846,7 @@
       <c r="W249" s="7"/>
     </row>
     <row r="250">
-      <c r="A250" s="1"/>
+      <c r="A250" s="2"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
@@ -6866,7 +6871,7 @@
       <c r="W250" s="7"/>
     </row>
     <row r="251">
-      <c r="A251" s="1"/>
+      <c r="A251" s="2"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
@@ -6891,7 +6896,7 @@
       <c r="W251" s="7"/>
     </row>
     <row r="252">
-      <c r="A252" s="1"/>
+      <c r="A252" s="2"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
@@ -6916,7 +6921,7 @@
       <c r="W252" s="7"/>
     </row>
     <row r="253">
-      <c r="A253" s="1"/>
+      <c r="A253" s="2"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
@@ -6941,7 +6946,7 @@
       <c r="W253" s="7"/>
     </row>
     <row r="254">
-      <c r="A254" s="1"/>
+      <c r="A254" s="2"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
@@ -6966,7 +6971,7 @@
       <c r="W254" s="7"/>
     </row>
     <row r="255">
-      <c r="A255" s="1"/>
+      <c r="A255" s="2"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
@@ -6991,7 +6996,7 @@
       <c r="W255" s="7"/>
     </row>
     <row r="256">
-      <c r="A256" s="1"/>
+      <c r="A256" s="2"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
@@ -7016,7 +7021,7 @@
       <c r="W256" s="7"/>
     </row>
     <row r="257">
-      <c r="A257" s="1"/>
+      <c r="A257" s="2"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
@@ -7041,7 +7046,7 @@
       <c r="W257" s="7"/>
     </row>
     <row r="258">
-      <c r="A258" s="1"/>
+      <c r="A258" s="2"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
@@ -7066,7 +7071,7 @@
       <c r="W258" s="7"/>
     </row>
     <row r="259">
-      <c r="A259" s="1"/>
+      <c r="A259" s="2"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
@@ -7091,7 +7096,7 @@
       <c r="W259" s="7"/>
     </row>
     <row r="260">
-      <c r="A260" s="1"/>
+      <c r="A260" s="2"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
@@ -7116,7 +7121,7 @@
       <c r="W260" s="7"/>
     </row>
     <row r="261">
-      <c r="A261" s="1"/>
+      <c r="A261" s="2"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
@@ -7141,7 +7146,7 @@
       <c r="W261" s="7"/>
     </row>
     <row r="262">
-      <c r="A262" s="1"/>
+      <c r="A262" s="2"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
@@ -7166,7 +7171,7 @@
       <c r="W262" s="7"/>
     </row>
     <row r="263">
-      <c r="A263" s="1"/>
+      <c r="A263" s="2"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
@@ -7191,7 +7196,7 @@
       <c r="W263" s="7"/>
     </row>
     <row r="264">
-      <c r="A264" s="1"/>
+      <c r="A264" s="2"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
@@ -7216,7 +7221,7 @@
       <c r="W264" s="7"/>
     </row>
     <row r="265">
-      <c r="A265" s="1"/>
+      <c r="A265" s="2"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
@@ -7241,7 +7246,7 @@
       <c r="W265" s="7"/>
     </row>
     <row r="266">
-      <c r="A266" s="1"/>
+      <c r="A266" s="2"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
@@ -7266,7 +7271,7 @@
       <c r="W266" s="7"/>
     </row>
     <row r="267">
-      <c r="A267" s="1"/>
+      <c r="A267" s="2"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
@@ -7291,7 +7296,7 @@
       <c r="W267" s="7"/>
     </row>
     <row r="268">
-      <c r="A268" s="1"/>
+      <c r="A268" s="2"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
@@ -7316,7 +7321,7 @@
       <c r="W268" s="7"/>
     </row>
     <row r="269">
-      <c r="A269" s="1"/>
+      <c r="A269" s="2"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
@@ -7341,7 +7346,7 @@
       <c r="W269" s="7"/>
     </row>
     <row r="270">
-      <c r="A270" s="1"/>
+      <c r="A270" s="2"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
@@ -7366,7 +7371,7 @@
       <c r="W270" s="7"/>
     </row>
     <row r="271">
-      <c r="A271" s="1"/>
+      <c r="A271" s="2"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
@@ -7391,7 +7396,7 @@
       <c r="W271" s="7"/>
     </row>
     <row r="272">
-      <c r="A272" s="1"/>
+      <c r="A272" s="2"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
@@ -7416,7 +7421,7 @@
       <c r="W272" s="7"/>
     </row>
     <row r="273">
-      <c r="A273" s="1"/>
+      <c r="A273" s="2"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
@@ -7441,7 +7446,7 @@
       <c r="W273" s="7"/>
     </row>
     <row r="274">
-      <c r="A274" s="1"/>
+      <c r="A274" s="2"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
@@ -7466,7 +7471,7 @@
       <c r="W274" s="7"/>
     </row>
     <row r="275">
-      <c r="A275" s="1"/>
+      <c r="A275" s="2"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
@@ -7491,7 +7496,7 @@
       <c r="W275" s="7"/>
     </row>
     <row r="276">
-      <c r="A276" s="1"/>
+      <c r="A276" s="2"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
@@ -7516,7 +7521,7 @@
       <c r="W276" s="7"/>
     </row>
     <row r="277">
-      <c r="A277" s="1"/>
+      <c r="A277" s="2"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
@@ -7541,7 +7546,7 @@
       <c r="W277" s="7"/>
     </row>
     <row r="278">
-      <c r="A278" s="1"/>
+      <c r="A278" s="2"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
@@ -7566,7 +7571,7 @@
       <c r="W278" s="7"/>
     </row>
     <row r="279">
-      <c r="A279" s="1"/>
+      <c r="A279" s="2"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
@@ -7591,7 +7596,7 @@
       <c r="W279" s="7"/>
     </row>
     <row r="280">
-      <c r="A280" s="1"/>
+      <c r="A280" s="2"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
@@ -7616,7 +7621,7 @@
       <c r="W280" s="7"/>
     </row>
     <row r="281">
-      <c r="A281" s="1"/>
+      <c r="A281" s="2"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
@@ -7641,7 +7646,7 @@
       <c r="W281" s="7"/>
     </row>
     <row r="282">
-      <c r="A282" s="1"/>
+      <c r="A282" s="2"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
@@ -7666,7 +7671,7 @@
       <c r="W282" s="7"/>
     </row>
     <row r="283">
-      <c r="A283" s="1"/>
+      <c r="A283" s="2"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
@@ -7691,7 +7696,7 @@
       <c r="W283" s="7"/>
     </row>
     <row r="284">
-      <c r="A284" s="1"/>
+      <c r="A284" s="2"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
@@ -7716,7 +7721,7 @@
       <c r="W284" s="7"/>
     </row>
     <row r="285">
-      <c r="A285" s="1"/>
+      <c r="A285" s="2"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
@@ -7741,7 +7746,7 @@
       <c r="W285" s="7"/>
     </row>
     <row r="286">
-      <c r="A286" s="1"/>
+      <c r="A286" s="2"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
@@ -7766,7 +7771,7 @@
       <c r="W286" s="7"/>
     </row>
     <row r="287">
-      <c r="A287" s="1"/>
+      <c r="A287" s="2"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
@@ -7791,7 +7796,7 @@
       <c r="W287" s="7"/>
     </row>
     <row r="288">
-      <c r="A288" s="1"/>
+      <c r="A288" s="2"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
@@ -7816,7 +7821,7 @@
       <c r="W288" s="7"/>
     </row>
     <row r="289">
-      <c r="A289" s="1"/>
+      <c r="A289" s="2"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
@@ -7841,7 +7846,7 @@
       <c r="W289" s="7"/>
     </row>
     <row r="290">
-      <c r="A290" s="1"/>
+      <c r="A290" s="2"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
@@ -7866,7 +7871,7 @@
       <c r="W290" s="7"/>
     </row>
     <row r="291">
-      <c r="A291" s="1"/>
+      <c r="A291" s="2"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
@@ -7891,7 +7896,7 @@
       <c r="W291" s="7"/>
     </row>
     <row r="292">
-      <c r="A292" s="1"/>
+      <c r="A292" s="2"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
@@ -7916,7 +7921,7 @@
       <c r="W292" s="7"/>
     </row>
     <row r="293">
-      <c r="A293" s="1"/>
+      <c r="A293" s="2"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
@@ -7941,7 +7946,7 @@
       <c r="W293" s="7"/>
     </row>
     <row r="294">
-      <c r="A294" s="1"/>
+      <c r="A294" s="2"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
@@ -7966,7 +7971,7 @@
       <c r="W294" s="7"/>
     </row>
     <row r="295">
-      <c r="A295" s="1"/>
+      <c r="A295" s="2"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
@@ -7991,7 +7996,7 @@
       <c r="W295" s="7"/>
     </row>
     <row r="296">
-      <c r="A296" s="1"/>
+      <c r="A296" s="2"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
@@ -8016,7 +8021,7 @@
       <c r="W296" s="7"/>
     </row>
     <row r="297">
-      <c r="A297" s="1"/>
+      <c r="A297" s="2"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
@@ -8041,7 +8046,7 @@
       <c r="W297" s="7"/>
     </row>
     <row r="298">
-      <c r="A298" s="1"/>
+      <c r="A298" s="2"/>
       <c r="B298" s="7"/>
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
@@ -8066,7 +8071,7 @@
       <c r="W298" s="7"/>
     </row>
     <row r="299">
-      <c r="A299" s="1"/>
+      <c r="A299" s="2"/>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
@@ -8091,7 +8096,7 @@
       <c r="W299" s="7"/>
     </row>
     <row r="300">
-      <c r="A300" s="1"/>
+      <c r="A300" s="2"/>
       <c r="B300" s="7"/>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
@@ -8116,7 +8121,7 @@
       <c r="W300" s="7"/>
     </row>
     <row r="301">
-      <c r="A301" s="1"/>
+      <c r="A301" s="2"/>
       <c r="B301" s="7"/>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
@@ -8141,7 +8146,7 @@
       <c r="W301" s="7"/>
     </row>
     <row r="302">
-      <c r="A302" s="1"/>
+      <c r="A302" s="2"/>
       <c r="B302" s="7"/>
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
@@ -8166,7 +8171,7 @@
       <c r="W302" s="7"/>
     </row>
     <row r="303">
-      <c r="A303" s="1"/>
+      <c r="A303" s="2"/>
       <c r="B303" s="7"/>
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
@@ -8191,7 +8196,7 @@
       <c r="W303" s="7"/>
     </row>
     <row r="304">
-      <c r="A304" s="1"/>
+      <c r="A304" s="2"/>
       <c r="B304" s="7"/>
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
@@ -8216,7 +8221,7 @@
       <c r="W304" s="7"/>
     </row>
     <row r="305">
-      <c r="A305" s="1"/>
+      <c r="A305" s="2"/>
       <c r="B305" s="7"/>
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
@@ -8241,7 +8246,7 @@
       <c r="W305" s="7"/>
     </row>
     <row r="306">
-      <c r="A306" s="1"/>
+      <c r="A306" s="2"/>
       <c r="B306" s="7"/>
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
@@ -8266,7 +8271,7 @@
       <c r="W306" s="7"/>
     </row>
     <row r="307">
-      <c r="A307" s="1"/>
+      <c r="A307" s="2"/>
       <c r="B307" s="7"/>
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
@@ -8291,7 +8296,7 @@
       <c r="W307" s="7"/>
     </row>
     <row r="308">
-      <c r="A308" s="1"/>
+      <c r="A308" s="2"/>
       <c r="B308" s="7"/>
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
@@ -8316,7 +8321,7 @@
       <c r="W308" s="7"/>
     </row>
     <row r="309">
-      <c r="A309" s="1"/>
+      <c r="A309" s="2"/>
       <c r="B309" s="7"/>
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
@@ -8341,7 +8346,7 @@
       <c r="W309" s="7"/>
     </row>
     <row r="310">
-      <c r="A310" s="1"/>
+      <c r="A310" s="2"/>
       <c r="B310" s="7"/>
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
@@ -8366,7 +8371,7 @@
       <c r="W310" s="7"/>
     </row>
     <row r="311">
-      <c r="A311" s="1"/>
+      <c r="A311" s="2"/>
       <c r="B311" s="7"/>
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
@@ -8391,7 +8396,7 @@
       <c r="W311" s="7"/>
     </row>
     <row r="312">
-      <c r="A312" s="1"/>
+      <c r="A312" s="2"/>
       <c r="B312" s="7"/>
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
@@ -8416,7 +8421,7 @@
       <c r="W312" s="7"/>
     </row>
     <row r="313">
-      <c r="A313" s="1"/>
+      <c r="A313" s="2"/>
       <c r="B313" s="7"/>
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
@@ -8441,7 +8446,7 @@
       <c r="W313" s="7"/>
     </row>
     <row r="314">
-      <c r="A314" s="1"/>
+      <c r="A314" s="2"/>
       <c r="B314" s="7"/>
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
@@ -8466,7 +8471,7 @@
       <c r="W314" s="7"/>
     </row>
     <row r="315">
-      <c r="A315" s="1"/>
+      <c r="A315" s="2"/>
       <c r="B315" s="7"/>
       <c r="C315" s="7"/>
       <c r="D315" s="7"/>
@@ -8491,7 +8496,7 @@
       <c r="W315" s="7"/>
     </row>
     <row r="316">
-      <c r="A316" s="1"/>
+      <c r="A316" s="2"/>
       <c r="B316" s="7"/>
       <c r="C316" s="7"/>
       <c r="D316" s="7"/>
@@ -8516,7 +8521,7 @@
       <c r="W316" s="7"/>
     </row>
     <row r="317">
-      <c r="A317" s="1"/>
+      <c r="A317" s="2"/>
       <c r="B317" s="7"/>
       <c r="C317" s="7"/>
       <c r="D317" s="7"/>
@@ -8541,7 +8546,7 @@
       <c r="W317" s="7"/>
     </row>
     <row r="318">
-      <c r="A318" s="1"/>
+      <c r="A318" s="2"/>
       <c r="B318" s="7"/>
       <c r="C318" s="7"/>
       <c r="D318" s="7"/>
@@ -8566,7 +8571,7 @@
       <c r="W318" s="7"/>
     </row>
     <row r="319">
-      <c r="A319" s="1"/>
+      <c r="A319" s="2"/>
       <c r="B319" s="7"/>
       <c r="C319" s="7"/>
       <c r="D319" s="7"/>
@@ -8591,7 +8596,7 @@
       <c r="W319" s="7"/>
     </row>
     <row r="320">
-      <c r="A320" s="1"/>
+      <c r="A320" s="2"/>
       <c r="B320" s="7"/>
       <c r="C320" s="7"/>
       <c r="D320" s="7"/>
@@ -8616,7 +8621,7 @@
       <c r="W320" s="7"/>
     </row>
     <row r="321">
-      <c r="A321" s="1"/>
+      <c r="A321" s="2"/>
       <c r="B321" s="7"/>
       <c r="C321" s="7"/>
       <c r="D321" s="7"/>
@@ -8641,7 +8646,7 @@
       <c r="W321" s="7"/>
     </row>
     <row r="322">
-      <c r="A322" s="1"/>
+      <c r="A322" s="2"/>
       <c r="B322" s="7"/>
       <c r="C322" s="7"/>
       <c r="D322" s="7"/>
@@ -8666,7 +8671,7 @@
       <c r="W322" s="7"/>
     </row>
     <row r="323">
-      <c r="A323" s="1"/>
+      <c r="A323" s="2"/>
       <c r="B323" s="7"/>
       <c r="C323" s="7"/>
       <c r="D323" s="7"/>
@@ -8691,7 +8696,7 @@
       <c r="W323" s="7"/>
     </row>
     <row r="324">
-      <c r="A324" s="1"/>
+      <c r="A324" s="2"/>
       <c r="B324" s="7"/>
       <c r="C324" s="7"/>
       <c r="D324" s="7"/>
@@ -8716,7 +8721,7 @@
       <c r="W324" s="7"/>
     </row>
     <row r="325">
-      <c r="A325" s="1"/>
+      <c r="A325" s="2"/>
       <c r="B325" s="7"/>
       <c r="C325" s="7"/>
       <c r="D325" s="7"/>
@@ -8741,7 +8746,7 @@
       <c r="W325" s="7"/>
     </row>
     <row r="326">
-      <c r="A326" s="1"/>
+      <c r="A326" s="2"/>
       <c r="B326" s="7"/>
       <c r="C326" s="7"/>
       <c r="D326" s="7"/>
@@ -8766,7 +8771,7 @@
       <c r="W326" s="7"/>
     </row>
     <row r="327">
-      <c r="A327" s="1"/>
+      <c r="A327" s="2"/>
       <c r="B327" s="7"/>
       <c r="C327" s="7"/>
       <c r="D327" s="7"/>
@@ -8791,7 +8796,7 @@
       <c r="W327" s="7"/>
     </row>
     <row r="328">
-      <c r="A328" s="1"/>
+      <c r="A328" s="2"/>
       <c r="B328" s="7"/>
       <c r="C328" s="7"/>
       <c r="D328" s="7"/>
@@ -8816,7 +8821,7 @@
       <c r="W328" s="7"/>
     </row>
     <row r="329">
-      <c r="A329" s="1"/>
+      <c r="A329" s="2"/>
       <c r="B329" s="7"/>
       <c r="C329" s="7"/>
       <c r="D329" s="7"/>
@@ -8841,7 +8846,7 @@
       <c r="W329" s="7"/>
     </row>
     <row r="330">
-      <c r="A330" s="1"/>
+      <c r="A330" s="2"/>
       <c r="B330" s="7"/>
       <c r="C330" s="7"/>
       <c r="D330" s="7"/>
@@ -8866,7 +8871,7 @@
       <c r="W330" s="7"/>
     </row>
     <row r="331">
-      <c r="A331" s="1"/>
+      <c r="A331" s="2"/>
       <c r="B331" s="7"/>
       <c r="C331" s="7"/>
       <c r="D331" s="7"/>
@@ -8891,7 +8896,7 @@
       <c r="W331" s="7"/>
     </row>
     <row r="332">
-      <c r="A332" s="1"/>
+      <c r="A332" s="2"/>
       <c r="B332" s="7"/>
       <c r="C332" s="7"/>
       <c r="D332" s="7"/>
@@ -8916,7 +8921,7 @@
       <c r="W332" s="7"/>
     </row>
     <row r="333">
-      <c r="A333" s="1"/>
+      <c r="A333" s="2"/>
       <c r="B333" s="7"/>
       <c r="C333" s="7"/>
       <c r="D333" s="7"/>
@@ -8941,7 +8946,7 @@
       <c r="W333" s="7"/>
     </row>
     <row r="334">
-      <c r="A334" s="1"/>
+      <c r="A334" s="2"/>
       <c r="B334" s="7"/>
       <c r="C334" s="7"/>
       <c r="D334" s="7"/>
@@ -8966,7 +8971,7 @@
       <c r="W334" s="7"/>
     </row>
     <row r="335">
-      <c r="A335" s="1"/>
+      <c r="A335" s="2"/>
       <c r="B335" s="7"/>
       <c r="C335" s="7"/>
       <c r="D335" s="7"/>
@@ -8991,7 +8996,7 @@
       <c r="W335" s="7"/>
     </row>
     <row r="336">
-      <c r="A336" s="1"/>
+      <c r="A336" s="2"/>
       <c r="B336" s="7"/>
       <c r="C336" s="7"/>
       <c r="D336" s="7"/>
@@ -9016,7 +9021,7 @@
       <c r="W336" s="7"/>
     </row>
     <row r="337">
-      <c r="A337" s="1"/>
+      <c r="A337" s="2"/>
       <c r="B337" s="7"/>
       <c r="C337" s="7"/>
       <c r="D337" s="7"/>
@@ -9041,7 +9046,7 @@
       <c r="W337" s="7"/>
     </row>
     <row r="338">
-      <c r="A338" s="1"/>
+      <c r="A338" s="2"/>
       <c r="B338" s="7"/>
       <c r="C338" s="7"/>
       <c r="D338" s="7"/>
@@ -9066,7 +9071,7 @@
       <c r="W338" s="7"/>
     </row>
     <row r="339">
-      <c r="A339" s="1"/>
+      <c r="A339" s="2"/>
       <c r="B339" s="7"/>
       <c r="C339" s="7"/>
       <c r="D339" s="7"/>
@@ -9091,7 +9096,7 @@
       <c r="W339" s="7"/>
     </row>
     <row r="340">
-      <c r="A340" s="1"/>
+      <c r="A340" s="2"/>
       <c r="B340" s="7"/>
       <c r="C340" s="7"/>
       <c r="D340" s="7"/>
@@ -9116,7 +9121,7 @@
       <c r="W340" s="7"/>
     </row>
     <row r="341">
-      <c r="A341" s="1"/>
+      <c r="A341" s="2"/>
       <c r="B341" s="7"/>
       <c r="C341" s="7"/>
       <c r="D341" s="7"/>
@@ -9141,7 +9146,7 @@
       <c r="W341" s="7"/>
     </row>
     <row r="342">
-      <c r="A342" s="1"/>
+      <c r="A342" s="2"/>
       <c r="B342" s="7"/>
       <c r="C342" s="7"/>
       <c r="D342" s="7"/>
@@ -9166,7 +9171,7 @@
       <c r="W342" s="7"/>
     </row>
     <row r="343">
-      <c r="A343" s="1"/>
+      <c r="A343" s="2"/>
       <c r="B343" s="7"/>
       <c r="C343" s="7"/>
       <c r="D343" s="7"/>
@@ -9191,7 +9196,7 @@
       <c r="W343" s="7"/>
     </row>
     <row r="344">
-      <c r="A344" s="1"/>
+      <c r="A344" s="2"/>
       <c r="B344" s="7"/>
       <c r="C344" s="7"/>
       <c r="D344" s="7"/>
@@ -9216,7 +9221,7 @@
       <c r="W344" s="7"/>
     </row>
     <row r="345">
-      <c r="A345" s="1"/>
+      <c r="A345" s="2"/>
       <c r="B345" s="7"/>
       <c r="C345" s="7"/>
       <c r="D345" s="7"/>
@@ -9241,7 +9246,7 @@
       <c r="W345" s="7"/>
     </row>
     <row r="346">
-      <c r="A346" s="1"/>
+      <c r="A346" s="2"/>
       <c r="B346" s="7"/>
       <c r="C346" s="7"/>
       <c r="D346" s="7"/>
@@ -9266,7 +9271,7 @@
       <c r="W346" s="7"/>
     </row>
     <row r="347">
-      <c r="A347" s="1"/>
+      <c r="A347" s="2"/>
       <c r="B347" s="7"/>
       <c r="C347" s="7"/>
       <c r="D347" s="7"/>
@@ -9291,7 +9296,7 @@
       <c r="W347" s="7"/>
     </row>
     <row r="348">
-      <c r="A348" s="1"/>
+      <c r="A348" s="2"/>
       <c r="B348" s="7"/>
       <c r="C348" s="7"/>
       <c r="D348" s="7"/>
@@ -9316,7 +9321,7 @@
       <c r="W348" s="7"/>
     </row>
     <row r="349">
-      <c r="A349" s="1"/>
+      <c r="A349" s="2"/>
       <c r="B349" s="7"/>
       <c r="C349" s="7"/>
       <c r="D349" s="7"/>
@@ -9341,7 +9346,7 @@
       <c r="W349" s="7"/>
     </row>
     <row r="350">
-      <c r="A350" s="1"/>
+      <c r="A350" s="2"/>
       <c r="B350" s="7"/>
       <c r="C350" s="7"/>
       <c r="D350" s="7"/>
@@ -9366,7 +9371,7 @@
       <c r="W350" s="7"/>
     </row>
     <row r="351">
-      <c r="A351" s="1"/>
+      <c r="A351" s="2"/>
       <c r="B351" s="7"/>
       <c r="C351" s="7"/>
       <c r="D351" s="7"/>
@@ -9391,7 +9396,7 @@
       <c r="W351" s="7"/>
     </row>
     <row r="352">
-      <c r="A352" s="1"/>
+      <c r="A352" s="2"/>
       <c r="B352" s="7"/>
       <c r="C352" s="7"/>
       <c r="D352" s="7"/>
@@ -9416,7 +9421,7 @@
       <c r="W352" s="7"/>
     </row>
     <row r="353">
-      <c r="A353" s="1"/>
+      <c r="A353" s="2"/>
       <c r="B353" s="7"/>
       <c r="C353" s="7"/>
       <c r="D353" s="7"/>
@@ -9441,7 +9446,7 @@
       <c r="W353" s="7"/>
     </row>
     <row r="354">
-      <c r="A354" s="1"/>
+      <c r="A354" s="2"/>
       <c r="B354" s="7"/>
       <c r="C354" s="7"/>
       <c r="D354" s="7"/>
@@ -9466,7 +9471,7 @@
       <c r="W354" s="7"/>
     </row>
     <row r="355">
-      <c r="A355" s="1"/>
+      <c r="A355" s="2"/>
       <c r="B355" s="7"/>
       <c r="C355" s="7"/>
       <c r="D355" s="7"/>
@@ -9491,7 +9496,7 @@
       <c r="W355" s="7"/>
     </row>
     <row r="356">
-      <c r="A356" s="1"/>
+      <c r="A356" s="2"/>
       <c r="B356" s="7"/>
       <c r="C356" s="7"/>
       <c r="D356" s="7"/>
@@ -9516,7 +9521,7 @@
       <c r="W356" s="7"/>
     </row>
     <row r="357">
-      <c r="A357" s="1"/>
+      <c r="A357" s="2"/>
       <c r="B357" s="7"/>
       <c r="C357" s="7"/>
       <c r="D357" s="7"/>
@@ -9541,7 +9546,7 @@
       <c r="W357" s="7"/>
     </row>
     <row r="358">
-      <c r="A358" s="1"/>
+      <c r="A358" s="2"/>
       <c r="B358" s="7"/>
       <c r="C358" s="7"/>
       <c r="D358" s="7"/>
@@ -9566,7 +9571,7 @@
       <c r="W358" s="7"/>
     </row>
     <row r="359">
-      <c r="A359" s="1"/>
+      <c r="A359" s="2"/>
       <c r="B359" s="7"/>
       <c r="C359" s="7"/>
       <c r="D359" s="7"/>
@@ -9591,7 +9596,7 @@
       <c r="W359" s="7"/>
     </row>
     <row r="360">
-      <c r="A360" s="1"/>
+      <c r="A360" s="2"/>
       <c r="B360" s="7"/>
       <c r="C360" s="7"/>
       <c r="D360" s="7"/>
@@ -9616,7 +9621,7 @@
       <c r="W360" s="7"/>
     </row>
     <row r="361">
-      <c r="A361" s="1"/>
+      <c r="A361" s="2"/>
       <c r="B361" s="7"/>
       <c r="C361" s="7"/>
       <c r="D361" s="7"/>
@@ -9641,7 +9646,7 @@
       <c r="W361" s="7"/>
     </row>
     <row r="362">
-      <c r="A362" s="1"/>
+      <c r="A362" s="2"/>
       <c r="B362" s="7"/>
       <c r="C362" s="7"/>
       <c r="D362" s="7"/>
@@ -9666,7 +9671,7 @@
       <c r="W362" s="7"/>
     </row>
     <row r="363">
-      <c r="A363" s="1"/>
+      <c r="A363" s="2"/>
       <c r="B363" s="7"/>
       <c r="C363" s="7"/>
       <c r="D363" s="7"/>
@@ -9691,7 +9696,7 @@
       <c r="W363" s="7"/>
     </row>
     <row r="364">
-      <c r="A364" s="1"/>
+      <c r="A364" s="2"/>
       <c r="B364" s="7"/>
       <c r="C364" s="7"/>
       <c r="D364" s="7"/>
@@ -9716,7 +9721,7 @@
       <c r="W364" s="7"/>
     </row>
     <row r="365">
-      <c r="A365" s="1"/>
+      <c r="A365" s="2"/>
       <c r="B365" s="7"/>
       <c r="C365" s="7"/>
       <c r="D365" s="7"/>
@@ -9741,7 +9746,7 @@
       <c r="W365" s="7"/>
     </row>
     <row r="366">
-      <c r="A366" s="1"/>
+      <c r="A366" s="2"/>
       <c r="B366" s="7"/>
       <c r="C366" s="7"/>
       <c r="D366" s="7"/>
@@ -9766,7 +9771,7 @@
       <c r="W366" s="7"/>
     </row>
     <row r="367">
-      <c r="A367" s="1"/>
+      <c r="A367" s="2"/>
       <c r="B367" s="7"/>
       <c r="C367" s="7"/>
       <c r="D367" s="7"/>
@@ -9791,7 +9796,7 @@
       <c r="W367" s="7"/>
     </row>
     <row r="368">
-      <c r="A368" s="1"/>
+      <c r="A368" s="2"/>
       <c r="B368" s="7"/>
       <c r="C368" s="7"/>
       <c r="D368" s="7"/>
@@ -9816,7 +9821,7 @@
       <c r="W368" s="7"/>
     </row>
     <row r="369">
-      <c r="A369" s="1"/>
+      <c r="A369" s="2"/>
       <c r="B369" s="7"/>
       <c r="C369" s="7"/>
       <c r="D369" s="7"/>
@@ -9841,7 +9846,7 @@
       <c r="W369" s="7"/>
     </row>
     <row r="370">
-      <c r="A370" s="1"/>
+      <c r="A370" s="2"/>
       <c r="B370" s="7"/>
       <c r="C370" s="7"/>
       <c r="D370" s="7"/>
@@ -9866,7 +9871,7 @@
       <c r="W370" s="7"/>
     </row>
     <row r="371">
-      <c r="A371" s="1"/>
+      <c r="A371" s="2"/>
       <c r="B371" s="7"/>
       <c r="C371" s="7"/>
       <c r="D371" s="7"/>
@@ -9891,7 +9896,7 @@
       <c r="W371" s="7"/>
     </row>
     <row r="372">
-      <c r="A372" s="1"/>
+      <c r="A372" s="2"/>
       <c r="B372" s="7"/>
       <c r="C372" s="7"/>
       <c r="D372" s="7"/>
@@ -9916,7 +9921,7 @@
       <c r="W372" s="7"/>
     </row>
     <row r="373">
-      <c r="A373" s="1"/>
+      <c r="A373" s="2"/>
       <c r="B373" s="7"/>
       <c r="C373" s="7"/>
       <c r="D373" s="7"/>
@@ -9941,7 +9946,7 @@
       <c r="W373" s="7"/>
     </row>
     <row r="374">
-      <c r="A374" s="1"/>
+      <c r="A374" s="2"/>
       <c r="B374" s="7"/>
       <c r="C374" s="7"/>
       <c r="D374" s="7"/>
@@ -9966,7 +9971,7 @@
       <c r="W374" s="7"/>
     </row>
     <row r="375">
-      <c r="A375" s="1"/>
+      <c r="A375" s="2"/>
       <c r="B375" s="7"/>
       <c r="C375" s="7"/>
       <c r="D375" s="7"/>
@@ -9991,7 +9996,7 @@
       <c r="W375" s="7"/>
     </row>
     <row r="376">
-      <c r="A376" s="1"/>
+      <c r="A376" s="2"/>
       <c r="B376" s="7"/>
       <c r="C376" s="7"/>
       <c r="D376" s="7"/>
@@ -10016,7 +10021,7 @@
       <c r="W376" s="7"/>
     </row>
     <row r="377">
-      <c r="A377" s="1"/>
+      <c r="A377" s="2"/>
       <c r="B377" s="7"/>
       <c r="C377" s="7"/>
       <c r="D377" s="7"/>
@@ -10041,7 +10046,7 @@
       <c r="W377" s="7"/>
     </row>
     <row r="378">
-      <c r="A378" s="1"/>
+      <c r="A378" s="2"/>
       <c r="B378" s="7"/>
       <c r="C378" s="7"/>
       <c r="D378" s="7"/>
@@ -10066,7 +10071,7 @@
       <c r="W378" s="7"/>
     </row>
     <row r="379">
-      <c r="A379" s="1"/>
+      <c r="A379" s="2"/>
       <c r="B379" s="7"/>
       <c r="C379" s="7"/>
       <c r="D379" s="7"/>
@@ -10091,7 +10096,7 @@
       <c r="W379" s="7"/>
     </row>
     <row r="380">
-      <c r="A380" s="1"/>
+      <c r="A380" s="2"/>
       <c r="B380" s="7"/>
       <c r="C380" s="7"/>
       <c r="D380" s="7"/>
@@ -10116,7 +10121,7 @@
       <c r="W380" s="7"/>
     </row>
     <row r="381">
-      <c r="A381" s="1"/>
+      <c r="A381" s="2"/>
       <c r="B381" s="7"/>
       <c r="C381" s="7"/>
       <c r="D381" s="7"/>
@@ -10141,7 +10146,7 @@
       <c r="W381" s="7"/>
     </row>
     <row r="382">
-      <c r="A382" s="1"/>
+      <c r="A382" s="2"/>
       <c r="B382" s="7"/>
       <c r="C382" s="7"/>
       <c r="D382" s="7"/>
@@ -10166,7 +10171,7 @@
       <c r="W382" s="7"/>
     </row>
     <row r="383">
-      <c r="A383" s="1"/>
+      <c r="A383" s="2"/>
       <c r="B383" s="7"/>
       <c r="C383" s="7"/>
       <c r="D383" s="7"/>
@@ -10191,7 +10196,7 @@
       <c r="W383" s="7"/>
     </row>
     <row r="384">
-      <c r="A384" s="1"/>
+      <c r="A384" s="2"/>
       <c r="B384" s="7"/>
       <c r="C384" s="7"/>
       <c r="D384" s="7"/>
@@ -10216,7 +10221,7 @@
       <c r="W384" s="7"/>
     </row>
     <row r="385">
-      <c r="A385" s="1"/>
+      <c r="A385" s="2"/>
       <c r="B385" s="7"/>
       <c r="C385" s="7"/>
       <c r="D385" s="7"/>
@@ -10241,7 +10246,7 @@
       <c r="W385" s="7"/>
     </row>
     <row r="386">
-      <c r="A386" s="1"/>
+      <c r="A386" s="2"/>
       <c r="B386" s="7"/>
       <c r="C386" s="7"/>
       <c r="D386" s="7"/>
@@ -10266,7 +10271,7 @@
       <c r="W386" s="7"/>
     </row>
     <row r="387">
-      <c r="A387" s="1"/>
+      <c r="A387" s="2"/>
       <c r="B387" s="7"/>
       <c r="C387" s="7"/>
       <c r="D387" s="7"/>
@@ -10291,7 +10296,7 @@
       <c r="W387" s="7"/>
     </row>
     <row r="388">
-      <c r="A388" s="1"/>
+      <c r="A388" s="2"/>
       <c r="B388" s="7"/>
       <c r="C388" s="7"/>
       <c r="D388" s="7"/>
@@ -10316,7 +10321,7 @@
       <c r="W388" s="7"/>
     </row>
     <row r="389">
-      <c r="A389" s="1"/>
+      <c r="A389" s="2"/>
       <c r="B389" s="7"/>
       <c r="C389" s="7"/>
       <c r="D389" s="7"/>
@@ -10341,7 +10346,7 @@
       <c r="W389" s="7"/>
     </row>
     <row r="390">
-      <c r="A390" s="1"/>
+      <c r="A390" s="2"/>
       <c r="B390" s="7"/>
       <c r="C390" s="7"/>
       <c r="D390" s="7"/>
@@ -10366,7 +10371,7 @@
       <c r="W390" s="7"/>
     </row>
     <row r="391">
-      <c r="A391" s="1"/>
+      <c r="A391" s="2"/>
       <c r="B391" s="7"/>
       <c r="C391" s="7"/>
       <c r="D391" s="7"/>
@@ -10391,7 +10396,7 @@
       <c r="W391" s="7"/>
     </row>
     <row r="392">
-      <c r="A392" s="1"/>
+      <c r="A392" s="2"/>
       <c r="B392" s="7"/>
       <c r="C392" s="7"/>
       <c r="D392" s="7"/>
@@ -10416,7 +10421,7 @@
       <c r="W392" s="7"/>
     </row>
     <row r="393">
-      <c r="A393" s="1"/>
+      <c r="A393" s="2"/>
       <c r="B393" s="7"/>
       <c r="C393" s="7"/>
       <c r="D393" s="7"/>
@@ -10441,7 +10446,7 @@
       <c r="W393" s="7"/>
     </row>
     <row r="394">
-      <c r="A394" s="1"/>
+      <c r="A394" s="2"/>
       <c r="B394" s="7"/>
       <c r="C394" s="7"/>
       <c r="D394" s="7"/>
@@ -10466,7 +10471,7 @@
       <c r="W394" s="7"/>
     </row>
     <row r="395">
-      <c r="A395" s="1"/>
+      <c r="A395" s="2"/>
       <c r="B395" s="7"/>
       <c r="C395" s="7"/>
       <c r="D395" s="7"/>
@@ -10491,7 +10496,7 @@
       <c r="W395" s="7"/>
     </row>
     <row r="396">
-      <c r="A396" s="1"/>
+      <c r="A396" s="2"/>
       <c r="B396" s="7"/>
       <c r="C396" s="7"/>
       <c r="D396" s="7"/>
@@ -10516,7 +10521,7 @@
       <c r="W396" s="7"/>
     </row>
     <row r="397">
-      <c r="A397" s="1"/>
+      <c r="A397" s="2"/>
       <c r="B397" s="7"/>
       <c r="C397" s="7"/>
       <c r="D397" s="7"/>
@@ -10541,7 +10546,7 @@
       <c r="W397" s="7"/>
     </row>
     <row r="398">
-      <c r="A398" s="1"/>
+      <c r="A398" s="2"/>
       <c r="B398" s="7"/>
       <c r="C398" s="7"/>
       <c r="D398" s="7"/>
@@ -10566,7 +10571,7 @@
       <c r="W398" s="7"/>
     </row>
     <row r="399">
-      <c r="A399" s="1"/>
+      <c r="A399" s="2"/>
       <c r="B399" s="7"/>
       <c r="C399" s="7"/>
       <c r="D399" s="7"/>
@@ -10591,7 +10596,7 @@
       <c r="W399" s="7"/>
     </row>
     <row r="400">
-      <c r="A400" s="1"/>
+      <c r="A400" s="2"/>
       <c r="B400" s="7"/>
       <c r="C400" s="7"/>
       <c r="D400" s="7"/>
@@ -10616,7 +10621,7 @@
       <c r="W400" s="7"/>
     </row>
     <row r="401">
-      <c r="A401" s="1"/>
+      <c r="A401" s="2"/>
       <c r="B401" s="7"/>
       <c r="C401" s="7"/>
       <c r="D401" s="7"/>
@@ -10641,7 +10646,7 @@
       <c r="W401" s="7"/>
     </row>
     <row r="402">
-      <c r="A402" s="1"/>
+      <c r="A402" s="2"/>
       <c r="B402" s="7"/>
       <c r="C402" s="7"/>
       <c r="D402" s="7"/>
@@ -10666,7 +10671,7 @@
       <c r="W402" s="7"/>
     </row>
     <row r="403">
-      <c r="A403" s="1"/>
+      <c r="A403" s="2"/>
       <c r="B403" s="7"/>
       <c r="C403" s="7"/>
       <c r="D403" s="7"/>
@@ -10691,7 +10696,7 @@
       <c r="W403" s="7"/>
     </row>
     <row r="404">
-      <c r="A404" s="1"/>
+      <c r="A404" s="2"/>
       <c r="B404" s="7"/>
       <c r="C404" s="7"/>
       <c r="D404" s="7"/>
@@ -10716,7 +10721,7 @@
       <c r="W404" s="7"/>
     </row>
     <row r="405">
-      <c r="A405" s="1"/>
+      <c r="A405" s="2"/>
       <c r="B405" s="7"/>
       <c r="C405" s="7"/>
       <c r="D405" s="7"/>
@@ -10741,7 +10746,7 @@
       <c r="W405" s="7"/>
     </row>
     <row r="406">
-      <c r="A406" s="1"/>
+      <c r="A406" s="2"/>
       <c r="B406" s="7"/>
       <c r="C406" s="7"/>
       <c r="D406" s="7"/>
@@ -10766,7 +10771,7 @@
       <c r="W406" s="7"/>
     </row>
     <row r="407">
-      <c r="A407" s="1"/>
+      <c r="A407" s="2"/>
       <c r="B407" s="7"/>
       <c r="C407" s="7"/>
       <c r="D407" s="7"/>
@@ -10791,7 +10796,7 @@
       <c r="W407" s="7"/>
     </row>
     <row r="408">
-      <c r="A408" s="1"/>
+      <c r="A408" s="2"/>
       <c r="B408" s="7"/>
       <c r="C408" s="7"/>
       <c r="D408" s="7"/>
@@ -10816,7 +10821,7 @@
       <c r="W408" s="7"/>
     </row>
     <row r="409">
-      <c r="A409" s="1"/>
+      <c r="A409" s="2"/>
       <c r="B409" s="7"/>
       <c r="C409" s="7"/>
       <c r="D409" s="7"/>
@@ -10841,7 +10846,7 @@
       <c r="W409" s="7"/>
     </row>
     <row r="410">
-      <c r="A410" s="1"/>
+      <c r="A410" s="2"/>
       <c r="B410" s="7"/>
       <c r="C410" s="7"/>
       <c r="D410" s="7"/>
@@ -10866,7 +10871,7 @@
       <c r="W410" s="7"/>
     </row>
     <row r="411">
-      <c r="A411" s="1"/>
+      <c r="A411" s="2"/>
       <c r="B411" s="7"/>
       <c r="C411" s="7"/>
       <c r="D411" s="7"/>
@@ -10891,7 +10896,7 @@
       <c r="W411" s="7"/>
     </row>
     <row r="412">
-      <c r="A412" s="1"/>
+      <c r="A412" s="2"/>
       <c r="B412" s="7"/>
       <c r="C412" s="7"/>
       <c r="D412" s="7"/>
@@ -10916,7 +10921,7 @@
       <c r="W412" s="7"/>
     </row>
     <row r="413">
-      <c r="A413" s="1"/>
+      <c r="A413" s="2"/>
       <c r="B413" s="7"/>
       <c r="C413" s="7"/>
       <c r="D413" s="7"/>
@@ -10941,7 +10946,7 @@
       <c r="W413" s="7"/>
     </row>
     <row r="414">
-      <c r="A414" s="1"/>
+      <c r="A414" s="2"/>
       <c r="B414" s="7"/>
       <c r="C414" s="7"/>
       <c r="D414" s="7"/>
@@ -10966,7 +10971,7 @@
       <c r="W414" s="7"/>
     </row>
     <row r="415">
-      <c r="A415" s="1"/>
+      <c r="A415" s="2"/>
       <c r="B415" s="7"/>
       <c r="C415" s="7"/>
       <c r="D415" s="7"/>
@@ -10991,7 +10996,7 @@
       <c r="W415" s="7"/>
     </row>
     <row r="416">
-      <c r="A416" s="1"/>
+      <c r="A416" s="2"/>
       <c r="B416" s="7"/>
       <c r="C416" s="7"/>
       <c r="D416" s="7"/>
@@ -11016,7 +11021,7 @@
       <c r="W416" s="7"/>
     </row>
     <row r="417">
-      <c r="A417" s="1"/>
+      <c r="A417" s="2"/>
       <c r="B417" s="7"/>
       <c r="C417" s="7"/>
       <c r="D417" s="7"/>
@@ -11041,7 +11046,7 @@
       <c r="W417" s="7"/>
     </row>
     <row r="418">
-      <c r="A418" s="1"/>
+      <c r="A418" s="2"/>
       <c r="B418" s="7"/>
       <c r="C418" s="7"/>
       <c r="D418" s="7"/>
@@ -11066,7 +11071,7 @@
       <c r="W418" s="7"/>
     </row>
     <row r="419">
-      <c r="A419" s="1"/>
+      <c r="A419" s="2"/>
       <c r="B419" s="7"/>
       <c r="C419" s="7"/>
       <c r="D419" s="7"/>
@@ -11091,7 +11096,7 @@
       <c r="W419" s="7"/>
     </row>
     <row r="420">
-      <c r="A420" s="1"/>
+      <c r="A420" s="2"/>
       <c r="B420" s="7"/>
       <c r="C420" s="7"/>
       <c r="D420" s="7"/>
@@ -11116,7 +11121,7 @@
       <c r="W420" s="7"/>
     </row>
     <row r="421">
-      <c r="A421" s="1"/>
+      <c r="A421" s="2"/>
       <c r="B421" s="7"/>
       <c r="C421" s="7"/>
       <c r="D421" s="7"/>
@@ -11141,7 +11146,7 @@
       <c r="W421" s="7"/>
     </row>
     <row r="422">
-      <c r="A422" s="1"/>
+      <c r="A422" s="2"/>
       <c r="B422" s="7"/>
       <c r="C422" s="7"/>
       <c r="D422" s="7"/>
@@ -11166,7 +11171,7 @@
       <c r="W422" s="7"/>
     </row>
     <row r="423">
-      <c r="A423" s="1"/>
+      <c r="A423" s="2"/>
       <c r="B423" s="7"/>
       <c r="C423" s="7"/>
       <c r="D423" s="7"/>
@@ -11191,7 +11196,7 @@
       <c r="W423" s="7"/>
     </row>
     <row r="424">
-      <c r="A424" s="1"/>
+      <c r="A424" s="2"/>
       <c r="B424" s="7"/>
       <c r="C424" s="7"/>
       <c r="D424" s="7"/>
@@ -11216,7 +11221,7 @@
       <c r="W424" s="7"/>
     </row>
     <row r="425">
-      <c r="A425" s="1"/>
+      <c r="A425" s="2"/>
       <c r="B425" s="7"/>
       <c r="C425" s="7"/>
       <c r="D425" s="7"/>
@@ -11241,7 +11246,7 @@
       <c r="W425" s="7"/>
     </row>
     <row r="426">
-      <c r="A426" s="1"/>
+      <c r="A426" s="2"/>
       <c r="B426" s="7"/>
       <c r="C426" s="7"/>
       <c r="D426" s="7"/>
@@ -11266,7 +11271,7 @@
       <c r="W426" s="7"/>
     </row>
     <row r="427">
-      <c r="A427" s="1"/>
+      <c r="A427" s="2"/>
       <c r="B427" s="7"/>
       <c r="C427" s="7"/>
       <c r="D427" s="7"/>
@@ -11291,7 +11296,7 @@
       <c r="W427" s="7"/>
     </row>
     <row r="428">
-      <c r="A428" s="1"/>
+      <c r="A428" s="2"/>
       <c r="B428" s="7"/>
       <c r="C428" s="7"/>
       <c r="D428" s="7"/>
@@ -11316,7 +11321,7 @@
       <c r="W428" s="7"/>
     </row>
     <row r="429">
-      <c r="A429" s="1"/>
+      <c r="A429" s="2"/>
       <c r="B429" s="7"/>
       <c r="C429" s="7"/>
       <c r="D429" s="7"/>
@@ -11341,7 +11346,7 @@
       <c r="W429" s="7"/>
     </row>
     <row r="430">
-      <c r="A430" s="1"/>
+      <c r="A430" s="2"/>
       <c r="B430" s="7"/>
       <c r="C430" s="7"/>
       <c r="D430" s="7"/>
@@ -11366,7 +11371,7 @@
       <c r="W430" s="7"/>
     </row>
     <row r="431">
-      <c r="A431" s="1"/>
+      <c r="A431" s="2"/>
       <c r="B431" s="7"/>
       <c r="C431" s="7"/>
       <c r="D431" s="7"/>
@@ -11391,7 +11396,7 @@
       <c r="W431" s="7"/>
     </row>
     <row r="432">
-      <c r="A432" s="1"/>
+      <c r="A432" s="2"/>
       <c r="B432" s="7"/>
       <c r="C432" s="7"/>
       <c r="D432" s="7"/>
@@ -11416,7 +11421,7 @@
       <c r="W432" s="7"/>
     </row>
     <row r="433">
-      <c r="A433" s="1"/>
+      <c r="A433" s="2"/>
       <c r="B433" s="7"/>
       <c r="C433" s="7"/>
       <c r="D433" s="7"/>
@@ -11441,7 +11446,7 @@
       <c r="W433" s="7"/>
     </row>
     <row r="434">
-      <c r="A434" s="1"/>
+      <c r="A434" s="2"/>
       <c r="B434" s="7"/>
       <c r="C434" s="7"/>
       <c r="D434" s="7"/>
@@ -11466,7 +11471,7 @@
       <c r="W434" s="7"/>
     </row>
     <row r="435">
-      <c r="A435" s="1"/>
+      <c r="A435" s="2"/>
       <c r="B435" s="7"/>
       <c r="C435" s="7"/>
       <c r="D435" s="7"/>
@@ -11491,7 +11496,7 @@
       <c r="W435" s="7"/>
     </row>
     <row r="436">
-      <c r="A436" s="1"/>
+      <c r="A436" s="2"/>
       <c r="B436" s="7"/>
       <c r="C436" s="7"/>
       <c r="D436" s="7"/>
@@ -11516,7 +11521,7 @@
       <c r="W436" s="7"/>
     </row>
     <row r="437">
-      <c r="A437" s="1"/>
+      <c r="A437" s="2"/>
       <c r="B437" s="7"/>
       <c r="C437" s="7"/>
       <c r="D437" s="7"/>
@@ -11541,7 +11546,7 @@
       <c r="W437" s="7"/>
     </row>
     <row r="438">
-      <c r="A438" s="1"/>
+      <c r="A438" s="2"/>
       <c r="B438" s="7"/>
       <c r="C438" s="7"/>
       <c r="D438" s="7"/>
@@ -11566,7 +11571,7 @@
       <c r="W438" s="7"/>
     </row>
     <row r="439">
-      <c r="A439" s="1"/>
+      <c r="A439" s="2"/>
       <c r="B439" s="7"/>
       <c r="C439" s="7"/>
       <c r="D439" s="7"/>
@@ -11591,7 +11596,7 @@
       <c r="W439" s="7"/>
     </row>
     <row r="440">
-      <c r="A440" s="1"/>
+      <c r="A440" s="2"/>
       <c r="B440" s="7"/>
       <c r="C440" s="7"/>
       <c r="D440" s="7"/>
@@ -11616,7 +11621,7 @@
       <c r="W440" s="7"/>
     </row>
     <row r="441">
-      <c r="A441" s="1"/>
+      <c r="A441" s="2"/>
       <c r="B441" s="7"/>
       <c r="C441" s="7"/>
       <c r="D441" s="7"/>
@@ -11641,7 +11646,7 @@
       <c r="W441" s="7"/>
     </row>
     <row r="442">
-      <c r="A442" s="1"/>
+      <c r="A442" s="2"/>
       <c r="B442" s="7"/>
       <c r="C442" s="7"/>
       <c r="D442" s="7"/>
@@ -11666,7 +11671,7 @@
       <c r="W442" s="7"/>
     </row>
     <row r="443">
-      <c r="A443" s="1"/>
+      <c r="A443" s="2"/>
       <c r="B443" s="7"/>
       <c r="C443" s="7"/>
       <c r="D443" s="7"/>
@@ -11691,7 +11696,7 @@
       <c r="W443" s="7"/>
     </row>
     <row r="444">
-      <c r="A444" s="1"/>
+      <c r="A444" s="2"/>
       <c r="B444" s="7"/>
       <c r="C444" s="7"/>
       <c r="D444" s="7"/>
@@ -11716,7 +11721,7 @@
       <c r="W444" s="7"/>
     </row>
     <row r="445">
-      <c r="A445" s="1"/>
+      <c r="A445" s="2"/>
       <c r="B445" s="7"/>
       <c r="C445" s="7"/>
       <c r="D445" s="7"/>
@@ -11741,7 +11746,7 @@
       <c r="W445" s="7"/>
     </row>
     <row r="446">
-      <c r="A446" s="1"/>
+      <c r="A446" s="2"/>
       <c r="B446" s="7"/>
       <c r="C446" s="7"/>
       <c r="D446" s="7"/>
@@ -11766,7 +11771,7 @@
       <c r="W446" s="7"/>
     </row>
     <row r="447">
-      <c r="A447" s="1"/>
+      <c r="A447" s="2"/>
       <c r="B447" s="7"/>
       <c r="C447" s="7"/>
       <c r="D447" s="7"/>
@@ -11791,7 +11796,7 @@
       <c r="W447" s="7"/>
     </row>
     <row r="448">
-      <c r="A448" s="1"/>
+      <c r="A448" s="2"/>
       <c r="B448" s="7"/>
       <c r="C448" s="7"/>
       <c r="D448" s="7"/>
@@ -11816,7 +11821,7 @@
       <c r="W448" s="7"/>
     </row>
     <row r="449">
-      <c r="A449" s="1"/>
+      <c r="A449" s="2"/>
       <c r="B449" s="7"/>
       <c r="C449" s="7"/>
       <c r="D449" s="7"/>
@@ -11841,7 +11846,7 @@
       <c r="W449" s="7"/>
     </row>
     <row r="450">
-      <c r="A450" s="1"/>
+      <c r="A450" s="2"/>
       <c r="B450" s="7"/>
       <c r="C450" s="7"/>
       <c r="D450" s="7"/>
@@ -11866,7 +11871,7 @@
       <c r="W450" s="7"/>
     </row>
     <row r="451">
-      <c r="A451" s="1"/>
+      <c r="A451" s="2"/>
       <c r="B451" s="7"/>
       <c r="C451" s="7"/>
       <c r="D451" s="7"/>
@@ -11891,7 +11896,7 @@
       <c r="W451" s="7"/>
     </row>
     <row r="452">
-      <c r="A452" s="1"/>
+      <c r="A452" s="2"/>
       <c r="B452" s="7"/>
       <c r="C452" s="7"/>
       <c r="D452" s="7"/>
@@ -11916,7 +11921,7 @@
       <c r="W452" s="7"/>
     </row>
     <row r="453">
-      <c r="A453" s="1"/>
+      <c r="A453" s="2"/>
       <c r="B453" s="7"/>
       <c r="C453" s="7"/>
       <c r="D453" s="7"/>
@@ -11941,7 +11946,7 @@
       <c r="W453" s="7"/>
     </row>
     <row r="454">
-      <c r="A454" s="1"/>
+      <c r="A454" s="2"/>
       <c r="B454" s="7"/>
       <c r="C454" s="7"/>
       <c r="D454" s="7"/>
@@ -11966,7 +11971,7 @@
       <c r="W454" s="7"/>
     </row>
     <row r="455">
-      <c r="A455" s="1"/>
+      <c r="A455" s="2"/>
       <c r="B455" s="7"/>
       <c r="C455" s="7"/>
       <c r="D455" s="7"/>
@@ -11991,7 +11996,7 @@
       <c r="W455" s="7"/>
     </row>
     <row r="456">
-      <c r="A456" s="1"/>
+      <c r="A456" s="2"/>
       <c r="B456" s="7"/>
       <c r="C456" s="7"/>
       <c r="D456" s="7"/>
@@ -12016,7 +12021,7 @@
       <c r="W456" s="7"/>
     </row>
     <row r="457">
-      <c r="A457" s="1"/>
+      <c r="A457" s="2"/>
       <c r="B457" s="7"/>
       <c r="C457" s="7"/>
       <c r="D457" s="7"/>
@@ -12041,7 +12046,7 @@
       <c r="W457" s="7"/>
     </row>
     <row r="458">
-      <c r="A458" s="1"/>
+      <c r="A458" s="2"/>
       <c r="B458" s="7"/>
       <c r="C458" s="7"/>
       <c r="D458" s="7"/>
@@ -12066,7 +12071,7 @@
       <c r="W458" s="7"/>
     </row>
     <row r="459">
-      <c r="A459" s="1"/>
+      <c r="A459" s="2"/>
       <c r="B459" s="7"/>
       <c r="C459" s="7"/>
       <c r="D459" s="7"/>
@@ -12091,7 +12096,7 @@
       <c r="W459" s="7"/>
     </row>
     <row r="460">
-      <c r="A460" s="1"/>
+      <c r="A460" s="2"/>
       <c r="B460" s="7"/>
       <c r="C460" s="7"/>
       <c r="D460" s="7"/>
@@ -12116,7 +12121,7 @@
       <c r="W460" s="7"/>
     </row>
     <row r="461">
-      <c r="A461" s="1"/>
+      <c r="A461" s="2"/>
       <c r="B461" s="7"/>
       <c r="C461" s="7"/>
       <c r="D461" s="7"/>
@@ -12141,7 +12146,7 @@
       <c r="W461" s="7"/>
     </row>
     <row r="462">
-      <c r="A462" s="1"/>
+      <c r="A462" s="2"/>
       <c r="B462" s="7"/>
       <c r="C462" s="7"/>
       <c r="D462" s="7"/>
@@ -12166,7 +12171,7 @@
       <c r="W462" s="7"/>
     </row>
     <row r="463">
-      <c r="A463" s="1"/>
+      <c r="A463" s="2"/>
       <c r="B463" s="7"/>
       <c r="C463" s="7"/>
       <c r="D463" s="7"/>
@@ -12191,7 +12196,7 @@
       <c r="W463" s="7"/>
     </row>
     <row r="464">
-      <c r="A464" s="1"/>
+      <c r="A464" s="2"/>
       <c r="B464" s="7"/>
       <c r="C464" s="7"/>
       <c r="D464" s="7"/>
@@ -12216,7 +12221,7 @@
       <c r="W464" s="7"/>
     </row>
     <row r="465">
-      <c r="A465" s="1"/>
+      <c r="A465" s="2"/>
       <c r="B465" s="7"/>
       <c r="C465" s="7"/>
       <c r="D465" s="7"/>
@@ -12241,7 +12246,7 @@
       <c r="W465" s="7"/>
     </row>
     <row r="466">
-      <c r="A466" s="1"/>
+      <c r="A466" s="2"/>
       <c r="B466" s="7"/>
       <c r="C466" s="7"/>
       <c r="D466" s="7"/>
@@ -12266,7 +12271,7 @@
       <c r="W466" s="7"/>
     </row>
     <row r="467">
-      <c r="A467" s="1"/>
+      <c r="A467" s="2"/>
       <c r="B467" s="7"/>
       <c r="C467" s="7"/>
       <c r="D467" s="7"/>
@@ -12291,7 +12296,7 @@
       <c r="W467" s="7"/>
     </row>
     <row r="468">
-      <c r="A468" s="1"/>
+      <c r="A468" s="2"/>
       <c r="B468" s="7"/>
       <c r="C468" s="7"/>
       <c r="D468" s="7"/>
@@ -12316,7 +12321,7 @@
       <c r="W468" s="7"/>
     </row>
     <row r="469">
-      <c r="A469" s="1"/>
+      <c r="A469" s="2"/>
       <c r="B469" s="7"/>
       <c r="C469" s="7"/>
       <c r="D469" s="7"/>
@@ -12341,7 +12346,7 @@
       <c r="W469" s="7"/>
     </row>
     <row r="470">
-      <c r="A470" s="1"/>
+      <c r="A470" s="2"/>
       <c r="B470" s="7"/>
       <c r="C470" s="7"/>
       <c r="D470" s="7"/>
@@ -12366,7 +12371,7 @@
       <c r="W470" s="7"/>
     </row>
     <row r="471">
-      <c r="A471" s="1"/>
+      <c r="A471" s="2"/>
       <c r="B471" s="7"/>
       <c r="C471" s="7"/>
       <c r="D471" s="7"/>
@@ -12391,7 +12396,7 @@
       <c r="W471" s="7"/>
     </row>
     <row r="472">
-      <c r="A472" s="1"/>
+      <c r="A472" s="2"/>
       <c r="B472" s="7"/>
       <c r="C472" s="7"/>
       <c r="D472" s="7"/>
@@ -12416,7 +12421,7 @@
       <c r="W472" s="7"/>
     </row>
     <row r="473">
-      <c r="A473" s="1"/>
+      <c r="A473" s="2"/>
       <c r="B473" s="7"/>
       <c r="C473" s="7"/>
       <c r="D473" s="7"/>
@@ -12441,7 +12446,7 @@
       <c r="W473" s="7"/>
     </row>
     <row r="474">
-      <c r="A474" s="1"/>
+      <c r="A474" s="2"/>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
       <c r="D474" s="7"/>
@@ -12466,7 +12471,7 @@
       <c r="W474" s="7"/>
     </row>
     <row r="475">
-      <c r="A475" s="1"/>
+      <c r="A475" s="2"/>
       <c r="B475" s="7"/>
       <c r="C475" s="7"/>
       <c r="D475" s="7"/>
@@ -12491,7 +12496,7 @@
       <c r="W475" s="7"/>
     </row>
     <row r="476">
-      <c r="A476" s="1"/>
+      <c r="A476" s="2"/>
       <c r="B476" s="7"/>
       <c r="C476" s="7"/>
       <c r="D476" s="7"/>
@@ -12516,7 +12521,7 @@
       <c r="W476" s="7"/>
     </row>
     <row r="477">
-      <c r="A477" s="1"/>
+      <c r="A477" s="2"/>
       <c r="B477" s="7"/>
       <c r="C477" s="7"/>
       <c r="D477" s="7"/>
@@ -12541,7 +12546,7 @@
       <c r="W477" s="7"/>
     </row>
     <row r="478">
-      <c r="A478" s="1"/>
+      <c r="A478" s="2"/>
       <c r="B478" s="7"/>
       <c r="C478" s="7"/>
       <c r="D478" s="7"/>
@@ -12566,7 +12571,7 @@
       <c r="W478" s="7"/>
     </row>
     <row r="479">
-      <c r="A479" s="1"/>
+      <c r="A479" s="2"/>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
       <c r="D479" s="7"/>
@@ -12591,7 +12596,7 @@
       <c r="W479" s="7"/>
     </row>
     <row r="480">
-      <c r="A480" s="1"/>
+      <c r="A480" s="2"/>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
       <c r="D480" s="7"/>
@@ -12616,7 +12621,7 @@
       <c r="W480" s="7"/>
     </row>
     <row r="481">
-      <c r="A481" s="1"/>
+      <c r="A481" s="2"/>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
       <c r="D481" s="7"/>
@@ -12641,7 +12646,7 @@
       <c r="W481" s="7"/>
     </row>
     <row r="482">
-      <c r="A482" s="1"/>
+      <c r="A482" s="2"/>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
       <c r="D482" s="7"/>
@@ -12666,7 +12671,7 @@
       <c r="W482" s="7"/>
     </row>
     <row r="483">
-      <c r="A483" s="1"/>
+      <c r="A483" s="2"/>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
       <c r="D483" s="7"/>
@@ -12691,7 +12696,7 @@
       <c r="W483" s="7"/>
     </row>
     <row r="484">
-      <c r="A484" s="1"/>
+      <c r="A484" s="2"/>
       <c r="B484" s="7"/>
       <c r="C484" s="7"/>
       <c r="D484" s="7"/>
@@ -12716,7 +12721,7 @@
       <c r="W484" s="7"/>
     </row>
     <row r="485">
-      <c r="A485" s="1"/>
+      <c r="A485" s="2"/>
       <c r="B485" s="7"/>
       <c r="C485" s="7"/>
       <c r="D485" s="7"/>
@@ -12741,7 +12746,7 @@
       <c r="W485" s="7"/>
     </row>
     <row r="486">
-      <c r="A486" s="1"/>
+      <c r="A486" s="2"/>
       <c r="B486" s="7"/>
       <c r="C486" s="7"/>
       <c r="D486" s="7"/>
@@ -12766,7 +12771,7 @@
       <c r="W486" s="7"/>
     </row>
     <row r="487">
-      <c r="A487" s="1"/>
+      <c r="A487" s="2"/>
       <c r="B487" s="7"/>
       <c r="C487" s="7"/>
       <c r="D487" s="7"/>
@@ -12791,7 +12796,7 @@
       <c r="W487" s="7"/>
     </row>
     <row r="488">
-      <c r="A488" s="1"/>
+      <c r="A488" s="2"/>
       <c r="B488" s="7"/>
       <c r="C488" s="7"/>
       <c r="D488" s="7"/>
@@ -12816,7 +12821,7 @@
       <c r="W488" s="7"/>
     </row>
     <row r="489">
-      <c r="A489" s="1"/>
+      <c r="A489" s="2"/>
       <c r="B489" s="7"/>
       <c r="C489" s="7"/>
       <c r="D489" s="7"/>
@@ -12841,7 +12846,7 @@
       <c r="W489" s="7"/>
     </row>
     <row r="490">
-      <c r="A490" s="1"/>
+      <c r="A490" s="2"/>
       <c r="B490" s="7"/>
       <c r="C490" s="7"/>
       <c r="D490" s="7"/>
@@ -12866,7 +12871,7 @@
       <c r="W490" s="7"/>
     </row>
     <row r="491">
-      <c r="A491" s="1"/>
+      <c r="A491" s="2"/>
       <c r="B491" s="7"/>
       <c r="C491" s="7"/>
       <c r="D491" s="7"/>
@@ -12891,7 +12896,7 @@
       <c r="W491" s="7"/>
     </row>
     <row r="492">
-      <c r="A492" s="1"/>
+      <c r="A492" s="2"/>
       <c r="B492" s="7"/>
       <c r="C492" s="7"/>
       <c r="D492" s="7"/>
@@ -12916,7 +12921,7 @@
       <c r="W492" s="7"/>
     </row>
     <row r="493">
-      <c r="A493" s="1"/>
+      <c r="A493" s="2"/>
       <c r="B493" s="7"/>
       <c r="C493" s="7"/>
       <c r="D493" s="7"/>
@@ -12941,7 +12946,7 @@
       <c r="W493" s="7"/>
     </row>
     <row r="494">
-      <c r="A494" s="1"/>
+      <c r="A494" s="2"/>
       <c r="B494" s="7"/>
       <c r="C494" s="7"/>
       <c r="D494" s="7"/>
@@ -12966,7 +12971,7 @@
       <c r="W494" s="7"/>
     </row>
     <row r="495">
-      <c r="A495" s="1"/>
+      <c r="A495" s="2"/>
       <c r="B495" s="7"/>
       <c r="C495" s="7"/>
       <c r="D495" s="7"/>
@@ -12991,7 +12996,7 @@
       <c r="W495" s="7"/>
     </row>
     <row r="496">
-      <c r="A496" s="1"/>
+      <c r="A496" s="2"/>
       <c r="B496" s="7"/>
       <c r="C496" s="7"/>
       <c r="D496" s="7"/>
@@ -13016,7 +13021,7 @@
       <c r="W496" s="7"/>
     </row>
     <row r="497">
-      <c r="A497" s="1"/>
+      <c r="A497" s="2"/>
       <c r="B497" s="7"/>
       <c r="C497" s="7"/>
       <c r="D497" s="7"/>
@@ -13041,7 +13046,7 @@
       <c r="W497" s="7"/>
     </row>
     <row r="498">
-      <c r="A498" s="1"/>
+      <c r="A498" s="2"/>
       <c r="B498" s="7"/>
       <c r="C498" s="7"/>
       <c r="D498" s="7"/>
@@ -13066,7 +13071,7 @@
       <c r="W498" s="7"/>
     </row>
     <row r="499">
-      <c r="A499" s="1"/>
+      <c r="A499" s="2"/>
       <c r="B499" s="7"/>
       <c r="C499" s="7"/>
       <c r="D499" s="7"/>
@@ -13091,7 +13096,7 @@
       <c r="W499" s="7"/>
     </row>
     <row r="500">
-      <c r="A500" s="1"/>
+      <c r="A500" s="2"/>
       <c r="B500" s="7"/>
       <c r="C500" s="7"/>
       <c r="D500" s="7"/>
@@ -13116,7 +13121,7 @@
       <c r="W500" s="7"/>
     </row>
     <row r="501">
-      <c r="A501" s="1"/>
+      <c r="A501" s="2"/>
       <c r="B501" s="7"/>
       <c r="C501" s="7"/>
       <c r="D501" s="7"/>
@@ -13141,7 +13146,7 @@
       <c r="W501" s="7"/>
     </row>
     <row r="502">
-      <c r="A502" s="1"/>
+      <c r="A502" s="2"/>
       <c r="B502" s="7"/>
       <c r="C502" s="7"/>
       <c r="D502" s="7"/>
@@ -13166,7 +13171,7 @@
       <c r="W502" s="7"/>
     </row>
     <row r="503">
-      <c r="A503" s="1"/>
+      <c r="A503" s="2"/>
       <c r="B503" s="7"/>
       <c r="C503" s="7"/>
       <c r="D503" s="7"/>
@@ -13191,7 +13196,7 @@
       <c r="W503" s="7"/>
     </row>
     <row r="504">
-      <c r="A504" s="1"/>
+      <c r="A504" s="2"/>
       <c r="B504" s="7"/>
       <c r="C504" s="7"/>
       <c r="D504" s="7"/>
@@ -13216,7 +13221,7 @@
       <c r="W504" s="7"/>
     </row>
     <row r="505">
-      <c r="A505" s="1"/>
+      <c r="A505" s="2"/>
       <c r="B505" s="7"/>
       <c r="C505" s="7"/>
       <c r="D505" s="7"/>
@@ -13241,7 +13246,7 @@
       <c r="W505" s="7"/>
     </row>
     <row r="506">
-      <c r="A506" s="1"/>
+      <c r="A506" s="2"/>
       <c r="B506" s="7"/>
       <c r="C506" s="7"/>
       <c r="D506" s="7"/>
@@ -13266,7 +13271,7 @@
       <c r="W506" s="7"/>
     </row>
     <row r="507">
-      <c r="A507" s="1"/>
+      <c r="A507" s="2"/>
       <c r="B507" s="7"/>
       <c r="C507" s="7"/>
       <c r="D507" s="7"/>
@@ -13291,7 +13296,7 @@
       <c r="W507" s="7"/>
     </row>
     <row r="508">
-      <c r="A508" s="1"/>
+      <c r="A508" s="2"/>
       <c r="B508" s="7"/>
       <c r="C508" s="7"/>
       <c r="D508" s="7"/>
@@ -13316,7 +13321,7 @@
       <c r="W508" s="7"/>
     </row>
     <row r="509">
-      <c r="A509" s="1"/>
+      <c r="A509" s="2"/>
       <c r="B509" s="7"/>
       <c r="C509" s="7"/>
       <c r="D509" s="7"/>
@@ -13341,7 +13346,7 @@
       <c r="W509" s="7"/>
     </row>
     <row r="510">
-      <c r="A510" s="1"/>
+      <c r="A510" s="2"/>
       <c r="B510" s="7"/>
       <c r="C510" s="7"/>
       <c r="D510" s="7"/>
@@ -13366,7 +13371,7 @@
       <c r="W510" s="7"/>
     </row>
     <row r="511">
-      <c r="A511" s="1"/>
+      <c r="A511" s="2"/>
       <c r="B511" s="7"/>
       <c r="C511" s="7"/>
       <c r="D511" s="7"/>
@@ -13391,7 +13396,7 @@
       <c r="W511" s="7"/>
     </row>
     <row r="512">
-      <c r="A512" s="1"/>
+      <c r="A512" s="2"/>
       <c r="B512" s="7"/>
       <c r="C512" s="7"/>
       <c r="D512" s="7"/>
@@ -13416,7 +13421,7 @@
       <c r="W512" s="7"/>
     </row>
     <row r="513">
-      <c r="A513" s="1"/>
+      <c r="A513" s="2"/>
       <c r="B513" s="7"/>
       <c r="C513" s="7"/>
       <c r="D513" s="7"/>
@@ -13441,7 +13446,7 @@
       <c r="W513" s="7"/>
     </row>
     <row r="514">
-      <c r="A514" s="1"/>
+      <c r="A514" s="2"/>
       <c r="B514" s="7"/>
       <c r="C514" s="7"/>
       <c r="D514" s="7"/>
@@ -13466,7 +13471,7 @@
       <c r="W514" s="7"/>
     </row>
     <row r="515">
-      <c r="A515" s="1"/>
+      <c r="A515" s="2"/>
       <c r="B515" s="7"/>
       <c r="C515" s="7"/>
       <c r="D515" s="7"/>
@@ -13491,7 +13496,7 @@
       <c r="W515" s="7"/>
     </row>
     <row r="516">
-      <c r="A516" s="1"/>
+      <c r="A516" s="2"/>
       <c r="B516" s="7"/>
       <c r="C516" s="7"/>
       <c r="D516" s="7"/>
@@ -13516,7 +13521,7 @@
       <c r="W516" s="7"/>
     </row>
     <row r="517">
-      <c r="A517" s="1"/>
+      <c r="A517" s="2"/>
       <c r="B517" s="7"/>
       <c r="C517" s="7"/>
       <c r="D517" s="7"/>
@@ -13541,7 +13546,7 @@
       <c r="W517" s="7"/>
     </row>
     <row r="518">
-      <c r="A518" s="1"/>
+      <c r="A518" s="2"/>
       <c r="B518" s="7"/>
       <c r="C518" s="7"/>
       <c r="D518" s="7"/>
@@ -13566,7 +13571,7 @@
       <c r="W518" s="7"/>
     </row>
     <row r="519">
-      <c r="A519" s="1"/>
+      <c r="A519" s="2"/>
       <c r="B519" s="7"/>
       <c r="C519" s="7"/>
       <c r="D519" s="7"/>
@@ -13591,7 +13596,7 @@
       <c r="W519" s="7"/>
     </row>
     <row r="520">
-      <c r="A520" s="1"/>
+      <c r="A520" s="2"/>
       <c r="B520" s="7"/>
       <c r="C520" s="7"/>
       <c r="D520" s="7"/>
@@ -13616,7 +13621,7 @@
       <c r="W520" s="7"/>
     </row>
     <row r="521">
-      <c r="A521" s="1"/>
+      <c r="A521" s="2"/>
       <c r="B521" s="7"/>
       <c r="C521" s="7"/>
       <c r="D521" s="7"/>
@@ -13641,7 +13646,7 @@
       <c r="W521" s="7"/>
     </row>
     <row r="522">
-      <c r="A522" s="1"/>
+      <c r="A522" s="2"/>
       <c r="B522" s="7"/>
       <c r="C522" s="7"/>
       <c r="D522" s="7"/>
@@ -13666,7 +13671,7 @@
       <c r="W522" s="7"/>
     </row>
     <row r="523">
-      <c r="A523" s="1"/>
+      <c r="A523" s="2"/>
       <c r="B523" s="7"/>
       <c r="C523" s="7"/>
       <c r="D523" s="7"/>
@@ -13691,7 +13696,7 @@
       <c r="W523" s="7"/>
     </row>
     <row r="524">
-      <c r="A524" s="1"/>
+      <c r="A524" s="2"/>
       <c r="B524" s="7"/>
       <c r="C524" s="7"/>
       <c r="D524" s="7"/>
@@ -13716,7 +13721,7 @@
       <c r="W524" s="7"/>
     </row>
     <row r="525">
-      <c r="A525" s="1"/>
+      <c r="A525" s="2"/>
       <c r="B525" s="7"/>
       <c r="C525" s="7"/>
       <c r="D525" s="7"/>
@@ -13741,7 +13746,7 @@
       <c r="W525" s="7"/>
     </row>
     <row r="526">
-      <c r="A526" s="1"/>
+      <c r="A526" s="2"/>
       <c r="B526" s="7"/>
       <c r="C526" s="7"/>
       <c r="D526" s="7"/>
@@ -13766,7 +13771,7 @@
       <c r="W526" s="7"/>
     </row>
     <row r="527">
-      <c r="A527" s="1"/>
+      <c r="A527" s="2"/>
       <c r="B527" s="7"/>
       <c r="C527" s="7"/>
       <c r="D527" s="7"/>
@@ -13791,7 +13796,7 @@
       <c r="W527" s="7"/>
     </row>
     <row r="528">
-      <c r="A528" s="1"/>
+      <c r="A528" s="2"/>
       <c r="B528" s="7"/>
       <c r="C528" s="7"/>
       <c r="D528" s="7"/>
@@ -13816,7 +13821,7 @@
       <c r="W528" s="7"/>
     </row>
     <row r="529">
-      <c r="A529" s="1"/>
+      <c r="A529" s="2"/>
       <c r="B529" s="7"/>
       <c r="C529" s="7"/>
       <c r="D529" s="7"/>
@@ -13841,7 +13846,7 @@
       <c r="W529" s="7"/>
     </row>
     <row r="530">
-      <c r="A530" s="1"/>
+      <c r="A530" s="2"/>
       <c r="B530" s="7"/>
       <c r="C530" s="7"/>
       <c r="D530" s="7"/>
@@ -13866,7 +13871,7 @@
       <c r="W530" s="7"/>
     </row>
     <row r="531">
-      <c r="A531" s="1"/>
+      <c r="A531" s="2"/>
       <c r="B531" s="7"/>
       <c r="C531" s="7"/>
       <c r="D531" s="7"/>
@@ -13891,7 +13896,7 @@
       <c r="W531" s="7"/>
     </row>
     <row r="532">
-      <c r="A532" s="1"/>
+      <c r="A532" s="2"/>
       <c r="B532" s="7"/>
       <c r="C532" s="7"/>
       <c r="D532" s="7"/>
@@ -13916,7 +13921,7 @@
       <c r="W532" s="7"/>
     </row>
     <row r="533">
-      <c r="A533" s="1"/>
+      <c r="A533" s="2"/>
       <c r="B533" s="7"/>
       <c r="C533" s="7"/>
       <c r="D533" s="7"/>
@@ -13941,7 +13946,7 @@
       <c r="W533" s="7"/>
     </row>
     <row r="534">
-      <c r="A534" s="1"/>
+      <c r="A534" s="2"/>
       <c r="B534" s="7"/>
       <c r="C534" s="7"/>
       <c r="D534" s="7"/>
@@ -13966,7 +13971,7 @@
       <c r="W534" s="7"/>
     </row>
     <row r="535">
-      <c r="A535" s="1"/>
+      <c r="A535" s="2"/>
       <c r="B535" s="7"/>
       <c r="C535" s="7"/>
       <c r="D535" s="7"/>
@@ -13991,7 +13996,7 @@
       <c r="W535" s="7"/>
     </row>
     <row r="536">
-      <c r="A536" s="1"/>
+      <c r="A536" s="2"/>
       <c r="B536" s="7"/>
       <c r="C536" s="7"/>
       <c r="D536" s="7"/>
@@ -14016,7 +14021,7 @@
       <c r="W536" s="7"/>
     </row>
     <row r="537">
-      <c r="A537" s="1"/>
+      <c r="A537" s="2"/>
       <c r="B537" s="7"/>
       <c r="C537" s="7"/>
       <c r="D537" s="7"/>
@@ -14041,7 +14046,7 @@
       <c r="W537" s="7"/>
     </row>
     <row r="538">
-      <c r="A538" s="1"/>
+      <c r="A538" s="2"/>
       <c r="B538" s="7"/>
       <c r="C538" s="7"/>
       <c r="D538" s="7"/>
@@ -14066,7 +14071,7 @@
       <c r="W538" s="7"/>
     </row>
     <row r="539">
-      <c r="A539" s="1"/>
+      <c r="A539" s="2"/>
       <c r="B539" s="7"/>
       <c r="C539" s="7"/>
       <c r="D539" s="7"/>
@@ -14091,7 +14096,7 @@
       <c r="W539" s="7"/>
     </row>
     <row r="540">
-      <c r="A540" s="1"/>
+      <c r="A540" s="2"/>
       <c r="B540" s="7"/>
       <c r="C540" s="7"/>
       <c r="D540" s="7"/>
@@ -14116,7 +14121,7 @@
       <c r="W540" s="7"/>
     </row>
     <row r="541">
-      <c r="A541" s="1"/>
+      <c r="A541" s="2"/>
       <c r="B541" s="7"/>
       <c r="C541" s="7"/>
       <c r="D541" s="7"/>
@@ -14141,7 +14146,7 @@
       <c r="W541" s="7"/>
     </row>
     <row r="542">
-      <c r="A542" s="1"/>
+      <c r="A542" s="2"/>
       <c r="B542" s="7"/>
       <c r="C542" s="7"/>
       <c r="D542" s="7"/>
@@ -14166,7 +14171,7 @@
       <c r="W542" s="7"/>
     </row>
     <row r="543">
-      <c r="A543" s="1"/>
+      <c r="A543" s="2"/>
       <c r="B543" s="7"/>
       <c r="C543" s="7"/>
       <c r="D543" s="7"/>
@@ -14191,7 +14196,7 @@
       <c r="W543" s="7"/>
     </row>
     <row r="544">
-      <c r="A544" s="1"/>
+      <c r="A544" s="2"/>
       <c r="B544" s="7"/>
       <c r="C544" s="7"/>
       <c r="D544" s="7"/>
@@ -14216,7 +14221,7 @@
       <c r="W544" s="7"/>
     </row>
     <row r="545">
-      <c r="A545" s="1"/>
+      <c r="A545" s="2"/>
       <c r="B545" s="7"/>
       <c r="C545" s="7"/>
       <c r="D545" s="7"/>
@@ -14241,7 +14246,7 @@
       <c r="W545" s="7"/>
     </row>
     <row r="546">
-      <c r="A546" s="1"/>
+      <c r="A546" s="2"/>
       <c r="B546" s="7"/>
       <c r="C546" s="7"/>
       <c r="D546" s="7"/>
@@ -14266,7 +14271,7 @@
       <c r="W546" s="7"/>
     </row>
     <row r="547">
-      <c r="A547" s="1"/>
+      <c r="A547" s="2"/>
       <c r="B547" s="7"/>
       <c r="C547" s="7"/>
       <c r="D547" s="7"/>
@@ -14291,7 +14296,7 @@
       <c r="W547" s="7"/>
     </row>
     <row r="548">
-      <c r="A548" s="1"/>
+      <c r="A548" s="2"/>
       <c r="B548" s="7"/>
       <c r="C548" s="7"/>
       <c r="D548" s="7"/>
@@ -14316,7 +14321,7 @@
       <c r="W548" s="7"/>
     </row>
     <row r="549">
-      <c r="A549" s="1"/>
+      <c r="A549" s="2"/>
       <c r="B549" s="7"/>
       <c r="C549" s="7"/>
       <c r="D549" s="7"/>
@@ -14341,7 +14346,7 @@
       <c r="W549" s="7"/>
     </row>
     <row r="550">
-      <c r="A550" s="1"/>
+      <c r="A550" s="2"/>
       <c r="B550" s="7"/>
       <c r="C550" s="7"/>
       <c r="D550" s="7"/>
@@ -14366,7 +14371,7 @@
       <c r="W550" s="7"/>
     </row>
     <row r="551">
-      <c r="A551" s="1"/>
+      <c r="A551" s="2"/>
       <c r="B551" s="7"/>
       <c r="C551" s="7"/>
       <c r="D551" s="7"/>
@@ -14391,7 +14396,7 @@
       <c r="W551" s="7"/>
     </row>
     <row r="552">
-      <c r="A552" s="1"/>
+      <c r="A552" s="2"/>
       <c r="B552" s="7"/>
       <c r="C552" s="7"/>
       <c r="D552" s="7"/>
@@ -14416,7 +14421,7 @@
       <c r="W552" s="7"/>
     </row>
     <row r="553">
-      <c r="A553" s="1"/>
+      <c r="A553" s="2"/>
       <c r="B553" s="7"/>
       <c r="C553" s="7"/>
       <c r="D553" s="7"/>
@@ -14441,7 +14446,7 @@
       <c r="W553" s="7"/>
     </row>
     <row r="554">
-      <c r="A554" s="1"/>
+      <c r="A554" s="2"/>
       <c r="B554" s="7"/>
       <c r="C554" s="7"/>
       <c r="D554" s="7"/>
@@ -14466,7 +14471,7 @@
       <c r="W554" s="7"/>
     </row>
     <row r="555">
-      <c r="A555" s="1"/>
+      <c r="A555" s="2"/>
       <c r="B555" s="7"/>
       <c r="C555" s="7"/>
       <c r="D555" s="7"/>
@@ -14491,7 +14496,7 @@
       <c r="W555" s="7"/>
     </row>
     <row r="556">
-      <c r="A556" s="1"/>
+      <c r="A556" s="2"/>
       <c r="B556" s="7"/>
       <c r="C556" s="7"/>
       <c r="D556" s="7"/>
@@ -14516,7 +14521,7 @@
       <c r="W556" s="7"/>
     </row>
     <row r="557">
-      <c r="A557" s="1"/>
+      <c r="A557" s="2"/>
       <c r="B557" s="7"/>
       <c r="C557" s="7"/>
       <c r="D557" s="7"/>
@@ -14541,7 +14546,7 @@
       <c r="W557" s="7"/>
     </row>
     <row r="558">
-      <c r="A558" s="1"/>
+      <c r="A558" s="2"/>
       <c r="B558" s="7"/>
       <c r="C558" s="7"/>
       <c r="D558" s="7"/>
@@ -14566,7 +14571,7 @@
       <c r="W558" s="7"/>
     </row>
     <row r="559">
-      <c r="A559" s="1"/>
+      <c r="A559" s="2"/>
       <c r="B559" s="7"/>
       <c r="C559" s="7"/>
       <c r="D559" s="7"/>
@@ -14591,7 +14596,7 @@
       <c r="W559" s="7"/>
     </row>
     <row r="560">
-      <c r="A560" s="1"/>
+      <c r="A560" s="2"/>
       <c r="B560" s="7"/>
       <c r="C560" s="7"/>
       <c r="D560" s="7"/>
@@ -14616,7 +14621,7 @@
       <c r="W560" s="7"/>
     </row>
     <row r="561">
-      <c r="A561" s="1"/>
+      <c r="A561" s="2"/>
       <c r="B561" s="7"/>
       <c r="C561" s="7"/>
       <c r="D561" s="7"/>
@@ -14641,7 +14646,7 @@
       <c r="W561" s="7"/>
     </row>
     <row r="562">
-      <c r="A562" s="1"/>
+      <c r="A562" s="2"/>
       <c r="B562" s="7"/>
       <c r="C562" s="7"/>
       <c r="D562" s="7"/>
@@ -14666,7 +14671,7 @@
       <c r="W562" s="7"/>
     </row>
     <row r="563">
-      <c r="A563" s="1"/>
+      <c r="A563" s="2"/>
       <c r="B563" s="7"/>
       <c r="C563" s="7"/>
       <c r="D563" s="7"/>
@@ -14691,7 +14696,7 @@
       <c r="W563" s="7"/>
     </row>
     <row r="564">
-      <c r="A564" s="1"/>
+      <c r="A564" s="2"/>
       <c r="B564" s="7"/>
       <c r="C564" s="7"/>
       <c r="D564" s="7"/>
@@ -14716,7 +14721,7 @@
       <c r="W564" s="7"/>
     </row>
     <row r="565">
-      <c r="A565" s="1"/>
+      <c r="A565" s="2"/>
       <c r="B565" s="7"/>
       <c r="C565" s="7"/>
       <c r="D565" s="7"/>
@@ -14741,7 +14746,7 @@
       <c r="W565" s="7"/>
     </row>
     <row r="566">
-      <c r="A566" s="1"/>
+      <c r="A566" s="2"/>
       <c r="B566" s="7"/>
       <c r="C566" s="7"/>
       <c r="D566" s="7"/>
@@ -14766,7 +14771,7 @@
       <c r="W566" s="7"/>
     </row>
     <row r="567">
-      <c r="A567" s="1"/>
+      <c r="A567" s="2"/>
       <c r="B567" s="7"/>
       <c r="C567" s="7"/>
       <c r="D567" s="7"/>
@@ -14791,7 +14796,7 @@
       <c r="W567" s="7"/>
     </row>
     <row r="568">
-      <c r="A568" s="1"/>
+      <c r="A568" s="2"/>
       <c r="B568" s="7"/>
       <c r="C568" s="7"/>
       <c r="D568" s="7"/>
@@ -14816,7 +14821,7 @@
       <c r="W568" s="7"/>
     </row>
     <row r="569">
-      <c r="A569" s="1"/>
+      <c r="A569" s="2"/>
       <c r="B569" s="7"/>
       <c r="C569" s="7"/>
       <c r="D569" s="7"/>
@@ -14841,7 +14846,7 @@
       <c r="W569" s="7"/>
     </row>
     <row r="570">
-      <c r="A570" s="1"/>
+      <c r="A570" s="2"/>
       <c r="B570" s="7"/>
       <c r="C570" s="7"/>
       <c r="D570" s="7"/>
@@ -14866,7 +14871,7 @@
       <c r="W570" s="7"/>
     </row>
     <row r="571">
-      <c r="A571" s="1"/>
+      <c r="A571" s="2"/>
       <c r="B571" s="7"/>
       <c r="C571" s="7"/>
       <c r="D571" s="7"/>
@@ -14891,7 +14896,7 @@
       <c r="W571" s="7"/>
     </row>
     <row r="572">
-      <c r="A572" s="1"/>
+      <c r="A572" s="2"/>
       <c r="B572" s="7"/>
       <c r="C572" s="7"/>
       <c r="D572" s="7"/>
@@ -14916,7 +14921,7 @@
       <c r="W572" s="7"/>
     </row>
     <row r="573">
-      <c r="A573" s="1"/>
+      <c r="A573" s="2"/>
       <c r="B573" s="7"/>
       <c r="C573" s="7"/>
       <c r="D573" s="7"/>
@@ -14941,7 +14946,7 @@
       <c r="W573" s="7"/>
     </row>
     <row r="574">
-      <c r="A574" s="1"/>
+      <c r="A574" s="2"/>
       <c r="B574" s="7"/>
       <c r="C574" s="7"/>
       <c r="D574" s="7"/>
@@ -14966,7 +14971,7 @@
       <c r="W574" s="7"/>
     </row>
     <row r="575">
-      <c r="A575" s="1"/>
+      <c r="A575" s="2"/>
       <c r="B575" s="7"/>
       <c r="C575" s="7"/>
       <c r="D575" s="7"/>
@@ -14991,7 +14996,7 @@
       <c r="W575" s="7"/>
     </row>
     <row r="576">
-      <c r="A576" s="1"/>
+      <c r="A576" s="2"/>
       <c r="B576" s="7"/>
       <c r="C576" s="7"/>
       <c r="D576" s="7"/>
@@ -15016,7 +15021,7 @@
       <c r="W576" s="7"/>
     </row>
     <row r="577">
-      <c r="A577" s="1"/>
+      <c r="A577" s="2"/>
       <c r="B577" s="7"/>
       <c r="C577" s="7"/>
       <c r="D577" s="7"/>
@@ -15041,7 +15046,7 @@
       <c r="W577" s="7"/>
     </row>
     <row r="578">
-      <c r="A578" s="1"/>
+      <c r="A578" s="2"/>
       <c r="B578" s="7"/>
       <c r="C578" s="7"/>
       <c r="D578" s="7"/>
@@ -15066,7 +15071,7 @@
       <c r="W578" s="7"/>
     </row>
     <row r="579">
-      <c r="A579" s="1"/>
+      <c r="A579" s="2"/>
       <c r="B579" s="7"/>
       <c r="C579" s="7"/>
       <c r="D579" s="7"/>
@@ -15091,7 +15096,7 @@
       <c r="W579" s="7"/>
     </row>
     <row r="580">
-      <c r="A580" s="1"/>
+      <c r="A580" s="2"/>
       <c r="B580" s="7"/>
       <c r="C580" s="7"/>
       <c r="D580" s="7"/>
@@ -15116,7 +15121,7 @@
       <c r="W580" s="7"/>
     </row>
     <row r="581">
-      <c r="A581" s="1"/>
+      <c r="A581" s="2"/>
       <c r="B581" s="7"/>
       <c r="C581" s="7"/>
       <c r="D581" s="7"/>
@@ -15141,7 +15146,7 @@
       <c r="W581" s="7"/>
     </row>
     <row r="582">
-      <c r="A582" s="1"/>
+      <c r="A582" s="2"/>
       <c r="B582" s="7"/>
       <c r="C582" s="7"/>
       <c r="D582" s="7"/>
@@ -15166,7 +15171,7 @@
       <c r="W582" s="7"/>
     </row>
     <row r="583">
-      <c r="A583" s="1"/>
+      <c r="A583" s="2"/>
       <c r="B583" s="7"/>
       <c r="C583" s="7"/>
       <c r="D583" s="7"/>
@@ -15191,7 +15196,7 @@
       <c r="W583" s="7"/>
     </row>
     <row r="584">
-      <c r="A584" s="1"/>
+      <c r="A584" s="2"/>
       <c r="B584" s="7"/>
       <c r="C584" s="7"/>
       <c r="D584" s="7"/>
@@ -15216,7 +15221,7 @@
       <c r="W584" s="7"/>
     </row>
     <row r="585">
-      <c r="A585" s="1"/>
+      <c r="A585" s="2"/>
       <c r="B585" s="7"/>
       <c r="C585" s="7"/>
       <c r="D585" s="7"/>
@@ -15241,7 +15246,7 @@
       <c r="W585" s="7"/>
     </row>
     <row r="586">
-      <c r="A586" s="1"/>
+      <c r="A586" s="2"/>
       <c r="B586" s="7"/>
       <c r="C586" s="7"/>
       <c r="D586" s="7"/>
@@ -15266,7 +15271,7 @@
       <c r="W586" s="7"/>
     </row>
     <row r="587">
-      <c r="A587" s="1"/>
+      <c r="A587" s="2"/>
       <c r="B587" s="7"/>
       <c r="C587" s="7"/>
       <c r="D587" s="7"/>
@@ -15291,7 +15296,7 @@
       <c r="W587" s="7"/>
     </row>
     <row r="588">
-      <c r="A588" s="1"/>
+      <c r="A588" s="2"/>
       <c r="B588" s="7"/>
       <c r="C588" s="7"/>
       <c r="D588" s="7"/>
@@ -15316,7 +15321,7 @@
       <c r="W588" s="7"/>
     </row>
     <row r="589">
-      <c r="A589" s="1"/>
+      <c r="A589" s="2"/>
       <c r="B589" s="7"/>
       <c r="C589" s="7"/>
       <c r="D589" s="7"/>
@@ -15341,7 +15346,7 @@
       <c r="W589" s="7"/>
     </row>
     <row r="590">
-      <c r="A590" s="1"/>
+      <c r="A590" s="2"/>
       <c r="B590" s="7"/>
       <c r="C590" s="7"/>
       <c r="D590" s="7"/>
@@ -15366,7 +15371,7 @@
       <c r="W590" s="7"/>
     </row>
     <row r="591">
-      <c r="A591" s="1"/>
+      <c r="A591" s="2"/>
       <c r="B591" s="7"/>
       <c r="C591" s="7"/>
       <c r="D591" s="7"/>
@@ -15391,7 +15396,7 @@
       <c r="W591" s="7"/>
     </row>
     <row r="592">
-      <c r="A592" s="1"/>
+      <c r="A592" s="2"/>
       <c r="B592" s="7"/>
       <c r="C592" s="7"/>
       <c r="D592" s="7"/>
@@ -15416,7 +15421,7 @@
       <c r="W592" s="7"/>
     </row>
     <row r="593">
-      <c r="A593" s="1"/>
+      <c r="A593" s="2"/>
       <c r="B593" s="7"/>
       <c r="C593" s="7"/>
       <c r="D593" s="7"/>
@@ -15441,7 +15446,7 @@
       <c r="W593" s="7"/>
     </row>
     <row r="594">
-      <c r="A594" s="1"/>
+      <c r="A594" s="2"/>
       <c r="B594" s="7"/>
       <c r="C594" s="7"/>
       <c r="D594" s="7"/>
@@ -15466,7 +15471,7 @@
       <c r="W594" s="7"/>
     </row>
     <row r="595">
-      <c r="A595" s="1"/>
+      <c r="A595" s="2"/>
       <c r="B595" s="7"/>
       <c r="C595" s="7"/>
       <c r="D595" s="7"/>
@@ -15491,7 +15496,7 @@
       <c r="W595" s="7"/>
     </row>
     <row r="596">
-      <c r="A596" s="1"/>
+      <c r="A596" s="2"/>
       <c r="B596" s="7"/>
       <c r="C596" s="7"/>
       <c r="D596" s="7"/>
@@ -15516,7 +15521,7 @@
       <c r="W596" s="7"/>
     </row>
     <row r="597">
-      <c r="A597" s="1"/>
+      <c r="A597" s="2"/>
       <c r="B597" s="7"/>
       <c r="C597" s="7"/>
       <c r="D597" s="7"/>
@@ -15541,7 +15546,7 @@
       <c r="W597" s="7"/>
     </row>
     <row r="598">
-      <c r="A598" s="1"/>
+      <c r="A598" s="2"/>
       <c r="B598" s="7"/>
       <c r="C598" s="7"/>
       <c r="D598" s="7"/>
@@ -15566,7 +15571,7 @@
       <c r="W598" s="7"/>
     </row>
     <row r="599">
-      <c r="A599" s="1"/>
+      <c r="A599" s="2"/>
       <c r="B599" s="7"/>
       <c r="C599" s="7"/>
       <c r="D599" s="7"/>
@@ -15591,7 +15596,7 @@
       <c r="W599" s="7"/>
     </row>
     <row r="600">
-      <c r="A600" s="1"/>
+      <c r="A600" s="2"/>
       <c r="B600" s="7"/>
       <c r="C600" s="7"/>
       <c r="D600" s="7"/>
@@ -15616,7 +15621,7 @@
       <c r="W600" s="7"/>
     </row>
     <row r="601">
-      <c r="A601" s="1"/>
+      <c r="A601" s="2"/>
       <c r="B601" s="7"/>
       <c r="C601" s="7"/>
       <c r="D601" s="7"/>
@@ -15641,7 +15646,7 @@
       <c r="W601" s="7"/>
     </row>
     <row r="602">
-      <c r="A602" s="1"/>
+      <c r="A602" s="2"/>
       <c r="B602" s="7"/>
       <c r="C602" s="7"/>
       <c r="D602" s="7"/>
@@ -15666,7 +15671,7 @@
       <c r="W602" s="7"/>
     </row>
     <row r="603">
-      <c r="A603" s="1"/>
+      <c r="A603" s="2"/>
       <c r="B603" s="7"/>
       <c r="C603" s="7"/>
       <c r="D603" s="7"/>
@@ -15691,7 +15696,7 @@
       <c r="W603" s="7"/>
     </row>
     <row r="604">
-      <c r="A604" s="1"/>
+      <c r="A604" s="2"/>
       <c r="B604" s="7"/>
       <c r="C604" s="7"/>
       <c r="D604" s="7"/>
@@ -15716,7 +15721,7 @@
       <c r="W604" s="7"/>
     </row>
     <row r="605">
-      <c r="A605" s="1"/>
+      <c r="A605" s="2"/>
       <c r="B605" s="7"/>
       <c r="C605" s="7"/>
       <c r="D605" s="7"/>
@@ -15741,7 +15746,7 @@
       <c r="W605" s="7"/>
     </row>
     <row r="606">
-      <c r="A606" s="1"/>
+      <c r="A606" s="2"/>
       <c r="B606" s="7"/>
       <c r="C606" s="7"/>
       <c r="D606" s="7"/>
@@ -15766,7 +15771,7 @@
       <c r="W606" s="7"/>
     </row>
     <row r="607">
-      <c r="A607" s="1"/>
+      <c r="A607" s="2"/>
       <c r="B607" s="7"/>
       <c r="C607" s="7"/>
       <c r="D607" s="7"/>
@@ -15791,7 +15796,7 @@
       <c r="W607" s="7"/>
     </row>
     <row r="608">
-      <c r="A608" s="1"/>
+      <c r="A608" s="2"/>
       <c r="B608" s="7"/>
       <c r="C608" s="7"/>
       <c r="D608" s="7"/>
@@ -15816,7 +15821,7 @@
       <c r="W608" s="7"/>
     </row>
     <row r="609">
-      <c r="A609" s="1"/>
+      <c r="A609" s="2"/>
       <c r="B609" s="7"/>
       <c r="C609" s="7"/>
       <c r="D609" s="7"/>
@@ -15841,7 +15846,7 @@
       <c r="W609" s="7"/>
     </row>
     <row r="610">
-      <c r="A610" s="1"/>
+      <c r="A610" s="2"/>
       <c r="B610" s="7"/>
       <c r="C610" s="7"/>
       <c r="D610" s="7"/>
@@ -15866,7 +15871,7 @@
       <c r="W610" s="7"/>
     </row>
     <row r="611">
-      <c r="A611" s="1"/>
+      <c r="A611" s="2"/>
       <c r="B611" s="7"/>
       <c r="C611" s="7"/>
       <c r="D611" s="7"/>
@@ -15891,7 +15896,7 @@
       <c r="W611" s="7"/>
     </row>
     <row r="612">
-      <c r="A612" s="1"/>
+      <c r="A612" s="2"/>
       <c r="B612" s="7"/>
       <c r="C612" s="7"/>
       <c r="D612" s="7"/>
@@ -15916,7 +15921,7 @@
       <c r="W612" s="7"/>
     </row>
     <row r="613">
-      <c r="A613" s="1"/>
+      <c r="A613" s="2"/>
       <c r="B613" s="7"/>
       <c r="C613" s="7"/>
       <c r="D613" s="7"/>
@@ -15941,7 +15946,7 @@
       <c r="W613" s="7"/>
     </row>
     <row r="614">
-      <c r="A614" s="1"/>
+      <c r="A614" s="2"/>
       <c r="B614" s="7"/>
       <c r="C614" s="7"/>
       <c r="D614" s="7"/>
@@ -15966,7 +15971,7 @@
       <c r="W614" s="7"/>
     </row>
     <row r="615">
-      <c r="A615" s="1"/>
+      <c r="A615" s="2"/>
       <c r="B615" s="7"/>
       <c r="C615" s="7"/>
       <c r="D615" s="7"/>
@@ -15991,7 +15996,7 @@
       <c r="W615" s="7"/>
     </row>
     <row r="616">
-      <c r="A616" s="1"/>
+      <c r="A616" s="2"/>
       <c r="B616" s="7"/>
       <c r="C616" s="7"/>
       <c r="D616" s="7"/>
@@ -16016,7 +16021,7 @@
       <c r="W616" s="7"/>
     </row>
     <row r="617">
-      <c r="A617" s="1"/>
+      <c r="A617" s="2"/>
       <c r="B617" s="7"/>
       <c r="C617" s="7"/>
       <c r="D617" s="7"/>
@@ -16041,7 +16046,7 @@
       <c r="W617" s="7"/>
     </row>
     <row r="618">
-      <c r="A618" s="1"/>
+      <c r="A618" s="2"/>
       <c r="B618" s="7"/>
       <c r="C618" s="7"/>
       <c r="D618" s="7"/>
@@ -16066,7 +16071,7 @@
       <c r="W618" s="7"/>
     </row>
     <row r="619">
-      <c r="A619" s="1"/>
+      <c r="A619" s="2"/>
       <c r="B619" s="7"/>
       <c r="C619" s="7"/>
       <c r="D619" s="7"/>
@@ -16091,7 +16096,7 @@
       <c r="W619" s="7"/>
     </row>
     <row r="620">
-      <c r="A620" s="1"/>
+      <c r="A620" s="2"/>
       <c r="B620" s="7"/>
       <c r="C620" s="7"/>
       <c r="D620" s="7"/>
@@ -16116,7 +16121,7 @@
       <c r="W620" s="7"/>
     </row>
     <row r="621">
-      <c r="A621" s="1"/>
+      <c r="A621" s="2"/>
       <c r="B621" s="7"/>
       <c r="C621" s="7"/>
       <c r="D621" s="7"/>
@@ -16141,7 +16146,7 @@
       <c r="W621" s="7"/>
     </row>
     <row r="622">
-      <c r="A622" s="1"/>
+      <c r="A622" s="2"/>
       <c r="B622" s="7"/>
       <c r="C622" s="7"/>
       <c r="D622" s="7"/>
@@ -16166,7 +16171,7 @@
       <c r="W622" s="7"/>
     </row>
     <row r="623">
-      <c r="A623" s="1"/>
+      <c r="A623" s="2"/>
       <c r="B623" s="7"/>
       <c r="C623" s="7"/>
       <c r="D623" s="7"/>
@@ -16191,7 +16196,7 @@
       <c r="W623" s="7"/>
     </row>
     <row r="624">
-      <c r="A624" s="1"/>
+      <c r="A624" s="2"/>
       <c r="B624" s="7"/>
       <c r="C624" s="7"/>
       <c r="D624" s="7"/>
@@ -16216,7 +16221,7 @@
       <c r="W624" s="7"/>
     </row>
     <row r="625">
-      <c r="A625" s="1"/>
+      <c r="A625" s="2"/>
       <c r="B625" s="7"/>
       <c r="C625" s="7"/>
       <c r="D625" s="7"/>
@@ -16241,7 +16246,7 @@
       <c r="W625" s="7"/>
     </row>
     <row r="626">
-      <c r="A626" s="1"/>
+      <c r="A626" s="2"/>
       <c r="B626" s="7"/>
       <c r="C626" s="7"/>
       <c r="D626" s="7"/>
@@ -16266,7 +16271,7 @@
       <c r="W626" s="7"/>
     </row>
     <row r="627">
-      <c r="A627" s="1"/>
+      <c r="A627" s="2"/>
       <c r="B627" s="7"/>
       <c r="C627" s="7"/>
       <c r="D627" s="7"/>
@@ -16291,7 +16296,7 @@
       <c r="W627" s="7"/>
     </row>
     <row r="628">
-      <c r="A628" s="1"/>
+      <c r="A628" s="2"/>
       <c r="B628" s="7"/>
       <c r="C628" s="7"/>
       <c r="D628" s="7"/>
@@ -16316,7 +16321,7 @@
       <c r="W628" s="7"/>
     </row>
     <row r="629">
-      <c r="A629" s="1"/>
+      <c r="A629" s="2"/>
       <c r="B629" s="7"/>
       <c r="C629" s="7"/>
       <c r="D629" s="7"/>
@@ -16341,7 +16346,7 @@
       <c r="W629" s="7"/>
     </row>
     <row r="630">
-      <c r="A630" s="1"/>
+      <c r="A630" s="2"/>
       <c r="B630" s="7"/>
       <c r="C630" s="7"/>
       <c r="D630" s="7"/>
@@ -16366,7 +16371,7 @@
       <c r="W630" s="7"/>
     </row>
     <row r="631">
-      <c r="A631" s="1"/>
+      <c r="A631" s="2"/>
       <c r="B631" s="7"/>
       <c r="C631" s="7"/>
       <c r="D631" s="7"/>
@@ -16391,7 +16396,7 @@
       <c r="W631" s="7"/>
     </row>
     <row r="632">
-      <c r="A632" s="1"/>
+      <c r="A632" s="2"/>
       <c r="B632" s="7"/>
       <c r="C632" s="7"/>
       <c r="D632" s="7"/>
@@ -16416,7 +16421,7 @@
       <c r="W632" s="7"/>
     </row>
     <row r="633">
-      <c r="A633" s="1"/>
+      <c r="A633" s="2"/>
       <c r="B633" s="7"/>
       <c r="C633" s="7"/>
       <c r="D633" s="7"/>
@@ -16441,7 +16446,7 @@
       <c r="W633" s="7"/>
     </row>
     <row r="634">
-      <c r="A634" s="1"/>
+      <c r="A634" s="2"/>
       <c r="B634" s="7"/>
       <c r="C634" s="7"/>
       <c r="D634" s="7"/>
@@ -16466,7 +16471,7 @@
       <c r="W634" s="7"/>
     </row>
     <row r="635">
-      <c r="A635" s="1"/>
+      <c r="A635" s="2"/>
       <c r="B635" s="7"/>
       <c r="C635" s="7"/>
       <c r="D635" s="7"/>
@@ -16491,7 +16496,7 @@
       <c r="W635" s="7"/>
     </row>
     <row r="636">
-      <c r="A636" s="1"/>
+      <c r="A636" s="2"/>
       <c r="B636" s="7"/>
       <c r="C636" s="7"/>
       <c r="D636" s="7"/>
@@ -16516,7 +16521,7 @@
       <c r="W636" s="7"/>
     </row>
     <row r="637">
-      <c r="A637" s="1"/>
+      <c r="A637" s="2"/>
       <c r="B637" s="7"/>
       <c r="C637" s="7"/>
       <c r="D637" s="7"/>
@@ -16541,7 +16546,7 @@
       <c r="W637" s="7"/>
     </row>
     <row r="638">
-      <c r="A638" s="1"/>
+      <c r="A638" s="2"/>
       <c r="B638" s="7"/>
       <c r="C638" s="7"/>
       <c r="D638" s="7"/>
@@ -16566,7 +16571,7 @@
       <c r="W638" s="7"/>
     </row>
     <row r="639">
-      <c r="A639" s="1"/>
+      <c r="A639" s="2"/>
       <c r="B639" s="7"/>
       <c r="C639" s="7"/>
       <c r="D639" s="7"/>
@@ -16591,7 +16596,7 @@
       <c r="W639" s="7"/>
     </row>
     <row r="640">
-      <c r="A640" s="1"/>
+      <c r="A640" s="2"/>
       <c r="B640" s="7"/>
       <c r="C640" s="7"/>
       <c r="D640" s="7"/>
@@ -16616,7 +16621,7 @@
       <c r="W640" s="7"/>
     </row>
     <row r="641">
-      <c r="A641" s="1"/>
+      <c r="A641" s="2"/>
       <c r="B641" s="7"/>
       <c r="C641" s="7"/>
       <c r="D641" s="7"/>
@@ -16641,7 +16646,7 @@
       <c r="W641" s="7"/>
     </row>
     <row r="642">
-      <c r="A642" s="1"/>
+      <c r="A642" s="2"/>
       <c r="B642" s="7"/>
       <c r="C642" s="7"/>
       <c r="D642" s="7"/>
@@ -16666,7 +16671,7 @@
       <c r="W642" s="7"/>
     </row>
     <row r="643">
-      <c r="A643" s="1"/>
+      <c r="A643" s="2"/>
       <c r="B643" s="7"/>
       <c r="C643" s="7"/>
       <c r="D643" s="7"/>
@@ -16691,7 +16696,7 @@
       <c r="W643" s="7"/>
     </row>
     <row r="644">
-      <c r="A644" s="1"/>
+      <c r="A644" s="2"/>
       <c r="B644" s="7"/>
       <c r="C644" s="7"/>
       <c r="D644" s="7"/>
@@ -16716,7 +16721,7 @@
       <c r="W644" s="7"/>
     </row>
     <row r="645">
-      <c r="A645" s="1"/>
+      <c r="A645" s="2"/>
       <c r="B645" s="7"/>
       <c r="C645" s="7"/>
       <c r="D645" s="7"/>
@@ -16741,7 +16746,7 @@
       <c r="W645" s="7"/>
     </row>
     <row r="646">
-      <c r="A646" s="1"/>
+      <c r="A646" s="2"/>
       <c r="B646" s="7"/>
       <c r="C646" s="7"/>
       <c r="D646" s="7"/>
@@ -16766,7 +16771,7 @@
       <c r="W646" s="7"/>
     </row>
     <row r="647">
-      <c r="A647" s="1"/>
+      <c r="A647" s="2"/>
       <c r="B647" s="7"/>
       <c r="C647" s="7"/>
       <c r="D647" s="7"/>
@@ -16791,7 +16796,7 @@
       <c r="W647" s="7"/>
     </row>
     <row r="648">
-      <c r="A648" s="1"/>
+      <c r="A648" s="2"/>
       <c r="B648" s="7"/>
       <c r="C648" s="7"/>
       <c r="D648" s="7"/>
@@ -16816,7 +16821,7 @@
       <c r="W648" s="7"/>
     </row>
     <row r="649">
-      <c r="A649" s="1"/>
+      <c r="A649" s="2"/>
       <c r="B649" s="7"/>
       <c r="C649" s="7"/>
       <c r="D649" s="7"/>
@@ -16841,7 +16846,7 @@
       <c r="W649" s="7"/>
     </row>
     <row r="650">
-      <c r="A650" s="1"/>
+      <c r="A650" s="2"/>
       <c r="B650" s="7"/>
       <c r="C650" s="7"/>
       <c r="D650" s="7"/>
@@ -16866,7 +16871,7 @@
       <c r="W650" s="7"/>
     </row>
     <row r="651">
-      <c r="A651" s="1"/>
+      <c r="A651" s="2"/>
       <c r="B651" s="7"/>
       <c r="C651" s="7"/>
       <c r="D651" s="7"/>
@@ -16891,7 +16896,7 @@
       <c r="W651" s="7"/>
     </row>
     <row r="652">
-      <c r="A652" s="1"/>
+      <c r="A652" s="2"/>
       <c r="B652" s="7"/>
       <c r="C652" s="7"/>
       <c r="D652" s="7"/>
@@ -16916,7 +16921,7 @@
       <c r="W652" s="7"/>
     </row>
     <row r="653">
-      <c r="A653" s="1"/>
+      <c r="A653" s="2"/>
       <c r="B653" s="7"/>
       <c r="C653" s="7"/>
       <c r="D653" s="7"/>
@@ -16941,7 +16946,7 @@
       <c r="W653" s="7"/>
     </row>
     <row r="654">
-      <c r="A654" s="1"/>
+      <c r="A654" s="2"/>
       <c r="B654" s="7"/>
       <c r="C654" s="7"/>
       <c r="D654" s="7"/>
@@ -16966,7 +16971,7 @@
       <c r="W654" s="7"/>
     </row>
     <row r="655">
-      <c r="A655" s="1"/>
+      <c r="A655" s="2"/>
       <c r="B655" s="7"/>
       <c r="C655" s="7"/>
       <c r="D655" s="7"/>
@@ -16991,7 +16996,7 @@
       <c r="W655" s="7"/>
     </row>
     <row r="656">
-      <c r="A656" s="1"/>
+      <c r="A656" s="2"/>
       <c r="B656" s="7"/>
       <c r="C656" s="7"/>
       <c r="D656" s="7"/>
@@ -17016,7 +17021,7 @@
       <c r="W656" s="7"/>
     </row>
     <row r="657">
-      <c r="A657" s="1"/>
+      <c r="A657" s="2"/>
       <c r="B657" s="7"/>
       <c r="C657" s="7"/>
       <c r="D657" s="7"/>
@@ -17041,7 +17046,7 @@
       <c r="W657" s="7"/>
     </row>
     <row r="658">
-      <c r="A658" s="1"/>
+      <c r="A658" s="2"/>
       <c r="B658" s="7"/>
       <c r="C658" s="7"/>
       <c r="D658" s="7"/>
@@ -17066,7 +17071,7 @@
       <c r="W658" s="7"/>
     </row>
     <row r="659">
-      <c r="A659" s="1"/>
+      <c r="A659" s="2"/>
       <c r="B659" s="7"/>
       <c r="C659" s="7"/>
       <c r="D659" s="7"/>
@@ -17091,7 +17096,7 @@
       <c r="W659" s="7"/>
     </row>
     <row r="660">
-      <c r="A660" s="1"/>
+      <c r="A660" s="2"/>
       <c r="B660" s="7"/>
       <c r="C660" s="7"/>
       <c r="D660" s="7"/>
@@ -17116,7 +17121,7 @@
       <c r="W660" s="7"/>
     </row>
     <row r="661">
-      <c r="A661" s="1"/>
+      <c r="A661" s="2"/>
       <c r="B661" s="7"/>
       <c r="C661" s="7"/>
       <c r="D661" s="7"/>
@@ -17141,7 +17146,7 @@
       <c r="W661" s="7"/>
     </row>
     <row r="662">
-      <c r="A662" s="1"/>
+      <c r="A662" s="2"/>
       <c r="B662" s="7"/>
       <c r="C662" s="7"/>
       <c r="D662" s="7"/>
@@ -17166,7 +17171,7 @@
       <c r="W662" s="7"/>
     </row>
     <row r="663">
-      <c r="A663" s="1"/>
+      <c r="A663" s="2"/>
       <c r="B663" s="7"/>
       <c r="C663" s="7"/>
       <c r="D663" s="7"/>
@@ -17191,7 +17196,7 @@
       <c r="W663" s="7"/>
     </row>
     <row r="664">
-      <c r="A664" s="1"/>
+      <c r="A664" s="2"/>
       <c r="B664" s="7"/>
       <c r="C664" s="7"/>
       <c r="D664" s="7"/>
@@ -17216,7 +17221,7 @@
       <c r="W664" s="7"/>
     </row>
     <row r="665">
-      <c r="A665" s="1"/>
+      <c r="A665" s="2"/>
       <c r="B665" s="7"/>
       <c r="C665" s="7"/>
       <c r="D665" s="7"/>
@@ -17241,7 +17246,7 @@
       <c r="W665" s="7"/>
     </row>
     <row r="666">
-      <c r="A666" s="1"/>
+      <c r="A666" s="2"/>
       <c r="B666" s="7"/>
       <c r="C666" s="7"/>
       <c r="D666" s="7"/>
@@ -17266,7 +17271,7 @@
       <c r="W666" s="7"/>
     </row>
     <row r="667">
-      <c r="A667" s="1"/>
+      <c r="A667" s="2"/>
       <c r="B667" s="7"/>
       <c r="C667" s="7"/>
       <c r="D667" s="7"/>
@@ -17291,7 +17296,7 @@
       <c r="W667" s="7"/>
     </row>
     <row r="668">
-      <c r="A668" s="1"/>
+      <c r="A668" s="2"/>
       <c r="B668" s="7"/>
       <c r="C668" s="7"/>
       <c r="D668" s="7"/>
@@ -17316,7 +17321,7 @@
       <c r="W668" s="7"/>
     </row>
     <row r="669">
-      <c r="A669" s="1"/>
+      <c r="A669" s="2"/>
       <c r="B669" s="7"/>
       <c r="C669" s="7"/>
       <c r="D669" s="7"/>
@@ -17341,7 +17346,7 @@
       <c r="W669" s="7"/>
     </row>
     <row r="670">
-      <c r="A670" s="1"/>
+      <c r="A670" s="2"/>
       <c r="B670" s="7"/>
       <c r="C670" s="7"/>
       <c r="D670" s="7"/>
@@ -17366,7 +17371,7 @@
       <c r="W670" s="7"/>
     </row>
     <row r="671">
-      <c r="A671" s="1"/>
+      <c r="A671" s="2"/>
       <c r="B671" s="7"/>
       <c r="C671" s="7"/>
       <c r="D671" s="7"/>
@@ -17391,7 +17396,7 @@
       <c r="W671" s="7"/>
     </row>
     <row r="672">
-      <c r="A672" s="1"/>
+      <c r="A672" s="2"/>
       <c r="B672" s="7"/>
       <c r="C672" s="7"/>
       <c r="D672" s="7"/>
@@ -17416,7 +17421,7 @@
       <c r="W672" s="7"/>
     </row>
     <row r="673">
-      <c r="A673" s="1"/>
+      <c r="A673" s="2"/>
       <c r="B673" s="7"/>
       <c r="C673" s="7"/>
       <c r="D673" s="7"/>
@@ -17441,7 +17446,7 @@
       <c r="W673" s="7"/>
     </row>
     <row r="674">
-      <c r="A674" s="1"/>
+      <c r="A674" s="2"/>
       <c r="B674" s="7"/>
       <c r="C674" s="7"/>
       <c r="D674" s="7"/>
@@ -17466,7 +17471,7 @@
       <c r="W674" s="7"/>
     </row>
     <row r="675">
-      <c r="A675" s="1"/>
+      <c r="A675" s="2"/>
       <c r="B675" s="7"/>
       <c r="C675" s="7"/>
       <c r="D675" s="7"/>
@@ -17491,7 +17496,7 @@
       <c r="W675" s="7"/>
     </row>
     <row r="676">
-      <c r="A676" s="1"/>
+      <c r="A676" s="2"/>
       <c r="B676" s="7"/>
       <c r="C676" s="7"/>
       <c r="D676" s="7"/>
@@ -17516,7 +17521,7 @@
       <c r="W676" s="7"/>
     </row>
     <row r="677">
-      <c r="A677" s="1"/>
+      <c r="A677" s="2"/>
       <c r="B677" s="7"/>
       <c r="C677" s="7"/>
       <c r="D677" s="7"/>
@@ -17541,7 +17546,7 @@
       <c r="W677" s="7"/>
     </row>
     <row r="678">
-      <c r="A678" s="1"/>
+      <c r="A678" s="2"/>
       <c r="B678" s="7"/>
       <c r="C678" s="7"/>
       <c r="D678" s="7"/>
@@ -17566,7 +17571,7 @@
       <c r="W678" s="7"/>
     </row>
     <row r="679">
-      <c r="A679" s="1"/>
+      <c r="A679" s="2"/>
       <c r="B679" s="7"/>
       <c r="C679" s="7"/>
       <c r="D679" s="7"/>
@@ -17591,7 +17596,7 @@
       <c r="W679" s="7"/>
     </row>
     <row r="680">
-      <c r="A680" s="1"/>
+      <c r="A680" s="2"/>
       <c r="B680" s="7"/>
       <c r="C680" s="7"/>
       <c r="D680" s="7"/>
@@ -17616,7 +17621,7 @@
       <c r="W680" s="7"/>
     </row>
     <row r="681">
-      <c r="A681" s="1"/>
+      <c r="A681" s="2"/>
       <c r="B681" s="7"/>
       <c r="C681" s="7"/>
       <c r="D681" s="7"/>
@@ -17641,7 +17646,7 @@
       <c r="W681" s="7"/>
     </row>
     <row r="682">
-      <c r="A682" s="1"/>
+      <c r="A682" s="2"/>
       <c r="B682" s="7"/>
       <c r="C682" s="7"/>
       <c r="D682" s="7"/>
@@ -17666,7 +17671,7 @@
       <c r="W682" s="7"/>
     </row>
     <row r="683">
-      <c r="A683" s="1"/>
+      <c r="A683" s="2"/>
       <c r="B683" s="7"/>
       <c r="C683" s="7"/>
       <c r="D683" s="7"/>
@@ -17691,7 +17696,7 @@
       <c r="W683" s="7"/>
     </row>
     <row r="684">
-      <c r="A684" s="1"/>
+      <c r="A684" s="2"/>
       <c r="B684" s="7"/>
       <c r="C684" s="7"/>
       <c r="D684" s="7"/>
@@ -17716,7 +17721,7 @@
       <c r="W684" s="7"/>
     </row>
     <row r="685">
-      <c r="A685" s="1"/>
+      <c r="A685" s="2"/>
       <c r="B685" s="7"/>
       <c r="C685" s="7"/>
       <c r="D685" s="7"/>
@@ -17741,7 +17746,7 @@
       <c r="W685" s="7"/>
     </row>
     <row r="686">
-      <c r="A686" s="1"/>
+      <c r="A686" s="2"/>
       <c r="B686" s="7"/>
       <c r="C686" s="7"/>
       <c r="D686" s="7"/>
@@ -17766,7 +17771,7 @@
       <c r="W686" s="7"/>
     </row>
     <row r="687">
-      <c r="A687" s="1"/>
+      <c r="A687" s="2"/>
       <c r="B687" s="7"/>
       <c r="C687" s="7"/>
       <c r="D687" s="7"/>
@@ -17791,7 +17796,7 @@
       <c r="W687" s="7"/>
     </row>
     <row r="688">
-      <c r="A688" s="1"/>
+      <c r="A688" s="2"/>
       <c r="B688" s="7"/>
       <c r="C688" s="7"/>
       <c r="D688" s="7"/>
@@ -17816,7 +17821,7 @@
       <c r="W688" s="7"/>
     </row>
     <row r="689">
-      <c r="A689" s="1"/>
+      <c r="A689" s="2"/>
       <c r="B689" s="7"/>
       <c r="C689" s="7"/>
       <c r="D689" s="7"/>
@@ -17841,7 +17846,7 @@
       <c r="W689" s="7"/>
     </row>
     <row r="690">
-      <c r="A690" s="1"/>
+      <c r="A690" s="2"/>
       <c r="B690" s="7"/>
       <c r="C690" s="7"/>
       <c r="D690" s="7"/>
@@ -17866,7 +17871,7 @@
       <c r="W690" s="7"/>
     </row>
     <row r="691">
-      <c r="A691" s="1"/>
+      <c r="A691" s="2"/>
       <c r="B691" s="7"/>
       <c r="C691" s="7"/>
       <c r="D691" s="7"/>
@@ -17891,7 +17896,7 @@
       <c r="W691" s="7"/>
     </row>
     <row r="692">
-      <c r="A692" s="1"/>
+      <c r="A692" s="2"/>
       <c r="B692" s="7"/>
       <c r="C692" s="7"/>
       <c r="D692" s="7"/>
@@ -17916,7 +17921,7 @@
       <c r="W692" s="7"/>
     </row>
     <row r="693">
-      <c r="A693" s="1"/>
+      <c r="A693" s="2"/>
       <c r="B693" s="7"/>
       <c r="C693" s="7"/>
       <c r="D693" s="7"/>
@@ -17941,7 +17946,7 @@
       <c r="W693" s="7"/>
     </row>
     <row r="694">
-      <c r="A694" s="1"/>
+      <c r="A694" s="2"/>
       <c r="B694" s="7"/>
       <c r="C694" s="7"/>
       <c r="D694" s="7"/>
@@ -17966,7 +17971,7 @@
       <c r="W694" s="7"/>
     </row>
     <row r="695">
-      <c r="A695" s="1"/>
+      <c r="A695" s="2"/>
       <c r="B695" s="7"/>
       <c r="C695" s="7"/>
       <c r="D695" s="7"/>
@@ -17991,7 +17996,7 @@
       <c r="W695" s="7"/>
     </row>
     <row r="696">
-      <c r="A696" s="1"/>
+      <c r="A696" s="2"/>
       <c r="B696" s="7"/>
       <c r="C696" s="7"/>
       <c r="D696" s="7"/>
@@ -18016,7 +18021,7 @@
       <c r="W696" s="7"/>
     </row>
     <row r="697">
-      <c r="A697" s="1"/>
+      <c r="A697" s="2"/>
       <c r="B697" s="7"/>
       <c r="C697" s="7"/>
       <c r="D697" s="7"/>
@@ -18041,7 +18046,7 @@
       <c r="W697" s="7"/>
     </row>
     <row r="698">
-      <c r="A698" s="1"/>
+      <c r="A698" s="2"/>
       <c r="B698" s="7"/>
       <c r="C698" s="7"/>
       <c r="D698" s="7"/>
@@ -18066,7 +18071,7 @@
       <c r="W698" s="7"/>
     </row>
     <row r="699">
-      <c r="A699" s="1"/>
+      <c r="A699" s="2"/>
       <c r="B699" s="7"/>
       <c r="C699" s="7"/>
       <c r="D699" s="7"/>
@@ -18091,7 +18096,7 @@
       <c r="W699" s="7"/>
     </row>
     <row r="700">
-      <c r="A700" s="1"/>
+      <c r="A700" s="2"/>
       <c r="B700" s="7"/>
       <c r="C700" s="7"/>
       <c r="D700" s="7"/>
@@ -18116,7 +18121,7 @@
       <c r="W700" s="7"/>
     </row>
     <row r="701">
-      <c r="A701" s="1"/>
+      <c r="A701" s="2"/>
       <c r="B701" s="7"/>
       <c r="C701" s="7"/>
       <c r="D701" s="7"/>
@@ -18141,7 +18146,7 @@
       <c r="W701" s="7"/>
     </row>
     <row r="702">
-      <c r="A702" s="1"/>
+      <c r="A702" s="2"/>
       <c r="B702" s="7"/>
       <c r="C702" s="7"/>
       <c r="D702" s="7"/>
@@ -18166,7 +18171,7 @@
       <c r="W702" s="7"/>
     </row>
     <row r="703">
-      <c r="A703" s="1"/>
+      <c r="A703" s="2"/>
       <c r="B703" s="7"/>
       <c r="C703" s="7"/>
       <c r="D703" s="7"/>
@@ -18191,7 +18196,7 @@
       <c r="W703" s="7"/>
     </row>
     <row r="704">
-      <c r="A704" s="1"/>
+      <c r="A704" s="2"/>
       <c r="B704" s="7"/>
       <c r="C704" s="7"/>
       <c r="D704" s="7"/>
@@ -18216,7 +18221,7 @@
       <c r="W704" s="7"/>
     </row>
     <row r="705">
-      <c r="A705" s="1"/>
+      <c r="A705" s="2"/>
       <c r="B705" s="7"/>
       <c r="C705" s="7"/>
       <c r="D705" s="7"/>
@@ -18241,7 +18246,7 @@
       <c r="W705" s="7"/>
     </row>
     <row r="706">
-      <c r="A706" s="1"/>
+      <c r="A706" s="2"/>
       <c r="B706" s="7"/>
       <c r="C706" s="7"/>
       <c r="D706" s="7"/>
@@ -18266,7 +18271,7 @@
       <c r="W706" s="7"/>
     </row>
     <row r="707">
-      <c r="A707" s="1"/>
+      <c r="A707" s="2"/>
       <c r="B707" s="7"/>
       <c r="C707" s="7"/>
       <c r="D707" s="7"/>
@@ -18291,7 +18296,7 @@
       <c r="W707" s="7"/>
     </row>
     <row r="708">
-      <c r="A708" s="1"/>
+      <c r="A708" s="2"/>
       <c r="B708" s="7"/>
       <c r="C708" s="7"/>
       <c r="D708" s="7"/>
@@ -18316,7 +18321,7 @@
       <c r="W708" s="7"/>
     </row>
     <row r="709">
-      <c r="A709" s="1"/>
+      <c r="A709" s="2"/>
       <c r="B709" s="7"/>
       <c r="C709" s="7"/>
       <c r="D709" s="7"/>
@@ -18341,7 +18346,7 @@
       <c r="W709" s="7"/>
     </row>
     <row r="710">
-      <c r="A710" s="1"/>
+      <c r="A710" s="2"/>
       <c r="B710" s="7"/>
       <c r="C710" s="7"/>
       <c r="D710" s="7"/>
@@ -18366,7 +18371,7 @@
       <c r="W710" s="7"/>
     </row>
     <row r="711">
-      <c r="A711" s="1"/>
+      <c r="A711" s="2"/>
       <c r="B711" s="7"/>
       <c r="C711" s="7"/>
       <c r="D711" s="7"/>
@@ -18391,7 +18396,7 @@
       <c r="W711" s="7"/>
     </row>
     <row r="712">
-      <c r="A712" s="1"/>
+      <c r="A712" s="2"/>
       <c r="B712" s="7"/>
       <c r="C712" s="7"/>
       <c r="D712" s="7"/>
@@ -18416,7 +18421,7 @@
       <c r="W712" s="7"/>
     </row>
     <row r="713">
-      <c r="A713" s="1"/>
+      <c r="A713" s="2"/>
       <c r="B713" s="7"/>
       <c r="C713" s="7"/>
       <c r="D713" s="7"/>
@@ -18441,7 +18446,7 @@
       <c r="W713" s="7"/>
     </row>
     <row r="714">
-      <c r="A714" s="1"/>
+      <c r="A714" s="2"/>
       <c r="B714" s="7"/>
       <c r="C714" s="7"/>
       <c r="D714" s="7"/>
@@ -18466,7 +18471,7 @@
       <c r="W714" s="7"/>
     </row>
     <row r="715">
-      <c r="A715" s="1"/>
+      <c r="A715" s="2"/>
       <c r="B715" s="7"/>
       <c r="C715" s="7"/>
       <c r="D715" s="7"/>
@@ -18491,7 +18496,7 @@
       <c r="W715" s="7"/>
     </row>
     <row r="716">
-      <c r="A716" s="1"/>
+      <c r="A716" s="2"/>
       <c r="B716" s="7"/>
       <c r="C716" s="7"/>
       <c r="D716" s="7"/>
@@ -18516,7 +18521,7 @@
       <c r="W716" s="7"/>
     </row>
     <row r="717">
-      <c r="A717" s="1"/>
+      <c r="A717" s="2"/>
       <c r="B717" s="7"/>
       <c r="C717" s="7"/>
       <c r="D717" s="7"/>
@@ -18541,7 +18546,7 @@
       <c r="W717" s="7"/>
     </row>
     <row r="718">
-      <c r="A718" s="1"/>
+      <c r="A718" s="2"/>
       <c r="B718" s="7"/>
       <c r="C718" s="7"/>
       <c r="D718" s="7"/>
@@ -18566,7 +18571,7 @@
       <c r="W718" s="7"/>
     </row>
     <row r="719">
-      <c r="A719" s="1"/>
+      <c r="A719" s="2"/>
       <c r="B719" s="7"/>
       <c r="C719" s="7"/>
       <c r="D719" s="7"/>
@@ -18591,7 +18596,7 @@
       <c r="W719" s="7"/>
     </row>
     <row r="720">
-      <c r="A720" s="1"/>
+      <c r="A720" s="2"/>
       <c r="B720" s="7"/>
       <c r="C720" s="7"/>
       <c r="D720" s="7"/>
@@ -18616,7 +18621,7 @@
       <c r="W720" s="7"/>
     </row>
     <row r="721">
-      <c r="A721" s="1"/>
+      <c r="A721" s="2"/>
       <c r="B721" s="7"/>
       <c r="C721" s="7"/>
       <c r="D721" s="7"/>
@@ -18641,7 +18646,7 @@
       <c r="W721" s="7"/>
     </row>
     <row r="722">
-      <c r="A722" s="1"/>
+      <c r="A722" s="2"/>
       <c r="B722" s="7"/>
       <c r="C722" s="7"/>
       <c r="D722" s="7"/>
@@ -18666,7 +18671,7 @@
       <c r="W722" s="7"/>
     </row>
     <row r="723">
-      <c r="A723" s="1"/>
+      <c r="A723" s="2"/>
       <c r="B723" s="7"/>
       <c r="C723" s="7"/>
       <c r="D723" s="7"/>
@@ -18691,7 +18696,7 @@
       <c r="W723" s="7"/>
     </row>
     <row r="724">
-      <c r="A724" s="1"/>
+      <c r="A724" s="2"/>
       <c r="B724" s="7"/>
       <c r="C724" s="7"/>
       <c r="D724" s="7"/>
@@ -18716,7 +18721,7 @@
       <c r="W724" s="7"/>
     </row>
     <row r="725">
-      <c r="A725" s="1"/>
+      <c r="A725" s="2"/>
       <c r="B725" s="7"/>
       <c r="C725" s="7"/>
       <c r="D725" s="7"/>
@@ -18741,7 +18746,7 @@
       <c r="W725" s="7"/>
     </row>
     <row r="726">
-      <c r="A726" s="1"/>
+      <c r="A726" s="2"/>
       <c r="B726" s="7"/>
       <c r="C726" s="7"/>
       <c r="D726" s="7"/>
@@ -18766,7 +18771,7 @@
       <c r="W726" s="7"/>
     </row>
     <row r="727">
-      <c r="A727" s="1"/>
+      <c r="A727" s="2"/>
       <c r="B727" s="7"/>
       <c r="C727" s="7"/>
       <c r="D727" s="7"/>
@@ -18791,7 +18796,7 @@
       <c r="W727" s="7"/>
     </row>
     <row r="728">
-      <c r="A728" s="1"/>
+      <c r="A728" s="2"/>
       <c r="B728" s="7"/>
       <c r="C728" s="7"/>
       <c r="D728" s="7"/>
@@ -18816,7 +18821,7 @@
       <c r="W728" s="7"/>
     </row>
     <row r="729">
-      <c r="A729" s="1"/>
+      <c r="A729" s="2"/>
       <c r="B729" s="7"/>
       <c r="C729" s="7"/>
       <c r="D729" s="7"/>
@@ -18841,7 +18846,7 @@
       <c r="W729" s="7"/>
     </row>
     <row r="730">
-      <c r="A730" s="1"/>
+      <c r="A730" s="2"/>
       <c r="B730" s="7"/>
       <c r="C730" s="7"/>
       <c r="D730" s="7"/>
@@ -18866,7 +18871,7 @@
       <c r="W730" s="7"/>
     </row>
     <row r="731">
-      <c r="A731" s="1"/>
+      <c r="A731" s="2"/>
       <c r="B731" s="7"/>
       <c r="C731" s="7"/>
       <c r="D731" s="7"/>
@@ -18891,7 +18896,7 @@
       <c r="W731" s="7"/>
     </row>
     <row r="732">
-      <c r="A732" s="1"/>
+      <c r="A732" s="2"/>
       <c r="B732" s="7"/>
       <c r="C732" s="7"/>
       <c r="D732" s="7"/>
@@ -18916,7 +18921,7 @@
       <c r="W732" s="7"/>
     </row>
     <row r="733">
-      <c r="A733" s="1"/>
+      <c r="A733" s="2"/>
       <c r="B733" s="7"/>
       <c r="C733" s="7"/>
       <c r="D733" s="7"/>
@@ -18941,7 +18946,7 @@
       <c r="W733" s="7"/>
     </row>
     <row r="734">
-      <c r="A734" s="1"/>
+      <c r="A734" s="2"/>
       <c r="B734" s="7"/>
       <c r="C734" s="7"/>
       <c r="D734" s="7"/>
@@ -18966,7 +18971,7 @@
       <c r="W734" s="7"/>
     </row>
     <row r="735">
-      <c r="A735" s="1"/>
+      <c r="A735" s="2"/>
       <c r="B735" s="7"/>
       <c r="C735" s="7"/>
       <c r="D735" s="7"/>
@@ -18991,7 +18996,7 @@
       <c r="W735" s="7"/>
     </row>
     <row r="736">
-      <c r="A736" s="1"/>
+      <c r="A736" s="2"/>
       <c r="B736" s="7"/>
       <c r="C736" s="7"/>
       <c r="D736" s="7"/>
@@ -19016,7 +19021,7 @@
       <c r="W736" s="7"/>
     </row>
     <row r="737">
-      <c r="A737" s="1"/>
+      <c r="A737" s="2"/>
       <c r="B737" s="7"/>
       <c r="C737" s="7"/>
       <c r="D737" s="7"/>
@@ -19041,7 +19046,7 @@
       <c r="W737" s="7"/>
     </row>
     <row r="738">
-      <c r="A738" s="1"/>
+      <c r="A738" s="2"/>
       <c r="B738" s="7"/>
       <c r="C738" s="7"/>
       <c r="D738" s="7"/>
@@ -19066,7 +19071,7 @@
       <c r="W738" s="7"/>
     </row>
     <row r="739">
-      <c r="A739" s="1"/>
+      <c r="A739" s="2"/>
       <c r="B739" s="7"/>
       <c r="C739" s="7"/>
       <c r="D739" s="7"/>
@@ -19091,7 +19096,7 @@
       <c r="W739" s="7"/>
     </row>
     <row r="740">
-      <c r="A740" s="1"/>
+      <c r="A740" s="2"/>
       <c r="B740" s="7"/>
       <c r="C740" s="7"/>
       <c r="D740" s="7"/>
@@ -19116,7 +19121,7 @@
       <c r="W740" s="7"/>
     </row>
     <row r="741">
-      <c r="A741" s="1"/>
+      <c r="A741" s="2"/>
       <c r="B741" s="7"/>
       <c r="C741" s="7"/>
       <c r="D741" s="7"/>
@@ -19141,7 +19146,7 @@
       <c r="W741" s="7"/>
     </row>
     <row r="742">
-      <c r="A742" s="1"/>
+      <c r="A742" s="2"/>
       <c r="B742" s="7"/>
       <c r="C742" s="7"/>
       <c r="D742" s="7"/>
@@ -19166,7 +19171,7 @@
       <c r="W742" s="7"/>
     </row>
     <row r="743">
-      <c r="A743" s="1"/>
+      <c r="A743" s="2"/>
       <c r="B743" s="7"/>
       <c r="C743" s="7"/>
       <c r="D743" s="7"/>
@@ -19191,7 +19196,7 @@
       <c r="W743" s="7"/>
     </row>
     <row r="744">
-      <c r="A744" s="1"/>
+      <c r="A744" s="2"/>
       <c r="B744" s="7"/>
       <c r="C744" s="7"/>
       <c r="D744" s="7"/>
@@ -19216,7 +19221,7 @@
       <c r="W744" s="7"/>
     </row>
     <row r="745">
-      <c r="A745" s="1"/>
+      <c r="A745" s="2"/>
       <c r="B745" s="7"/>
       <c r="C745" s="7"/>
       <c r="D745" s="7"/>
@@ -19241,7 +19246,7 @@
       <c r="W745" s="7"/>
     </row>
     <row r="746">
-      <c r="A746" s="1"/>
+      <c r="A746" s="2"/>
       <c r="B746" s="7"/>
       <c r="C746" s="7"/>
       <c r="D746" s="7"/>
@@ -19266,7 +19271,7 @@
       <c r="W746" s="7"/>
     </row>
     <row r="747">
-      <c r="A747" s="1"/>
+      <c r="A747" s="2"/>
       <c r="B747" s="7"/>
       <c r="C747" s="7"/>
       <c r="D747" s="7"/>
@@ -19291,7 +19296,7 @@
       <c r="W747" s="7"/>
     </row>
     <row r="748">
-      <c r="A748" s="1"/>
+      <c r="A748" s="2"/>
       <c r="B748" s="7"/>
       <c r="C748" s="7"/>
       <c r="D748" s="7"/>
@@ -19316,7 +19321,7 @@
       <c r="W748" s="7"/>
     </row>
     <row r="749">
-      <c r="A749" s="1"/>
+      <c r="A749" s="2"/>
       <c r="B749" s="7"/>
       <c r="C749" s="7"/>
       <c r="D749" s="7"/>
@@ -19341,7 +19346,7 @@
       <c r="W749" s="7"/>
     </row>
     <row r="750">
-      <c r="A750" s="1"/>
+      <c r="A750" s="2"/>
       <c r="B750" s="7"/>
       <c r="C750" s="7"/>
       <c r="D750" s="7"/>
@@ -19366,7 +19371,7 @@
       <c r="W750" s="7"/>
     </row>
     <row r="751">
-      <c r="A751" s="1"/>
+      <c r="A751" s="2"/>
       <c r="B751" s="7"/>
       <c r="C751" s="7"/>
       <c r="D751" s="7"/>
@@ -19391,7 +19396,7 @@
       <c r="W751" s="7"/>
     </row>
     <row r="752">
-      <c r="A752" s="1"/>
+      <c r="A752" s="2"/>
       <c r="B752" s="7"/>
       <c r="C752" s="7"/>
       <c r="D752" s="7"/>
@@ -19416,7 +19421,7 @@
       <c r="W752" s="7"/>
     </row>
     <row r="753">
-      <c r="A753" s="1"/>
+      <c r="A753" s="2"/>
       <c r="B753" s="7"/>
       <c r="C753" s="7"/>
       <c r="D753" s="7"/>
@@ -19441,7 +19446,7 @@
       <c r="W753" s="7"/>
     </row>
     <row r="754">
-      <c r="A754" s="1"/>
+      <c r="A754" s="2"/>
       <c r="B754" s="7"/>
       <c r="C754" s="7"/>
       <c r="D754" s="7"/>
@@ -19466,7 +19471,7 @@
       <c r="W754" s="7"/>
     </row>
     <row r="755">
-      <c r="A755" s="1"/>
+      <c r="A755" s="2"/>
       <c r="B755" s="7"/>
       <c r="C755" s="7"/>
       <c r="D755" s="7"/>
@@ -19491,7 +19496,7 @@
       <c r="W755" s="7"/>
     </row>
     <row r="756">
-      <c r="A756" s="1"/>
+      <c r="A756" s="2"/>
       <c r="B756" s="7"/>
       <c r="C756" s="7"/>
       <c r="D756" s="7"/>
@@ -19516,7 +19521,7 @@
       <c r="W756" s="7"/>
     </row>
     <row r="757">
-      <c r="A757" s="1"/>
+      <c r="A757" s="2"/>
       <c r="B757" s="7"/>
       <c r="C757" s="7"/>
       <c r="D757" s="7"/>
@@ -19541,7 +19546,7 @@
       <c r="W757" s="7"/>
     </row>
     <row r="758">
-      <c r="A758" s="1"/>
+      <c r="A758" s="2"/>
       <c r="B758" s="7"/>
       <c r="C758" s="7"/>
       <c r="D758" s="7"/>
@@ -19566,7 +19571,7 @@
       <c r="W758" s="7"/>
     </row>
     <row r="759">
-      <c r="A759" s="1"/>
+      <c r="A759" s="2"/>
       <c r="B759" s="7"/>
       <c r="C759" s="7"/>
       <c r="D759" s="7"/>
@@ -19591,7 +19596,7 @@
       <c r="W759" s="7"/>
     </row>
     <row r="760">
-      <c r="A760" s="1"/>
+      <c r="A760" s="2"/>
       <c r="B760" s="7"/>
       <c r="C760" s="7"/>
       <c r="D760" s="7"/>
@@ -19616,7 +19621,7 @@
       <c r="W760" s="7"/>
     </row>
     <row r="761">
-      <c r="A761" s="1"/>
+      <c r="A761" s="2"/>
       <c r="B761" s="7"/>
       <c r="C761" s="7"/>
       <c r="D761" s="7"/>
@@ -19641,7 +19646,7 @@
       <c r="W761" s="7"/>
     </row>
     <row r="762">
-      <c r="A762" s="1"/>
+      <c r="A762" s="2"/>
       <c r="B762" s="7"/>
       <c r="C762" s="7"/>
       <c r="D762" s="7"/>
@@ -19666,7 +19671,7 @@
       <c r="W762" s="7"/>
     </row>
     <row r="763">
-      <c r="A763" s="1"/>
+      <c r="A763" s="2"/>
       <c r="B763" s="7"/>
       <c r="C763" s="7"/>
       <c r="D763" s="7"/>
@@ -19691,7 +19696,7 @@
       <c r="W763" s="7"/>
     </row>
     <row r="764">
-      <c r="A764" s="1"/>
+      <c r="A764" s="2"/>
       <c r="B764" s="7"/>
       <c r="C764" s="7"/>
       <c r="D764" s="7"/>
@@ -19716,7 +19721,7 @@
       <c r="W764" s="7"/>
     </row>
     <row r="765">
-      <c r="A765" s="1"/>
+      <c r="A765" s="2"/>
       <c r="B765" s="7"/>
       <c r="C765" s="7"/>
       <c r="D765" s="7"/>
@@ -19741,7 +19746,7 @@
       <c r="W765" s="7"/>
     </row>
     <row r="766">
-      <c r="A766" s="1"/>
+      <c r="A766" s="2"/>
       <c r="B766" s="7"/>
       <c r="C766" s="7"/>
       <c r="D766" s="7"/>
@@ -19766,7 +19771,7 @@
       <c r="W766" s="7"/>
     </row>
     <row r="767">
-      <c r="A767" s="1"/>
+      <c r="A767" s="2"/>
       <c r="B767" s="7"/>
       <c r="C767" s="7"/>
       <c r="D767" s="7"/>
@@ -19791,7 +19796,7 @@
       <c r="W767" s="7"/>
     </row>
     <row r="768">
-      <c r="A768" s="1"/>
+      <c r="A768" s="2"/>
       <c r="B768" s="7"/>
       <c r="C768" s="7"/>
       <c r="D768" s="7"/>
@@ -19816,7 +19821,7 @@
       <c r="W768" s="7"/>
     </row>
     <row r="769">
-      <c r="A769" s="1"/>
+      <c r="A769" s="2"/>
       <c r="B769" s="7"/>
       <c r="C769" s="7"/>
       <c r="D769" s="7"/>
@@ -19841,7 +19846,7 @@
       <c r="W769" s="7"/>
     </row>
     <row r="770">
-      <c r="A770" s="1"/>
+      <c r="A770" s="2"/>
       <c r="B770" s="7"/>
       <c r="C770" s="7"/>
       <c r="D770" s="7"/>
@@ -19866,7 +19871,7 @@
       <c r="W770" s="7"/>
     </row>
     <row r="771">
-      <c r="A771" s="1"/>
+      <c r="A771" s="2"/>
       <c r="B771" s="7"/>
       <c r="C771" s="7"/>
       <c r="D771" s="7"/>
@@ -19891,7 +19896,7 @@
       <c r="W771" s="7"/>
     </row>
     <row r="772">
-      <c r="A772" s="1"/>
+      <c r="A772" s="2"/>
       <c r="B772" s="7"/>
       <c r="C772" s="7"/>
       <c r="D772" s="7"/>
@@ -19916,7 +19921,7 @@
       <c r="W772" s="7"/>
     </row>
     <row r="773">
-      <c r="A773" s="1"/>
+      <c r="A773" s="2"/>
       <c r="B773" s="7"/>
       <c r="C773" s="7"/>
       <c r="D773" s="7"/>
@@ -19941,7 +19946,7 @@
       <c r="W773" s="7"/>
     </row>
     <row r="774">
-      <c r="A774" s="1"/>
+      <c r="A774" s="2"/>
       <c r="B774" s="7"/>
       <c r="C774" s="7"/>
       <c r="D774" s="7"/>
@@ -19966,7 +19971,7 @@
       <c r="W774" s="7"/>
     </row>
     <row r="775">
-      <c r="A775" s="1"/>
+      <c r="A775" s="2"/>
       <c r="B775" s="7"/>
       <c r="C775" s="7"/>
       <c r="D775" s="7"/>
@@ -19991,7 +19996,7 @@
       <c r="W775" s="7"/>
     </row>
     <row r="776">
-      <c r="A776" s="1"/>
+      <c r="A776" s="2"/>
       <c r="B776" s="7"/>
       <c r="C776" s="7"/>
       <c r="D776" s="7"/>
@@ -20016,7 +20021,7 @@
       <c r="W776" s="7"/>
     </row>
     <row r="777">
-      <c r="A777" s="1"/>
+      <c r="A777" s="2"/>
       <c r="B777" s="7"/>
       <c r="C777" s="7"/>
       <c r="D777" s="7"/>
@@ -20041,7 +20046,7 @@
       <c r="W777" s="7"/>
     </row>
     <row r="778">
-      <c r="A778" s="1"/>
+      <c r="A778" s="2"/>
       <c r="B778" s="7"/>
       <c r="C778" s="7"/>
       <c r="D778" s="7"/>
@@ -20066,7 +20071,7 @@
       <c r="W778" s="7"/>
     </row>
     <row r="779">
-      <c r="A779" s="1"/>
+      <c r="A779" s="2"/>
       <c r="B779" s="7"/>
       <c r="C779" s="7"/>
       <c r="D779" s="7"/>
@@ -20091,7 +20096,7 @@
       <c r="W779" s="7"/>
     </row>
     <row r="780">
-      <c r="A780" s="1"/>
+      <c r="A780" s="2"/>
       <c r="B780" s="7"/>
       <c r="C780" s="7"/>
       <c r="D780" s="7"/>
@@ -20116,7 +20121,7 @@
       <c r="W780" s="7"/>
     </row>
     <row r="781">
-      <c r="A781" s="1"/>
+      <c r="A781" s="2"/>
       <c r="B781" s="7"/>
       <c r="C781" s="7"/>
       <c r="D781" s="7"/>
@@ -20141,7 +20146,7 @@
       <c r="W781" s="7"/>
     </row>
     <row r="782">
-      <c r="A782" s="1"/>
+      <c r="A782" s="2"/>
       <c r="B782" s="7"/>
       <c r="C782" s="7"/>
       <c r="D782" s="7"/>
@@ -20166,7 +20171,7 @@
       <c r="W782" s="7"/>
     </row>
     <row r="783">
-      <c r="A783" s="1"/>
+      <c r="A783" s="2"/>
       <c r="B783" s="7"/>
       <c r="C783" s="7"/>
       <c r="D783" s="7"/>
@@ -20191,7 +20196,7 @@
       <c r="W783" s="7"/>
     </row>
     <row r="784">
-      <c r="A784" s="1"/>
+      <c r="A784" s="2"/>
       <c r="B784" s="7"/>
       <c r="C784" s="7"/>
       <c r="D784" s="7"/>
@@ -20216,7 +20221,7 @@
       <c r="W784" s="7"/>
     </row>
     <row r="785">
-      <c r="A785" s="1"/>
+      <c r="A785" s="2"/>
       <c r="B785" s="7"/>
       <c r="C785" s="7"/>
       <c r="D785" s="7"/>
@@ -20241,7 +20246,7 @@
       <c r="W785" s="7"/>
     </row>
     <row r="786">
-      <c r="A786" s="1"/>
+      <c r="A786" s="2"/>
       <c r="B786" s="7"/>
       <c r="C786" s="7"/>
       <c r="D786" s="7"/>
@@ -20266,7 +20271,7 @@
       <c r="W786" s="7"/>
     </row>
     <row r="787">
-      <c r="A787" s="1"/>
+      <c r="A787" s="2"/>
       <c r="B787" s="7"/>
       <c r="C787" s="7"/>
       <c r="D787" s="7"/>
@@ -20291,7 +20296,7 @@
       <c r="W787" s="7"/>
     </row>
     <row r="788">
-      <c r="A788" s="1"/>
+      <c r="A788" s="2"/>
       <c r="B788" s="7"/>
       <c r="C788" s="7"/>
       <c r="D788" s="7"/>
@@ -20316,7 +20321,7 @@
       <c r="W788" s="7"/>
     </row>
     <row r="789">
-      <c r="A789" s="1"/>
+      <c r="A789" s="2"/>
       <c r="B789" s="7"/>
       <c r="C789" s="7"/>
       <c r="D789" s="7"/>
@@ -20341,7 +20346,7 @@
       <c r="W789" s="7"/>
     </row>
     <row r="790">
-      <c r="A790" s="1"/>
+      <c r="A790" s="2"/>
       <c r="B790" s="7"/>
       <c r="C790" s="7"/>
       <c r="D790" s="7"/>
@@ -20366,7 +20371,7 @@
       <c r="W790" s="7"/>
     </row>
     <row r="791">
-      <c r="A791" s="1"/>
+      <c r="A791" s="2"/>
       <c r="B791" s="7"/>
       <c r="C791" s="7"/>
       <c r="D791" s="7"/>
@@ -20391,7 +20396,7 @@
       <c r="W791" s="7"/>
     </row>
     <row r="792">
-      <c r="A792" s="1"/>
+      <c r="A792" s="2"/>
       <c r="B792" s="7"/>
       <c r="C792" s="7"/>
       <c r="D792" s="7"/>
@@ -20416,7 +20421,7 @@
       <c r="W792" s="7"/>
     </row>
     <row r="793">
-      <c r="A793" s="1"/>
+      <c r="A793" s="2"/>
       <c r="B793" s="7"/>
       <c r="C793" s="7"/>
       <c r="D793" s="7"/>
@@ -20441,7 +20446,7 @@
       <c r="W793" s="7"/>
     </row>
     <row r="794">
-      <c r="A794" s="1"/>
+      <c r="A794" s="2"/>
       <c r="B794" s="7"/>
       <c r="C794" s="7"/>
       <c r="D794" s="7"/>
@@ -20466,7 +20471,7 @@
       <c r="W794" s="7"/>
     </row>
     <row r="795">
-      <c r="A795" s="1"/>
+      <c r="A795" s="2"/>
       <c r="B795" s="7"/>
       <c r="C795" s="7"/>
       <c r="D795" s="7"/>
@@ -20491,7 +20496,7 @@
       <c r="W795" s="7"/>
     </row>
     <row r="796">
-      <c r="A796" s="1"/>
+      <c r="A796" s="2"/>
       <c r="B796" s="7"/>
       <c r="C796" s="7"/>
       <c r="D796" s="7"/>
@@ -20516,7 +20521,7 @@
       <c r="W796" s="7"/>
     </row>
     <row r="797">
-      <c r="A797" s="1"/>
+      <c r="A797" s="2"/>
       <c r="B797" s="7"/>
       <c r="C797" s="7"/>
       <c r="D797" s="7"/>
@@ -20541,7 +20546,7 @@
       <c r="W797" s="7"/>
     </row>
     <row r="798">
-      <c r="A798" s="1"/>
+      <c r="A798" s="2"/>
       <c r="B798" s="7"/>
       <c r="C798" s="7"/>
       <c r="D798" s="7"/>
@@ -20566,7 +20571,7 @@
       <c r="W798" s="7"/>
     </row>
     <row r="799">
-      <c r="A799" s="1"/>
+      <c r="A799" s="2"/>
       <c r="B799" s="7"/>
       <c r="C799" s="7"/>
       <c r="D799" s="7"/>
@@ -20591,7 +20596,7 @@
       <c r="W799" s="7"/>
     </row>
     <row r="800">
-      <c r="A800" s="1"/>
+      <c r="A800" s="2"/>
       <c r="B800" s="7"/>
       <c r="C800" s="7"/>
       <c r="D800" s="7"/>
@@ -20616,7 +20621,7 @@
       <c r="W800" s="7"/>
     </row>
     <row r="801">
-      <c r="A801" s="1"/>
+      <c r="A801" s="2"/>
       <c r="B801" s="7"/>
       <c r="C801" s="7"/>
       <c r="D801" s="7"/>
@@ -20641,7 +20646,7 @@
       <c r="W801" s="7"/>
     </row>
     <row r="802">
-      <c r="A802" s="1"/>
+      <c r="A802" s="2"/>
       <c r="B802" s="7"/>
       <c r="C802" s="7"/>
       <c r="D802" s="7"/>
@@ -20666,7 +20671,7 @@
       <c r="W802" s="7"/>
     </row>
     <row r="803">
-      <c r="A803" s="1"/>
+      <c r="A803" s="2"/>
       <c r="B803" s="7"/>
       <c r="C803" s="7"/>
       <c r="D803" s="7"/>
@@ -20691,7 +20696,7 @@
       <c r="W803" s="7"/>
     </row>
     <row r="804">
-      <c r="A804" s="1"/>
+      <c r="A804" s="2"/>
       <c r="B804" s="7"/>
       <c r="C804" s="7"/>
       <c r="D804" s="7"/>
@@ -20716,7 +20721,7 @@
       <c r="W804" s="7"/>
     </row>
     <row r="805">
-      <c r="A805" s="1"/>
+      <c r="A805" s="2"/>
       <c r="B805" s="7"/>
       <c r="C805" s="7"/>
       <c r="D805" s="7"/>
@@ -20741,7 +20746,7 @@
       <c r="W805" s="7"/>
     </row>
     <row r="806">
-      <c r="A806" s="1"/>
+      <c r="A806" s="2"/>
       <c r="B806" s="7"/>
       <c r="C806" s="7"/>
       <c r="D806" s="7"/>
@@ -20766,7 +20771,7 @@
       <c r="W806" s="7"/>
     </row>
     <row r="807">
-      <c r="A807" s="1"/>
+      <c r="A807" s="2"/>
       <c r="B807" s="7"/>
       <c r="C807" s="7"/>
       <c r="D807" s="7"/>
@@ -20791,7 +20796,7 @@
       <c r="W807" s="7"/>
     </row>
     <row r="808">
-      <c r="A808" s="1"/>
+      <c r="A808" s="2"/>
       <c r="B808" s="7"/>
       <c r="C808" s="7"/>
       <c r="D808" s="7"/>
@@ -20816,7 +20821,7 @@
       <c r="W808" s="7"/>
     </row>
     <row r="809">
-      <c r="A809" s="1"/>
+      <c r="A809" s="2"/>
       <c r="B809" s="7"/>
       <c r="C809" s="7"/>
       <c r="D809" s="7"/>
@@ -20841,7 +20846,7 @@
       <c r="W809" s="7"/>
     </row>
     <row r="810">
-      <c r="A810" s="1"/>
+      <c r="A810" s="2"/>
       <c r="B810" s="7"/>
       <c r="C810" s="7"/>
       <c r="D810" s="7"/>
@@ -20866,7 +20871,7 @@
       <c r="W810" s="7"/>
     </row>
     <row r="811">
-      <c r="A811" s="1"/>
+      <c r="A811" s="2"/>
       <c r="B811" s="7"/>
       <c r="C811" s="7"/>
       <c r="D811" s="7"/>
@@ -20891,7 +20896,7 @@
       <c r="W811" s="7"/>
     </row>
     <row r="812">
-      <c r="A812" s="1"/>
+      <c r="A812" s="2"/>
       <c r="B812" s="7"/>
       <c r="C812" s="7"/>
       <c r="D812" s="7"/>
@@ -20916,7 +20921,7 @@
       <c r="W812" s="7"/>
     </row>
     <row r="813">
-      <c r="A813" s="1"/>
+      <c r="A813" s="2"/>
       <c r="B813" s="7"/>
       <c r="C813" s="7"/>
       <c r="D813" s="7"/>
@@ -20941,7 +20946,7 @@
       <c r="W813" s="7"/>
     </row>
     <row r="814">
-      <c r="A814" s="1"/>
+      <c r="A814" s="2"/>
       <c r="B814" s="7"/>
       <c r="C814" s="7"/>
       <c r="D814" s="7"/>
@@ -20966,7 +20971,7 @@
       <c r="W814" s="7"/>
     </row>
     <row r="815">
-      <c r="A815" s="1"/>
+      <c r="A815" s="2"/>
       <c r="B815" s="7"/>
       <c r="C815" s="7"/>
       <c r="D815" s="7"/>
@@ -20991,7 +20996,7 @@
       <c r="W815" s="7"/>
     </row>
     <row r="816">
-      <c r="A816" s="1"/>
+      <c r="A816" s="2"/>
       <c r="B816" s="7"/>
       <c r="C816" s="7"/>
       <c r="D816" s="7"/>
@@ -21016,7 +21021,7 @@
       <c r="W816" s="7"/>
     </row>
     <row r="817">
-      <c r="A817" s="1"/>
+      <c r="A817" s="2"/>
       <c r="B817" s="7"/>
       <c r="C817" s="7"/>
       <c r="D817" s="7"/>
@@ -21041,7 +21046,7 @@
       <c r="W817" s="7"/>
     </row>
     <row r="818">
-      <c r="A818" s="1"/>
+      <c r="A818" s="2"/>
       <c r="B818" s="7"/>
       <c r="C818" s="7"/>
       <c r="D818" s="7"/>
@@ -21066,7 +21071,7 @@
       <c r="W818" s="7"/>
     </row>
     <row r="819">
-      <c r="A819" s="1"/>
+      <c r="A819" s="2"/>
       <c r="B819" s="7"/>
       <c r="C819" s="7"/>
       <c r="D819" s="7"/>
@@ -21091,7 +21096,7 @@
       <c r="W819" s="7"/>
     </row>
     <row r="820">
-      <c r="A820" s="1"/>
+      <c r="A820" s="2"/>
       <c r="B820" s="7"/>
       <c r="C820" s="7"/>
       <c r="D820" s="7"/>
@@ -21116,7 +21121,7 @@
       <c r="W820" s="7"/>
     </row>
     <row r="821">
-      <c r="A821" s="1"/>
+      <c r="A821" s="2"/>
       <c r="B821" s="7"/>
       <c r="C821" s="7"/>
       <c r="D821" s="7"/>
@@ -21141,7 +21146,7 @@
       <c r="W821" s="7"/>
     </row>
     <row r="822">
-      <c r="A822" s="1"/>
+      <c r="A822" s="2"/>
       <c r="B822" s="7"/>
       <c r="C822" s="7"/>
       <c r="D822" s="7"/>
@@ -21166,7 +21171,7 @@
       <c r="W822" s="7"/>
     </row>
     <row r="823">
-      <c r="A823" s="1"/>
+      <c r="A823" s="2"/>
       <c r="B823" s="7"/>
       <c r="C823" s="7"/>
       <c r="D823" s="7"/>
@@ -21191,7 +21196,7 @@
       <c r="W823" s="7"/>
     </row>
     <row r="824">
-      <c r="A824" s="1"/>
+      <c r="A824" s="2"/>
       <c r="B824" s="7"/>
       <c r="C824" s="7"/>
       <c r="D824" s="7"/>
@@ -21216,7 +21221,7 @@
       <c r="W824" s="7"/>
     </row>
     <row r="825">
-      <c r="A825" s="1"/>
+      <c r="A825" s="2"/>
       <c r="B825" s="7"/>
       <c r="C825" s="7"/>
       <c r="D825" s="7"/>
@@ -21241,7 +21246,7 @@
       <c r="W825" s="7"/>
     </row>
     <row r="826">
-      <c r="A826" s="1"/>
+      <c r="A826" s="2"/>
       <c r="B826" s="7"/>
       <c r="C826" s="7"/>
       <c r="D826" s="7"/>
@@ -21266,7 +21271,7 @@
       <c r="W826" s="7"/>
     </row>
     <row r="827">
-      <c r="A827" s="1"/>
+      <c r="A827" s="2"/>
       <c r="B827" s="7"/>
       <c r="C827" s="7"/>
       <c r="D827" s="7"/>
@@ -21291,7 +21296,7 @@
       <c r="W827" s="7"/>
     </row>
     <row r="828">
-      <c r="A828" s="1"/>
+      <c r="A828" s="2"/>
       <c r="B828" s="7"/>
       <c r="C828" s="7"/>
       <c r="D828" s="7"/>
@@ -21316,7 +21321,7 @@
       <c r="W828" s="7"/>
     </row>
     <row r="829">
-      <c r="A829" s="1"/>
+      <c r="A829" s="2"/>
       <c r="B829" s="7"/>
       <c r="C829" s="7"/>
       <c r="D829" s="7"/>
@@ -21341,7 +21346,7 @@
       <c r="W829" s="7"/>
     </row>
     <row r="830">
-      <c r="A830" s="1"/>
+      <c r="A830" s="2"/>
       <c r="B830" s="7"/>
       <c r="C830" s="7"/>
       <c r="D830" s="7"/>
@@ -21366,7 +21371,7 @@
       <c r="W830" s="7"/>
     </row>
     <row r="831">
-      <c r="A831" s="1"/>
+      <c r="A831" s="2"/>
       <c r="B831" s="7"/>
       <c r="C831" s="7"/>
       <c r="D831" s="7"/>
@@ -21391,7 +21396,7 @@
       <c r="W831" s="7"/>
     </row>
     <row r="832">
-      <c r="A832" s="1"/>
+      <c r="A832" s="2"/>
       <c r="B832" s="7"/>
       <c r="C832" s="7"/>
       <c r="D832" s="7"/>
@@ -21416,7 +21421,7 @@
       <c r="W832" s="7"/>
     </row>
     <row r="833">
-      <c r="A833" s="1"/>
+      <c r="A833" s="2"/>
       <c r="B833" s="7"/>
       <c r="C833" s="7"/>
       <c r="D833" s="7"/>
@@ -21441,7 +21446,7 @@
       <c r="W833" s="7"/>
     </row>
     <row r="834">
-      <c r="A834" s="1"/>
+      <c r="A834" s="2"/>
       <c r="B834" s="7"/>
       <c r="C834" s="7"/>
       <c r="D834" s="7"/>
@@ -21466,7 +21471,7 @@
       <c r="W834" s="7"/>
     </row>
     <row r="835">
-      <c r="A835" s="1"/>
+      <c r="A835" s="2"/>
       <c r="B835" s="7"/>
       <c r="C835" s="7"/>
       <c r="D835" s="7"/>
@@ -21491,7 +21496,7 @@
       <c r="W835" s="7"/>
     </row>
     <row r="836">
-      <c r="A836" s="1"/>
+      <c r="A836" s="2"/>
       <c r="B836" s="7"/>
       <c r="C836" s="7"/>
       <c r="D836" s="7"/>
@@ -21516,7 +21521,7 @@
       <c r="W836" s="7"/>
     </row>
     <row r="837">
-      <c r="A837" s="1"/>
+      <c r="A837" s="2"/>
       <c r="B837" s="7"/>
       <c r="C837" s="7"/>
       <c r="D837" s="7"/>
@@ -21541,7 +21546,7 @@
       <c r="W837" s="7"/>
     </row>
     <row r="838">
-      <c r="A838" s="1"/>
+      <c r="A838" s="2"/>
       <c r="B838" s="7"/>
       <c r="C838" s="7"/>
       <c r="D838" s="7"/>
@@ -21566,7 +21571,7 @@
       <c r="W838" s="7"/>
     </row>
     <row r="839">
-      <c r="A839" s="1"/>
+      <c r="A839" s="2"/>
       <c r="B839" s="7"/>
       <c r="C839" s="7"/>
       <c r="D839" s="7"/>
@@ -21591,7 +21596,7 @@
       <c r="W839" s="7"/>
     </row>
     <row r="840">
-      <c r="A840" s="1"/>
+      <c r="A840" s="2"/>
       <c r="B840" s="7"/>
       <c r="C840" s="7"/>
       <c r="D840" s="7"/>
@@ -21616,7 +21621,7 @@
       <c r="W840" s="7"/>
     </row>
     <row r="841">
-      <c r="A841" s="1"/>
+      <c r="A841" s="2"/>
       <c r="B841" s="7"/>
       <c r="C841" s="7"/>
       <c r="D841" s="7"/>
@@ -21641,7 +21646,7 @@
       <c r="W841" s="7"/>
     </row>
     <row r="842">
-      <c r="A842" s="1"/>
+      <c r="A842" s="2"/>
       <c r="B842" s="7"/>
       <c r="C842" s="7"/>
       <c r="D842" s="7"/>
@@ -21666,7 +21671,7 @@
       <c r="W842" s="7"/>
     </row>
     <row r="843">
-      <c r="A843" s="1"/>
+      <c r="A843" s="2"/>
       <c r="B843" s="7"/>
       <c r="C843" s="7"/>
       <c r="D843" s="7"/>
@@ -21691,7 +21696,7 @@
       <c r="W843" s="7"/>
     </row>
     <row r="844">
-      <c r="A844" s="1"/>
+      <c r="A844" s="2"/>
       <c r="B844" s="7"/>
       <c r="C844" s="7"/>
       <c r="D844" s="7"/>
@@ -21716,7 +21721,7 @@
       <c r="W844" s="7"/>
     </row>
     <row r="845">
-      <c r="A845" s="1"/>
+      <c r="A845" s="2"/>
       <c r="B845" s="7"/>
       <c r="C845" s="7"/>
       <c r="D845" s="7"/>
@@ -21741,7 +21746,7 @@
       <c r="W845" s="7"/>
     </row>
     <row r="846">
-      <c r="A846" s="1"/>
+      <c r="A846" s="2"/>
       <c r="B846" s="7"/>
       <c r="C846" s="7"/>
       <c r="D846" s="7"/>
@@ -21766,7 +21771,7 @@
       <c r="W846" s="7"/>
     </row>
     <row r="847">
-      <c r="A847" s="1"/>
+      <c r="A847" s="2"/>
       <c r="B847" s="7"/>
       <c r="C847" s="7"/>
       <c r="D847" s="7"/>
@@ -21791,7 +21796,7 @@
       <c r="W847" s="7"/>
     </row>
     <row r="848">
-      <c r="A848" s="1"/>
+      <c r="A848" s="2"/>
       <c r="B848" s="7"/>
       <c r="C848" s="7"/>
       <c r="D848" s="7"/>
@@ -21816,7 +21821,7 @@
       <c r="W848" s="7"/>
     </row>
     <row r="849">
-      <c r="A849" s="1"/>
+      <c r="A849" s="2"/>
       <c r="B849" s="7"/>
       <c r="C849" s="7"/>
       <c r="D849" s="7"/>
@@ -21841,7 +21846,7 @@
       <c r="W849" s="7"/>
     </row>
     <row r="850">
-      <c r="A850" s="1"/>
+      <c r="A850" s="2"/>
       <c r="B850" s="7"/>
       <c r="C850" s="7"/>
       <c r="D850" s="7"/>
@@ -21866,7 +21871,7 @@
       <c r="W850" s="7"/>
     </row>
     <row r="851">
-      <c r="A851" s="1"/>
+      <c r="A851" s="2"/>
       <c r="B851" s="7"/>
       <c r="C851" s="7"/>
       <c r="D851" s="7"/>
@@ -21891,7 +21896,7 @@
       <c r="W851" s="7"/>
     </row>
     <row r="852">
-      <c r="A852" s="1"/>
+      <c r="A852" s="2"/>
       <c r="B852" s="7"/>
       <c r="C852" s="7"/>
       <c r="D852" s="7"/>
@@ -21916,7 +21921,7 @@
       <c r="W852" s="7"/>
     </row>
     <row r="853">
-      <c r="A853" s="1"/>
+      <c r="A853" s="2"/>
       <c r="B853" s="7"/>
       <c r="C853" s="7"/>
       <c r="D853" s="7"/>
@@ -21941,7 +21946,7 @@
       <c r="W853" s="7"/>
     </row>
     <row r="854">
-      <c r="A854" s="1"/>
+      <c r="A854" s="2"/>
       <c r="B854" s="7"/>
       <c r="C854" s="7"/>
       <c r="D854" s="7"/>
@@ -21966,7 +21971,7 @@
       <c r="W854" s="7"/>
     </row>
     <row r="855">
-      <c r="A855" s="1"/>
+      <c r="A855" s="2"/>
       <c r="B855" s="7"/>
       <c r="C855" s="7"/>
       <c r="D855" s="7"/>
@@ -21991,7 +21996,7 @@
       <c r="W855" s="7"/>
     </row>
     <row r="856">
-      <c r="A856" s="1"/>
+      <c r="A856" s="2"/>
       <c r="B856" s="7"/>
       <c r="C856" s="7"/>
       <c r="D856" s="7"/>
@@ -22016,7 +22021,7 @@
       <c r="W856" s="7"/>
     </row>
     <row r="857">
-      <c r="A857" s="1"/>
+      <c r="A857" s="2"/>
       <c r="B857" s="7"/>
       <c r="C857" s="7"/>
       <c r="D857" s="7"/>
@@ -22041,7 +22046,7 @@
       <c r="W857" s="7"/>
     </row>
     <row r="858">
-      <c r="A858" s="1"/>
+      <c r="A858" s="2"/>
       <c r="B858" s="7"/>
       <c r="C858" s="7"/>
       <c r="D858" s="7"/>
@@ -22066,7 +22071,7 @@
       <c r="W858" s="7"/>
     </row>
     <row r="859">
-      <c r="A859" s="1"/>
+      <c r="A859" s="2"/>
       <c r="B859" s="7"/>
       <c r="C859" s="7"/>
       <c r="D859" s="7"/>
@@ -22091,7 +22096,7 @@
       <c r="W859" s="7"/>
     </row>
     <row r="860">
-      <c r="A860" s="1"/>
+      <c r="A860" s="2"/>
       <c r="B860" s="7"/>
       <c r="C860" s="7"/>
       <c r="D860" s="7"/>
@@ -22116,7 +22121,7 @@
       <c r="W860" s="7"/>
     </row>
     <row r="861">
-      <c r="A861" s="1"/>
+      <c r="A861" s="2"/>
       <c r="B861" s="7"/>
       <c r="C861" s="7"/>
       <c r="D861" s="7"/>
@@ -22141,7 +22146,7 @@
       <c r="W861" s="7"/>
     </row>
     <row r="862">
-      <c r="A862" s="1"/>
+      <c r="A862" s="2"/>
       <c r="B862" s="7"/>
       <c r="C862" s="7"/>
       <c r="D862" s="7"/>
@@ -22166,7 +22171,7 @@
       <c r="W862" s="7"/>
     </row>
     <row r="863">
-      <c r="A863" s="1"/>
+      <c r="A863" s="2"/>
       <c r="B863" s="7"/>
       <c r="C863" s="7"/>
       <c r="D863" s="7"/>
@@ -22191,7 +22196,7 @@
       <c r="W863" s="7"/>
     </row>
     <row r="864">
-      <c r="A864" s="1"/>
+      <c r="A864" s="2"/>
       <c r="B864" s="7"/>
       <c r="C864" s="7"/>
       <c r="D864" s="7"/>
@@ -22216,7 +22221,7 @@
       <c r="W864" s="7"/>
     </row>
     <row r="865">
-      <c r="A865" s="1"/>
+      <c r="A865" s="2"/>
       <c r="B865" s="7"/>
       <c r="C865" s="7"/>
       <c r="D865" s="7"/>
@@ -22241,7 +22246,7 @@
       <c r="W865" s="7"/>
     </row>
     <row r="866">
-      <c r="A866" s="1"/>
+      <c r="A866" s="2"/>
       <c r="B866" s="7"/>
       <c r="C866" s="7"/>
       <c r="D866" s="7"/>
@@ -22266,7 +22271,7 @@
       <c r="W866" s="7"/>
     </row>
     <row r="867">
-      <c r="A867" s="1"/>
+      <c r="A867" s="2"/>
       <c r="B867" s="7"/>
       <c r="C867" s="7"/>
       <c r="D867" s="7"/>
@@ -22291,7 +22296,7 @@
       <c r="W867" s="7"/>
     </row>
     <row r="868">
-      <c r="A868" s="1"/>
+      <c r="A868" s="2"/>
       <c r="B868" s="7"/>
       <c r="C868" s="7"/>
       <c r="D868" s="7"/>
@@ -22316,7 +22321,7 @@
       <c r="W868" s="7"/>
     </row>
     <row r="869">
-      <c r="A869" s="1"/>
+      <c r="A869" s="2"/>
       <c r="B869" s="7"/>
       <c r="C869" s="7"/>
       <c r="D869" s="7"/>
@@ -22341,7 +22346,7 @@
       <c r="W869" s="7"/>
     </row>
     <row r="870">
-      <c r="A870" s="1"/>
+      <c r="A870" s="2"/>
       <c r="B870" s="7"/>
       <c r="C870" s="7"/>
       <c r="D870" s="7"/>
@@ -22366,7 +22371,7 @@
       <c r="W870" s="7"/>
     </row>
     <row r="871">
-      <c r="A871" s="1"/>
+      <c r="A871" s="2"/>
       <c r="B871" s="7"/>
       <c r="C871" s="7"/>
       <c r="D871" s="7"/>
@@ -22391,7 +22396,7 @@
       <c r="W871" s="7"/>
     </row>
     <row r="872">
-      <c r="A872" s="1"/>
+      <c r="A872" s="2"/>
       <c r="B872" s="7"/>
       <c r="C872" s="7"/>
       <c r="D872" s="7"/>
@@ -22416,7 +22421,7 @@
       <c r="W872" s="7"/>
     </row>
     <row r="873">
-      <c r="A873" s="1"/>
+      <c r="A873" s="2"/>
       <c r="B873" s="7"/>
       <c r="C873" s="7"/>
       <c r="D873" s="7"/>
@@ -22441,7 +22446,7 @@
       <c r="W873" s="7"/>
     </row>
     <row r="874">
-      <c r="A874" s="1"/>
+      <c r="A874" s="2"/>
       <c r="B874" s="7"/>
       <c r="C874" s="7"/>
       <c r="D874" s="7"/>
@@ -22466,7 +22471,7 @@
       <c r="W874" s="7"/>
     </row>
     <row r="875">
-      <c r="A875" s="1"/>
+      <c r="A875" s="2"/>
       <c r="B875" s="7"/>
       <c r="C875" s="7"/>
       <c r="D875" s="7"/>
@@ -22491,7 +22496,7 @@
       <c r="W875" s="7"/>
     </row>
     <row r="876">
-      <c r="A876" s="1"/>
+      <c r="A876" s="2"/>
       <c r="B876" s="7"/>
       <c r="C876" s="7"/>
       <c r="D876" s="7"/>
@@ -22516,7 +22521,7 @@
       <c r="W876" s="7"/>
     </row>
     <row r="877">
-      <c r="A877" s="1"/>
+      <c r="A877" s="2"/>
       <c r="B877" s="7"/>
       <c r="C877" s="7"/>
       <c r="D877" s="7"/>
@@ -22541,7 +22546,7 @@
       <c r="W877" s="7"/>
     </row>
     <row r="878">
-      <c r="A878" s="1"/>
+      <c r="A878" s="2"/>
       <c r="B878" s="7"/>
       <c r="C878" s="7"/>
       <c r="D878" s="7"/>
@@ -22566,7 +22571,7 @@
       <c r="W878" s="7"/>
     </row>
     <row r="879">
-      <c r="A879" s="1"/>
+      <c r="A879" s="2"/>
       <c r="B879" s="7"/>
       <c r="C879" s="7"/>
       <c r="D879" s="7"/>
@@ -22591,7 +22596,7 @@
       <c r="W879" s="7"/>
     </row>
     <row r="880">
-      <c r="A880" s="1"/>
+      <c r="A880" s="2"/>
       <c r="B880" s="7"/>
       <c r="C880" s="7"/>
       <c r="D880" s="7"/>
@@ -22616,7 +22621,7 @@
       <c r="W880" s="7"/>
     </row>
     <row r="881">
-      <c r="A881" s="1"/>
+      <c r="A881" s="2"/>
       <c r="B881" s="7"/>
       <c r="C881" s="7"/>
       <c r="D881" s="7"/>
@@ -22641,7 +22646,7 @@
       <c r="W881" s="7"/>
     </row>
     <row r="882">
-      <c r="A882" s="1"/>
+      <c r="A882" s="2"/>
       <c r="B882" s="7"/>
       <c r="C882" s="7"/>
       <c r="D882" s="7"/>
@@ -22666,7 +22671,7 @@
       <c r="W882" s="7"/>
     </row>
     <row r="883">
-      <c r="A883" s="1"/>
+      <c r="A883" s="2"/>
       <c r="B883" s="7"/>
       <c r="C883" s="7"/>
       <c r="D883" s="7"/>
@@ -22691,7 +22696,7 @@
       <c r="W883" s="7"/>
     </row>
     <row r="884">
-      <c r="A884" s="1"/>
+      <c r="A884" s="2"/>
       <c r="B884" s="7"/>
       <c r="C884" s="7"/>
       <c r="D884" s="7"/>
@@ -22716,7 +22721,7 @@
       <c r="W884" s="7"/>
     </row>
     <row r="885">
-      <c r="A885" s="1"/>
+      <c r="A885" s="2"/>
       <c r="B885" s="7"/>
       <c r="C885" s="7"/>
       <c r="D885" s="7"/>
@@ -22741,7 +22746,7 @@
       <c r="W885" s="7"/>
     </row>
     <row r="886">
-      <c r="A886" s="1"/>
+      <c r="A886" s="2"/>
       <c r="B886" s="7"/>
       <c r="C886" s="7"/>
       <c r="D886" s="7"/>
@@ -22766,7 +22771,7 @@
       <c r="W886" s="7"/>
     </row>
     <row r="887">
-      <c r="A887" s="1"/>
+      <c r="A887" s="2"/>
       <c r="B887" s="7"/>
       <c r="C887" s="7"/>
       <c r="D887" s="7"/>
@@ -22791,7 +22796,7 @@
       <c r="W887" s="7"/>
     </row>
     <row r="888">
-      <c r="A888" s="1"/>
+      <c r="A888" s="2"/>
       <c r="B888" s="7"/>
       <c r="C888" s="7"/>
       <c r="D888" s="7"/>
@@ -22816,7 +22821,7 @@
       <c r="W888" s="7"/>
     </row>
     <row r="889">
-      <c r="A889" s="1"/>
+      <c r="A889" s="2"/>
       <c r="B889" s="7"/>
       <c r="C889" s="7"/>
       <c r="D889" s="7"/>
@@ -22841,7 +22846,7 @@
       <c r="W889" s="7"/>
     </row>
     <row r="890">
-      <c r="A890" s="1"/>
+      <c r="A890" s="2"/>
       <c r="B890" s="7"/>
       <c r="C890" s="7"/>
       <c r="D890" s="7"/>
@@ -22866,7 +22871,7 @@
       <c r="W890" s="7"/>
     </row>
     <row r="891">
-      <c r="A891" s="1"/>
+      <c r="A891" s="2"/>
       <c r="B891" s="7"/>
       <c r="C891" s="7"/>
       <c r="D891" s="7"/>
@@ -22891,7 +22896,7 @@
       <c r="W891" s="7"/>
     </row>
     <row r="892">
-      <c r="A892" s="1"/>
+      <c r="A892" s="2"/>
       <c r="B892" s="7"/>
       <c r="C892" s="7"/>
       <c r="D892" s="7"/>
@@ -22916,7 +22921,7 @@
       <c r="W892" s="7"/>
     </row>
     <row r="893">
-      <c r="A893" s="1"/>
+      <c r="A893" s="2"/>
       <c r="B893" s="7"/>
       <c r="C893" s="7"/>
       <c r="D893" s="7"/>
@@ -22941,7 +22946,7 @@
       <c r="W893" s="7"/>
     </row>
     <row r="894">
-      <c r="A894" s="1"/>
+      <c r="A894" s="2"/>
       <c r="B894" s="7"/>
       <c r="C894" s="7"/>
       <c r="D894" s="7"/>
@@ -22966,7 +22971,7 @@
       <c r="W894" s="7"/>
     </row>
     <row r="895">
-      <c r="A895" s="1"/>
+      <c r="A895" s="2"/>
       <c r="B895" s="7"/>
       <c r="C895" s="7"/>
       <c r="D895" s="7"/>
@@ -22991,7 +22996,7 @@
       <c r="W895" s="7"/>
     </row>
     <row r="896">
-      <c r="A896" s="1"/>
+      <c r="A896" s="2"/>
       <c r="B896" s="7"/>
       <c r="C896" s="7"/>
       <c r="D896" s="7"/>
@@ -23016,7 +23021,7 @@
       <c r="W896" s="7"/>
     </row>
     <row r="897">
-      <c r="A897" s="1"/>
+      <c r="A897" s="2"/>
       <c r="B897" s="7"/>
       <c r="C897" s="7"/>
       <c r="D897" s="7"/>
@@ -23041,7 +23046,7 @@
       <c r="W897" s="7"/>
     </row>
     <row r="898">
-      <c r="A898" s="1"/>
+      <c r="A898" s="2"/>
       <c r="B898" s="7"/>
       <c r="C898" s="7"/>
       <c r="D898" s="7"/>
@@ -23066,7 +23071,7 @@
       <c r="W898" s="7"/>
     </row>
     <row r="899">
-      <c r="A899" s="1"/>
+      <c r="A899" s="2"/>
       <c r="B899" s="7"/>
       <c r="C899" s="7"/>
       <c r="D899" s="7"/>
@@ -23091,7 +23096,7 @@
       <c r="W899" s="7"/>
     </row>
     <row r="900">
-      <c r="A900" s="1"/>
+      <c r="A900" s="2"/>
       <c r="B900" s="7"/>
       <c r="C900" s="7"/>
       <c r="D900" s="7"/>
@@ -23116,7 +23121,7 @@
       <c r="W900" s="7"/>
     </row>
     <row r="901">
-      <c r="A901" s="1"/>
+      <c r="A901" s="2"/>
       <c r="B901" s="7"/>
       <c r="C901" s="7"/>
       <c r="D901" s="7"/>
@@ -23141,7 +23146,7 @@
       <c r="W901" s="7"/>
     </row>
     <row r="902">
-      <c r="A902" s="1"/>
+      <c r="A902" s="2"/>
       <c r="B902" s="7"/>
       <c r="C902" s="7"/>
       <c r="D902" s="7"/>
@@ -23166,7 +23171,7 @@
       <c r="W902" s="7"/>
     </row>
     <row r="903">
-      <c r="A903" s="1"/>
+      <c r="A903" s="2"/>
       <c r="B903" s="7"/>
       <c r="C903" s="7"/>
       <c r="D903" s="7"/>
@@ -23191,7 +23196,7 @@
       <c r="W903" s="7"/>
     </row>
     <row r="904">
-      <c r="A904" s="1"/>
+      <c r="A904" s="2"/>
       <c r="B904" s="7"/>
       <c r="C904" s="7"/>
       <c r="D904" s="7"/>
@@ -23216,7 +23221,7 @@
       <c r="W904" s="7"/>
     </row>
     <row r="905">
-      <c r="A905" s="1"/>
+      <c r="A905" s="2"/>
       <c r="B905" s="7"/>
       <c r="C905" s="7"/>
       <c r="D905" s="7"/>
@@ -23241,7 +23246,7 @@
       <c r="W905" s="7"/>
     </row>
     <row r="906">
-      <c r="A906" s="1"/>
+      <c r="A906" s="2"/>
       <c r="B906" s="7"/>
       <c r="C906" s="7"/>
       <c r="D906" s="7"/>
@@ -23266,7 +23271,7 @@
       <c r="W906" s="7"/>
     </row>
     <row r="907">
-      <c r="A907" s="1"/>
+      <c r="A907" s="2"/>
       <c r="B907" s="7"/>
       <c r="C907" s="7"/>
       <c r="D907" s="7"/>
@@ -23291,7 +23296,7 @@
       <c r="W907" s="7"/>
     </row>
     <row r="908">
-      <c r="A908" s="1"/>
+      <c r="A908" s="2"/>
       <c r="B908" s="7"/>
       <c r="C908" s="7"/>
       <c r="D908" s="7"/>
@@ -23316,7 +23321,7 @@
       <c r="W908" s="7"/>
     </row>
     <row r="909">
-      <c r="A909" s="1"/>
+      <c r="A909" s="2"/>
       <c r="B909" s="7"/>
       <c r="C909" s="7"/>
       <c r="D909" s="7"/>
@@ -23341,7 +23346,7 @@
       <c r="W909" s="7"/>
     </row>
     <row r="910">
-      <c r="A910" s="1"/>
+      <c r="A910" s="2"/>
       <c r="B910" s="7"/>
       <c r="C910" s="7"/>
       <c r="D910" s="7"/>
@@ -23366,7 +23371,7 @@
       <c r="W910" s="7"/>
     </row>
     <row r="911">
-      <c r="A911" s="1"/>
+      <c r="A911" s="2"/>
       <c r="B911" s="7"/>
       <c r="C911" s="7"/>
       <c r="D911" s="7"/>
@@ -23391,7 +23396,7 @@
       <c r="W911" s="7"/>
     </row>
     <row r="912">
-      <c r="A912" s="1"/>
+      <c r="A912" s="2"/>
       <c r="B912" s="7"/>
       <c r="C912" s="7"/>
       <c r="D912" s="7"/>
@@ -23416,7 +23421,7 @@
       <c r="W912" s="7"/>
     </row>
     <row r="913">
-      <c r="A913" s="1"/>
+      <c r="A913" s="2"/>
       <c r="B913" s="7"/>
       <c r="C913" s="7"/>
       <c r="D913" s="7"/>
@@ -23441,7 +23446,7 @@
       <c r="W913" s="7"/>
     </row>
     <row r="914">
-      <c r="A914" s="1"/>
+      <c r="A914" s="2"/>
       <c r="B914" s="7"/>
       <c r="C914" s="7"/>
       <c r="D914" s="7"/>
@@ -23466,7 +23471,7 @@
       <c r="W914" s="7"/>
     </row>
     <row r="915">
-      <c r="A915" s="1"/>
+      <c r="A915" s="2"/>
       <c r="B915" s="7"/>
       <c r="C915" s="7"/>
       <c r="D915" s="7"/>
@@ -23491,7 +23496,7 @@
       <c r="W915" s="7"/>
     </row>
     <row r="916">
-      <c r="A916" s="1"/>
+      <c r="A916" s="2"/>
       <c r="B916" s="7"/>
       <c r="C916" s="7"/>
       <c r="D916" s="7"/>
@@ -23516,7 +23521,7 @@
       <c r="W916" s="7"/>
     </row>
     <row r="917">
-      <c r="A917" s="1"/>
+      <c r="A917" s="2"/>
       <c r="B917" s="7"/>
       <c r="C917" s="7"/>
       <c r="D917" s="7"/>
@@ -23541,7 +23546,7 @@
       <c r="W917" s="7"/>
     </row>
     <row r="918">
-      <c r="A918" s="1"/>
+      <c r="A918" s="2"/>
       <c r="B918" s="7"/>
       <c r="C918" s="7"/>
       <c r="D918" s="7"/>
@@ -23566,7 +23571,7 @@
       <c r="W918" s="7"/>
     </row>
     <row r="919">
-      <c r="A919" s="1"/>
+      <c r="A919" s="2"/>
       <c r="B919" s="7"/>
       <c r="C919" s="7"/>
       <c r="D919" s="7"/>
@@ -23591,7 +23596,7 @@
       <c r="W919" s="7"/>
     </row>
     <row r="920">
-      <c r="A920" s="1"/>
+      <c r="A920" s="2"/>
       <c r="B920" s="7"/>
       <c r="C920" s="7"/>
       <c r="D920" s="7"/>
@@ -23616,7 +23621,7 @@
       <c r="W920" s="7"/>
     </row>
     <row r="921">
-      <c r="A921" s="1"/>
+      <c r="A921" s="2"/>
       <c r="B921" s="7"/>
       <c r="C921" s="7"/>
       <c r="D921" s="7"/>
@@ -23641,7 +23646,7 @@
       <c r="W921" s="7"/>
     </row>
     <row r="922">
-      <c r="A922" s="1"/>
+      <c r="A922" s="2"/>
       <c r="B922" s="7"/>
       <c r="C922" s="7"/>
       <c r="D922" s="7"/>
@@ -23666,7 +23671,7 @@
       <c r="W922" s="7"/>
     </row>
     <row r="923">
-      <c r="A923" s="1"/>
+      <c r="A923" s="2"/>
       <c r="B923" s="7"/>
       <c r="C923" s="7"/>
       <c r="D923" s="7"/>
@@ -23691,7 +23696,7 @@
       <c r="W923" s="7"/>
     </row>
     <row r="924">
-      <c r="A924" s="1"/>
+      <c r="A924" s="2"/>
       <c r="B924" s="7"/>
       <c r="C924" s="7"/>
       <c r="D924" s="7"/>
@@ -23716,7 +23721,7 @@
       <c r="W924" s="7"/>
     </row>
     <row r="925">
-      <c r="A925" s="1"/>
+      <c r="A925" s="2"/>
       <c r="B925" s="7"/>
       <c r="C925" s="7"/>
       <c r="D925" s="7"/>
@@ -23741,7 +23746,7 @@
       <c r="W925" s="7"/>
     </row>
     <row r="926">
-      <c r="A926" s="1"/>
+      <c r="A926" s="2"/>
       <c r="B926" s="7"/>
       <c r="C926" s="7"/>
       <c r="D926" s="7"/>
@@ -23766,7 +23771,7 @@
       <c r="W926" s="7"/>
     </row>
     <row r="927">
-      <c r="A927" s="1"/>
+      <c r="A927" s="2"/>
       <c r="B927" s="7"/>
       <c r="C927" s="7"/>
       <c r="D927" s="7"/>
@@ -23791,7 +23796,7 @@
       <c r="W927" s="7"/>
     </row>
     <row r="928">
-      <c r="A928" s="1"/>
+      <c r="A928" s="2"/>
       <c r="B928" s="7"/>
       <c r="C928" s="7"/>
       <c r="D928" s="7"/>
@@ -23816,7 +23821,7 @@
       <c r="W928" s="7"/>
     </row>
     <row r="929">
-      <c r="A929" s="1"/>
+      <c r="A929" s="2"/>
       <c r="B929" s="7"/>
       <c r="C929" s="7"/>
       <c r="D929" s="7"/>
@@ -23841,7 +23846,7 @@
       <c r="W929" s="7"/>
     </row>
     <row r="930">
-      <c r="A930" s="1"/>
+      <c r="A930" s="2"/>
       <c r="B930" s="7"/>
       <c r="C930" s="7"/>
       <c r="D930" s="7"/>
@@ -23866,7 +23871,7 @@
       <c r="W930" s="7"/>
     </row>
     <row r="931">
-      <c r="A931" s="1"/>
+      <c r="A931" s="2"/>
       <c r="B931" s="7"/>
       <c r="C931" s="7"/>
       <c r="D931" s="7"/>
@@ -23891,7 +23896,7 @@
       <c r="W931" s="7"/>
     </row>
     <row r="932">
-      <c r="A932" s="1"/>
+      <c r="A932" s="2"/>
       <c r="B932" s="7"/>
       <c r="C932" s="7"/>
       <c r="D932" s="7"/>
@@ -23916,7 +23921,7 @@
       <c r="W932" s="7"/>
     </row>
     <row r="933">
-      <c r="A933" s="1"/>
+      <c r="A933" s="2"/>
       <c r="B933" s="7"/>
       <c r="C933" s="7"/>
       <c r="D933" s="7"/>
@@ -23941,7 +23946,7 @@
       <c r="W933" s="7"/>
     </row>
     <row r="934">
-      <c r="A934" s="1"/>
+      <c r="A934" s="2"/>
       <c r="B934" s="7"/>
       <c r="C934" s="7"/>
       <c r="D934" s="7"/>
@@ -23966,7 +23971,7 @@
       <c r="W934" s="7"/>
     </row>
     <row r="935">
-      <c r="A935" s="1"/>
+      <c r="A935" s="2"/>
       <c r="B935" s="7"/>
       <c r="C935" s="7"/>
       <c r="D935" s="7"/>
@@ -23991,7 +23996,7 @@
       <c r="W935" s="7"/>
     </row>
     <row r="936">
-      <c r="A936" s="1"/>
+      <c r="A936" s="2"/>
       <c r="B936" s="7"/>
       <c r="C936" s="7"/>
       <c r="D936" s="7"/>
@@ -24016,7 +24021,7 @@
       <c r="W936" s="7"/>
     </row>
     <row r="937">
-      <c r="A937" s="1"/>
+      <c r="A937" s="2"/>
       <c r="B937" s="7"/>
       <c r="C937" s="7"/>
       <c r="D937" s="7"/>
@@ -24041,7 +24046,7 @@
       <c r="W937" s="7"/>
     </row>
     <row r="938">
-      <c r="A938" s="1"/>
+      <c r="A938" s="2"/>
       <c r="B938" s="7"/>
       <c r="C938" s="7"/>
       <c r="D938" s="7"/>
@@ -24066,7 +24071,7 @@
       <c r="W938" s="7"/>
     </row>
     <row r="939">
-      <c r="A939" s="1"/>
+      <c r="A939" s="2"/>
       <c r="B939" s="7"/>
       <c r="C939" s="7"/>
       <c r="D939" s="7"/>
@@ -24091,7 +24096,7 @@
       <c r="W939" s="7"/>
     </row>
     <row r="940">
-      <c r="A940" s="1"/>
+      <c r="A940" s="2"/>
       <c r="B940" s="7"/>
       <c r="C940" s="7"/>
       <c r="D940" s="7"/>
@@ -24116,7 +24121,7 @@
       <c r="W940" s="7"/>
     </row>
     <row r="941">
-      <c r="A941" s="1"/>
+      <c r="A941" s="2"/>
       <c r="B941" s="7"/>
       <c r="C941" s="7"/>
       <c r="D941" s="7"/>
@@ -24141,7 +24146,7 @@
       <c r="W941" s="7"/>
     </row>
     <row r="942">
-      <c r="A942" s="1"/>
+      <c r="A942" s="2"/>
       <c r="B942" s="7"/>
       <c r="C942" s="7"/>
       <c r="D942" s="7"/>
@@ -24166,7 +24171,7 @@
       <c r="W942" s="7"/>
     </row>
     <row r="943">
-      <c r="A943" s="1"/>
+      <c r="A943" s="2"/>
       <c r="B943" s="7"/>
       <c r="C943" s="7"/>
       <c r="D943" s="7"/>
@@ -24191,7 +24196,7 @@
       <c r="W943" s="7"/>
     </row>
     <row r="944">
-      <c r="A944" s="1"/>
+      <c r="A944" s="2"/>
       <c r="B944" s="7"/>
       <c r="C944" s="7"/>
       <c r="D944" s="7"/>
@@ -24216,7 +24221,7 @@
       <c r="W944" s="7"/>
     </row>
     <row r="945">
-      <c r="A945" s="1"/>
+      <c r="A945" s="2"/>
       <c r="B945" s="7"/>
       <c r="C945" s="7"/>
       <c r="D945" s="7"/>
@@ -24241,7 +24246,7 @@
       <c r="W945" s="7"/>
     </row>
     <row r="946">
-      <c r="A946" s="1"/>
+      <c r="A946" s="2"/>
       <c r="B946" s="7"/>
       <c r="C946" s="7"/>
       <c r="D946" s="7"/>
@@ -24266,7 +24271,7 @@
       <c r="W946" s="7"/>
     </row>
     <row r="947">
-      <c r="A947" s="1"/>
+      <c r="A947" s="2"/>
       <c r="B947" s="7"/>
       <c r="C947" s="7"/>
       <c r="D947" s="7"/>
@@ -24291,7 +24296,7 @@
       <c r="W947" s="7"/>
     </row>
     <row r="948">
-      <c r="A948" s="1"/>
+      <c r="A948" s="2"/>
       <c r="B948" s="7"/>
       <c r="C948" s="7"/>
       <c r="D948" s="7"/>
@@ -24316,7 +24321,7 @@
       <c r="W948" s="7"/>
     </row>
     <row r="949">
-      <c r="A949" s="1"/>
+      <c r="A949" s="2"/>
       <c r="B949" s="7"/>
       <c r="C949" s="7"/>
       <c r="D949" s="7"/>
@@ -24341,7 +24346,7 @@
       <c r="W949" s="7"/>
     </row>
     <row r="950">
-      <c r="A950" s="1"/>
+      <c r="A950" s="2"/>
       <c r="B950" s="7"/>
       <c r="C950" s="7"/>
       <c r="D950" s="7"/>
@@ -24366,7 +24371,7 @@
       <c r="W950" s="7"/>
     </row>
     <row r="951">
-      <c r="A951" s="1"/>
+      <c r="A951" s="2"/>
       <c r="B951" s="7"/>
       <c r="C951" s="7"/>
       <c r="D951" s="7"/>
@@ -24391,7 +24396,7 @@
       <c r="W951" s="7"/>
     </row>
     <row r="952">
-      <c r="A952" s="1"/>
+      <c r="A952" s="2"/>
       <c r="B952" s="7"/>
       <c r="C952" s="7"/>
       <c r="D952" s="7"/>
@@ -24416,7 +24421,7 @@
       <c r="W952" s="7"/>
     </row>
     <row r="953">
-      <c r="A953" s="1"/>
+      <c r="A953" s="2"/>
       <c r="B953" s="7"/>
       <c r="C953" s="7"/>
       <c r="D953" s="7"/>
@@ -24441,7 +24446,7 @@
       <c r="W953" s="7"/>
     </row>
     <row r="954">
-      <c r="A954" s="1"/>
+      <c r="A954" s="2"/>
       <c r="B954" s="7"/>
       <c r="C954" s="7"/>
       <c r="D954" s="7"/>
@@ -24466,7 +24471,7 @@
       <c r="W954" s="7"/>
     </row>
     <row r="955">
-      <c r="A955" s="1"/>
+      <c r="A955" s="2"/>
       <c r="B955" s="7"/>
       <c r="C955" s="7"/>
       <c r="D955" s="7"/>
@@ -24491,7 +24496,7 @@
       <c r="W955" s="7"/>
     </row>
     <row r="956">
-      <c r="A956" s="1"/>
+      <c r="A956" s="2"/>
       <c r="B956" s="7"/>
       <c r="C956" s="7"/>
       <c r="D956" s="7"/>
@@ -24516,7 +24521,7 @@
       <c r="W956" s="7"/>
     </row>
     <row r="957">
-      <c r="A957" s="1"/>
+      <c r="A957" s="2"/>
       <c r="B957" s="7"/>
       <c r="C957" s="7"/>
       <c r="D957" s="7"/>
@@ -24541,7 +24546,7 @@
       <c r="W957" s="7"/>
     </row>
     <row r="958">
-      <c r="A958" s="1"/>
+      <c r="A958" s="2"/>
       <c r="B958" s="7"/>
       <c r="C958" s="7"/>
       <c r="D958" s="7"/>
@@ -24566,7 +24571,7 @@
       <c r="W958" s="7"/>
     </row>
     <row r="959">
-      <c r="A959" s="1"/>
+      <c r="A959" s="2"/>
       <c r="B959" s="7"/>
       <c r="C959" s="7"/>
       <c r="D959" s="7"/>
@@ -24591,7 +24596,7 @@
       <c r="W959" s="7"/>
     </row>
     <row r="960">
-      <c r="A960" s="1"/>
+      <c r="A960" s="2"/>
       <c r="B960" s="7"/>
       <c r="C960" s="7"/>
       <c r="D960" s="7"/>
@@ -24616,7 +24621,7 @@
       <c r="W960" s="7"/>
     </row>
     <row r="961">
-      <c r="A961" s="1"/>
+      <c r="A961" s="2"/>
       <c r="B961" s="7"/>
       <c r="C961" s="7"/>
       <c r="D961" s="7"/>
@@ -24641,7 +24646,7 @@
       <c r="W961" s="7"/>
     </row>
     <row r="962">
-      <c r="A962" s="1"/>
+      <c r="A962" s="2"/>
       <c r="B962" s="7"/>
       <c r="C962" s="7"/>
       <c r="D962" s="7"/>
@@ -24666,7 +24671,7 @@
       <c r="W962" s="7"/>
     </row>
     <row r="963">
-      <c r="A963" s="1"/>
+      <c r="A963" s="2"/>
       <c r="B963" s="7"/>
       <c r="C963" s="7"/>
       <c r="D963" s="7"/>
@@ -24691,7 +24696,7 @@
       <c r="W963" s="7"/>
     </row>
     <row r="964">
-      <c r="A964" s="1"/>
+      <c r="A964" s="2"/>
       <c r="B964" s="7"/>
       <c r="C964" s="7"/>
       <c r="D964" s="7"/>
@@ -24716,7 +24721,7 @@
       <c r="W964" s="7"/>
     </row>
     <row r="965">
-      <c r="A965" s="1"/>
+      <c r="A965" s="2"/>
       <c r="B965" s="7"/>
       <c r="C965" s="7"/>
       <c r="D965" s="7"/>
@@ -24741,7 +24746,7 @@
       <c r="W965" s="7"/>
     </row>
     <row r="966">
-      <c r="A966" s="1"/>
+      <c r="A966" s="2"/>
       <c r="B966" s="7"/>
       <c r="C966" s="7"/>
       <c r="D966" s="7"/>
@@ -24766,7 +24771,7 @@
       <c r="W966" s="7"/>
     </row>
     <row r="967">
-      <c r="A967" s="1"/>
+      <c r="A967" s="2"/>
       <c r="B967" s="7"/>
       <c r="C967" s="7"/>
       <c r="D967" s="7"/>
@@ -24791,7 +24796,7 @@
       <c r="W967" s="7"/>
     </row>
     <row r="968">
-      <c r="A968" s="1"/>
+      <c r="A968" s="2"/>
       <c r="B968" s="7"/>
       <c r="C968" s="7"/>
       <c r="D968" s="7"/>
@@ -24816,7 +24821,7 @@
       <c r="W968" s="7"/>
     </row>
     <row r="969">
-      <c r="A969" s="1"/>
+      <c r="A969" s="2"/>
       <c r="B969" s="7"/>
       <c r="C969" s="7"/>
       <c r="D969" s="7"/>
@@ -24841,7 +24846,7 @@
       <c r="W969" s="7"/>
     </row>
     <row r="970">
-      <c r="A970" s="1"/>
+      <c r="A970" s="2"/>
       <c r="B970" s="7"/>
       <c r="C970" s="7"/>
       <c r="D970" s="7"/>
@@ -24866,7 +24871,7 @@
       <c r="W970" s="7"/>
     </row>
     <row r="971">
-      <c r="A971" s="1"/>
+      <c r="A971" s="2"/>
       <c r="B971" s="7"/>
       <c r="C971" s="7"/>
       <c r="D971" s="7"/>
@@ -24891,7 +24896,7 @@
       <c r="W971" s="7"/>
     </row>
     <row r="972">
-      <c r="A972" s="1"/>
+      <c r="A972" s="2"/>
       <c r="B972" s="7"/>
       <c r="C972" s="7"/>
       <c r="D972" s="7"/>
@@ -24916,7 +24921,7 @@
       <c r="W972" s="7"/>
     </row>
     <row r="973">
-      <c r="A973" s="1"/>
+      <c r="A973" s="2"/>
       <c r="B973" s="7"/>
       <c r="C973" s="7"/>
       <c r="D973" s="7"/>
@@ -24941,7 +24946,7 @@
       <c r="W973" s="7"/>
     </row>
     <row r="974">
-      <c r="A974" s="1"/>
+      <c r="A974" s="2"/>
       <c r="B974" s="7"/>
       <c r="C974" s="7"/>
       <c r="D974" s="7"/>
@@ -24966,7 +24971,7 @@
       <c r="W974" s="7"/>
     </row>
     <row r="975">
-      <c r="A975" s="1"/>
+      <c r="A975" s="2"/>
       <c r="B975" s="7"/>
       <c r="C975" s="7"/>
       <c r="D975" s="7"/>
@@ -24991,7 +24996,7 @@
       <c r="W975" s="7"/>
     </row>
     <row r="976">
-      <c r="A976" s="1"/>
+      <c r="A976" s="2"/>
       <c r="B976" s="7"/>
       <c r="C976" s="7"/>
       <c r="D976" s="7"/>
@@ -25016,7 +25021,7 @@
       <c r="W976" s="7"/>
     </row>
     <row r="977">
-      <c r="A977" s="1"/>
+      <c r="A977" s="2"/>
       <c r="B977" s="7"/>
       <c r="C977" s="7"/>
       <c r="D977" s="7"/>
@@ -25041,7 +25046,7 @@
       <c r="W977" s="7"/>
     </row>
     <row r="978">
-      <c r="A978" s="1"/>
+      <c r="A978" s="2"/>
       <c r="B978" s="7"/>
       <c r="C978" s="7"/>
       <c r="D978" s="7"/>
@@ -25066,7 +25071,7 @@
       <c r="W978" s="7"/>
     </row>
     <row r="979">
-      <c r="A979" s="1"/>
+      <c r="A979" s="2"/>
       <c r="B979" s="7"/>
       <c r="C979" s="7"/>
       <c r="D979" s="7"/>
@@ -25091,7 +25096,7 @@
       <c r="W979" s="7"/>
     </row>
     <row r="980">
-      <c r="A980" s="1"/>
+      <c r="A980" s="2"/>
       <c r="B980" s="7"/>
       <c r="C980" s="7"/>
       <c r="D980" s="7"/>
@@ -25116,7 +25121,7 @@
       <c r="W980" s="7"/>
     </row>
     <row r="981">
-      <c r="A981" s="1"/>
+      <c r="A981" s="2"/>
       <c r="B981" s="7"/>
       <c r="C981" s="7"/>
       <c r="D981" s="7"/>
@@ -25141,7 +25146,7 @@
       <c r="W981" s="7"/>
     </row>
     <row r="982">
-      <c r="A982" s="1"/>
+      <c r="A982" s="2"/>
       <c r="B982" s="7"/>
       <c r="C982" s="7"/>
       <c r="D982" s="7"/>
@@ -25166,7 +25171,7 @@
       <c r="W982" s="7"/>
     </row>
     <row r="983">
-      <c r="A983" s="1"/>
+      <c r="A983" s="2"/>
       <c r="B983" s="7"/>
       <c r="C983" s="7"/>
       <c r="D983" s="7"/>
@@ -25191,7 +25196,7 @@
       <c r="W983" s="7"/>
     </row>
     <row r="984">
-      <c r="A984" s="1"/>
+      <c r="A984" s="2"/>
       <c r="B984" s="7"/>
       <c r="C984" s="7"/>
       <c r="D984" s="7"/>
@@ -25216,7 +25221,7 @@
       <c r="W984" s="7"/>
     </row>
     <row r="985">
-      <c r="A985" s="1"/>
+      <c r="A985" s="2"/>
       <c r="B985" s="7"/>
       <c r="C985" s="7"/>
       <c r="D985" s="7"/>
@@ -25241,7 +25246,7 @@
       <c r="W985" s="7"/>
     </row>
     <row r="986">
-      <c r="A986" s="1"/>
+      <c r="A986" s="2"/>
       <c r="B986" s="7"/>
       <c r="C986" s="7"/>
       <c r="D986" s="7"/>
@@ -25266,7 +25271,7 @@
       <c r="W986" s="7"/>
     </row>
     <row r="987">
-      <c r="A987" s="1"/>
+      <c r="A987" s="2"/>
       <c r="B987" s="7"/>
       <c r="C987" s="7"/>
       <c r="D987" s="7"/>
@@ -25291,7 +25296,7 @@
       <c r="W987" s="7"/>
     </row>
     <row r="988">
-      <c r="A988" s="1"/>
+      <c r="A988" s="2"/>
       <c r="B988" s="7"/>
       <c r="C988" s="7"/>
       <c r="D988" s="7"/>
@@ -25316,7 +25321,7 @@
       <c r="W988" s="7"/>
     </row>
     <row r="989">
-      <c r="A989" s="1"/>
+      <c r="A989" s="2"/>
       <c r="B989" s="7"/>
       <c r="C989" s="7"/>
       <c r="D989" s="7"/>
@@ -25341,7 +25346,7 @@
       <c r="W989" s="7"/>
     </row>
     <row r="990">
-      <c r="A990" s="1"/>
+      <c r="A990" s="2"/>
       <c r="B990" s="7"/>
       <c r="C990" s="7"/>
       <c r="D990" s="7"/>
@@ -25366,7 +25371,7 @@
       <c r="W990" s="7"/>
     </row>
     <row r="991">
-      <c r="A991" s="1"/>
+      <c r="A991" s="2"/>
       <c r="B991" s="7"/>
       <c r="C991" s="7"/>
       <c r="D991" s="7"/>
@@ -25391,7 +25396,7 @@
       <c r="W991" s="7"/>
     </row>
     <row r="992">
-      <c r="A992" s="1"/>
+      <c r="A992" s="2"/>
       <c r="B992" s="7"/>
       <c r="C992" s="7"/>
       <c r="D992" s="7"/>
@@ -25416,7 +25421,7 @@
       <c r="W992" s="7"/>
     </row>
     <row r="993">
-      <c r="A993" s="1"/>
+      <c r="A993" s="2"/>
       <c r="B993" s="7"/>
       <c r="C993" s="7"/>
       <c r="D993" s="7"/>
@@ -25441,7 +25446,7 @@
       <c r="W993" s="7"/>
     </row>
     <row r="994">
-      <c r="A994" s="1"/>
+      <c r="A994" s="2"/>
       <c r="B994" s="7"/>
       <c r="C994" s="7"/>
       <c r="D994" s="7"/>
@@ -25466,7 +25471,7 @@
       <c r="W994" s="7"/>
     </row>
     <row r="995">
-      <c r="A995" s="1"/>
+      <c r="A995" s="2"/>
       <c r="B995" s="7"/>
       <c r="C995" s="7"/>
       <c r="D995" s="7"/>
@@ -25491,7 +25496,7 @@
       <c r="W995" s="7"/>
     </row>
     <row r="996">
-      <c r="A996" s="1"/>
+      <c r="A996" s="2"/>
       <c r="B996" s="7"/>
       <c r="C996" s="7"/>
       <c r="D996" s="7"/>
@@ -25516,7 +25521,7 @@
       <c r="W996" s="7"/>
     </row>
     <row r="997">
-      <c r="A997" s="1"/>
+      <c r="A997" s="2"/>
       <c r="B997" s="7"/>
       <c r="C997" s="7"/>
       <c r="D997" s="7"/>
@@ -25541,7 +25546,7 @@
       <c r="W997" s="7"/>
     </row>
     <row r="998">
-      <c r="A998" s="1"/>
+      <c r="A998" s="2"/>
       <c r="B998" s="7"/>
       <c r="C998" s="7"/>
       <c r="D998" s="7"/>
@@ -25566,7 +25571,7 @@
       <c r="W998" s="7"/>
     </row>
     <row r="999">
-      <c r="A999" s="1"/>
+      <c r="A999" s="2"/>
       <c r="B999" s="7"/>
       <c r="C999" s="7"/>
       <c r="D999" s="7"/>
@@ -25591,7 +25596,7 @@
       <c r="W999" s="7"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="1"/>
+      <c r="A1000" s="2"/>
       <c r="B1000" s="7"/>
       <c r="C1000" s="7"/>
       <c r="D1000" s="7"/>
@@ -25616,7 +25621,7 @@
       <c r="W1000" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
+  <mergeCells count="98">
     <mergeCell ref="H12:H15"/>
     <mergeCell ref="I12:I15"/>
     <mergeCell ref="J12:J15"/>
@@ -25628,33 +25633,53 @@
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="F12:F15"/>
     <mergeCell ref="G12:G15"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="L17:L18"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="D17:D18"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="I21:I22"/>
     <mergeCell ref="J21:J22"/>
     <mergeCell ref="K21:K22"/>
     <mergeCell ref="L21:L22"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="H23:H24"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="K2:K4"/>
@@ -25677,6 +25702,10 @@
     <mergeCell ref="F5:F8"/>
     <mergeCell ref="G5:G8"/>
     <mergeCell ref="H5:H8"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
@@ -25684,15 +25713,13 @@
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -25707,58 +25734,58 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
